--- a/testrail-import/Report-Suite_Parts-Velocity-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Parts-Velocity-Report_testrail-import.xlsx
@@ -814,14 +814,14 @@
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1. The Type filter is the first control in the filter row.
-2. It is single-select and offers exactly: Both, Inventory, Catalogue.
+2. It is single-select and offers exactly three choices: Both, Inventory, and a choice for special-order catalog parts that were never put into stock. (That third choice's exact on-screen label is confirmed in the build — the spec calls it "Catalogue" and a rename is being considered.)
 3. On a first visit the default is Both.
-4. Both is an explicit selection returning inventory and catalogue rows together - a deliberate filter value, not the absence of a filter.</t>
+4. Both is an explicit selection returning inventory and special-order rows together - a deliberate filter value, not the absence of a filter.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>specs/parts-velocity.md S2-R1</t>
+          <t>SV-8642 (specs/parts-velocity.md S2-R1 — 'Catalogue' label rename PENDING per kickoff video P31 43:34-44:12; latest-info user ruling 2026-07-28: update per latest info now, correct at the live build check later)</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
@@ -1203,19 +1203,19 @@
       <c r="F16" s="2" t="inlineStr">
         <is>
           <t>1. With Type = Both, select any bin in the Bin filter.
-2. Look for catalogue rows in the result.
-3. Set Type = Catalogue while the Bin filter is still active.</t>
+2. Look for special-order (catalogue) rows in the result.
+3. Set the Type filter to the special-order (catalogue) choice while the Bin filter is still active.</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1. With any Bin filter active, ALL catalogue rows are excluded (catalogue parts have no bin location).
-2. Type = Catalogue combined with any Bin filter yields an empty result showing the empty state - this is by design, not a defect.</t>
+          <t>1. With any Bin filter active, ALL special-order (catalogue) rows are excluded (they have no bin location).
+2. The special-order (catalogue) choice combined with any Bin filter yields an empty result showing the empty state - this is by design, not a defect.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>specs/parts-velocity.md S2-R8</t>
+          <t>SV-8642 (specs/parts-velocity.md S2-R8 — 'Catalogue' label rename PENDING per kickoff video P31 43:34-44:12; latest-info user ruling 2026-07-28: update per latest info now, correct at the live build check later)</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
@@ -1224,7 +1224,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Location filter is the rightmost control, defaults to the active location, and scopes to accessible locations only</t>
+          <t>Location filter is rightmost, defaults to the active location, accessible-only</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1253,7 +1253,8 @@
           <t>1. Look at the rightmost control in the filter row.
 2. Note which location is selected by default and compare it to the location selected in the application's global location switcher.
 3. Open the filter and read the list of locations.
-4. Select a second location, then select the 'All Locations' option.</t>
+4. Select a second location, then select the 'All Locations' option.
+5. With 'All Locations' active, look at how the rows tell you which location they belong to.</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1262,12 +1263,13 @@
 2. On a first visit it defaults to the user's currently active location (the one in the global location switcher).
 3. The list holds the locations the signed-in user has access to, plus an 'All Locations' option.
 4. Each selection reloads the data scoped to the chosen set; 'All Locations' means all locations the user can ACCESS, never beyond - a location the user cannot access is never included.
-5. The location scope cascades through every metric like the other filters.</t>
+5. The location scope cascades through every metric like the other filters.
+6. With 'All Locations' active you can tell which location each row's data belongs to — a location label or marking is shown. (Exactly where and how it appears is confirmed in the build.)</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>specs/parts-velocity.md S2-R9</t>
+          <t>SV-8642 (specs/parts-velocity.md S2-R9 — per-row location identifier in All-Locations view ADDED per kickoff video P10 40:58-41:20, user ruling 2026-07-28: video overrides spec (video newer, last-update-wins))</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
@@ -1372,7 +1374,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>A user with access to only one location still sees the Location filter with a single selectable location</t>
+          <t>The Location filter is hidden for a user with access to only one location</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1398,20 +1400,19 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1. Look at the Location filter in the toolbar.
-2. Open it and read the options.</t>
+          <t>1. Look for the Location filter in the toolbar.
+2. Then sign in as a user with access to two or more locations and look again.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1. The Location filter is still shown.
-2. It offers a single selectable location (the user's one location).
-3. Report behavior is unchanged from single-location use.</t>
+          <t>1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
+2. For the user with access to two or more locations the Location filter IS shown.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>specs/parts-velocity.md S2-E4</t>
+          <t>SV-8642 (specs/parts-velocity.md S2-E4 — expectation FLIPPED by kickoff video P33 46:10-46:28, user ruling 2026-07-28: video overrides spec (video newer, last-update-wins))</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
@@ -1652,13 +1653,13 @@
       <c r="G25" s="2" t="inlineStr">
         <is>
           <t>1. The header row is sticky - it stays visible while the body scrolls.
-2. The Type column shows Inventory or Catalogue as plain text (no badge or chip styling).
+2. The Type column shows each row's kind as plain text (no badge or chip styling): Inventory, or the special-order catalogue kind. (The special-order kind's exact on-screen word is confirmed in the build — the spec says "Catalogue", a rename is being considered, and it must stay short enough for a column.)
 3. ALL columns - header and cell data, including numbers and money - are left-aligned on screen. (The exports right-align numerics instead: a deliberate export-only difference.)</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>specs/parts-velocity.md S3-R4; S3-R5; S3-R8</t>
+          <t>SV-8643 (specs/parts-velocity.md S3-R4; S3-R5; S3-R8 — Type value 'Catalogue' rename PENDING per kickoff video P31 43:34-44:12; latest-info user ruling 2026-07-28: update per latest info now, correct at the live build check later)</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
@@ -3468,7 +3469,7 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>specs/parts-velocity.md S6-R10; S3-R8</t>
+          <t>SV-8646 (specs/parts-velocity.md S6-R10; S3-R8)</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr"/>
@@ -3754,7 +3755,7 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>specs/parts-velocity.md §2 (server-paginated); S2-R10</t>
+          <t>SV-8642 (specs/parts-velocity.md §2 (server-paginated); S2-R10)</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr"/>
@@ -3801,7 +3802,7 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>specs/parts-velocity.md S2-R10</t>
+          <t>SV-8642 (specs/parts-velocity.md S2-R10)</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr"/>

--- a/testrail-import/Report-Suite_Parts-Velocity-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Parts-Velocity-Report_testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J71"/>
+  <dimension ref="A1:J68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -780,7 +780,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Type filter is single-select, first in the filter row, with options Both, Inventory, Catalogue (default Both)</t>
+          <t>Type filter: single-select, first in row, three options, default Both; reloads</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -801,14 +801,16 @@
       <c r="E8" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded.
-2. This is a first visit (no saved view), so the first-visit defaults apply.</t>
+2. This is a first visit (no saved view), so the first-visit defaults apply.
+3. Both inventory parts and special-order (catalogue) parts have sales activity in the selected date range.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
           <t>1. Look at the first control in the filter row of the toolbar.
 2. Open the Type filter and read its options.
-3. Note which option is selected by default.</t>
+3. Note which option is selected by default.
+4. Select each Type option in turn and watch the table.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -816,12 +818,13 @@
           <t>1. The Type filter is the first control in the filter row.
 2. It is single-select and offers exactly three choices: Both, Inventory, and a choice for special-order catalog parts that were never put into stock. (That third choice's exact on-screen label is confirmed in the build — the spec calls it "Catalogue" and a rename is being considered.)
 3. On a first visit the default is Both.
-4. Both is an explicit selection returning inventory and special-order rows together - a deliberate filter value, not the absence of a filter.</t>
+4. Both is an explicit selection returning inventory and special-order rows together - a deliberate filter value, not the absence of a filter.
+5. Each selection immediately reloads the report limited to that type (no separate Apply step) — under Inventory every row's Type column reads Inventory; under the special-order (catalogue) choice every row shows that type; under Both, rows of both kinds appear.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>SV-8642 (specs/parts-velocity.md S2-R1 — 'Catalogue' label rename PENDING per kickoff video P31 43:34-44:12; latest-info user ruling 2026-07-28: update per latest info now, correct at the live build check later)</t>
+          <t>SV-8642 (specs/parts-velocity.md S2-R1; S3-R5 — 'Catalogue' label rename PENDING per kickoff video P31 43:34-44:12; latest-info user ruling 2026-07-28)</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
@@ -830,7 +833,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Selecting a Type value immediately reloads the data limited to that type</t>
+          <t>Date range selector offers exactly the eleven bounded options and no All Time</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -850,65 +853,16 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1. You are on the Parts Velocity report with data loaded.
-2. Both inventory parts and catalogue (special-order) parts have sales activity in the selected date range, so both types appear under Both.</t>
+          <t>1. You are on the Parts Velocity report with data loaded.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1. With Type = Both, note that the Type column shows both Inventory and Catalogue rows.
-2. Select Type = Inventory.
-3. Select Type = Catalogue.</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>1. Each selection immediately reloads the report data (no separate Apply step).
-2. With Inventory selected, every row's Type column reads Inventory.
-3. With Catalogue selected, every row's Type column reads Catalogue.</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>specs/parts-velocity.md S2-R1; S3-R5</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Date range selector offers exactly the eleven bounded options and no All Time</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>PV — Filters</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1. You are on the Parts Velocity report with data loaded.</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>1. Open the date range selector and read every option.
 2. Select a non-custom option (for example Last Month).</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>1. The options are exactly: Today, Yesterday, This Week, Last Week, This Month, Last Month, This Year, Last Year, This Quarter, Last Quarter, Custom.
 2. There is NO 'All Time' option - the report always operates over a bounded date window (deliberate, per the spec's Out of Scope).
@@ -916,41 +870,41 @@
 4. The named ranges use the application's standard shared calendar boundaries (the same boundaries every report's date picker uses).</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S2-R2; §2 Out of Scope</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Custom date range requires valid start and end dates and rejects a span over 366 days</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>PV — Filters</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded.</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>1. Open the date range selector and choose Custom.
 2. Pick only a start date and observe - then pick an end date earlier than the start and observe.
@@ -958,7 +912,7 @@
 4. Now try a custom span wider than 366 days (for example 400 days).</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>1. A date picker opens requiring both a start and an end date.
 2. The report does not reload until both dates are valid; a start after the end is not accepted.
@@ -966,49 +920,49 @@
 4. A span wider than 366 days (counting both the start and end dates) is rejected - the selection is not applied.</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S2-R3</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Category and Vendor multi-select filters limit the table to matching parts</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>PV — Filters</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded.
 2. Parts with different categories and different vendors have activity in the range.</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>1. Open the Category filter and select one category; then add a second category.
 2. Clear the Category filter.
 3. Open the Vendor filter and select one vendor; then add a second vendor.</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>1. Both filters allow selecting more than one value (multi-select).
 2. With categories selected, only parts in any of the selected categories are shown.
@@ -1016,42 +970,42 @@
 4. Each change reloads the data from the server.</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S2-R4; S2-R5; S2-R10</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Toolbar search matches part number or description, case-insensitively, and is page-specific</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>PV — Filters</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded.
 2. A part exists whose part number you know, and another whose description contains a distinctive word.</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>1. Find the search input in the report's own toolbar (not the application's global search bar).
 2. Type part of a known part number, in the wrong letter case (for example lower case for an upper-case part number).
@@ -1059,7 +1013,7 @@
 4. Clear it and type a category or vendor name that matches no part number or description.</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>1. The search input is part of the report's toolbar (page-specific), separate from the global search bar.
 2. The part-number search matches despite the different letter case (case-insensitive 'contains' match).
@@ -1067,42 +1021,42 @@
 4. Category and vendor names are NOT searched - use their dedicated filters instead (deliberate, to avoid false matches on common words).</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S2-R6; §3 Key Decisions</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>All active filters combine with AND logic</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>PV — Filters</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded.
 2. You know one part's type, category, and vendor.</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>1. Set the Type filter to that part's type.
 2. Add the part's category in the Category filter.
@@ -1110,145 +1064,145 @@
 4. Change the Vendor filter to the part's actual vendor.</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>1. After steps 1-2 the part is still listed (it satisfies both filters).
 2. After step 3 the part disappears - a part must satisfy EVERY active filter to appear (AND logic, not OR).
 3. After step 4 the part is listed again.</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S2-R7</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Bin multi-select filter limits the table to inventory parts stocked in the selected bins</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>PV — Filters</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded.
 2. Inventory parts are stocked in at least two different bin locations.</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>1. Open the Bin filter and select one bin location.
 2. Add a second bin location.</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>1. Each selection reloads the data from the server.
 2. Only inventory parts stocked in ANY of the selected bins are shown.
 3. The filter allows more than one bin (multi-select).</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S2-R8</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Any Bin filter excludes all catalogue rows - Type Catalogue plus a Bin filter is empty by design</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>PV — Filters</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded.
 2. Catalogue rows are present under Type = Both (a catalogue part has in-window activity).</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>1. With Type = Both, select any bin in the Bin filter.
 2. Look for special-order (catalogue) rows in the result.
 3. Set the Type filter to the special-order (catalogue) choice while the Bin filter is still active.</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>1. With any Bin filter active, ALL special-order (catalogue) rows are excluded (they have no bin location).
 2. The special-order (catalogue) choice combined with any Bin filter yields an empty result showing the empty state - this is by design, not a defect.</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>SV-8642 (specs/parts-velocity.md S2-R8 — 'Catalogue' label rename PENDING per kickoff video P31 43:34-44:12; latest-info user ruling 2026-07-28: update per latest info now, correct at the live build check later)</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Location filter is rightmost, defaults to the active location, accessible-only</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>PV — Filters</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in as a user with access to at least two locations.
 2. You are on the Parts Velocity report on a first visit (no saved view).</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>1. Look at the rightmost control in the filter row.
 2. Note which location is selected by default and compare it to the location selected in the application's global location switcher.
@@ -1257,7 +1211,7 @@
 5. With 'All Locations' active, look at how the rows tell you which location they belong to.</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>1. The Location filter is the rightmost control in the filter row and is multi-select.
 2. On a first visit it defaults to the user's currently active location (the one in the global location switcher).
@@ -1267,9 +1221,55 @@
 6. With 'All Locations' active you can tell which location each row's data belongs to — a location label or marking is shown. (Exactly where and how it appears is confirmed in the build.)</t>
         </is>
       </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>SV-8642 (specs/parts-velocity.md S2-R9 — per-row location identifier in All-Locations view ADDED per kickoff video P10 40:58-41:20, user ruling 2026-07-28: video overrides spec (video newer, last-update-wins))</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Empty state shows the standard no-data message when no parts match the filters</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>PV — Filters</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1. You are on the Parts Velocity report with data loaded.</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1. Type a nonsense string (for example 'zzqx-no-such-part') into the toolbar search so no part matches.
+2. Read the message shown in the data area.</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1. The server returns zero rows and the table shows the empty state.
+2. The empty-state label reads exactly: "Empty bays, endless possibilities. Get Going!" (the application's standard reports no-data label).</t>
+        </is>
+      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>SV-8642 (specs/parts-velocity.md S2-R9 — per-row location identifier in All-Locations view ADDED per kickoff video P10 40:58-41:20, user ruling 2026-07-28: video overrides spec (video newer, last-update-wins))</t>
+          <t>specs/parts-velocity.md S2-R11; S2-N1; §7</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
@@ -1278,7 +1278,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Empty state shows the standard no-data message when no parts match the filters</t>
+          <t>Parts with no category, vendor, or bin assigned are excluded when that filter is active</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1297,58 +1297,12 @@
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>1. You are on the Parts Velocity report with data loaded.</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>1. Type a nonsense string (for example 'zzqx-no-such-part') into the toolbar search so no part matches.
-2. Read the message shown in the data area.</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>1. The server returns zero rows and the table shows the empty state.
-2. The empty-state label reads exactly: "Empty bays, endless possibilities. Get Going!" (the application's standard reports no-data label).</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>specs/parts-velocity.md S2-R11; S2-N1; §7</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Parts with no category, vendor, or bin assigned are excluded when that filter is active</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>PV — Filters</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded.
 2. A part with in-window activity exists that has NO category assigned; another with NO vendor; an inventory part with NO bin location.</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>1. Confirm the three parts appear with no filters active.
 2. Activate any Category filter and look for the category-less part.
@@ -1356,16 +1310,63 @@
 4. Clear it, activate any Bin filter, and look for the bin-less inventory part.</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>1. The part with no category does not appear when any Category filter is active.
 2. The part with no vendor does not appear when any Vendor filter is active.
 3. The inventory part with no bin location does not appear when any Bin filter is active.</t>
         </is>
       </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>specs/parts-velocity.md S2-E1; S2-E2; S2-E3</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>The Location filter is hidden for a user with access to only one location</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>PV — Filters</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in as a user with access to exactly one location.
+2. You are on the Parts Velocity report with data loaded.</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1. Look for the Location filter in the toolbar.
+2. Then sign in as a user with access to two or more locations and look again.</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
+2. For the user with access to two or more locations the Location filter IS shown.</t>
+        </is>
+      </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>specs/parts-velocity.md S2-E1; S2-E2; S2-E3</t>
+          <t>SV-8642 (specs/parts-velocity.md S2-E4 — expectation FLIPPED by kickoff video P33 46:10-46:28, user ruling 2026-07-28: video overrides spec (video newer, last-update-wins))</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
@@ -1374,12 +1375,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>The Location filter is hidden for a user with access to only one location</t>
+          <t>An inventory part stocked at two selected locations shows as two rows with per-location stock figures</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>PV — Filters</t>
+          <t>PV — Row Model</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1389,160 +1390,113 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in as a user with access to exactly one location.
-2. You are on the Parts Velocity report with data loaded.</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1. Look for the Location filter in the toolbar.
-2. Then sign in as a user with access to two or more locations and look again.</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
-2. For the user with access to two or more locations the Location filter IS shown.</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>SV-8642 (specs/parts-velocity.md S2-E4 — expectation FLIPPED by kickoff video P33 46:10-46:28, user ruling 2026-07-28: video overrides spec (video newer, last-update-wins))</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>An inventory part stocked at two selected locations shows as two rows with per-location stock figures</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>PV — Row Model</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>1. The same part number is stocked as an inventory part at two locations the user can access, with different On Hand / Min / Max values at each.
 2. You are on the Parts Velocity report with both locations selected in the Location filter.</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>1. Search for the part number in the toolbar search.
 2. Count the rows returned for it and read each row's On Hand, Min, and Max.</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>1. The part appears as TWO inventory rows - one per selected location (an inventory part is a per-location stock record).
 2. Each row carries only that one location's On Hand, Min, and Max.
 3. On Hand / Min / Max are NEVER summed across locations.</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S3-R1a; §3 Key Decisions</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>A catalogue part shows as one merged row with values summed across the selected locations</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>PV — Row Model</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>1. The same catalogue (special-order, vendor-sourced) part was requested on invoiced/paid work orders at two locations the user can access, inside the window.
 2. You are on the Parts Velocity report with both locations selected.</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>1. Search for the catalogue part.
 2. Count its rows and read its movement and money values.
 3. Compare against the per-location values with only one location selected at a time.</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>1. The catalogue part appears as a SINGLE row (one row per catalogue part, merged across the selected locations).
 2. Its movement and profitability values are the SUM of the per-location values.
 3. Its inventory-only columns (On Hand, Turns / Yr, Min, Max) show — (em-dash), because catalogue parts are not stocked.</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S3-R1a; §3 Key Decisions</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Rows load ranked by Demand descending with the descending indicator on the Demand header</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>PV — Row Model</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report on a first visit (no saved sort).
 2. Several parts have different Demand counts in the window; at least one inventory and one catalogue part share the same Demand count.</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>1. Let the report load without clicking any header.
 2. Read the Demand column top to bottom.
@@ -1550,7 +1504,7 @@
 4. Look at the Demand column header.</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>1. Rows are ranked by Demand, descending - the most-active parts first.
 2. Inventory and catalogue rows are ranked together in one list.
@@ -1558,42 +1512,42 @@
 4. The Demand header shows the descending sort indicator - this initial order IS the active sort (it is what the remembered view saves until you click another header).</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S3-R2</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Clicking a column header sorts ascending first, toggles on re-click, and places null values first-ascending / last-descending</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>PV — Row Model</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded.
 2. Both inventory and catalogue rows are present (so a nullable column such as On Hand has both values and — cells).</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>1. Click the header of a column that is not currently sorted (for example On Hand).
 2. Click the same header again.
@@ -1601,7 +1555,7 @@
 4. Try clicking the headers of several other columns.</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>1. The first click sorts that column ASCENDING; the header shows a direction indicator (an arrow).
 2. Clicking the active sort column again reverses the direction; the arrow flips.
@@ -1609,90 +1563,90 @@
 4. Every column is sortable; each header click re-fetches the data (server-resolved) and shows the first page of the re-sorted result; ties keep a stable order.</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S3-R3</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Sticky header, all-left alignment on screen, and plain-text Type values</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>PV — Row Model</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with enough rows to scroll the table body vertically.</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>1. Scroll the table body down and watch the header row.
 2. Read the Type column values.
 3. Look at the alignment of every header label and cell, including numeric and money columns.</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>1. The header row is sticky - it stays visible while the body scrolls.
 2. The Type column shows each row's kind as plain text (no badge or chip styling): Inventory, or the special-order catalogue kind. (The special-order kind's exact on-screen word is confirmed in the build — the spec says "Catalogue", a rename is being considered, and it must stay short enough for a column.)
 3. ALL columns - header and cell data, including numbers and money - are left-aligned on screen. (The exports right-align numerics instead: a deliberate export-only difference.)</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>SV-8643 (specs/parts-velocity.md S3-R4; S3-R5; S3-R8 — Type value 'Catalogue' rename PENDING per kickoff video P31 43:34-44:12; latest-info user ruling 2026-07-28: update per latest info now, correct at the live build check later)</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Info icons on Units Sold, Demand, and Turns / Yr show the exact spec descriptions and never trigger a sort</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>PV — Row Model</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded.
 2. The Turns / Yr column has been enabled via the column picker (it is hidden by default).</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>1. Look immediately to the right of the Units Sold, Demand, and Turns / Yr header labels.
 2. Hover each grey info icon and read the description.
@@ -1700,7 +1654,7 @@
 4. Click/activate an icon and watch whether the column sort changes.</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>1. Each of the three headers carries a grey info icon, shown always (not hover-to-reveal) whenever its column is visible; the Turns / Yr icon appears only once that column is enabled.
 2. Units Sold shows exactly: "Units taken out of inventory stock on invoiced work orders in this date range. This is stock movement, so it can differ from the units billed behind Revenue and Sell Price."
@@ -1710,50 +1664,50 @@
 6. No other column header carries an info icon.</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S3-R6</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Description, Category, and Vendor truncate with an ellipsis and show in full on hover; Part # is never truncated</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>PV — Row Model</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>1. A part with a very long description (and a long category and vendor name) has in-window activity.
 2. A part with a long part number exists.
 3. You are on the Parts Velocity report with those parts visible.</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>1. Look at the long Description, Category, and Vendor cells.
 2. Hover each truncated cell.
 3. Look at the long Part # cell.</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>1. Long Description, Category, and Vendor text is truncated with an ellipsis on screen.
 2. The full value shows on native hover (browser tooltip).
@@ -1761,49 +1715,49 @@
 4. The CSV export carries the full untruncated Description / Category / Vendor values.</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S3-R7</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Null values render as an em-dash only in the nullable fields; counts and Revenue/Margin are never null</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>PV — Row Model</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with all 20 columns enabled.
 2. A catalogue row is visible, plus an inventory row with no in-window activity that stays in the report via on-hand stock.</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>1. On the catalogue row, read On Hand, Turns / Yr, Min, and Max.
 2. On the no-activity inventory row, read Units Sold, Units Returned, Sold via WO, Sold via Parts Sale, Demand, Revenue, and Margin.
 3. On the same row, read Unit Cost, Sell Price, Margin %, and Last Sale (assuming no billed units, no revenue, and no recorded sale ever).</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>1. On Hand, Turns / Yr, Min, and Max show — (em-dash) on catalogue rows - always.
 2. The count metrics and money totals are NEVER null: Units Sold / Units Returned / Sold via WO / Sold via Parts Sale show 0.00, Demand shows 0, Revenue and Margin show $0.00.
@@ -1811,152 +1765,197 @@
 4. Every null renders as the same — (em-dash) glyph, in the table and in all exports.</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S3-R9; S5-R5</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>An inventory part is excluded only when it has no movement, under one unit on hand, AND no billed revenue</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>PV — Row Model</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>1. Inventory part A: zero stock movement in the window, less than one unit on hand, zero billed revenue in the window.
 2. Inventory part B: zero stock movement and zero on hand, but billed revenue in the window (e.g. a drop-ship sale billed without a stock decrement).</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>1. Search for part A in the report.
 2. Search for part B in the report.</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>1. Part A does NOT appear - it fails all three keep-criteria (no movement, under one on hand, no revenue) so it carries nothing to act on.
 2. Part B DOES appear - a part with billed Revenue &gt; 0 is always kept even with no stock movement and no on-hand stock.
 3. (Catalogue parts have no such rule: a never-requested catalogue part simply produces no row.)</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S3-N1</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>A sale invoiced then fully reversed in-window shows Demand 1 with Units Sold 0.00, and negative movement shows a leading minus</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>PV — Row Model</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>1. Inventory part C: one sale invoiced AND fully reversed inside the window, and the part still has on-hand stock (so it stays in the result set).
 2. Inventory part D: reversals exceed sales in the window (net-negative movement), with on-hand stock or other billed revenue keeping it in the result set.</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>1. Find part C and read its Demand and Units Sold.
 2. Find part D and read its Units Sold.</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>1. Part C shows Demand 1 (the reversal does not decrement the Demand count) with Units Sold 0.00 (the reversal nets the movement to zero).
 2. Part D shows a NEGATIVE Units Sold with a leading minus (e.g. -3.00) - negative movement is not floored to zero.
 3. A fully-reversed part with zero net movement, no on-hand stock, and no residual revenue would be excluded per S3-N1 (Demand alone is not a keep-criterion).</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S3-E1; S5-R5</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Column picker lists all 20 available columns with toggles and never offers the internal on-hand cost</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>PV — Columns &amp; Remembered View</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded.</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>1. Open the column picker from its toolbar button.
 2. Count the columns listed and check each has a toggle.
 3. Look for any on-hand cost / inventory-value entry.</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>1. The picker lists all 20 available columns, each with a toggle: Type, Part #, Description, Category, Vendor, Units Sold, Units Returned, Sold via WO, Sold via Parts Sale, Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand, Turns / Yr, Min, Max.
 2. No on-hand cost column is offered - the report computes one internally but it is never selectable and never displayed.</t>
         </is>
       </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>specs/parts-velocity.md S4-R1; S4-R4; S5-R6</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>First visit shows exactly the 14 default columns in the specified order</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>PV — Columns &amp; Remembered View</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>1. You are on the Parts Velocity report on a first visit (no saved column selection).</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>1. Read the visible column headers left to right without touching the picker.</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>1. Exactly these 14 columns show, in this left-to-right order: Type, Part #, Description, Category, Vendor, Units Sold, Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand.
+2. The other 6 columns start hidden: Units Returned, Sold via WO, Sold via Parts Sale, Turns / Yr, Min, Max.</t>
+        </is>
+      </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>specs/parts-velocity.md S4-R1; S4-R4; S5-R6</t>
+          <t>specs/parts-velocity.md S4-R2; S4-R3</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
@@ -1965,7 +1964,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>First visit shows exactly the 14 default columns in the specified order</t>
+          <t>A re-enabled column returns to its canonical slot and toggling takes effect immediately without a reload</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1980,115 +1979,70 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1. You are on the Parts Velocity report on a first visit (no saved column selection).</t>
+          <t>1. You are on the Parts Velocity report with data loaded.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>1. Read the visible column headers left to right without touching the picker.</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>1. Exactly these 14 columns show, in this left-to-right order: Type, Part #, Description, Category, Vendor, Units Sold, Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand.
-2. The other 6 columns start hidden: Units Returned, Sold via WO, Sold via Parts Sale, Turns / Yr, Min, Max.</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>specs/parts-velocity.md S4-R2; S4-R3</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>A re-enabled column returns to its canonical slot and toggling takes effect immediately without a reload</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>PV — Columns &amp; Remembered View</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>1. You are on the Parts Velocity report with data loaded.</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>1. In the column picker, enable Min, then Units Returned, then Turns / Yr - in that (non-canonical) order.
 2. Watch the table as each toggle is flipped.
 3. Read the resulting header order.</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>1. Each toggle takes effect immediately - the table re-renders without a page reload.
 2. Columns always render in the fixed canonical left-to-right order regardless of the order they were toggled on: Type, Part #, Description, Category, Vendor, Units Sold, Units Returned, Sold via WO, Sold via Parts Sale, Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand, Turns / Yr, Min, Max.
 3. So Units Returned slots in right after Units Sold, Turns / Yr after On Hand, and Min before Max - not appended at the end.</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S4-R4; S4-R5</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>Filters, column selection, and sort are remembered per browser and restored before the first data fetch</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>PV — Columns &amp; Remembered View</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded.</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>1. Set a non-default view: Type = Inventory, date range = Last Month, pick a category, enable Turns / Yr, and sort by Revenue descending.
 2. Leave the report (navigate elsewhere), then return to it.
 3. Reload the page (browser refresh) and observe again.</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>1. On return, every saved setting is restored: Type = Inventory, Last Month, the chosen category, the column set including Turns / Yr, and the Revenue-descending sort.
 2. The saved values are applied BEFORE the first data fetch - the report does not flash the defaults and then re-query.
@@ -2096,53 +2050,100 @@
 4. The same holds after a full page reload.</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S4-R6; S1-R2</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>A saved value that is no longer valid falls back to that setting's default on restore</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>PV — Columns &amp; Remembered View</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>1. A saved view exists in this browser that includes a location the user can no longer access (e.g. access was removed after the view was saved), or a custom date range that is now malformed.</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>1. Return to the Parts Velocity report with that stale saved view in place.
 2. Observe which location / date range the report loads with.</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>1. The invalid saved value is NOT sent to the server.
 2. That one setting falls back to its default (e.g. the location falls back to the active location); the other saved settings still restore normally.
 3. The report loads without an error.</t>
         </is>
       </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>specs/parts-velocity.md S4-R6</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>A different user signing in on the same browser inherits the saved view</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>PV — Columns &amp; Remembered View</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>1. User 1 has saved a clearly non-default view on this browser (e.g. Type = Catalogue, Last Quarter).
+2. User 2 can open the report.</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>1. Sign out user 1 and sign in user 2 on the SAME browser.
+2. Open the Parts Velocity report.</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>1. User 2 sees user 1's saved view (Type = Catalogue, Last Quarter, the saved columns and sort).
+2. This is by design: storage is per browser, not tied to the account - there is no per-account separation.</t>
+        </is>
+      </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S4-R6</t>
@@ -2154,7 +2155,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>A different user signing in on the same browser inherits the saved view</t>
+          <t>All 20 columns can be hidden; the empty selection is not restored and an export then contains no data columns</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2174,158 +2175,66 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1. User 1 has saved a clearly non-default view on this browser (e.g. Type = Catalogue, Last Quarter).
-2. User 2 can open the report.</t>
+          <t>1. You are on the Parts Velocity report with data loaded.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>1. Sign out user 1 and sign in user 2 on the SAME browser.
-2. Open the Parts Velocity report.</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>1. User 2 sees user 1's saved view (Type = Catalogue, Last Quarter, the saved columns and sort).
-2. This is by design: storage is per browser, not tied to the account - there is no per-account separation.</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>specs/parts-velocity.md S4-R6</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>A saved view with a stale schema version is ignored and the current defaults load</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>PV — Columns &amp; Remembered View</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>1. The browser holds a saved view whose stored schema version does not match the current version of the report's saved format (seed by editing the stored value's version marker in browser storage).</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the Parts Velocity report with the stale-version saved view in place.</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>1. The stale view is ignored entirely.
-2. The report loads the current defaults: This Year, Both, the active location, the 14-column default set, Demand descending.</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>specs/parts-velocity.md S4-N1</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>All 20 columns can be hidden; the empty selection is not restored and an export then contains no data columns</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>PV — Columns &amp; Remembered View</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>1. You are on the Parts Velocity report with data loaded.</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>1. In the column picker, switch OFF all 20 columns.
 2. Trigger a CSV export while zero columns are enabled.
 3. Leave the report and return to it.</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>1. The picker enforces no minimum - all 20 columns can be switched off, leaving a grid with no data columns for the rest of the session.
 2. The export produces a file containing only the header/metadata rows and no data columns.
 3. On the next visit the all-hidden selection is NOT restored - the report falls back to the default 14-column set (the saved column selection returns to the last NON-EMPTY selection; all-hidden is the exception).</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S4-E1; S4-R6</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>Units Sold for an inventory part is net stock movement: invoicing adds, reversing subtracts, returns do not affect it</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>PV — Columns &amp; Calculations</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>1. An inventory part with known starting stock.
 2. You can invoice work orders, reverse/void an invoice, and initiate a part return for that part inside the report window.</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>1. Invoice a work order selling 5 units of the part; reload the report and read Units Sold.
 2. Reverse/void an invoice that sold 2 units in the window; reload and read Units Sold.
 3. Initiate a part return for 1 unit of the part; reload and read Units Sold.</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>1. After step 1, Units Sold increases by 5.00 (invoicing a work order adds the units sold - a stock-movement event).
 2. After step 2, Units Sold decreases by 2.00 (reversing/voiding an invoice adds stock back and is subtracted - Units Sold is net of invoice reversals).
@@ -2333,90 +2242,90 @@
 4. Units Sold can be 0.00 or negative when reversals exceed sales.</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S5-R1; S5-R4 (Units Sold, inventory); §4</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>Units Sold for a catalogue part is the total in-window vendor-request quantity, net of reversed sales</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>PV — Columns &amp; Calculations</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>1. A catalogue (vendor-sourced, special-order) part is requested on invoiced or paid work orders in the window - e.g. 3 units on one work order and 2 on another.
 2. One further in-window sale of the same catalogue part has been reversed/voided.</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>1. Find the catalogue part's row and read Units Sold.
 2. Compare against the sum of the in-window vendor-request quantities, leaving out the reversed sale.</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>1. Units Sold equals the total quantity across the part's in-window vendor requests (3 + 2 = 5.00 in the example), summed across the selected locations.
 2. The reversed/voided sale is EXCLUDED from the total (net of reversals, per S5-R4b).
 3. Only requests on work orders at status Invoiced or Paid count; the window is anchored to the work-order date.</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S5-R2; S5-R4 (Units Sold, catalogue); S5-R4b</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>Units Returned counts initiated part returns and parts-sale credits, and cancelling a return removes its quantity</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>PV — Columns &amp; Calculations</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>1. A part with in-window sales (so its row exists) and the Units Returned column enabled via the column picker.
 2. You can initiate a work-order part return, a parts-sale credit, and cancel a return.</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>1. Initiate a work-order part return for 2 units of the part; reload and read Units Returned.
 2. Create a parts-sale credit returning 1 more unit; reload and read Units Returned.
@@ -2424,7 +2333,7 @@
 4. Reverse/void an unrelated invoice for the part; reload and read Units Returned.</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>1. After step 1, Units Returned increases by 2.00 (the return record is counted when the return is initiated).
 2. After step 2, it increases by 1.00 more (a parts-sale credit also creates a part-return record).
@@ -2432,50 +2341,50 @@
 4. After step 4, Units Returned is UNCHANGED - invoice reversals are not returns (they affect Units Sold instead).</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S5-R3; S5-R4 (Units Returned); §3 Key Decisions</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>Units Returned is windowed by initiation date, ignores invoice status, and excludes core-charge returns</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>PV — Columns &amp; Calculations</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>1. A part sold in a PREVIOUS window whose return is initiated inside the CURRENT window (and the part has current-window activity or stock so its row exists).
 2. A core-charge return exists for a part in the window.
 3. The Units Returned column is enabled.</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>1. Select the current window and read the part's Units Returned.
 2. Select the previous window (when the sale happened) and read Units Returned again.
 3. Check the part with the core-charge return.</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>1. The return counts in the window of its INITIATION date - so it appears in the current window even though the sale was earlier (a return and its originating sale can fall in different report windows; each uses its own natural event date).
 2. In the previous window the return does not count (only the sale's own metrics do).
@@ -2484,49 +2393,49 @@
 5. A part whose ONLY in-window event is a return (no sale, no stock, no revenue) produces no row at all (per S3-N1) - accepted behavior, the row axis is sales/stock activity.</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S5-R3</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>Sold via WO counts Service-type work orders and Sold via Parts Sale counts Parts-type work orders, windowed by work-order date</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>PV — Columns &amp; Calculations</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>1. A part sold in the window on an invoiced SERVICE work order (e.g. 4 units) and on an invoiced PARTS SALE / Parts-type work order created in Parts → Parts Sale (e.g. 3 units).
 2. The Sold via WO and Sold via Parts Sale columns are enabled.</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>1. Read the part's Sold via WO value.
 2. Read the part's Sold via Parts Sale value.
 3. Move the date range so the work orders' end dates fall outside the window and re-read both.</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>1. Sold via WO shows the total part quantity on Service-type invoiced/paid work orders whose work-order date is in the window (4.00 in the example), net of reversed/voided sales.
 2. Sold via Parts Sale shows the total on Parts-type invoiced/paid work orders (counter sales) in the window (3.00), net of reversed/voided sales.
@@ -2534,50 +2443,50 @@
 4. Both workflows feed the report - a parts sale is a separate workflow from a service work order but counts fully.</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S5-R4 (Sold via WO / Sold via Parts Sale); §5 Assumptions</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>Demand counts each transaction once regardless of quantity, and a reversal neither adds nor subtracts</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>PV — Columns &amp; Calculations</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>1. An inventory part sold in the window on two invoiced work orders - one for 1 unit, one for 10 units.
 2. A catalogue part with two in-window vendor requests.
 3. One of the inventory part's in-window sales is then reversed/voided.</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>1. Read the inventory part's Demand before the reversal.
 2. Reverse/void one of its invoices and re-read Demand.
 3. Read the catalogue part's Demand.</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>1. The inventory part's Demand is 2 - each stock-decrementing invoicing event counts ONCE no matter how many units were on it (1 unit and 10 units each count as one).
 2. After the reversal, Demand is STILL 2 - a reversal event neither adds to nor subtracts from the count (while Units Sold nets down).
@@ -2585,49 +2494,49 @@
 4. Demand is the report's default ranking signal (a whole number, never null - 0 when none).</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S5-R4 (Demand); §4; §3 Key Decisions</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>Last Sale shows whole days since the most recent sale over ALL-TIME history, scoped to the selected locations</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>PV — Columns &amp; Calculations</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>1. A part whose most recent sale was N days ago, OUTSIDE the currently selected date range (e.g. range = This Month, last sale 42 days ago).
 2. The part still appears in the report (it has on-hand stock).
 3. For the location check: the part's most recent sale at location A is more recent than at location B.</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>1. Read the part's Last Sale value with the narrow date range selected.
 2. Switch the Location filter between location A and location B and re-read Last Sale.</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>1. Last Sale shows the whole days between today and the part's most recent sale measured over ALL-TIME history - it IGNORES the selected date range (e.g. '42 days' even though the range is This Month).
 2. It IS scoped to the selected location(s): with only location B selected, Last Sale reflects B's own most recent sale.
@@ -2635,84 +2544,84 @@
 4. For a catalogue part, the anchor is its most recent vendor-sourced invoiced/paid request.</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S5-R4 (Last Sale); §4; S5-R5</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>On Hand shows the row's own location stock, and Min / Max are read-only stored thresholds with no editing from the report</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>PV — Columns &amp; Calculations</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>1. An inventory part with a known on-hand quantity and stored Min / Max reorder thresholds at one location.
 2. The Min and Max columns are enabled via the column picker.</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>1. Read the part's On Hand, Min, and Max in the report and compare with the inventory record.
 2. Try clicking / double-clicking the Min and Max cells and look for any edit control or slide-over.</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>1. On Hand equals the part's CURRENT on-hand quantity at that row's location (never summed across locations).
 2. Min and Max show the stored minimum / maximum reorder thresholds for that location, as whole numbers (— when not set).
 3. Min and Max are READ-ONLY display columns - no edit control or slide-over opens; editing part attributes from this report is out of scope in this version.</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S5-R4 (On Hand / Min / Max); §2 Out of Scope; S5-R5</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>Turns / Yr annualizes the in-window sales rate against On Hand, shows 0.00 at zero stock, and can be negative</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>PV — Columns &amp; Calculations</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>1. The Turns / Yr column is enabled.
 2. Part A: known Units Sold over a known window with On Hand &gt; 0 (e.g. Units Sold 10.00 over a 30-day window with 5 on hand).
@@ -2720,14 +2629,14 @@
 4. Part C: negative Units Sold (reversals exceed sales) with stock on hand.</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>1. Compute the expected value for part A: (Units Sold ÷ Window days × 365) ÷ On Hand - e.g. (10 ÷ 30 × 365) ÷ 5 = 24.33.
 2. Compare against the displayed Turns / Yr for part A.
 3. Read Turns / Yr for parts B and C, and for any catalogue row.</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>1. Part A's Turns / Yr matches the formula (two decimals, e.g. 24.33); the window is the whole-day span inclusive of both dates with a floor of 1 day.
 2. Part B shows 0.00 (renders 0.00 when On Hand is 0 - not an error, not —).
@@ -2735,48 +2644,48 @@
 4. Catalogue rows always show — (not applicable).</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S5-R4 (Turns / Yr); S5 Definitions (Window)</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>Revenue, Margin, Unit Cost, Sell Price, and Margin % follow the billed-line formulas, computed unrounded and rounded once</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>PV — Columns &amp; Calculations</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>1. A part with known billed lines in the window - e.g. two invoiced work-order part lines: 2 units at $50.00 sell / $30.00 cost, and 1 unit at $40.00 sell / $30.00 cost.
 2. All five profitability columns are visible.</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>1. Compute the expected values: Revenue = (2×50)+(1×40) = $140.00; COGS = (2×30)+(1×30) = $90.00; billed units = 3; Margin = 140−90 = $50.00; Unit Cost = 90÷3 = $30.00; Sell Price = 140÷3 = $46.67; Margin % = 50÷140×100 = 35.7%.
 2. Compare each against the part's displayed row.</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>1. Revenue = the summed billed sell amount (each line's stored sell price × quantity) in the window.
 2. Margin = Revenue − COGS (the summed billed cost captured at billing time).
@@ -2786,99 +2695,99 @@
 6. The same formulas apply to inventory and catalogue rows (for catalogue, from the vendor part requests).</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S5-R4a; §4</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>A reversed/voided sale is excluded from every billed-line column (Revenue, Margin, Unit Cost, Sell Price, Sold via WO, Sold via Parts Sale, catalogue Units Sold)</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>PV — Columns &amp; Calculations</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>1. A part with two in-window billed sales of known amounts, one of which you then reverse/void.
 2. All movement and profitability columns are visible.</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>1. Record the part's Revenue, Margin, Unit Cost, Sell Price, Margin %, Sold via WO / Sold via Parts Sale (and Units Sold for a catalogue part).
 2. Reverse/void one of the two sales.
 3. Reload the report and re-read every column.</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>1. After the reversal, ALL the billed-line columns drop to reflect only the remaining sale - the reversed/voided sale is excluded from Revenue, Margin, Unit Cost, Sell Price, Margin %, Sold via WO, Sold via Parts Sale, and (for catalogue) Units Sold.
 2. This netting is consistent with inventory Units Sold, which already nets reversals via the stock add-back.
 3. A voided sale therefore inflates NO column.</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S5-R4b; S5-R4a; §3 Key Decisions</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Unit Cost / Sell Price and Margin % use independent null triggers, so mixed rows are valid</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>PV — Columns &amp; Calculations</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>1. Row 1: a part with booked revenue but ZERO billed units in the window (e.g. a credit/adjustment line carrying revenue with no billed quantity).
 2. Row 2: a part with billed units &gt; 0 but Revenue $0.00 (e.g. billed at a $0 sell price).
 3. Row 3: a part with both billed units ≤ 0 and Revenue ≤ 0.</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>1. Read Unit Cost, Sell Price, Margin %, Revenue, and Margin on row 1.
 2. Read the same columns on row 2.
 3. Read the same columns on row 3.</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>1. Row 1: Unit Cost and Sell Price show — (billed units ≤ 0) while Revenue and Margin show dollar amounts AND Margin % is still computed from Revenue - a valid mixed row, not a defect.
 2. Row 2: Sell Price shows $0.00 (a number) while Margin % shows — (Revenue ≤ 0) - also valid.
@@ -2886,47 +2795,47 @@
 4. The three triggers are independent: Unit Cost/Sell Price null on billed units ≤ 0; Margin % null on Revenue ≤ 0.</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S5-R4a (null rules + mixed-row paragraph); S3-R9</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>On-screen number formats match the spec for every column type, and rounding is half away from zero</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>PV — Columns &amp; Calculations</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>1. All 20 columns are enabled and rows exist with large (1,000+), negative, and null values across the column types.</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>1. Read a large count value (Units Sold etc.), a negative count, a large money value, a negative money value, a Margin % value, a Demand value, Min/Max values, and a Last Sale value.
 2. Seed a Margin % that lands exactly on a rounding tie (e.g. computes to 8.45% / -8.45%) and read the display.</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>1. Units Sold, Units Returned, Sold via WO, Sold via Parts Sale, On Hand, Turns / Yr: two decimals with thousands separators (1,250.00); negatives with a leading minus (-3.00).
 2. Unit Cost, Sell Price, Revenue, Margin: currency with $, two decimals, thousands separators ($1,250.00); negatives with a leading minus and NO parentheses (-$45.00).
@@ -2935,147 +2844,147 @@
 5. Rounding is half AWAY from zero: 8.45% displays 8.5% and -8.45% displays -8.5% (a tie rounds up in magnitude); this applies to all money and one-decimal values.</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S5-R5; S5-R7 (rounding)</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>Core parts are excluded from both the inventory and catalogue result sets</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>PV — Columns &amp; Calculations</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>1. An inventory part flagged as a core has in-window sales activity and on-hand stock.
 2. A vendor-sourced core part was requested on an invoiced/paid work order in the window.</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>1. Search the report for the inventory core part (Type = Both).
 2. Search for the catalogue core part.</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>1. The inventory core part does NOT appear in the report despite its activity and stock.
 2. The catalogue core part does NOT appear either.
 3. Parts flagged as a core are excluded from both result sets by design.</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S5-R1; S5-R2; §3 Key Decisions</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>Movement and billed bases may differ for an inventory row (expected), while Sold via WO + Sold via Parts Sale equals the billed units</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>PV — Columns &amp; Calculations</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>1. An inventory part with a billed sale that produced NO matching stock decrement (e.g. a drop-ship or negative-stock sale) plus normal stocked sales in the window.
 2. A catalogue part with in-window vendor requests.
 3. Units Sold, Sold via WO, Sold via Parts Sale, and the profitability columns are visible.</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>1. On the inventory row, compare Units Sold against Revenue ÷ Sell Price (the billed units).
 2. On the same row, add Sold via WO + Sold via Parts Sale and compare against the billed units.
 3. On the catalogue row, compare Units Sold, Sold via WO + Sold via Parts Sale, and the billed units.</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>1. On the inventory row, Units Sold (stock movement) DIFFERS from the billed units behind Revenue/Sell Price - this is CORRECT behavior, not a defect (the Units Sold tooltip calls it out).
 2. Sold via WO + Sold via Parts Sale together DO equal the billed-units basis (work orders are only Service- or Parts-type) - but neither equals the movement-based Units Sold.
 3. On the catalogue row, everything reconciles: Units Sold = Sold via WO + Sold via Parts Sale = billed units (they share the vendor-request quantity as one source).</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S5-R7; §3 Key Decisions</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>Window anchors: inventory movement metrics use the movement event date while billed columns use the work-order date</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>PV — Columns &amp; Calculations</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>1. A work order whose END date falls in window W1 but whose invoicing (stock-movement event) happened in window W2 for an inventory part.
 2. Both W1 and W2 are selectable ranges.</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>1. Select window W1 and read the part's Units Sold / Demand vs its Revenue / Sold via WO.
 2. Select window W2 and read the same columns.
 3. Select a single-day range (Today) and check the report still computes (window floor).</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>1. In W1 (work-order date in window): the billed columns (Revenue, Margin, Unit Cost, Sell Price, Margin %, Sold via WO, Sold via Parts Sale) count the sale, while inventory Units Sold / Demand do NOT (their movement event is outside W1).
 2. In W2 (movement date in window): Units Sold / Demand count it, the billed columns do not - the two anchors CAN differ for an inventory part and that is intended.
@@ -3083,238 +2992,238 @@
 4. Last Sale is not windowed at all (all-time).</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S5 Definitions (Window / Work-order date); S5-R7</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>The overflow button opens an export menu with Download (PDF) and Download (CSV) in that order</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>PV — Exports</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded.</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>1. Find the ⋯ overflow button - the leftmost control in the toolbar's action cluster.
 2. Click it and read the menu items top to bottom.</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>1. The ⋯ overflow button sits leftmost in the toolbar's action cluster.
 2. The menu holds exactly two items, in this order: Download (PDF), then Download (CSV).</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S6-R1</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>Both exports reflect the filters and search active at the time of export</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>PV — Exports</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded across types, categories, and locations.</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>1. Set a distinctive filter mix: Type = Inventory, a single category, a short date range, and a search string.
 2. Download the CSV and open it.
 3. Download the PDF and open it.</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>1. Both files contain only the rows matching the date range, type, category, vendor, bin, location, and search active at export time - not a full unfiltered dump.
 2. The exported rows match what the on-screen grid was showing.</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S6-R2; §3 Key Decisions</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>Exports include only the enabled columns, in the canonical on-screen order</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>PV — Exports</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded.</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>1. Hide two default columns (e.g. Category, Margin %) and enable a hidden one (e.g. Units Returned).
 2. Download the CSV and read its column headers in order.
 3. Download the PDF and read its columns in order.</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>1. Both exports contain ONLY the currently enabled columns - the hidden ones are absent.
 2. Columns appear in the CANONICAL order (the fixed on-screen order) - the re-enabled Units Returned sits right after Units Sold, NOT appended at the end.
 3. The export mirrors the visible grid.</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S6-R3; S4-R4</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>Exports reflect the active sort - including Min/Max sorts, the default Demand order, and identical null placement</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>PV — Exports</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded, including rows with — values in a sortable column (e.g. On Hand on catalogue rows).
 2. Min and Max are enabled.</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>1. Without clicking any header (default Demand descending), download the CSV and check the row order.
 2. Sort by Min ascending, export, and check the order including where the — rows land.
 3. Sort by On Hand descending, export, and check the null placement.</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>1. The default Demand-descending order is exported when the user has not chosen another column.
 2. Every column's sort is honored in the export - including Min and Max.
 3. The export renders the EXACT server order, including null placement (nulls first on ascending, last on descending) - the export and the on-screen grid match; there is no on-screen-vs-export null-sorting difference.</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S6-R4; S3-R3</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>PDF: named velocity-report.pdf, A3 landscape, titled Parts Velocity, with 18-character text truncation but Part # untruncated</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>PV — Exports</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded, including a part with a Description, Category, and Vendor each longer than 18 characters and a long Part #.</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>1. Download the PDF and check the saved filename.
 2. Open it and check the page format and title.
 3. Find the long-text part's row and read Description, Category, Vendor, and Part #.</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>1. The file downloads as velocity-report.pdf.
 2. The PDF is formatted for A3 landscape and titled Parts Velocity.
@@ -3322,106 +3231,204 @@
 4. Part # is NOT truncated.</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S6-R5; S6-R6</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>CSV: named velocity-report.csv with full untruncated text values and Last Sale as a raw integer</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>PV — Exports</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded, including a part with a Description longer than 18 characters and a part with a Last Sale value.</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>1. Download the CSV and check the saved filename.
 2. Open it and read the long part's Description, Category, and Vendor.
 3. Read the Last Sale column value.</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>1. The file downloads as velocity-report.csv.
 2. The CSV carries the FULL, untruncated Description / Category / Vendor values (unlike the PDF's 18-character cut).
 3. Last Sale is a raw integer in the CSV (e.g. 42) - the 'N days' wording is PDF/on-screen only.</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S6-R5; S6-R6; S6-R8</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>Null values render as an em-dash in both exports, and Last Sale renders as 'N days' in the PDF</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>PV — Exports</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>1. Rows with null values exist (a catalogue row for On Hand / Turns / Yr / Min / Max; a row with billed units 0 for Unit Cost / Sell Price; a never-sold row for Last Sale).
 2. All nullable columns are enabled.</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>1. Download the CSV and locate the null cells.
 2. Download the PDF and locate the same cells.
 3. In the PDF, read a non-null Last Sale value.</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>1. A null value renders as — (em-dash) in BOTH the CSV and the PDF, in every nullable field: Unit Cost, Sell Price, Margin %, On Hand, Turns / Yr, Last Sale, Min, Max.
 2. Revenue, Margin, and the count metrics are never null in the exports either ($0.00 / 0.00 / 0).
 3. In the PDF, Last Sale renders as 'N days' (e.g. 42 days).</t>
         </is>
       </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>specs/parts-velocity.md S6-R7; S6-R8; S3-R9</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>PDF export alignment: Type centered, text left, numeric and money right</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>PV — Exports</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>1. You are on the Parts Velocity report with data loaded and several columns of each kind visible.</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>1. Download the PDF and look at the alignment of each column.
+2. Download the CSV and open it in a plain text editor to confirm it is plain comma-separated values (a CSV file carries no alignment of its own).</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>1. In the PDF, the Type column is CENTERED.
+2. In the PDF, the text columns (Part #, Description, Category, Vendor) are left-aligned.
+3. In the PDF, EVERY numeric and money column is right-aligned.
+4. This is a deliberate export-only treatment - the on-screen table is all-left-aligned; the difference is documented, not a defect.
+5. The CSV is plain data — the alignment assertions apply to the PDF only; how a spreadsheet displays the CSV is not part of this test.</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>SV-8646 (specs/parts-velocity.md S6-R10; S3-R8)</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Export toasts: exact success texts; server or fallback error text on failure</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>PV — Exports</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>1. You are on the Parts Velocity report with data loaded.
+2. You can force an export failure (e.g. drop the network connection just before triggering the download, or induce a server error).</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>1. Download the CSV and the PDF normally and read each toast.
+2. Trigger a CSV export under the failure condition and read the toast.
+3. Trigger a PDF export under the failure condition and read the toast.</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>1. On success the toasts read exactly "Velocity report exported (CSV)" / "Velocity report exported (PDF)" and auto-fade — UPPERCASE (CSV)/(PDF).
+2. An error toast is shown on failure; when the server provides a message, that server message is shown.
+3. Otherwise the failure toast reads exactly: "Failed to export velocity report (csv)" or "Failed to export velocity report (pdf)" — lowercase (csv)/(pdf); the success/failure casing mix is the shipped wording, documented as-is (not a bug).</t>
+        </is>
+      </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>specs/parts-velocity.md S6-R7; S6-R8; S3-R9</t>
+          <t>specs/parts-velocity.md S6-R9; S6-N1; §7 (casing note)</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr"/>
@@ -3430,12 +3437,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Export alignment: Type centered, text columns left-aligned, numeric and money columns right-aligned</t>
+          <t>The report uses the standard two-tone layout: white card surfaces on a soft blue-grey backdrop with an edge-to-edge table</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>PV — Exports</t>
+          <t>PV — Visual Conformance</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -3450,207 +3457,64 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>1. You are on the Parts Velocity report with data loaded and several columns of each kind visible.</t>
+          <t>1. You are on the Parts Velocity report with data loaded, in light mode.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>1. Download the PDF and look at the alignment of each column.
-2. Open the CSV in a spreadsheet tool and check the produced alignment/formatting where applicable.</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>1. In the exports, the Type column is CENTERED.
-2. The text columns (Part #, Description, Category, Vendor) are left-aligned.
-3. EVERY numeric and money column is right-aligned.
-4. This is a deliberate export-only treatment - the on-screen table is all-left-aligned; the difference is documented, not a defect.</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>SV-8646 (specs/parts-velocity.md S6-R10; S3-R8)</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>Successful downloads show the exact success toasts with uppercase (CSV)/(PDF)</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>PV — Exports</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>1. You are on the Parts Velocity report with data loaded.</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>1. Download the CSV and read the toast.
-2. Download the PDF and read the toast.</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t>1. On CSV success, a success toast reads exactly: "Velocity report exported (CSV)" and auto-fades.
-2. On PDF success, it reads exactly: "Velocity report exported (PDF)" and auto-fades.
-3. The success toasts use UPPERCASE (CSV)/(PDF) - the failure toasts use lowercase; that casing mix is the shipped wording, documented as-is (not a bug).</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>specs/parts-velocity.md S6-R9; §7 (casing note)</t>
-        </is>
-      </c>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>A failed export shows the server message when available, otherwise the exact fallback error toast with lowercase (csv)/(pdf)</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>PV — Exports</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>1. You are on the Parts Velocity report with data loaded.
-2. You can force an export failure (e.g. drop the network connection just before triggering the download, or induce a server error).</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>1. Trigger a CSV export under the failure condition and read the toast.
-2. Trigger a PDF export under the failure condition and read the toast.</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>1. An error toast is shown on failure.
-2. When the server provides a message, that server message is shown.
-3. Otherwise the toast reads exactly: "Failed to export velocity report (csv)" or "Failed to export velocity report (pdf)" - lowercase (csv)/(pdf), per the documented shipped casing.</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>specs/parts-velocity.md S6-N1; §7</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>The report uses the standard two-tone layout: white card surfaces on a soft blue-grey backdrop with an edge-to-edge table</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>PV — Visual Conformance</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>1. You are on the Parts Velocity report with data loaded, in light mode.</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>1. Look at the page background, the toolbar, and the table surfaces.
 2. Look at the card corners and the table's horizontal extent.</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>1. White card surfaces (toolbar + table cells) sit on the standard soft blue-grey page background (the application's two-tone report theme).
 2. There is NO card border-radius - the table runs edge to edge.
 3. The layout matches the application's other reports (consistency goal, §1).</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S7-R1; §2</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>Toolbar and table detail styling: paddings, white header with 1px top border, white body cells, 2rem edge padding</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>PV — Visual Conformance</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded (use browser devtools to measure paddings).</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>1. Inspect the toolbar's background and internal padding.
 2. Inspect the table header cells and the border between header and toolbar.
 3. Inspect the body cells and the first/last cell padding in a row.</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>1. The toolbar background is white (black in dark mode) with internal padding 32px top, 2rem right, 24px bottom, 2rem left.
 2. Header cells have a white background and a 1px top border separating them from the toolbar.
@@ -3658,251 +3522,251 @@
 4. The leftmost cell in every row (header and body) has 2rem left padding; the rightmost cell has 2rem right padding.</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S7-R2; S7-R3; S7-R4; S7-R5</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>Dark mode is supported and the grey info icon keeps at least 3:1 contrast in both modes</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>PV — Visual Conformance</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded and dark mode available in the application.</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>1. Switch the application to dark mode.
 2. Look at the page background, toolbar, and cells.
 3. Check the grey ⓘ info icon against its cell background in dark mode, then again in light mode.</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>1. The report supports dark mode: page background, toolbar, and cells use their dark-mode equivalents.
 2. The grey ⓘ info icon uses a token meeting at least a 3:1 contrast ratio against the cell background in BOTH light and dark mode.</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S7-R6</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>The report is server-paginated - the backend returns one page of rows at a time</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>PV — API</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with more rows in the result set than one page holds.
 2. Browser devtools (network tab) are open to observe the backend requests.</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>1. Load the report and observe the backend data request and its response size.
 2. Move to the next page of rows and observe the traffic.</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>1. The backend returns ONE page of rows at a time - the full result set is not shipped to the browser.
 2. Paging is resolved on the server: moving to another page issues a fresh backend request for that page.
 3. This keeps the report responsive at scale (organizations can carry 50-60k parts, multiplied across locations).</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>SV-8642 (specs/parts-velocity.md §2 (server-paginated); S2-R10)</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>Every filter or search change re-queries the server and returns the first page of the new result set</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>PV — API</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded and the browser devtools network tab open.</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>1. Change each of these in turn and watch the network traffic: Type, date range, Bin, Location, Category, Vendor, and the toolbar search.
 2. After a filter change while on a later page, note which page of results is shown.</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>1. EACH change (Type, date range, Bin, Location, Category, Vendor, search) triggers a fresh server-side data load.
 2. There is no client-side-only narrowing - every filter or search change re-queries the server.
 3. Each change returns the FIRST page of the new result set.</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>SV-8642 (specs/parts-velocity.md S2-R10)</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>Header-click sorting re-queries the server with nulls first on ascending and last on descending as a server sort semantic</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>PV — API</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded (including rows with null values in a sortable column) and the network tab open.</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>1. Click a column header and watch the network traffic and the returned order.
 2. Click it again (reverse direction) and observe.
 3. Note where the null rows land in the server-returned order for each direction.</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>1. Each header click re-fetches the data from the server, ordered by the chosen column and direction, returning the first page of the re-sorted result set.
 2. Null values are placed FIRST on ascending and LAST on descending - as a server sort semantic, so the same order appears on screen and in the exports.
 3. Ties keep a stable order (no explicit secondary key).</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S3-R3</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>The backend denies both the report data and the export to a user without Inventory Reports → View</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>PV — API</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in as a Reports-section user whose role lacks the Inventory Reports → View permission.
 2. Browser devtools (network tab) are open.</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>1. Open the Parts Velocity report and observe the backend data request's outcome.
 2. Attempt the export and observe the backend export request's outcome.</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>1. The backend REFUSES the report data request - the user is denied the data (the UI shows the standard access-denied state).
 2. The backend likewise refuses the export request - no file is produced.
 3. Both loading and exporting are gated by the same Inventory Reports → View permission.</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S1-R4; S1-N2</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr"/>
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/Report-Suite_Parts-Velocity-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Parts-Velocity-Report_testrail-import.xlsx
@@ -802,7 +802,7 @@
         <is>
           <t>1. You are on the Parts Velocity report with data loaded.
 2. This is a first visit (no saved view), so the first-visit defaults apply.
-3. Both inventory parts and special-order (catalogue) parts have sales activity in the selected date range.</t>
+3. Both inventory parts and special-order parts (the "Special Order" type) have sales activity in the selected date range.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -816,15 +816,15 @@
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1. The Type filter is the first control in the filter row.
-2. It is single-select and offers exactly three choices: Both, Inventory, and a choice for special-order catalog parts that were never put into stock. (That third choice's exact on-screen label is confirmed in the build — the spec calls it "Catalogue" and a rename is being considered.)
+2. It is single-select and offers exactly three choices: Both, Inventory, and Special Order (special-order catalog parts that were never put into stock).
 3. On a first visit the default is Both.
-4. Both is an explicit selection returning inventory and special-order rows together - a deliberate filter value, not the absence of a filter.
-5. Each selection immediately reloads the report limited to that type (no separate Apply step) — under Inventory every row's Type column reads Inventory; under the special-order (catalogue) choice every row shows that type; under Both, rows of both kinds appear.</t>
+4. Both is an explicit selection returning inventory and Special Order rows together - a deliberate filter value, not the absence of a filter.
+5. Each selection immediately reloads the report limited to that type (no separate Apply step) - under Inventory every row's Type column reads Inventory; under Special Order every row's Type column reads Special Order; under Both, rows of both kinds appear.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>SV-8642 (specs/parts-velocity.md S2-R1; S3-R5 — 'Catalogue' label rename PENDING per kickoff video P31 43:34-44:12; latest-info user ruling 2026-07-28)</t>
+          <t>SV-8642 (specs/parts-velocity.md S2-R1; S3-R5 - 'Catalogue' RENAMED to the exact label 'Special Order' [Type filter, Type column, export] per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source, last-update-wins), confirming kickoff video P31)</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
@@ -1130,7 +1130,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Any Bin filter excludes all catalogue rows - Type Catalogue plus a Bin filter is empty by design</t>
+          <t>Bin filter excludes special-order rows; Bin plus that Type is empty by design</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1151,25 +1151,25 @@
       <c r="E15" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded.
-2. Catalogue rows are present under Type = Both (a catalogue part has in-window activity).</t>
+2. Special Order rows are present under Type = Both (a Special Order part has in-window activity).</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
           <t>1. With Type = Both, select any bin in the Bin filter.
-2. Look for special-order (catalogue) rows in the result.
-3. Set the Type filter to the special-order (catalogue) choice while the Bin filter is still active.</t>
+2. Look for Special Order rows in the result.
+3. Set the Type filter to Special Order while the Bin filter is still active.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1. With any Bin filter active, ALL special-order (catalogue) rows are excluded (they have no bin location).
-2. The special-order (catalogue) choice combined with any Bin filter yields an empty result showing the empty state - this is by design, not a defect.</t>
+          <t>1. With any Bin filter active, ALL Special Order rows are excluded (they have no bin location).
+2. Special Order combined with any Bin filter yields an empty result showing the empty state - this is by design, not a defect.</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>SV-8642 (specs/parts-velocity.md S2-R8 — 'Catalogue' label rename PENDING per kickoff video P31 43:34-44:12; latest-info user ruling 2026-07-28: update per latest info now, correct at the live build check later)</t>
+          <t>SV-8642 (specs/parts-velocity.md S2-R8 - 'Catalogue' RENAMED to the exact label 'Special Order' per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source, last-update-wins), confirming kickoff video P31)</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
@@ -1218,12 +1218,13 @@
 3. The list holds the locations the signed-in user has access to, plus an 'All Locations' option.
 4. Each selection reloads the data scoped to the chosen set; 'All Locations' means all locations the user can ACCESS, never beyond - a location the user cannot access is never included.
 5. The location scope cascades through every metric like the other filters.
-6. With 'All Locations' active you can tell which location each row's data belongs to — a location label or marking is shown. (Exactly where and how it appears is confirmed in the build.)</t>
+6. With 'All Locations' active you can tell which location each row's data belongs to — a location label or marking is shown. (Exactly where and how it appears is confirmed in the build.)
+7. The page itself shows which location(s) the report is currently scoped to (the new on-screen scope indicator - exactly where and how it appears is confirmed in the build).</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>SV-8642 (specs/parts-velocity.md S2-R9 — per-row location identifier in All-Locations view ADDED per kickoff video P10 40:58-41:20, user ruling 2026-07-28: video overrides spec (video newer, last-update-wins))</t>
+          <t>SV-8642 (specs/parts-velocity.md S2-R9 — per-row location identifier in All-Locations view ADDED per kickoff video P10 40:58-41:20, user ruling 2026-07-28: video overrides spec (video newer, last-update-wins)) + on-screen location-scope indicator per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source, last-update-wins)</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
@@ -1607,13 +1608,13 @@
       <c r="G24" s="2" t="inlineStr">
         <is>
           <t>1. The header row is sticky - it stays visible while the body scrolls.
-2. The Type column shows each row's kind as plain text (no badge or chip styling): Inventory, or the special-order catalogue kind. (The special-order kind's exact on-screen word is confirmed in the build — the spec says "Catalogue", a rename is being considered, and it must stay short enough for a column.)
+2. The Type column shows each row's kind as plain text (no badge or chip styling): "Inventory" or "Special Order".
 3. ALL columns - header and cell data, including numbers and money - are left-aligned on screen. (The exports right-align numerics instead: a deliberate export-only difference.)</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>SV-8643 (specs/parts-velocity.md S3-R4; S3-R5; S3-R8 — Type value 'Catalogue' rename PENDING per kickoff video P31 43:34-44:12; latest-info user ruling 2026-07-28: update per latest info now, correct at the live build check later)</t>
+          <t>SV-8643 (specs/parts-velocity.md S3-R4; S3-R5; S3-R8 - Type value 'Catalogue' RENAMED to the exact label 'Special Order' per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source, last-update-wins), confirming kickoff video P31)</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
@@ -3082,12 +3083,13 @@
       <c r="G54" s="2" t="inlineStr">
         <is>
           <t>1. Both files contain only the rows matching the date range, type, category, vendor, bin, location, and search active at export time - not a full unfiltered dump.
-2. The exported rows match what the on-screen grid was showing.</t>
+2. The exported rows match what the on-screen grid was showing.
+3. Each file (PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to (exact position in the file is confirmed in the build).</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>specs/parts-velocity.md S6-R2; §3 Key Decisions</t>
+          <t>SV-8646 (specs/parts-velocity.md S6-R2; §3 Key Decisions + Locations: line in every CSV/PDF export per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source, last-update-wins))</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr"/>
@@ -3193,7 +3195,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>PDF: named velocity-report.pdf, A3 landscape, titled Parts Velocity, with 18-character text truncation but Part # untruncated</t>
+          <t>PDF: filename, A3 landscape, title, text truncation, and the shop logo</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3228,12 +3230,13 @@
           <t>1. The file downloads as velocity-report.pdf.
 2. The PDF is formatted for A3 landscape and titled Parts Velocity.
 3. Description, Category, and Vendor are truncated to 18 characters in the PDF.
-4. Part # is NOT truncated.</t>
+4. Part # is NOT truncated.
+5. The shop logo shows at the top of the PDF when one is set, with the same logo treatment as the other reports in the suite (fallback behaviour when no logo is set is confirmed in the build; the CSV never includes a logo).</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>specs/parts-velocity.md S6-R5; S6-R6</t>
+          <t>SV-8646 (specs/parts-velocity.md S6-R5; S6-R6 + same-logo-treatment for every report per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source, last-update-wins))</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr"/>
@@ -3628,7 +3631,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Every filter or search change re-queries the server and returns the first page of the new result set</t>
+          <t>Each filter or search change re-queries the server and returns page one</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">

--- a/testrail-import/Report-Suite_Parts-Velocity-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Parts-Velocity-Report_testrail-import.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Parts Velocity" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parts Velocity" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J68"/>
+  <dimension ref="A1:J69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -2528,13 +2528,15 @@
         <is>
           <t>1. A part whose most recent sale was N days ago, OUTSIDE the currently selected date range (e.g. range = This Month, last sale 42 days ago).
 2. The part still appears in the report (it has on-hand stock).
-3. For the location check: the part's most recent sale at location A is more recent than at location B.</t>
+3. For the location check: the part's most recent sale at location A is more recent than at location B.
+4. For the reversal check: a ZZAUTOTEST part whose MOST RECENT sale can be reversed, and an older sale of the same part also exists.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
           <t>1. Read the part's Last Sale value with the narrow date range selected.
-2. Switch the Location filter between location A and location B and re-read Last Sale.</t>
+2. Switch the Location filter between location A and location B and re-read Last Sale.
+3. Reverse the part's most recent sale invoice and re-read Last Sale.</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -2542,12 +2544,13 @@
           <t>1. Last Sale shows the whole days between today and the part's most recent sale measured over ALL-TIME history - it IGNORES the selected date range (e.g. '42 days' even though the range is This Month).
 2. It IS scoped to the selected location(s): with only location B selected, Last Sale reflects B's own most recent sale.
 3. Format is 'N days' (e.g. 42 days); a part with no recorded sale ever shows —.
-4. For a catalogue part, the anchor is its most recent vendor-sourced invoiced/paid request.</t>
+4. For a catalogue part, the anchor is its most recent vendor-sourced invoiced/paid request.
+5. When the most recent sale is reversed, Last Sale re-anchors to the previous remaining sale (the day count grows accordingly); if no other sale remains it shows —.</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>specs/parts-velocity.md S5-R4 (Last Sale); §4; S5-R5</t>
+          <t>specs/parts-velocity.md S5-R4 (Last Sale); §4; S5-R5; tech-plan-2026-07-29 B3.1 (last-sale re-anchor on reversal — spec-silent)</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
@@ -3440,84 +3443,134 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>An over-cap Parts Velocity export is refused with the too-large message</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>PV — Exports</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. A filter/location combination exists whose filtered set EXCEEDS the export row cap (widest date range + all locations; seed ZZAUTOTEST parts in bulk if needed, or use the largest available data set).</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>1. Set the filters so the filtered set exceeds the export row cap.
+2. Request the CSV download and read what happens.
+3. Request the PDF download and read what happens.
+4. Narrow the date range or filters below the cap and request a download again.</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>1. Neither the CSV nor the PDF is produced — no download starts.
+2. A clear too-large message appears telling the user to narrow the date range or filters, then try again — the standard wording is "This report is too large to export. Narrow the date range or filters, then try again."
+3. After narrowing below the cap, the downloads work again.</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>SV-8646 (specs/parts-velocity.md Story 6 exports — spec silent on a cap; tech-plan-2026-07-29 A3/FR-F4: suite-wide 10,000-row export cap, locked by Chris 2026-07-21)</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
           <t>The report uses the standard two-tone layout: white card surfaces on a soft blue-grey backdrop with an edge-to-edge table</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>PV — Visual Conformance</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded, in light mode.</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>1. Look at the page background, the toolbar, and the table surfaces.
 2. Look at the card corners and the table's horizontal extent.</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>1. White card surfaces (toolbar + table cells) sit on the standard soft blue-grey page background (the application's two-tone report theme).
 2. There is NO card border-radius - the table runs edge to edge.
 3. The layout matches the application's other reports (consistency goal, §1).</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S7-R1; §2</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>Toolbar and table detail styling: paddings, white header with 1px top border, white body cells, 2rem edge padding</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>PV — Visual Conformance</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded (use browser devtools to measure paddings).</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>1. Inspect the toolbar's background and internal padding.
 2. Inspect the table header cells and the border between header and toolbar.
 3. Inspect the body cells and the first/last cell padding in a row.</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>1. The toolbar background is white (black in dark mode) with internal padding 32px top, 2rem right, 24px bottom, 2rem left.
 2. Header cells have a white background and a 1px top border separating them from the toolbar.
@@ -3525,251 +3578,251 @@
 4. The leftmost cell in every row (header and body) has 2rem left padding; the rightmost cell has 2rem right padding.</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S7-R2; S7-R3; S7-R4; S7-R5</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>Dark mode is supported and the grey info icon keeps at least 3:1 contrast in both modes</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>PV — Visual Conformance</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded and dark mode available in the application.</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>1. Switch the application to dark mode.
 2. Look at the page background, toolbar, and cells.
 3. Check the grey ⓘ info icon against its cell background in dark mode, then again in light mode.</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>1. The report supports dark mode: page background, toolbar, and cells use their dark-mode equivalents.
 2. The grey ⓘ info icon uses a token meeting at least a 3:1 contrast ratio against the cell background in BOTH light and dark mode.</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S7-R6</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>The report is server-paginated - the backend returns one page of rows at a time</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>PV — API</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with more rows in the result set than one page holds.
 2. Browser devtools (network tab) are open to observe the backend requests.</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>1. Load the report and observe the backend data request and its response size.
 2. Move to the next page of rows and observe the traffic.</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>1. The backend returns ONE page of rows at a time - the full result set is not shipped to the browser.
 2. Paging is resolved on the server: moving to another page issues a fresh backend request for that page.
 3. This keeps the report responsive at scale (organizations can carry 50-60k parts, multiplied across locations).</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>SV-8642 (specs/parts-velocity.md §2 (server-paginated); S2-R10)</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>Each filter or search change re-queries the server and returns page one</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>PV — API</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded and the browser devtools network tab open.</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>1. Change each of these in turn and watch the network traffic: Type, date range, Bin, Location, Category, Vendor, and the toolbar search.
 2. After a filter change while on a later page, note which page of results is shown.</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>1. EACH change (Type, date range, Bin, Location, Category, Vendor, search) triggers a fresh server-side data load.
 2. There is no client-side-only narrowing - every filter or search change re-queries the server.
 3. Each change returns the FIRST page of the new result set.</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>SV-8642 (specs/parts-velocity.md S2-R10)</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>Header-click sorting re-queries the server with nulls first on ascending and last on descending as a server sort semantic</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>PV — API</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded (including rows with null values in a sortable column) and the network tab open.</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>1. Click a column header and watch the network traffic and the returned order.
 2. Click it again (reverse direction) and observe.
 3. Note where the null rows land in the server-returned order for each direction.</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>1. Each header click re-fetches the data from the server, ordered by the chosen column and direction, returning the first page of the re-sorted result set.
 2. Null values are placed FIRST on ascending and LAST on descending - as a server sort semantic, so the same order appears on screen and in the exports.
 3. Ties keep a stable order (no explicit secondary key).</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S3-R3</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>The backend denies both the report data and the export to a user without Inventory Reports → View</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>PV — API</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in as a Reports-section user whose role lacks the Inventory Reports → View permission.
 2. Browser devtools (network tab) are open.</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>1. Open the Parts Velocity report and observe the backend data request's outcome.
 2. Attempt the export and observe the backend export request's outcome.</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>1. The backend REFUSES the report data request - the user is denied the data (the UI shows the standard access-denied state).
 2. The backend likewise refuses the export request - no file is produced.
 3. Both loading and exporting are gated by the same Inventory Reports → View permission.</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S1-R4; S1-N2</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr"/>
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/Report-Suite_Parts-Velocity-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Parts-Velocity-Report_testrail-import.xlsx
@@ -524,13 +524,13 @@
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>1. A Parts section heading exists in the Reports navigation (this feature creates it - the application had no Parts reports before).
-2. Under Parts there is an entry labeled Parts Velocity (the only Parts report in this release).
+2. Under Parts there is an entry labeled Parts Velocity; Inventory Value also lives under Parts. The order of the two inside the Parts section is not fixed — do not fail the test on which of them comes first.
 3. Clicking it opens the Parts Velocity report.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>specs/parts-velocity.md S1-R1</t>
+          <t>SV-8641 (specs/parts-velocity.md S1-R1 — the spec's 'only report' sentence is superseded: Parts Velocity and Inventory Value BOTH live under Parts per the PRD companion video 2026-07-30 00:35-01:18; PV S1-R1 vs IV S1-R1 inconsistency flagged to SPEC-WATCH)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>

--- a/testrail-import/Report-Suite_Parts-Velocity-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Parts-Velocity-Report_testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J69"/>
+  <dimension ref="A1:J70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>SV-8642 (specs/parts-velocity.md S2-E4 — expectation FLIPPED by kickoff video P33 46:10-46:28, user ruling 2026-07-28: video overrides spec (video newer, last-update-wins))</t>
+          <t>SV-8642 (PV spec S2-E4 — RULED HIDDEN by Chris Ward answer 2026-07-31 Q1=A "classic spec drift"; the S2-E4 "still sees the filter" note is stale, spec edit pending)</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
@@ -1376,179 +1376,234 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>The Location column shows only with more than one location, leftmost before Type</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>PV — Filters</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1. You are on the Parts Velocity report as a user with access to two or more locations, with data loaded.
+2. The same inventory part is stocked at two of those locations, and at least one Special Order part has vendor requests at two of them.</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1. Select two or more locations and read the column headers from the left.
+2. Read the Location cell on each of the two inventory rows for the part stocked at both locations.
+3. Read the Location cell on the merged Special Order row.
+4. Open the column picker and look for Location in the list.
+5. Narrow to a single location and read the headers again.
+6. Change the selection between one location, several, and "All Locations", watching the filter control's width.</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1. With more than one location in scope a Location column is shown as the LEFTMOST column, before Type.
+2. Each inventory row shows its own location's name (an inventory row is one part at one location).
+3. The merged Special Order row shows "Multiple", because it is summed across the selected locations.
+4. Location is NOT one of the 20 columns in the picker — it is managed by the location scope, not by you.
+5. With a single location in scope the Location column is hidden.
+6. The Location filter control keeps the same width whichever label it shows — one location, several, or "All locations" — so the toolbar does not shift as you change the selection.</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>SV-8642 (PV spec v4 2026-07-29 S2-R12; S3-R10; S7-R8 — per-row Location column, leftmost before Type, "Multiple" on the merged special-order row, not in the picker)</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
           <t>An inventory part stocked at two selected locations shows as two rows with per-location stock figures</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>PV — Row Model</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>1. The same part number is stocked as an inventory part at two locations the user can access, with different On Hand / Min / Max values at each.
 2. You are on the Parts Velocity report with both locations selected in the Location filter.</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>1. Search for the part number in the toolbar search.
 2. Count the rows returned for it and read each row's On Hand, Min, and Max.</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>1. The part appears as TWO inventory rows - one per selected location (an inventory part is a per-location stock record).
 2. Each row carries only that one location's On Hand, Min, and Max.
 3. On Hand / Min / Max are NEVER summed across locations.</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S3-R1a; §3 Key Decisions</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>A catalogue part shows as one merged row with values summed across the selected locations</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>A Special Order part is one merged row summed across selected locations</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>PV — Row Model</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>1. The same catalogue (special-order, vendor-sourced) part was requested on invoiced/paid work orders at two locations the user can access, inside the window.
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>1. The same special-order (vendor-sourced) part was requested on invoiced/paid work orders at two locations the user can access, inside the window.
 2. You are on the Parts Velocity report with both locations selected.</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>1. Search for the catalogue part.
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>1. Search for the special-order part.
 2. Count its rows and read its movement and money values.
 3. Compare against the per-location values with only one location selected at a time.</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>1. The catalogue part appears as a SINGLE row (one row per catalogue part, merged across the selected locations).
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1. The special-order part appears as a SINGLE row (one row per special-order part, merged across the selected locations).
 2. Its movement and profitability values are the SUM of the per-location values.
-3. Its inventory-only columns (On Hand, Turns / Yr, Min, Max) show — (em-dash), because catalogue parts are not stocked.</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>specs/parts-velocity.md S3-R1a; §3 Key Decisions</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Rows load ranked by Demand descending with the descending indicator on the Demand header</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
+3. Its inventory-only columns (On Hand, Turns / Yr, Min, Max) show — (em-dash), because special-order parts are not stocked.</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>SV-8643 (specs/parts-velocity.md S3-R1a; §3 Key Decisions)</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Rows load ranked by Demand descending, indicator on the Demand header</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>PV — Row Model</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report on a first visit (no saved sort).
-2. Several parts have different Demand counts in the window; at least one inventory and one catalogue part share the same Demand count.</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
+2. Several parts have different Demand counts in the window; at least one inventory and one special-order part share the same Demand count.</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>1. Let the report load without clicking any header.
 2. Read the Demand column top to bottom.
-3. Find the inventory and catalogue rows with equal Demand and note their relative order.
+3. Find the inventory and special-order rows with equal Demand and note their relative order.
 4. Look at the Demand column header.</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>1. Rows are ranked by Demand, descending - the most-active parts first.
-2. Inventory and catalogue rows are ranked together in one list.
-3. Rows with equal Demand keep inventory-before-catalogue order.
+2. Inventory and special-order rows are ranked together in one list.
+3. Rows with equal Demand keep inventory-before-special-order order.
 4. The Demand header shows the descending sort indicator - this initial order IS the active sort (it is what the remembered view saves until you click another header).</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>specs/parts-velocity.md S3-R2</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Clicking a column header sorts ascending first, toggles on re-click, and places null values first-ascending / last-descending</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>SV-8643 (specs/parts-velocity.md S3-R2)</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>A header click sorts ascending first, toggles, and places nulls by direction</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>PV — Row Model</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded.
-2. Both inventory and catalogue rows are present (so a nullable column such as On Hand has both values and — cells).</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
+2. Both inventory and special-order rows are present (so a nullable column such as On Hand has both values and — cells).</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>1. Click the header of a column that is not currently sorted (for example On Hand).
 2. Click the same header again.
@@ -1556,7 +1611,7 @@
 4. Try clicking the headers of several other columns.</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>1. The first click sorts that column ASCENDING; the header shows a direction indicator (an arrow).
 2. Clicking the active sort column again reverses the direction; the arrow flips.
@@ -1564,90 +1619,90 @@
 4. Every column is sortable; each header click re-fetches the data (server-resolved) and shows the first page of the re-sorted result; ties keep a stable order.</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>specs/parts-velocity.md S3-R3</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>SV-8643 (specs/parts-velocity.md S3-R3)</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Sticky header, all-left alignment on screen, and plain-text Type values</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>PV — Row Model</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with enough rows to scroll the table body vertically.</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>1. Scroll the table body down and watch the header row.
 2. Read the Type column values.
 3. Look at the alignment of every header label and cell, including numeric and money columns.</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>1. The header row is sticky - it stays visible while the body scrolls.
 2. The Type column shows each row's kind as plain text (no badge or chip styling): "Inventory" or "Special Order".
 3. ALL columns - header and cell data, including numbers and money - are left-aligned on screen. (The exports right-align numerics instead: a deliberate export-only difference.)</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>SV-8643 (specs/parts-velocity.md S3-R4; S3-R5; S3-R8 - Type value 'Catalogue' RENAMED to the exact label 'Special Order' per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source, last-update-wins), confirming kickoff video P31)</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Info icons on Units Sold, Demand, and Turns / Yr show the exact spec descriptions and never trigger a sort</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>PV — Row Model</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded.
 2. The Turns / Yr column has been enabled via the column picker (it is hidden by default).</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>1. Look immediately to the right of the Units Sold, Demand, and Turns / Yr header labels.
 2. Hover each grey info icon and read the description.
@@ -1655,7 +1710,7 @@
 4. Click/activate an icon and watch whether the column sort changes.</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>1. Each of the three headers carries a grey info icon, shown always (not hover-to-reveal) whenever its column is visible; the Turns / Yr icon appears only once that column is enabled.
 2. Units Sold shows exactly: "Units taken out of inventory stock on invoiced work orders in this date range. This is stock movement, so it can differ from the units billed behind Revenue and Sell Price."
@@ -1665,50 +1720,50 @@
 6. No other column header carries an info icon.</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S3-R6</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Description, Category, and Vendor truncate with an ellipsis and show in full on hover; Part # is never truncated</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>PV — Row Model</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>1. A part with a very long description (and a long category and vendor name) has in-window activity.
 2. A part with a long part number exists.
 3. You are on the Parts Velocity report with those parts visible.</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>1. Look at the long Description, Category, and Vendor cells.
 2. Hover each truncated cell.
 3. Look at the long Part # cell.</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>1. Long Description, Category, and Vendor text is truncated with an ellipsis on screen.
 2. The full value shows on native hover (browser tooltip).
@@ -1716,247 +1771,202 @@
 4. The CSV export carries the full untruncated Description / Category / Vendor values.</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S3-R7</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Null values render as an em-dash only in the nullable fields; counts and Revenue/Margin are never null</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Em-dash only in nullable fields; counts and Revenue/Margin are never null</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>PV — Row Model</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with all 20 columns enabled.
-2. A catalogue row is visible, plus an inventory row with no in-window activity that stays in the report via on-hand stock.</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>1. On the catalogue row, read On Hand, Turns / Yr, Min, and Max.
-2. On the no-activity inventory row, read Units Sold, Units Returned, Sold via WO, Sold via Parts Sale, Demand, Revenue, and Margin.
+2. A special-order row is visible, plus an inventory row with no in-window activity that stays in the report via on-hand stock.</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>1. On the special-order row, read On Hand, Turns / Yr, Min, and Max.
+2. On the no-activity inventory row, read Units Sold, Units Returned, Sold (WO), Sold (Parts Sale), Demand, Revenue, and Margin.
 3. On the same row, read Unit Cost, Sell Price, Margin %, and Last Sale (assuming no billed units, no revenue, and no recorded sale ever).</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>1. On Hand, Turns / Yr, Min, and Max show — (em-dash) on catalogue rows - always.
-2. The count metrics and money totals are NEVER null: Units Sold / Units Returned / Sold via WO / Sold via Parts Sale show 0.00, Demand shows 0, Revenue and Margin show $0.00.
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>1. On Hand, Turns / Yr, Min, and Max show — (em-dash) on special-order rows - always.
+2. The count metrics and money totals are NEVER null: Units Sold / Units Returned / Sold (WO) / Sold (Parts Sale) show 0.00, Demand shows 0, Revenue and Margin show $0.00.
 3. Unit Cost and Sell Price show — when billed units are zero or less; Margin % shows — when Revenue is zero or less; Last Sale shows — when the row has no recorded sale.
 4. Every null renders as the same — (em-dash) glyph, in the table and in all exports.</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>specs/parts-velocity.md S3-R9; S5-R5</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>An inventory part is excluded only when it has no movement, under one unit on hand, AND no billed revenue</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>SV-8643 (specs/parts-velocity.md S3-R9; S5-R5)</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>An inventory part drops out only with no movement, no stock and no revenue</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>PV — Row Model</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>1. Inventory part A: zero stock movement in the window, less than one unit on hand, zero billed revenue in the window.
 2. Inventory part B: zero stock movement and zero on hand, but billed revenue in the window (e.g. a drop-ship sale billed without a stock decrement).</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>1. Search for part A in the report.
 2. Search for part B in the report.</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>1. Part A does NOT appear - it fails all three keep-criteria (no movement, under one on hand, no revenue) so it carries nothing to act on.
 2. Part B DOES appear - a part with billed Revenue &gt; 0 is always kept even with no stock movement and no on-hand stock.
-3. (Catalogue parts have no such rule: a never-requested catalogue part simply produces no row.)</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>specs/parts-velocity.md S3-N1</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+3. (Special Order parts have no such rule: a never-requested special-order part simply produces no row.)</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>SV-8643 (specs/parts-velocity.md S3-N1)</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>A sale invoiced then fully reversed in-window shows Demand 1 with Units Sold 0.00, and negative movement shows a leading minus</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>PV — Row Model</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>1. Inventory part C: one sale invoiced AND fully reversed inside the window, and the part still has on-hand stock (so it stays in the result set).
 2. Inventory part D: reversals exceed sales in the window (net-negative movement), with on-hand stock or other billed revenue keeping it in the result set.</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>1. Find part C and read its Demand and Units Sold.
 2. Find part D and read its Units Sold.</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>1. Part C shows Demand 1 (the reversal does not decrement the Demand count) with Units Sold 0.00 (the reversal nets the movement to zero).
 2. Part D shows a NEGATIVE Units Sold with a leading minus (e.g. -3.00) - negative movement is not floored to zero.
 3. A fully-reversed part with zero net movement, no on-hand stock, and no residual revenue would be excluded per S3-N1 (Demand alone is not a keep-criterion).</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S3-E1; S5-R5</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>Column picker lists all 20 available columns with toggles and never offers the internal on-hand cost</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Column picker lists all 20 columns and never offers the internal cost</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>PV — Columns &amp; Remembered View</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded.</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>1. Open the column picker from its toolbar button.
 2. Count the columns listed and check each has a toggle.
 3. Look for any on-hand cost / inventory-value entry.</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>1. The picker lists all 20 available columns, each with a toggle: Type, Part #, Description, Category, Vendor, Units Sold, Units Returned, Sold via WO, Sold via Parts Sale, Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand, Turns / Yr, Min, Max.
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>1. The picker lists all 20 available columns, each with a toggle: Type, Part #, Description, Category, Vendor, Units Sold, Units Returned, Sold (WO), Sold (Parts Sale), Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand, Turns / Yr, Min, Max.
 2. No on-hand cost column is offered - the report computes one internally but it is never selectable and never displayed.</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>specs/parts-velocity.md S4-R1; S4-R4; S5-R6</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>First visit shows exactly the 14 default columns in the specified order</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>PV — Columns &amp; Remembered View</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>1. You are on the Parts Velocity report on a first visit (no saved column selection).</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>1. Read the visible column headers left to right without touching the picker.</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>1. Exactly these 14 columns show, in this left-to-right order: Type, Part #, Description, Category, Vendor, Units Sold, Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand.
-2. The other 6 columns start hidden: Units Returned, Sold via WO, Sold via Parts Sale, Turns / Yr, Min, Max.</t>
-        </is>
-      </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>specs/parts-velocity.md S4-R2; S4-R3</t>
+          <t>SV-8644 (specs/parts-velocity.md S4-R1; S4-R4; S5-R6)</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
@@ -1965,7 +1975,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>A re-enabled column returns to its canonical slot and toggling takes effect immediately without a reload</t>
+          <t>First visit shows exactly the 14 default columns in the specified order</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1980,70 +1990,115 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>1. You are on the Parts Velocity report on a first visit (no saved column selection).</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>1. Read the visible column headers left to right without touching the picker.</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>1. Exactly these 14 columns show, in this left-to-right order: Type, Part #, Description, Category, Vendor, Units Sold, Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand.
+2. The other 6 columns start hidden: Units Returned, Sold (WO), Sold (Parts Sale), Turns / Yr, Min, Max.</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>SV-8644 (specs/parts-velocity.md S4-R2; S4-R3)</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>A re-enabled column returns to its canonical slot, with no reload</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>PV — Columns &amp; Remembered View</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded.</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>1. In the column picker, enable Min, then Units Returned, then Turns / Yr - in that (non-canonical) order.
 2. Watch the table as each toggle is flipped.
 3. Read the resulting header order.</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>1. Each toggle takes effect immediately - the table re-renders without a page reload.
-2. Columns always render in the fixed canonical left-to-right order regardless of the order they were toggled on: Type, Part #, Description, Category, Vendor, Units Sold, Units Returned, Sold via WO, Sold via Parts Sale, Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand, Turns / Yr, Min, Max.
+2. Columns always render in the fixed canonical left-to-right order regardless of the order they were toggled on: Type, Part #, Description, Category, Vendor, Units Sold, Units Returned, Sold (WO), Sold (Parts Sale), Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand, Turns / Yr, Min, Max.
 3. So Units Returned slots in right after Units Sold, Turns / Yr after On Hand, and Min before Max - not appended at the end.</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>specs/parts-velocity.md S4-R4; S4-R5</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>SV-8644 (specs/parts-velocity.md S4-R4; S4-R5)</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Filters, column selection, and sort are remembered per browser and restored before the first data fetch</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>PV — Columns &amp; Remembered View</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded.</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>1. Set a non-default view: Type = Inventory, date range = Last Month, pick a category, enable Turns / Yr, and sort by Revenue descending.
 2. Leave the report (navigate elsewhere), then return to it.
 3. Reload the page (browser refresh) and observe again.</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>1. On return, every saved setting is restored: Type = Inventory, Last Month, the chosen category, the column set including Turns / Yr, and the Revenue-descending sort.
 2. The saved values are applied BEFORE the first data fetch - the report does not flash the defaults and then re-query.
@@ -2051,191 +2106,191 @@
 4. The same holds after a full page reload.</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S4-R6; S1-R2</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>A saved value that is no longer valid falls back to that setting's default on restore</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>PV — Columns &amp; Remembered View</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>1. A saved view exists in this browser that includes a location the user can no longer access (e.g. access was removed after the view was saved), or a custom date range that is now malformed.</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>1. Return to the Parts Velocity report with that stale saved view in place.
 2. Observe which location / date range the report loads with.</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>1. The invalid saved value is NOT sent to the server.
 2. That one setting falls back to its default (e.g. the location falls back to the active location); the other saved settings still restore normally.
 3. The report loads without an error.</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S4-R6</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>A different user signing in on the same browser inherits the saved view</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>PV — Columns &amp; Remembered View</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>1. User 1 has saved a clearly non-default view on this browser (e.g. Type = Catalogue, Last Quarter).
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>1. User 1 has saved a clearly non-default view on this browser (e.g. Type = Special Order, Last Quarter).
 2. User 2 can open the report.</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>1. Sign out user 1 and sign in user 2 on the SAME browser.
 2. Open the Parts Velocity report.</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>1. User 2 sees user 1's saved view (Type = Catalogue, Last Quarter, the saved columns and sort).
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>1. User 2 sees user 1's saved view (Type = Special Order, Last Quarter, the saved columns and sort).
 2. This is by design: storage is per browser, not tied to the account - there is no per-account separation.</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>specs/parts-velocity.md S4-R6</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>SV-8644 (specs/parts-velocity.md S4-R6)</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>All 20 columns can be hidden; the empty selection is not restored and an export then contains no data columns</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>PV — Columns &amp; Remembered View</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded.</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>1. In the column picker, switch OFF all 20 columns.
 2. Trigger a CSV export while zero columns are enabled.
 3. Leave the report and return to it.</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>1. The picker enforces no minimum - all 20 columns can be switched off, leaving a grid with no data columns for the rest of the session.
 2. The export produces a file containing only the header/metadata rows and no data columns.
 3. On the next visit the all-hidden selection is NOT restored - the report falls back to the default 14-column set (the saved column selection returns to the last NON-EMPTY selection; all-hidden is the exception).</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S4-E1; S4-R6</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>Units Sold for an inventory part is net stock movement: invoicing adds, reversing subtracts, returns do not affect it</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>PV — Columns &amp; Calculations</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>1. An inventory part with known starting stock.
 2. You can invoice work orders, reverse/void an invoice, and initiate a part return for that part inside the report window.</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>1. Invoice a work order selling 5 units of the part; reload the report and read Units Sold.
 2. Reverse/void an invoice that sold 2 units in the window; reload and read Units Sold.
 3. Initiate a part return for 1 unit of the part; reload and read Units Sold.</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>1. After step 1, Units Sold increases by 5.00 (invoicing a work order adds the units sold - a stock-movement event).
 2. After step 2, Units Sold decreases by 2.00 (reversing/voiding an invoice adds stock back and is subtracted - Units Sold is net of invoice reversals).
@@ -2243,57 +2298,9 @@
 4. Units Sold can be 0.00 or negative when reversals exceed sales.</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S5-R1; S5-R4 (Units Sold, inventory); §4</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>Units Sold for a catalogue part is the total in-window vendor-request quantity, net of reversed sales</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>PV — Columns &amp; Calculations</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>1. A catalogue (vendor-sourced, special-order) part is requested on invoiced or paid work orders in the window - e.g. 3 units on one work order and 2 on another.
-2. One further in-window sale of the same catalogue part has been reversed/voided.</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>1. Find the catalogue part's row and read Units Sold.
-2. Compare against the sum of the in-window vendor-request quantities, leaving out the reversed sale.</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>1. Units Sold equals the total quantity across the part's in-window vendor requests (3 + 2 = 5.00 in the example), summed across the selected locations.
-2. The reversed/voided sale is EXCLUDED from the total (net of reversals, per S5-R4b).
-3. Only requests on work orders at status Invoiced or Paid count; the window is anchored to the work-order date.</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>specs/parts-velocity.md S5-R2; S5-R4 (Units Sold, catalogue); S5-R4b</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
@@ -2302,31 +2309,79 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>Special Order Units Sold = in-window request quantity, net of reversals</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>PV — Columns &amp; Calculations</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>1. A special-order (vendor-sourced) part is requested on invoiced or paid work orders in the window - e.g. 3 units on one work order and 2 on another.
+2. One further in-window sale of the same special-order part has been reversed/voided.</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>1. Find the special-order part's row and read Units Sold.
+2. Compare against the sum of the in-window vendor-request quantities, leaving out the reversed sale.</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>1. Units Sold equals the total quantity across the part's in-window vendor requests (3 + 2 = 5.00 in the example), summed across the selected locations.
+2. The reversed/voided sale is EXCLUDED from the total (net of reversals).
+3. Only requests on work orders at status Invoiced or Paid count; the window is anchored to the work-order date.</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>SV-8645 (specs/parts-velocity.md S5-R2; S5-R4 (Units Sold, catalogue); S5-R4b)</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
           <t>Units Returned counts initiated part returns and parts-sale credits, and cancelling a return removes its quantity</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>PV — Columns &amp; Calculations</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>1. A part with in-window sales (so its row exists) and the Units Returned column enabled via the column picker.
 2. You can initiate a work-order part return, a parts-sale credit, and cancel a return.</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>1. Initiate a work-order part return for 2 units of the part; reload and read Units Returned.
 2. Create a parts-sale credit returning 1 more unit; reload and read Units Returned.
@@ -2334,7 +2389,7 @@
 4. Reverse/void an unrelated invoice for the part; reload and read Units Returned.</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>1. After step 1, Units Returned increases by 2.00 (the return record is counted when the return is initiated).
 2. After step 2, it increases by 1.00 more (a parts-sale credit also creates a part-return record).
@@ -2342,50 +2397,50 @@
 4. After step 4, Units Returned is UNCHANGED - invoice reversals are not returns (they affect Units Sold instead).</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S5-R3; S5-R4 (Units Returned); §3 Key Decisions</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>Units Returned is windowed by initiation date, ignores invoice status, and excludes core-charge returns</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>PV — Columns &amp; Calculations</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>1. A part sold in a PREVIOUS window whose return is initiated inside the CURRENT window (and the part has current-window activity or stock so its row exists).
 2. A core-charge return exists for a part in the window.
 3. The Units Returned column is enabled.</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>1. Select the current window and read the part's Units Returned.
 2. Select the previous window (when the sale happened) and read Units Returned again.
 3. Check the part with the core-charge return.</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>1. The return counts in the window of its INITIATION date - so it appears in the current window even though the sale was earlier (a return and its originating sale can fall in different report windows; each uses its own natural event date).
 2. In the previous window the return does not count (only the sale's own metrics do).
@@ -2394,137 +2449,137 @@
 5. A part whose ONLY in-window event is a return (no sale, no stock, no revenue) produces no row at all (per S3-N1) - accepted behavior, the row axis is sales/stock activity.</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S5-R3</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>Sold via WO counts Service-type work orders and Sold via Parts Sale counts Parts-type work orders, windowed by work-order date</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Sold (WO) counts Service work orders, Sold (Parts Sale) counts Parts</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>PV — Columns &amp; Calculations</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>1. A part sold in the window on an invoiced SERVICE work order (e.g. 4 units) and on an invoiced PARTS SALE / Parts-type work order created in Parts → Parts Sale (e.g. 3 units).
-2. The Sold via WO and Sold via Parts Sale columns are enabled.</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>1. Read the part's Sold via WO value.
-2. Read the part's Sold via Parts Sale value.
+2. The Sold (WO) and Sold (Parts Sale) columns are enabled.</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>1. Read the part's Sold (WO) value.
+2. Read the part's Sold (Parts Sale) value.
 3. Move the date range so the work orders' end dates fall outside the window and re-read both.</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>1. Sold via WO shows the total part quantity on Service-type invoiced/paid work orders whose work-order date is in the window (4.00 in the example), net of reversed/voided sales.
-2. Sold via Parts Sale shows the total on Parts-type invoiced/paid work orders (counter sales) in the window (3.00), net of reversed/voided sales.
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>1. Sold (WO) shows the total part quantity on Service-type invoiced/paid work orders whose work-order date is in the window (4.00 in the example), net of reversed/voided sales.
+2. Sold (Parts Sale) shows the total on Parts-type invoiced/paid work orders (counter sales) in the window (3.00), net of reversed/voided sales.
 3. Both are windowed by the WORK-ORDER date (its end date) - with the range moved off those dates, both drop out.
 4. Both workflows feed the report - a parts sale is a separate workflow from a service work order but counts fully.</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>specs/parts-velocity.md S5-R4 (Sold via WO / Sold via Parts Sale); §5 Assumptions</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Demand counts each transaction once regardless of quantity, and a reversal neither adds nor subtracts</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>SV-8645 (specs/parts-velocity.md S5-R4 (Sold via WO / Sold via Parts Sale); §5 Assumptions)</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Demand counts each transaction once; a reversal neither adds nor subtracts</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>PV — Columns &amp; Calculations</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>1. An inventory part sold in the window on two invoiced work orders - one for 1 unit, one for 10 units.
-2. A catalogue part with two in-window vendor requests.
+2. A special-order part with two in-window vendor requests.
 3. One of the inventory part's in-window sales is then reversed/voided.</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>1. Read the inventory part's Demand before the reversal.
 2. Reverse/void one of its invoices and re-read Demand.
-3. Read the catalogue part's Demand.</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
+3. Read the special-order part's Demand.</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>1. The inventory part's Demand is 2 - each stock-decrementing invoicing event counts ONCE no matter how many units were on it (1 unit and 10 units each count as one).
 2. After the reversal, Demand is STILL 2 - a reversal event neither adds to nor subtracts from the count (while Units Sold nets down).
-3. The catalogue part's Demand is 2 - the count of its in-window vendor part requests.
+3. The special-order part's Demand is 2 - the count of its in-window vendor part requests.
 4. Demand is the report's default ranking signal (a whole number, never null - 0 when none).</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>specs/parts-velocity.md S5-R4 (Demand); §4; §3 Key Decisions</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>Last Sale shows whole days since the most recent sale over ALL-TIME history, scoped to the selected locations</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>SV-8645 (specs/parts-velocity.md S5-R4 (Demand); §4; §3 Key Decisions)</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Last Sale is whole days since the most recent sale over all-time history</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>PV — Columns &amp; Calculations</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>1. A part whose most recent sale was N days ago, OUTSIDE the currently selected date range (e.g. range = This Month, last sale 42 days ago).
 2. The part still appears in the report (it has on-hand stock).
@@ -2532,100 +2587,100 @@
 4. For the reversal check: a ZZAUTOTEST part whose MOST RECENT sale can be reversed, and an older sale of the same part also exists.</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>1. Read the part's Last Sale value with the narrow date range selected.
 2. Switch the Location filter between location A and location B and re-read Last Sale.
 3. Reverse the part's most recent sale invoice and re-read Last Sale.</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>1. Last Sale shows the whole days between today and the part's most recent sale measured over ALL-TIME history - it IGNORES the selected date range (e.g. '42 days' even though the range is This Month).
 2. It IS scoped to the selected location(s): with only location B selected, Last Sale reflects B's own most recent sale.
 3. Format is 'N days' (e.g. 42 days); a part with no recorded sale ever shows —.
-4. For a catalogue part, the anchor is its most recent vendor-sourced invoiced/paid request.
+4. For a special-order part, the anchor is its most recent vendor-sourced invoiced/paid request.
 5. When the most recent sale is reversed, Last Sale re-anchors to the previous remaining sale (the day count grows accordingly); if no other sale remains it shows —.</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>specs/parts-velocity.md S5-R4 (Last Sale); §4; S5-R5; tech-plan-2026-07-29 B3.1 (last-sale re-anchor on reversal — spec-silent)</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>SV-8645 (specs/parts-velocity.md S5-R4 (Last Sale); §4; S5-R5; tech-plan-2026-07-29 B3.1 (last-sale re-anchor on reversal — spec-silent))</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>On Hand shows the row's own location stock, and Min / Max are read-only stored thresholds with no editing from the report</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>PV — Columns &amp; Calculations</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>1. An inventory part with a known on-hand quantity and stored Min / Max reorder thresholds at one location.
 2. The Min and Max columns are enabled via the column picker.</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>1. Read the part's On Hand, Min, and Max in the report and compare with the inventory record.
 2. Try clicking / double-clicking the Min and Max cells and look for any edit control or slide-over.</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>1. On Hand equals the part's CURRENT on-hand quantity at that row's location (never summed across locations).
 2. Min and Max show the stored minimum / maximum reorder thresholds for that location, as whole numbers (— when not set).
 3. Min and Max are READ-ONLY display columns - no edit control or slide-over opens; editing part attributes from this report is out of scope in this version.</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S5-R4 (On Hand / Min / Max); §2 Out of Scope; S5-R5</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>Turns / Yr annualizes the in-window sales rate against On Hand, shows 0.00 at zero stock, and can be negative</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Turns / Yr annualizes the sales rate, is 0.00 at zero stock, can be negative</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>PV — Columns &amp; Calculations</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>1. The Turns / Yr column is enabled.
 2. Part A: known Units Sold over a known window with On Hand &gt; 0 (e.g. Units Sold 10.00 over a 30-day window with 5 on hand).
@@ -2633,165 +2688,165 @@
 4. Part C: negative Units Sold (reversals exceed sales) with stock on hand.</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>1. Compute the expected value for part A: (Units Sold ÷ Window days × 365) ÷ On Hand - e.g. (10 ÷ 30 × 365) ÷ 5 = 24.33.
 2. Compare against the displayed Turns / Yr for part A.
-3. Read Turns / Yr for parts B and C, and for any catalogue row.</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
+3. Read Turns / Yr for parts B and C, and for any special-order row.</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>1. Part A's Turns / Yr matches the formula (two decimals, e.g. 24.33); the window is the whole-day span inclusive of both dates with a floor of 1 day.
 2. Part B shows 0.00 (renders 0.00 when On Hand is 0 - not an error, not —).
 3. Part C shows a NEGATIVE Turns / Yr with a leading minus (because Units Sold can be negative).
-4. Catalogue rows always show — (not applicable).</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>specs/parts-velocity.md S5-R4 (Turns / Yr); S5 Definitions (Window)</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>Revenue, Margin, Unit Cost, Sell Price, and Margin % follow the billed-line formulas, computed unrounded and rounded once</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
+4. Special Order rows always show — (not applicable).</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>SV-8645 (specs/parts-velocity.md S5-R4 (Turns / Yr); S5 Definitions (Window))</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Revenue, Margin, Unit Cost, Sell Price and Margin % use the billed formulas</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>PV — Columns &amp; Calculations</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>1. A part with known billed lines in the window - e.g. two invoiced work-order part lines: 2 units at $50.00 sell / $30.00 cost, and 1 unit at $40.00 sell / $30.00 cost.
 2. All five profitability columns are visible.</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>1. Compute the expected values: Revenue = (2×50)+(1×40) = $140.00; COGS = (2×30)+(1×30) = $90.00; billed units = 3; Margin = 140−90 = $50.00; Unit Cost = 90÷3 = $30.00; Sell Price = 140÷3 = $46.67; Margin % = 50÷140×100 = 35.7%.
 2. Compare each against the part's displayed row.</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>1. Revenue = the summed billed sell amount (each line's stored sell price × quantity) in the window.
 2. Margin = Revenue − COGS (the summed billed cost captured at billing time).
 3. Unit Cost = COGS ÷ billed units; Sell Price = Revenue ÷ billed units.
 4. Margin % = (Revenue − COGS) ÷ Revenue × 100, shown to one decimal.
 5. All five are computed from the RAW (unrounded) Revenue / COGS / billed-units totals and rounded ONCE at the end - not built from already-rounded intermediates.
-6. The same formulas apply to inventory and catalogue rows (for catalogue, from the vendor part requests).</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>specs/parts-velocity.md S5-R4a; §4</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>A reversed/voided sale is excluded from every billed-line column (Revenue, Margin, Unit Cost, Sell Price, Sold via WO, Sold via Parts Sale, catalogue Units Sold)</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
+6. The same formulas apply to inventory and special-order rows (for special-order, from the vendor part requests).</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>SV-8645 (specs/parts-velocity.md S5-R4a; §4)</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>A reversed or voided sale is excluded from every billed-line column</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>PV — Columns &amp; Calculations</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>1. A part with two in-window billed sales of known amounts, one of which you then reverse/void.
 2. All movement and profitability columns are visible.</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>1. Record the part's Revenue, Margin, Unit Cost, Sell Price, Margin %, Sold via WO / Sold via Parts Sale (and Units Sold for a catalogue part).
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>1. Record the part's Revenue, Margin, Unit Cost, Sell Price, Margin %, Sold (WO) / Sold (Parts Sale) (and Units Sold for a special-order part).
 2. Reverse/void one of the two sales.
 3. Reload the report and re-read every column.</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>1. After the reversal, ALL the billed-line columns drop to reflect only the remaining sale - the reversed/voided sale is excluded from Revenue, Margin, Unit Cost, Sell Price, Margin %, Sold via WO, Sold via Parts Sale, and (for catalogue) Units Sold.
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>1. After the reversal, ALL the billed-line columns drop to reflect only the remaining sale - the reversed/voided sale is excluded from Revenue, Margin, Unit Cost, Sell Price, Margin %, Sold (WO), Sold (Parts Sale), and (for special-order) Units Sold.
 2. This netting is consistent with inventory Units Sold, which already nets reversals via the stock add-back.
 3. A voided sale therefore inflates NO column.</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>specs/parts-velocity.md S5-R4b; S5-R4a; §3 Key Decisions</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>SV-8645 (specs/parts-velocity.md S5-R4b; S5-R4a; §3 Key Decisions)</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>Unit Cost / Sell Price and Margin % use independent null triggers, so mixed rows are valid</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>PV — Columns &amp; Calculations</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>1. Row 1: a part with booked revenue but ZERO billed units in the window (e.g. a credit/adjustment line carrying revenue with no billed quantity).
 2. Row 2: a part with billed units &gt; 0 but Revenue $0.00 (e.g. billed at a $0 sell price).
 3. Row 3: a part with both billed units ≤ 0 and Revenue ≤ 0.</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>1. Read Unit Cost, Sell Price, Margin %, Revenue, and Margin on row 1.
 2. Read the same columns on row 2.
 3. Read the same columns on row 3.</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>1. Row 1: Unit Cost and Sell Price show — (billed units ≤ 0) while Revenue and Margin show dollar amounts AND Margin % is still computed from Revenue - a valid mixed row, not a defect.
 2. Row 2: Sell Price shows $0.00 (a number) while Margin % shows — (Revenue ≤ 0) - also valid.
@@ -2799,156 +2854,106 @@
 4. The three triggers are independent: Unit Cost/Sell Price null on billed units ≤ 0; Margin % null on Revenue ≤ 0.</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S5-R4a (null rules + mixed-row paragraph); S3-R9</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>On-screen number formats match the spec for every column type, and rounding is half away from zero</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Number formats match the spec per column; rounding is half away from zero</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>PV — Columns &amp; Calculations</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>1. All 20 columns are enabled and rows exist with large (1,000+), negative, and null values across the column types.</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>1. Read a large count value (Units Sold etc.), a negative count, a large money value, a negative money value, a Margin % value, a Demand value, Min/Max values, and a Last Sale value.
 2. Seed a Margin % that lands exactly on a rounding tie (e.g. computes to 8.45% / -8.45%) and read the display.</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>1. Units Sold, Units Returned, Sold via WO, Sold via Parts Sale, On Hand, Turns / Yr: two decimals with thousands separators (1,250.00); negatives with a leading minus (-3.00).
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>1. Units Sold, Units Returned, Sold (WO), Sold (Parts Sale), On Hand, Turns / Yr: two decimals with thousands separators (1,250.00); negatives with a leading minus (-3.00).
 2. Unit Cost, Sell Price, Revenue, Margin: currency with $, two decimals, thousands separators ($1,250.00); negatives with a leading minus and NO parentheses (-$45.00).
 3. Margin %: one decimal with a trailing % (33.8%); negatives with a leading minus, no + on positives (-8.4%).
 4. Demand: whole number. Min, Max: whole numbers (— when null). Last Sale: 'N days' (42 days), — when null.
 5. Rounding is half AWAY from zero: 8.45% displays 8.5% and -8.45% displays -8.5% (a tie rounds up in magnitude); this applies to all money and one-decimal values.</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>specs/parts-velocity.md S5-R5; S5-R7 (rounding)</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>Core parts are excluded from both the inventory and catalogue result sets</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>SV-8645 (specs/parts-velocity.md S5-R5; S5-R7 (rounding))</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Core parts are excluded from both the inventory and special-order result sets</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>PV — Columns &amp; Calculations</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>1. An inventory part flagged as a core has in-window sales activity and on-hand stock.
 2. A vendor-sourced core part was requested on an invoiced/paid work order in the window.</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>1. Search the report for the inventory core part (Type = Both).
-2. Search for the catalogue core part.</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
+2. Search for the special-order core part.</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>1. The inventory core part does NOT appear in the report despite its activity and stock.
-2. The catalogue core part does NOT appear either.
+2. The special-order core part does NOT appear either.
 3. Parts flagged as a core are excluded from both result sets by design.</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>specs/parts-velocity.md S5-R1; S5-R2; §3 Key Decisions</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>Movement and billed bases may differ for an inventory row (expected), while Sold via WO + Sold via Parts Sale equals the billed units</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>PV — Columns &amp; Calculations</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>1. An inventory part with a billed sale that produced NO matching stock decrement (e.g. a drop-ship or negative-stock sale) plus normal stocked sales in the window.
-2. A catalogue part with in-window vendor requests.
-3. Units Sold, Sold via WO, Sold via Parts Sale, and the profitability columns are visible.</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>1. On the inventory row, compare Units Sold against Revenue ÷ Sell Price (the billed units).
-2. On the same row, add Sold via WO + Sold via Parts Sale and compare against the billed units.
-3. On the catalogue row, compare Units Sold, Sold via WO + Sold via Parts Sale, and the billed units.</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>1. On the inventory row, Units Sold (stock movement) DIFFERS from the billed units behind Revenue/Sell Price - this is CORRECT behavior, not a defect (the Units Sold tooltip calls it out).
-2. Sold via WO + Sold via Parts Sale together DO equal the billed-units basis (work orders are only Service- or Parts-type) - but neither equals the movement-based Units Sold.
-3. On the catalogue row, everything reconciles: Units Sold = Sold via WO + Sold via Parts Sale = billed units (they share the vendor-request quantity as one source).</t>
-        </is>
-      </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>specs/parts-velocity.md S5-R7; §3 Key Decisions</t>
+          <t>SV-8645 (specs/parts-velocity.md S5-R1; S5-R2; §3 Key Decisions)</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
@@ -2957,7 +2962,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Window anchors: inventory movement metrics use the movement event date while billed columns use the work-order date</t>
+          <t>Movement and billed bases may differ; Sold (WO) + Sold (Parts Sale) = billed</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2976,259 +2981,309 @@
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>1. An inventory part with a billed sale that produced NO matching stock decrement (e.g. a drop-ship or negative-stock sale) plus normal stocked sales in the window.
+2. A special-order part with in-window vendor requests.
+3. Units Sold, Sold (WO), Sold (Parts Sale), and the profitability columns are visible.</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>1. On the inventory row, compare Units Sold against Revenue ÷ Sell Price (the billed units).
+2. On the same row, add Sold (WO) + Sold (Parts Sale) and compare against the billed units.
+3. On the special-order row, compare Units Sold, Sold (WO) + Sold (Parts Sale), and the billed units.</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>1. On the inventory row, Units Sold (stock movement) DIFFERS from the billed units behind Revenue/Sell Price - this is CORRECT behavior, not a defect (the Units Sold tooltip calls it out).
+2. Sold (WO) + Sold (Parts Sale) together DO equal the billed-units basis (work orders are only Service- or Parts-type) - but neither equals the movement-based Units Sold.
+3. On the special-order row, everything reconciles: Units Sold = Sold (WO) + Sold (Parts Sale) = billed units (they share the vendor-request quantity as one source).</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>SV-8645 (specs/parts-velocity.md S5-R7; §3 Key Decisions)</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Window anchors: movement uses the event date, billed uses the WO date</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>PV — Columns &amp; Calculations</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>1. A work order whose END date falls in window W1 but whose invoicing (stock-movement event) happened in window W2 for an inventory part.
 2. Both W1 and W2 are selectable ranges.</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>1. Select window W1 and read the part's Units Sold / Demand vs its Revenue / Sold via WO.
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>1. Select window W1 and read the part's Units Sold / Demand vs its Revenue / Sold (WO).
 2. Select window W2 and read the same columns.
 3. Select a single-day range (Today) and check the report still computes (window floor).</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>1. In W1 (work-order date in window): the billed columns (Revenue, Margin, Unit Cost, Sell Price, Margin %, Sold via WO, Sold via Parts Sale) count the sale, while inventory Units Sold / Demand do NOT (their movement event is outside W1).
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>1. In W1 (work-order date in window): the billed columns (Revenue, Margin, Unit Cost, Sell Price, Margin %, Sold (WO), Sold (Parts Sale)) count the sale, while inventory Units Sold / Demand do NOT (their movement event is outside W1).
 2. In W2 (movement date in window): Units Sold / Demand count it, the billed columns do not - the two anchors CAN differ for an inventory part and that is intended.
 3. The window is the whole-day span inclusive of BOTH the start and end dates, with a floor of 1 day - a single-day range (Today) computes normally (Window = 1 for the Turns / Yr divisor).
 4. Last Sale is not windowed at all (all-time).</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>specs/parts-velocity.md S5 Definitions (Window / Work-order date); S5-R7</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>SV-8645 (specs/parts-velocity.md S5 Definitions (Window / Work-order date); S5-R7)</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>The overflow button opens an export menu with Download (PDF) and Download (CSV) in that order</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>PV — Exports</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded.</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>1. Find the ⋯ overflow button - the leftmost control in the toolbar's action cluster.
 2. Click it and read the menu items top to bottom.</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>1. The ⋯ overflow button sits leftmost in the toolbar's action cluster.
 2. The menu holds exactly two items, in this order: Download (PDF), then Download (CSV).</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S6-R1</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>Both exports reflect the filters and search active at the time of export</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>PV — Exports</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded across types, categories, and locations.</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>1. Set a distinctive filter mix: Type = Inventory, a single category, a short date range, and a search string.
 2. Download the CSV and open it.
 3. Download the PDF and open it.</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>1. Both files contain only the rows matching the date range, type, category, vendor, bin, location, and search active at export time - not a full unfiltered dump.
 2. The exported rows match what the on-screen grid was showing.
 3. Each file (PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to (exact position in the file is confirmed in the build).</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>SV-8646 (specs/parts-velocity.md S6-R2; §3 Key Decisions + Locations: line in every CSV/PDF export per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source, last-update-wins))</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>Exports include only the enabled columns, in the canonical on-screen order</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>PV — Exports</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded.</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>1. Hide two default columns (e.g. Category, Margin %) and enable a hidden one (e.g. Units Returned).
 2. Download the CSV and read its column headers in order.
 3. Download the PDF and read its columns in order.</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>1. Both exports contain ONLY the currently enabled columns - the hidden ones are absent.
 2. Columns appear in the CANONICAL order (the fixed on-screen order) - the re-enabled Units Returned sits right after Units Sold, NOT appended at the end.
 3. The export mirrors the visible grid.</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S6-R3; S4-R4</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>Exports reflect the active sort - including Min/Max sorts, the default Demand order, and identical null placement</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Exports reflect the active sort, including Min/Max and null placement</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>PV — Exports</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>1. You are on the Parts Velocity report with data loaded, including rows with — values in a sortable column (e.g. On Hand on catalogue rows).
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>1. You are on the Parts Velocity report with data loaded, including rows with — values in a sortable column (e.g. On Hand on special-order rows).
 2. Min and Max are enabled.</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>1. Without clicking any header (default Demand descending), download the CSV and check the row order.
 2. Sort by Min ascending, export, and check the order including where the — rows land.
 3. Sort by On Hand descending, export, and check the null placement.</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>1. The default Demand-descending order is exported when the user has not chosen another column.
 2. Every column's sort is honored in the export - including Min and Max.
 3. The export renders the EXACT server order, including null placement (nulls first on ascending, last on descending) - the export and the on-screen grid match; there is no on-screen-vs-export null-sorting difference.</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>specs/parts-velocity.md S6-R4; S3-R3</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>SV-8646 (specs/parts-velocity.md S6-R4; S3-R3)</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>PDF: filename, A3 landscape, title, text truncation, and the shop logo</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>PV — Exports</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded, including a part with a Description, Category, and Vendor each longer than 18 characters and a long Part #.</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>1. Download the PDF and check the saved filename.
 2. Open it and check the page format and title.
 3. Find the long-text part's row and read Description, Category, Vendor, and Part #.</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>1. The file downloads as velocity-report.pdf.
 2. The PDF is formatted for A3 landscape and titled Parts Velocity.
@@ -3237,144 +3292,144 @@
 5. The shop logo shows at the top of the PDF when one is set, with the same logo treatment as the other reports in the suite (fallback behaviour when no logo is set is confirmed in the build; the CSV never includes a logo).</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>SV-8646 (specs/parts-velocity.md S6-R5; S6-R6 + same-logo-treatment for every report per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source, last-update-wins))</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>CSV: named velocity-report.csv with full untruncated text values and Last Sale as a raw integer</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>PV — Exports</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded, including a part with a Description longer than 18 characters and a part with a Last Sale value.</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>1. Download the CSV and check the saved filename.
 2. Open it and read the long part's Description, Category, and Vendor.
 3. Read the Last Sale column value.</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>1. The file downloads as velocity-report.csv.
 2. The CSV carries the FULL, untruncated Description / Category / Vendor values (unlike the PDF's 18-character cut).
 3. Last Sale is a raw integer in the CSV (e.g. 42) - the 'N days' wording is PDF/on-screen only.</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S6-R5; S6-R6; S6-R8</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>Null values render as an em-dash in both exports, and Last Sale renders as 'N days' in the PDF</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Em-dash in both exports; Last Sale reads "N days" in the PDF</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>PV — Exports</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>1. Rows with null values exist (a catalogue row for On Hand / Turns / Yr / Min / Max; a row with billed units 0 for Unit Cost / Sell Price; a never-sold row for Last Sale).
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>1. Rows with null values exist (a special-order row for On Hand / Turns / Yr / Min / Max; a row with billed units 0 for Unit Cost / Sell Price; a never-sold row for Last Sale).
 2. All nullable columns are enabled.</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>1. Download the CSV and locate the null cells.
 2. Download the PDF and locate the same cells.
 3. In the PDF, read a non-null Last Sale value.</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>1. A null value renders as — (em-dash) in BOTH the CSV and the PDF, in every nullable field: Unit Cost, Sell Price, Margin %, On Hand, Turns / Yr, Last Sale, Min, Max.
 2. Revenue, Margin, and the count metrics are never null in the exports either ($0.00 / 0.00 / 0).
 3. In the PDF, Last Sale renders as 'N days' (e.g. 42 days).</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>specs/parts-velocity.md S6-R7; S6-R8; S3-R9</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>SV-8646 (specs/parts-velocity.md S6-R7; S6-R8; S3-R9)</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>PDF export alignment: Type centered, text left, numeric and money right</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>PV — Exports</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded and several columns of each kind visible.</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>1. Download the PDF and look at the alignment of each column.
 2. Download the CSV and open it in a plain text editor to confirm it is plain comma-separated values (a CSV file carries no alignment of its own).</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>1. In the PDF, the Type column is CENTERED.
 2. In the PDF, the text columns (Part #, Description, Category, Vendor) are left-aligned.
@@ -3383,91 +3438,91 @@
 5. The CSV is plain data — the alignment assertions apply to the PDF only; how a spreadsheet displays the CSV is not part of this test.</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>SV-8646 (specs/parts-velocity.md S6-R10; S3-R8)</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>Export toasts: exact success texts; server or fallback error text on failure</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>PV — Exports</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded.
 2. You can force an export failure (e.g. drop the network connection just before triggering the download, or induce a server error).</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>1. Download the CSV and the PDF normally and read each toast.
 2. Trigger a CSV export under the failure condition and read the toast.
 3. Trigger a PDF export under the failure condition and read the toast.</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>1. On success the toasts read exactly "Velocity report exported (CSV)" / "Velocity report exported (PDF)" and auto-fade — UPPERCASE (CSV)/(PDF).
 2. An error toast is shown on failure; when the server provides a message, that server message is shown.
 3. Otherwise the failure toast reads exactly: "Failed to export velocity report (csv)" or "Failed to export velocity report (pdf)" — lowercase (csv)/(pdf); the success/failure casing mix is the shipped wording, documented as-is (not a bug).</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S6-R9; S6-N1; §7 (casing note)</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>An over-cap Parts Velocity export is refused with the too-large message</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>PV — Exports</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. A filter/location combination exists whose filtered set EXCEEDS the export row cap (widest date range + all locations; seed ZZAUTOTEST parts in bulk if needed, or use the largest available data set).</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>1. Set the filters so the filtered set exceeds the export row cap.
 2. Request the CSV download and read what happens.
@@ -3475,102 +3530,102 @@
 4. Narrow the date range or filters below the cap and request a download again.</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>1. Neither the CSV nor the PDF is produced — no download starts.
 2. A clear too-large message appears telling the user to narrow the date range or filters, then try again — the standard wording is "This report is too large to export. Narrow the date range or filters, then try again."
 3. After narrowing below the cap, the downloads work again.</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>SV-8646 (specs/parts-velocity.md Story 6 exports — spec silent on a cap; tech-plan-2026-07-29 A3/FR-F4: suite-wide 10,000-row export cap, locked by Chris 2026-07-21)</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>The report uses the standard two-tone layout: white card surfaces on a soft blue-grey backdrop with an edge-to-edge table</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>PV — Visual Conformance</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded, in light mode.</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>1. Look at the page background, the toolbar, and the table surfaces.
 2. Look at the card corners and the table's horizontal extent.</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>1. White card surfaces (toolbar + table cells) sit on the standard soft blue-grey page background (the application's two-tone report theme).
 2. There is NO card border-radius - the table runs edge to edge.
 3. The layout matches the application's other reports (consistency goal, §1).</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S7-R1; §2</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>Toolbar and table detail styling: paddings, white header with 1px top border, white body cells, 2rem edge padding</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>PV — Visual Conformance</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded (use browser devtools to measure paddings).</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>1. Inspect the toolbar's background and internal padding.
 2. Inspect the table header cells and the border between header and toolbar.
 3. Inspect the body cells and the first/last cell padding in a row.</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>1. The toolbar background is white (black in dark mode) with internal padding 32px top, 2rem right, 24px bottom, 2rem left.
 2. Header cells have a white background and a 1px top border separating them from the toolbar.
@@ -3578,251 +3633,251 @@
 4. The leftmost cell in every row (header and body) has 2rem left padding; the rightmost cell has 2rem right padding.</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S7-R2; S7-R3; S7-R4; S7-R5</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>Dark mode is supported and the grey info icon keeps at least 3:1 contrast in both modes</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>PV — Visual Conformance</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded and dark mode available in the application.</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>1. Switch the application to dark mode.
 2. Look at the page background, toolbar, and cells.
 3. Check the grey ⓘ info icon against its cell background in dark mode, then again in light mode.</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>1. The report supports dark mode: page background, toolbar, and cells use their dark-mode equivalents.
 2. The grey ⓘ info icon uses a token meeting at least a 3:1 contrast ratio against the cell background in BOTH light and dark mode.</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S7-R6</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>The report is server-paginated - the backend returns one page of rows at a time</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>PV — API</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with more rows in the result set than one page holds.
 2. Browser devtools (network tab) are open to observe the backend requests.</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>1. Load the report and observe the backend data request and its response size.
 2. Move to the next page of rows and observe the traffic.</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>1. The backend returns ONE page of rows at a time - the full result set is not shipped to the browser.
 2. Paging is resolved on the server: moving to another page issues a fresh backend request for that page.
 3. This keeps the report responsive at scale (organizations can carry 50-60k parts, multiplied across locations).</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>SV-8642 (specs/parts-velocity.md §2 (server-paginated); S2-R10)</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>Each filter or search change re-queries the server and returns page one</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>PV — API</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded and the browser devtools network tab open.</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>1. Change each of these in turn and watch the network traffic: Type, date range, Bin, Location, Category, Vendor, and the toolbar search.
 2. After a filter change while on a later page, note which page of results is shown.</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>1. EACH change (Type, date range, Bin, Location, Category, Vendor, search) triggers a fresh server-side data load.
 2. There is no client-side-only narrowing - every filter or search change re-queries the server.
 3. Each change returns the FIRST page of the new result set.</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>SV-8642 (specs/parts-velocity.md S2-R10)</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>Header-click sorting re-queries the server with nulls first on ascending and last on descending as a server sort semantic</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>PV — API</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded (including rows with null values in a sortable column) and the network tab open.</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>1. Click a column header and watch the network traffic and the returned order.
 2. Click it again (reverse direction) and observe.
 3. Note where the null rows land in the server-returned order for each direction.</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>1. Each header click re-fetches the data from the server, ordered by the chosen column and direction, returning the first page of the re-sorted result set.
 2. Null values are placed FIRST on ascending and LAST on descending - as a server sort semantic, so the same order appears on screen and in the exports.
 3. Ties keep a stable order (no explicit secondary key).</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S3-R3</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>The backend denies both the report data and the export to a user without Inventory Reports → View</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>PV — API</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in as a Reports-section user whose role lacks the Inventory Reports → View permission.
 2. Browser devtools (network tab) are open.</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>1. Open the Parts Velocity report and observe the backend data request's outcome.
 2. Attempt the export and observe the backend export request's outcome.</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>1. The backend REFUSES the report data request - the user is denied the data (the UI shows the standard access-denied state).
 2. The backend likewise refuses the export request - no file is produced.
 3. Both loading and exporting are gated by the same Inventory Reports → View permission.</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>specs/parts-velocity.md S1-R4; S1-N2</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr"/>
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/Report-Suite_Parts-Velocity-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Parts-Velocity-Report_testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J70"/>
+  <dimension ref="A1:J72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -530,7 +530,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>SV-8641 (specs/parts-velocity.md S1-R1 — the spec's 'only report' sentence is superseded: Parts Velocity and Inventory Value BOTH live under Parts per the PRD companion video 2026-07-30 00:35-01:18; PV S1-R1 vs IV S1-R1 inconsistency flagged to SPEC-WATCH)</t>
+          <t>SV-8641 (PV spec S1-R1 — spec's 'only report' sentence superseded: Parts Velocity and Inventory Value BOTH live under Parts per PRD video 2026-07-30 00:35-01:18; PV-vs-IV S1-R1 clash on SPEC-WATCH)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -578,7 +578,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>specs/parts-velocity.md S1-R2; S4-R6</t>
+          <t>SV-8641 (specs/parts-velocity.md S1-R2; S4-R6)</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -587,7 +587,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>A loading indicator shows while data loads and old rows are replaced only when new data returns</t>
+          <t>A loading indicator shows and old rows are replaced only when data returns</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -627,7 +627,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>specs/parts-velocity.md S1-R3</t>
+          <t>SV-8641 (specs/parts-velocity.md S1-R3)</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
@@ -636,7 +636,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>A user with the Inventory Reports → View permission can load the report and export it</t>
+          <t>A user with Inventory Reports View can load the report and export it</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>specs/parts-velocity.md S1-R4</t>
+          <t>SV-8641 (specs/parts-velocity.md S1-R4)</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
@@ -685,7 +685,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>A user without the Manager or Office User role does not see the Parts Velocity navigation entry</t>
+          <t>Without the Manager or Office User role the report entry is not shown</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>specs/parts-velocity.md S1-N1</t>
+          <t>SV-8641 (specs/parts-velocity.md S1-N1)</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
@@ -731,7 +731,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>A user with Reports access but without Inventory Reports → View sees the entry but is denied the data and the export</t>
+          <t>Reports access without Inventory Reports View: entry shows; data denied</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>specs/parts-velocity.md S1-N2; S1-R4</t>
+          <t>SV-8641 (specs/parts-velocity.md S1-N2; S1-R4)</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>SV-8642 (specs/parts-velocity.md S2-R1; S3-R5 - 'Catalogue' RENAMED to the exact label 'Special Order' [Type filter, Type column, export] per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source, last-update-wins), confirming kickoff video P31)</t>
+          <t>SV-8642 (PV spec S2-R1; S3-R5 - 'Catalogue' RENAMED to the exact label 'Special Order' [Type filter; Type column; export] per Chris Ward msg 2026-07-29 [newest-wins] [cf video P31])</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
@@ -872,7 +872,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>specs/parts-velocity.md S2-R2; §2 Out of Scope</t>
+          <t>SV-8642 (specs/parts-velocity.md S2-R2; §2 Out of Scope)</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
@@ -881,7 +881,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Custom date range requires valid start and end dates and rejects a span over 366 days</t>
+          <t>A Custom date range needs valid dates and rejects a span over 366 days</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>specs/parts-velocity.md S2-R3</t>
+          <t>SV-8642 (specs/parts-velocity.md S2-R3)</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
@@ -972,7 +972,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>specs/parts-velocity.md S2-R4; S2-R5; S2-R10</t>
+          <t>SV-8642 (specs/parts-velocity.md S2-R4; S2-R5; S2-R10)</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
@@ -981,7 +981,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Toolbar search matches part number or description, case-insensitively, and is page-specific</t>
+          <t>Toolbar search matches part number or description, case-insensitively</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>specs/parts-velocity.md S2-R6; §3 Key Decisions</t>
+          <t>SV-8642 (specs/parts-velocity.md S2-R6; §3 Key Decisions)</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>specs/parts-velocity.md S2-R7</t>
+          <t>SV-8642 (specs/parts-velocity.md S2-R7)</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
@@ -1082,7 +1082,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Bin multi-select filter limits the table to inventory parts stocked in the selected bins</t>
+          <t>The Bin multi-select limits the table to parts stocked in those bins</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>specs/parts-velocity.md S2-R8</t>
+          <t>SV-8642 (specs/parts-velocity.md S2-R8)</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>SV-8642 (specs/parts-velocity.md S2-R8 - 'Catalogue' RENAMED to the exact label 'Special Order' per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source, last-update-wins), confirming kickoff video P31)</t>
+          <t>SV-8642 (PV spec S2-R8 - 'Catalogue' RENAMED to the exact label 'Special Order' per Chris Ward msg 2026-07-29 [newest-wins] [cf video P31])</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>SV-8642 (specs/parts-velocity.md S2-R9 — per-row location identifier in All-Locations view ADDED per kickoff video P10 40:58-41:20, user ruling 2026-07-28: video overrides spec (video newer, last-update-wins)) + on-screen location-scope indicator per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source, last-update-wins)</t>
+          <t>SV-8642 (PV spec S2-R9 — per-row location identifier in All-Locations view ADDED per kickoff video P10; [ruling 2026-07-28 video-overrides-spec]) + on-screen location-scope indicator per Chris Ward msg 2026-07-29 [newest-wins]</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>specs/parts-velocity.md S2-R11; S2-N1; §7</t>
+          <t>SV-8642 (specs/parts-velocity.md S2-R11; S2-N1; §7)</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Parts with no category, vendor, or bin assigned are excluded when that filter is active</t>
+          <t>Parts with no category; vendor or bin are excluded when that filter is on</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>specs/parts-velocity.md S2-E1; S2-E2; S2-E3</t>
+          <t>SV-8642 (specs/parts-velocity.md S2-E1; S2-E2; S2-E3)</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
@@ -1329,7 +1329,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>The Location filter is hidden for a user with access to only one location</t>
+          <t>Parts Velocity: the Location filter is hidden for a one-location user</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>SV-8642 (PV spec S2-E4 — RULED HIDDEN by Chris Ward answer 2026-07-31 Q1=A "classic spec drift"; the S2-E4 "still sees the filter" note is stale, spec edit pending)</t>
+          <t>SV-8642 (PV spec S2-E4 — RULED HIDDEN by Chris Ward answer 2026-07-31 Q1=A "classic spec drift"; the S2-E4 "still sees the filter" note is stale; spec edit pending)</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>SV-8642 (PV spec v4 2026-07-29 S2-R12; S3-R10; S7-R8 — per-row Location column, leftmost before Type, "Multiple" on the merged special-order row, not in the picker)</t>
+          <t>SV-8642 (PV spec v4 2026-07-29 S2-R12; S3-R10; S7-R8 — per-row Location column; leftmost before Type; "Multiple" on the merged special-order row; not in the picker)</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
@@ -1431,7 +1431,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>An inventory part stocked at two selected locations shows as two rows with per-location stock figures</t>
+          <t>A part stocked at two selected locations shows as two per-location rows</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>specs/parts-velocity.md S3-R1a; §3 Key Decisions</t>
+          <t>SV-8643 (specs/parts-velocity.md S3-R1a; §3 Key Decisions)</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
@@ -1669,7 +1669,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>SV-8643 (specs/parts-velocity.md S3-R4; S3-R5; S3-R8 - Type value 'Catalogue' RENAMED to the exact label 'Special Order' per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source, last-update-wins), confirming kickoff video P31)</t>
+          <t>SV-8643 (PV spec S3-R4; S3-R5; S3-R8 - Type value 'Catalogue' RENAMED to the exact label 'Special Order' per Chris Ward msg 2026-07-29 [newest-wins] [cf video P31])</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
@@ -1678,7 +1678,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Info icons on Units Sold, Demand, and Turns / Yr show the exact spec descriptions and never trigger a sort</t>
+          <t>Info icons sit on Units Sold; Demand and Turns / Yr with descriptions</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>specs/parts-velocity.md S3-R6</t>
+          <t>SV-8643 (specs/parts-velocity.md S3-R6)</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
@@ -1731,7 +1731,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Description, Category, and Vendor truncate with an ellipsis and show in full on hover; Part # is never truncated</t>
+          <t>Description; Category and Vendor truncate on hover; Part # never does</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>specs/parts-velocity.md S3-R7</t>
+          <t>SV-8643 (specs/parts-velocity.md S3-R7)</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
@@ -1880,7 +1880,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>A sale invoiced then fully reversed in-window shows Demand 1 with Units Sold 0.00, and negative movement shows a leading minus</t>
+          <t>A sale invoiced then fully reversed shows Demand 1 with Units Sold 0.00</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
         <is>
           <t>1. Part C shows Demand 1 (the reversal does not decrement the Demand count) with Units Sold 0.00 (the reversal nets the movement to zero).
 2. Part D shows a NEGATIVE Units Sold with a leading minus (e.g. -3.00) - negative movement is not floored to zero.
-3. A fully-reversed part with zero net movement, no on-hand stock, and no residual revenue would be excluded per S3-N1 (Demand alone is not a keep-criterion).</t>
+3. A fully-reversed part with zero net movement, no on-hand stock, and no residual revenue would be excluded altogether (a Demand count alone does not keep a row).</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>specs/parts-velocity.md S3-E1; S5-R5</t>
+          <t>SV-8643 (specs/parts-velocity.md S3-E1; S5-R5)</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
@@ -2068,7 +2068,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Filters, column selection, and sort are remembered per browser and restored before the first data fetch</t>
+          <t>Filters; columns and sort are remembered per browser before the first fetch</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>specs/parts-velocity.md S4-R6; S1-R2</t>
+          <t>SV-8644 (specs/parts-velocity.md S4-R6; S1-R2)</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
@@ -2117,7 +2117,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>A saved value that is no longer valid falls back to that setting's default on restore</t>
+          <t>A saved value that is no longer valid falls back to that setting's default</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>specs/parts-velocity.md S4-R6</t>
+          <t>SV-8644 (specs/parts-velocity.md S4-R6)</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
@@ -2211,7 +2211,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>All 20 columns can be hidden; the empty selection is not restored and an export then contains no data columns</t>
+          <t>All 20 columns can be hidden; the empty selection is never restored</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>specs/parts-velocity.md S4-E1; S4-R6</t>
+          <t>SV-8644 (specs/parts-velocity.md S4-E1; S4-R6)</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
@@ -2259,7 +2259,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Units Sold for an inventory part is net stock movement: invoicing adds, reversing subtracts, returns do not affect it</t>
+          <t>Units Sold for an inventory part is net stock movement</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>specs/parts-velocity.md S5-R1; S5-R4 (Units Sold, inventory); §4</t>
+          <t>SV-8645 (specs/parts-velocity.md S5-R1; S5-R4 (Units Sold; inventory); §4)</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>SV-8645 (specs/parts-velocity.md S5-R2; S5-R4 (Units Sold, catalogue); S5-R4b)</t>
+          <t>SV-8645 (specs/parts-velocity.md S5-R2; S5-R4 (Units Sold; catalogue); S5-R4b)</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
@@ -2357,7 +2357,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Units Returned counts initiated part returns and parts-sale credits, and cancelling a return removes its quantity</t>
+          <t>Units Returned counts initiated part returns and parts-sale credits</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>specs/parts-velocity.md S5-R3; S5-R4 (Units Returned); §3 Key Decisions</t>
+          <t>SV-8645 (specs/parts-velocity.md S5-R3; S5-R4 (Units Returned); §3 Key Decisions)</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
@@ -2408,7 +2408,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Units Returned is windowed by initiation date, ignores invoice status, and excludes core-charge returns</t>
+          <t>Units Returned is windowed by initiation date, ignores invoice status</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2446,12 +2446,12 @@
 2. In the previous window the return does not count (only the sale's own metrics do).
 3. Core-charge returns are EXCLUDED from Units Returned.
 4. Units Returned is independent of the work order's current invoice status.
-5. A part whose ONLY in-window event is a return (no sale, no stock, no revenue) produces no row at all (per S3-N1) - accepted behavior, the row axis is sales/stock activity.</t>
+5. A part whose ONLY in-window event is a return (no sale, no stock, no revenue) produces no row at all - accepted behavior, the row axis is sales/stock activity.</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>specs/parts-velocity.md S5-R3</t>
+          <t>SV-8645 (specs/parts-velocity.md S5-R3)</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
@@ -2614,7 +2614,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>On Hand shows the row's own location stock, and Min / Max are read-only stored thresholds with no editing from the report</t>
+          <t>On Hand shows the row's own location stock</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2653,7 +2653,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>specs/parts-velocity.md S5-R4 (On Hand / Min / Max); §2 Out of Scope; S5-R5</t>
+          <t>SV-8645 (specs/parts-velocity.md S5-R4 (On Hand / Min / Max); §2 Out of Scope; S5-R5)</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
@@ -2814,7 +2814,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Unit Cost / Sell Price and Margin % use independent null triggers, so mixed rows are valid</t>
+          <t>Unit Cost / Sell Price and Margin % use independent null triggers</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>specs/parts-velocity.md S5-R4a (null rules + mixed-row paragraph); S3-R9</t>
+          <t>SV-8645 (specs/parts-velocity.md S5-R4a (null rules + mixed-row paragraph); S3-R9)</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
@@ -3062,374 +3062,427 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>The overflow button opens an export menu with Download (PDF) and Download (CSV) in that order</t>
+          <t>Units Sold keeps an exact part-of-a-unit quantity and is never rounded off</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
+          <t>PV — Columns &amp; Calculations</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>1. You can sign in with a role that opens the Parts Velocity report.
+2. A ZZAUTOTEST inventory part is in stock with a known unit cost, and there is enough on the shelf to sell a part-of-a-unit quantity such as 2.5.
+3. Today's date falls inside the date range you will use on the report.</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>1. Open a ZZAUTOTEST work order and add that part to it with the quantity 2.5.
+2. Approve the part line, then invoice the work order.
+3. Sign out and sign back in, so nothing is being read from the browser's memory.
+4. Open the Parts Velocity report for a date range that includes today and find that part's row.
+5. Read the Units Sold value, then switch the On Hand column on and read that too.</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>1. Units Sold reads exactly 2.50 — not 2.00, not 3.00, not blank and not a dash.
+2. It still reads exactly 2.50 after the sign-out and sign-back-in, which proves the part-of-a-unit quantity was really stored and not just shown once.
+3. On Hand has gone down by exactly 2.50 from what it was before the sale.
+4. No value anywhere on the row has been quietly rounded to a whole number.</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>SV-8589 (PV spec S5-R1 Units Sold net stock movement + S5-R5 two-decimal movement format; tech-plan-2026-07-29 Phase 0 / PR-1 D2; SV-8589 verbatim Tests: 'fractional-quantity round-trip regression')</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>The overflow button opens Download (PDF) then Download (CSV) in that order</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>PV — Exports</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded.</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>1. Find the ⋯ overflow button - the leftmost control in the toolbar's action cluster.
 2. Click it and read the menu items top to bottom.</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>1. The ⋯ overflow button sits leftmost in the toolbar's action cluster.
 2. The menu holds exactly two items, in this order: Download (PDF), then Download (CSV).</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>specs/parts-velocity.md S6-R1</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>SV-8646 (specs/parts-velocity.md S6-R1)</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>Both exports reflect the filters and search active at the time of export</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>PV — Exports</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded across types, categories, and locations.</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>1. Set a distinctive filter mix: Type = Inventory, a single category, a short date range, and a search string.
 2. Download the CSV and open it.
 3. Download the PDF and open it.</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>1. Both files contain only the rows matching the date range, type, category, vendor, bin, location, and search active at export time - not a full unfiltered dump.
 2. The exported rows match what the on-screen grid was showing.
 3. Each file (PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to (exact position in the file is confirmed in the build).</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>SV-8646 (specs/parts-velocity.md S6-R2; §3 Key Decisions + Locations: line in every CSV/PDF export per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source, last-update-wins))</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>SV-8646 (specs/parts-velocity.md S6-R2; §3 Key Decisions + Locations: line in every CSV/PDF export per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source; last-update-wins))</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>Exports include only the enabled columns, in the canonical on-screen order</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>PV — Exports</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded.</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>1. Hide two default columns (e.g. Category, Margin %) and enable a hidden one (e.g. Units Returned).
 2. Download the CSV and read its column headers in order.
 3. Download the PDF and read its columns in order.</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>1. Both exports contain ONLY the currently enabled columns - the hidden ones are absent.
 2. Columns appear in the CANONICAL order (the fixed on-screen order) - the re-enabled Units Returned sits right after Units Sold, NOT appended at the end.
 3. The export mirrors the visible grid.</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>specs/parts-velocity.md S6-R3; S4-R4</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>SV-8646 (specs/parts-velocity.md S6-R3; S4-R4)</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>Exports reflect the active sort, including Min/Max and null placement</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>PV — Exports</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded, including rows with — values in a sortable column (e.g. On Hand on special-order rows).
 2. Min and Max are enabled.</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>1. Without clicking any header (default Demand descending), download the CSV and check the row order.
 2. Sort by Min ascending, export, and check the order including where the — rows land.
 3. Sort by On Hand descending, export, and check the null placement.</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>1. The default Demand-descending order is exported when the user has not chosen another column.
 2. Every column's sort is honored in the export - including Min and Max.
 3. The export renders the EXACT server order, including null placement (nulls first on ascending, last on descending) - the export and the on-screen grid match; there is no on-screen-vs-export null-sorting difference.</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>SV-8646 (specs/parts-velocity.md S6-R4; S3-R3)</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>PDF: filename, A3 landscape, title, text truncation, and the shop logo</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>PV — Exports</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded, including a part with a Description, Category, and Vendor each longer than 18 characters and a long Part #.</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>1. Download the PDF and check the saved filename.
 2. Open it and check the page format and title.
 3. Find the long-text part's row and read Description, Category, Vendor, and Part #.</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>1. The file downloads as velocity-report.pdf.
 2. The PDF is formatted for A3 landscape and titled Parts Velocity.
 3. Description, Category, and Vendor are truncated to 18 characters in the PDF.
 4. Part # is NOT truncated.
-5. The shop logo shows at the top of the PDF when one is set, with the same logo treatment as the other reports in the suite (fallback behaviour when no logo is set is confirmed in the build; the CSV never includes a logo).</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>SV-8646 (specs/parts-velocity.md S6-R5; S6-R6 + same-logo-treatment for every report per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source, last-update-wins))</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>CSV: named velocity-report.csv with full untruncated text values and Last Sale as a raw integer</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
+5. The shop logo shows at the top of the PDF when one is set. With no uploaded logo the PDF shows the bundled ShopView default logo instead of a blank space, the same as the other reports in this suite. The CSV never includes a logo.</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>SV-8646 (specs/parts-velocity.md S6-R5; S6-R6 + same-logo-treatment for every report per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source; last-update-wins))</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>CSV is named velocity-report.csv and holds full untruncated text values</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>PV — Exports</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded, including a part with a Description longer than 18 characters and a part with a Last Sale value.</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>1. Download the CSV and check the saved filename.
 2. Open it and read the long part's Description, Category, and Vendor.
 3. Read the Last Sale column value.</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>1. The file downloads as velocity-report.csv.
 2. The CSV carries the FULL, untruncated Description / Category / Vendor values (unlike the PDF's 18-character cut).
 3. Last Sale is a raw integer in the CSV (e.g. 42) - the 'N days' wording is PDF/on-screen only.</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>specs/parts-velocity.md S6-R5; S6-R6; S6-R8</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>SV-8646 (specs/parts-velocity.md S6-R5; S6-R6; S6-R8)</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>Em-dash in both exports; Last Sale reads "N days" in the PDF</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>PV — Exports</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>1. Rows with null values exist (a special-order row for On Hand / Turns / Yr / Min / Max; a row with billed units 0 for Unit Cost / Sell Price; a never-sold row for Last Sale).
 2. All nullable columns are enabled.</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>1. Download the CSV and locate the null cells.
 2. Download the PDF and locate the same cells.
 3. In the PDF, read a non-null Last Sale value.</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>1. A null value renders as — (em-dash) in BOTH the CSV and the PDF, in every nullable field: Unit Cost, Sell Price, Margin %, On Hand, Turns / Yr, Last Sale, Min, Max.
 2. Revenue, Margin, and the count metrics are never null in the exports either ($0.00 / 0.00 / 0).
 3. In the PDF, Last Sale renders as 'N days' (e.g. 42 days).</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>SV-8646 (specs/parts-velocity.md S6-R7; S6-R8; S3-R9)</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>PDF export alignment: Type centered, text left, numeric and money right</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>PV — Exports</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded and several columns of each kind visible.</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>1. Download the PDF and look at the alignment of each column.
 2. Download the CSV and open it in a plain text editor to confirm it is plain comma-separated values (a CSV file carries no alignment of its own).</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>1. In the PDF, the Type column is CENTERED.
 2. In the PDF, the text columns (Part #, Description, Category, Vendor) are left-aligned.
@@ -3438,91 +3491,91 @@
 5. The CSV is plain data — the alignment assertions apply to the PDF only; how a spreadsheet displays the CSV is not part of this test.</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>SV-8646 (specs/parts-velocity.md S6-R10; S3-R8)</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>Export toasts: exact success texts; server or fallback error text on failure</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>PV — Exports</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded.
 2. You can force an export failure (e.g. drop the network connection just before triggering the download, or induce a server error).</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>1. Download the CSV and the PDF normally and read each toast.
 2. Trigger a CSV export under the failure condition and read the toast.
 3. Trigger a PDF export under the failure condition and read the toast.</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>1. On success the toasts read exactly "Velocity report exported (CSV)" / "Velocity report exported (PDF)" and auto-fade — UPPERCASE (CSV)/(PDF).
 2. An error toast is shown on failure; when the server provides a message, that server message is shown.
 3. Otherwise the failure toast reads exactly: "Failed to export velocity report (csv)" or "Failed to export velocity report (pdf)" — lowercase (csv)/(pdf); the success/failure casing mix is the shipped wording, documented as-is (not a bug).</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>specs/parts-velocity.md S6-R9; S6-N1; §7 (casing note)</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>SV-8646 (specs/parts-velocity.md S6-R9; S6-N1; §7 (casing note))</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>An over-cap Parts Velocity export is refused with the too-large message</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>PV — Exports</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. A filter/location combination exists whose filtered set EXCEEDS the export row cap (widest date range + all locations; seed ZZAUTOTEST parts in bulk if needed, or use the largest available data set).</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>1. Set the filters so the filtered set exceeds the export row cap.
 2. Request the CSV download and read what happens.
@@ -3530,102 +3583,102 @@
 4. Narrow the date range or filters below the cap and request a download again.</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>1. Neither the CSV nor the PDF is produced — no download starts.
 2. A clear too-large message appears telling the user to narrow the date range or filters, then try again — the standard wording is "This report is too large to export. Narrow the date range or filters, then try again."
 3. After narrowing below the cap, the downloads work again.</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>SV-8646 (specs/parts-velocity.md Story 6 exports — spec silent on a cap; tech-plan-2026-07-29 A3/FR-F4: suite-wide 10,000-row export cap, locked by Chris 2026-07-21)</t>
-        </is>
-      </c>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>The report uses the standard two-tone layout: white card surfaces on a soft blue-grey backdrop with an edge-to-edge table</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>SV-8646 (specs/parts-velocity.md Story 6 exports — spec silent on a cap; tech-plan-2026-07-29 A3/FR-F4: suite-wide 10; 000-row export cap; locked by Chris 2026-07-21)</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>The report uses the standard two-tone layout</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>PV — Visual Conformance</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded, in light mode.</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>1. Look at the page background, the toolbar, and the table surfaces.
 2. Look at the card corners and the table's horizontal extent.</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>1. White card surfaces (toolbar + table cells) sit on the standard soft blue-grey page background (the application's two-tone report theme).
 2. There is NO card border-radius - the table runs edge to edge.
-3. The layout matches the application's other reports (consistency goal, §1).</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>specs/parts-velocity.md S7-R1; §2</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>Toolbar and table detail styling: paddings, white header with 1px top border, white body cells, 2rem edge padding</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
+3. The layout matches the application's other reports.</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>SV-8647 (specs/parts-velocity.md S7-R1; §2)</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Toolbar and table detail styling matches the suite paddings and borders</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>PV — Visual Conformance</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded (use browser devtools to measure paddings).</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>1. Inspect the toolbar's background and internal padding.
 2. Inspect the table header cells and the border between header and toolbar.
 3. Inspect the body cells and the first/last cell padding in a row.</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>1. The toolbar background is white (black in dark mode) with internal padding 32px top, 2rem right, 24px bottom, 2rem left.
 2. Header cells have a white background and a 1px top border separating them from the toolbar.
@@ -3633,251 +3686,304 @@
 4. The leftmost cell in every row (header and body) has 2rem left padding; the rightmost cell has 2rem right padding.</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>specs/parts-velocity.md S7-R2; S7-R3; S7-R4; S7-R5</t>
-        </is>
-      </c>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>Dark mode is supported and the grey info icon keeps at least 3:1 contrast in both modes</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>SV-8647 (specs/parts-velocity.md S7-R2; S7-R3; S7-R4; S7-R5)</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Dark mode is supported and the grey info icon keeps 3:1 contrast in both</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>PV — Visual Conformance</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded and dark mode available in the application.</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>1. Switch the application to dark mode.
 2. Look at the page background, toolbar, and cells.
 3. Check the grey ⓘ info icon against its cell background in dark mode, then again in light mode.</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>1. The report supports dark mode: page background, toolbar, and cells use their dark-mode equivalents.
 2. The grey ⓘ info icon uses a token meeting at least a 3:1 contrast ratio against the cell background in BOTH light and dark mode.</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>specs/parts-velocity.md S7-R6</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>SV-8647 (specs/parts-velocity.md S7-R6)</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>The report is server-paginated - the backend returns one page of rows at a time</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>PV — API</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with more rows in the result set than one page holds.
 2. Browser devtools (network tab) are open to observe the backend requests.</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>1. Load the report and observe the backend data request and its response size.
 2. Move to the next page of rows and observe the traffic.</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>1. The backend returns ONE page of rows at a time - the full result set is not shipped to the browser.
 2. Paging is resolved on the server: moving to another page issues a fresh backend request for that page.
 3. This keeps the report responsive at scale (organizations can carry 50-60k parts, multiplied across locations).</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>SV-8642 (specs/parts-velocity.md §2 (server-paginated); S2-R10)</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>Each filter or search change re-queries the server and returns page one</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>PV — API</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded and the browser devtools network tab open.</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>1. Change each of these in turn and watch the network traffic: Type, date range, Bin, Location, Category, Vendor, and the toolbar search.
 2. After a filter change while on a later page, note which page of results is shown.</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>1. EACH change (Type, date range, Bin, Location, Category, Vendor, search) triggers a fresh server-side data load.
 2. There is no client-side-only narrowing - every filter or search change re-queries the server.
 3. Each change returns the FIRST page of the new result set.</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>SV-8642 (specs/parts-velocity.md S2-R10)</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>Header-click sorting re-queries the server with nulls first on ascending and last on descending as a server sort semantic</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Header-click sorting re-queries the server; nulls first asc and last desc</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>PV — API</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded (including rows with null values in a sortable column) and the network tab open.</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>1. Click a column header and watch the network traffic and the returned order.
 2. Click it again (reverse direction) and observe.
 3. Note where the null rows land in the server-returned order for each direction.</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>1. Each header click re-fetches the data from the server, ordered by the chosen column and direction, returning the first page of the re-sorted result set.
 2. Null values are placed FIRST on ascending and LAST on descending - as a server sort semantic, so the same order appears on screen and in the exports.
 3. Ties keep a stable order (no explicit secondary key).</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>specs/parts-velocity.md S3-R3</t>
-        </is>
-      </c>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>The backend denies both the report data and the export to a user without Inventory Reports → View</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>SV-8643 (specs/parts-velocity.md S3-R3)</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>The backend denies report data AND export without Inventory Reports View</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>PV — API</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in as a Reports-section user whose role lacks the Inventory Reports → View permission.
 2. Browser devtools (network tab) are open.</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>1. Open the Parts Velocity report and observe the backend data request's outcome.
 2. Attempt the export and observe the backend export request's outcome.</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>1. The backend REFUSES the report data request - the user is denied the data (the UI shows the standard access-denied state).
 2. The backend likewise refuses the export request - no file is produced.
 3. Both loading and exporting are gated by the same Inventory Reports → View permission.</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>specs/parts-velocity.md S1-R4; S1-N2</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>SV-8641 (specs/parts-velocity.md S1-R4; S1-N2)</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>QuickBooks amount for a part-of-a-unit sale is exact and never inflated</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>PV — API</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>1. The test company is connected to QuickBooks.
+2. The part-of-a-unit sale has been made and invoiced — a ZZAUTOTEST part sold in a quantity such as 2.5, at a known unit cost such as $10.00.
+3. You can sign in to that QuickBooks company and look at its journal entries.</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>1. Write down the quantity sold and the part's unit cost, and work out the correct amount by hand (2.5 x $10.00 = $25.00).
+2. Let the invoice go across to QuickBooks the normal way the shop does it.
+3. In QuickBooks, open the journal entry that was created for that invoice.
+4. Read the inventory / cost amount on that journal entry.
+5. Go back to the Parts Velocity report and read the same part's Units Sold value.</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>1. The QuickBooks amount is exactly the hand-worked figure to the cent — $25.00 for 2.5 at $10.00.
+2. It is NOT a whole-unit amount such as $20.00 or $30.00, and it is NOT a bigger, multiplied figure.
+3. The quantity behind the QuickBooks amount matches the Units Sold value on the report (2.50) — the two systems agree.
+4. No second or correcting journal entry is created to patch up a wrong amount.</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>SV-8589 (verbatim Tests: 'QB journal amount exact from fractional movement'; Goal: 'QB journal-entry sync multiplies these into dollar amounts'; tech-plan-2026-07-29 Phase 0 / PR-1 D2 - no report spec covers QuickBooks)</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/Report-Suite_Parts-Velocity-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Parts-Velocity-Report_testrail-import.xlsx
@@ -1407,7 +1407,8 @@
 3. Read the Location cell on the merged Special Order row.
 4. Open the column picker and look for Location in the list.
 5. Narrow to a single location and read the headers again.
-6. Change the selection between one location, several, and "All Locations", watching the filter control's width.</t>
+6. Change the selection between one location, several, and "All Locations", watching the filter control's width.
+7. With more than one location still selected, download the CSV and the PDF and read their columns from the left.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1417,12 +1418,13 @@
 3. The merged Special Order row shows "Multiple", because it is summed across the selected locations.
 4. Location is NOT one of the 20 columns in the picker — it is managed by the location scope, not by you.
 5. With a single location in scope the Location column is hidden.
-6. The Location filter control keeps the same width whichever label it shows — one location, several, or "All locations" — so the toolbar does not shift as you change the selection.</t>
+6. The Location filter control keeps the same width whichever label it shows — one location, several, or "All locations" — so the toolbar does not shift as you change the selection.
+7. Both downloads include the Location column in the same position it holds on screen (leftmost, before Type), with the same values — each inventory row's own location, and "Multiple" on the merged Special Order row.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>SV-8642 (PV spec v4 2026-07-29 S2-R12; S3-R10; S7-R8 — per-row Location column; leftmost before Type; "Multiple" on the merged special-order row; not in the picker)</t>
+          <t>SV-8642; SV-8646 (PV spec v4 2026-07-29 S2-R12; S3-R10; S7-R8; S6-R11 — per-row Location column; leftmost before Type; "Multiple" on the merged special-order row; not in the picker; S6-R11 = the same column in both exports)</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
@@ -2005,13 +2007,14 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1. Exactly these 14 columns show, in this left-to-right order: Type, Part #, Description, Category, Vendor, Units Sold, Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand.
-2. The other 6 columns start hidden: Units Returned, Sold (WO), Sold (Parts Sale), Turns / Yr, Min, Max.</t>
+          <t>1. With a single location in scope exactly these 14 columns show, in this left-to-right order: Type, Part #, Description, Category, Vendor, Units Sold, Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand.
+2. The other 6 columns start hidden: Units Returned, Sold (WO), Sold (Parts Sale), Turns / Yr, Min, Max.
+3. When more than one location is in scope the automatic Location column shows as well, leftmost before Type — 15 columns. It is not part of the 14-column default set and is not in the column picker, so its presence is expected and is not a failure of this test.</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>SV-8644 (specs/parts-velocity.md S4-R2; S4-R3)</t>
+          <t>SV-8644; SV-8643 (PV spec v4 2026-07-29 S4-R2; S4-R3 + Story 3 S3-R10 — the 14 default-visible columns and the 6 hidden ones; plus the automatic Location column leftmost when more than one location is in scope)</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
@@ -2053,13 +2056,13 @@
       <c r="G33" s="2" t="inlineStr">
         <is>
           <t>1. Each toggle takes effect immediately - the table re-renders without a page reload.
-2. Columns always render in the fixed canonical left-to-right order regardless of the order they were toggled on: Type, Part #, Description, Category, Vendor, Units Sold, Units Returned, Sold (WO), Sold (Parts Sale), Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand, Turns / Yr, Min, Max.
+2. Columns always render in the fixed canonical left-to-right order regardless of the order they were toggled on (with the automatic Location column, when shown, sitting leftmost before Type): Type, Part #, Description, Category, Vendor, Units Sold, Units Returned, Sold (WO), Sold (Parts Sale), Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand, Turns / Yr, Min, Max.
 3. So Units Returned slots in right after Units Sold, Turns / Yr after On Hand, and Min before Max - not appended at the end.</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>SV-8644 (specs/parts-velocity.md S4-R4; S4-R5)</t>
+          <t>SV-8644; SV-8643 (PV spec v4 2026-07-29 S4-R4; S4-R5 + Story 3 S3-R10 — canonical column order and immediate re-render; plus the automatic Location column leftmost when shown)</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr"/>

--- a/testrail-import/Report-Suite_Parts-Velocity-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Parts-Velocity-Report_testrail-import.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parts Velocity" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Parts Velocity" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/testrail-import/Report-Suite_Parts-Velocity-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Parts-Velocity-Report_testrail-import.xlsx
@@ -511,7 +511,7 @@
       <c r="E2" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App as a user with the Manager or Office User role.
-2. Your role has the Inventory Reports → View permission.</t>
+2. Your role has the ordinary reports access.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -530,7 +530,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>SV-8641 (PV spec S1-R1 — spec's 'only report' sentence superseded: Parts Velocity and Inventory Value BOTH live under Parts per PRD video 2026-07-30 00:35-01:18; PV-vs-IV S1-R1 clash on SPEC-WATCH)</t>
+          <t>SV-8641 (PV spec S1-R1 — the "only report" sentence is superseded: Parts Velocity and Inventory Value BOTH live under Parts per the PRD video 2026-07-30; access = the one ordinary reports permission per QA lead 2026-08-03)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -636,7 +636,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>A user with Inventory Reports View can load the report and export it</t>
+          <t>A user with ordinary reports access can load the report and export it</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -657,7 +657,7 @@
       <c r="E5" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in as a user with the Manager or Office User role.
-2. That user's role has the Inventory Reports → View permission.
+2. That user's role has the ordinary reports access (the standard "can this person see reports" setting).
 3. Some parts have sales activity in the selected date range.</t>
         </is>
       </c>
@@ -671,12 +671,13 @@
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>1. The report data loads and rows are shown.
-2. The export downloads successfully (both loading the report and exporting it are allowed by the Inventory Reports → View permission).</t>
+2. The export downloads successfully — both opening the report and exporting it are allowed by the same ordinary reports access.
+3. Note for the tester: for now ONE ordinary reports access opens all six of these new reports; none of them has a permission of its own. If the build demands a separate report permission before this works, mark this Failed and report it — do not change the test.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>SV-8641 (specs/parts-velocity.md S1-R4)</t>
+          <t>SV-8641 (PV spec S1-R4 — one reports permission for all six ruled by Chris Ward Q2=A + QA lead 2026-08-03 "ONE permission FOR NOW"; PV S1-R4 still names Inventory Reports &gt; View — his spec edit owed)</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>

--- a/testrail-import/Report-Suite_Parts-Velocity-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Parts-Velocity-Report_testrail-import.xlsx
@@ -732,7 +732,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Reports access without Inventory Reports View: entry shows; data denied</t>
+          <t>Ordinary reports access alone opens Parts Velocity and its export</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -753,26 +753,27 @@
       <c r="E7" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in as a user with the Manager or Office User role.
-2. That user's role does NOT have the Inventory Reports → View permission.</t>
+2. That user's role has the ordinary reports access turned on (the standard "can this person see reports" setting) and no other reports-related permission turned on.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
           <t>1. Open the Reports section and look for the Parts Velocity entry under Parts.
 2. Click the Parts Velocity entry.
-3. If any export control is reachable, try to export.</t>
+3. Use the export control on the report and download a file.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1. The Parts Velocity navigation entry is still visible (the entry follows Reports-section access, not the report permission).
-2. On opening the report, the standard access-denied state is shown instead of data.
-3. The export is likewise denied - no file downloads.</t>
+          <t>1. The Parts Velocity entry is visible in the Reports navigation under Parts.
+2. Opening it shows the report data - not an access-denied screen.
+3. The export downloads.
+4. Note for the tester: for now ONE ordinary reports access opens all six of these new reports, and no report has a permission of its own. If an extra Parts or Inventory reports permission does exist and switching it OFF blocks this report or its export, that is wrong - mark this Failed and report it. If a separate per-report permission is ever added on purpose in a later release, this test will be updated first, so treat that as a planned change and not as a bug.</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>SV-8641 (specs/parts-velocity.md S1-N2; S1-R4)</t>
+          <t>SV-8641 (PV spec S1-N2; S1-R4 - RESCOPED 2026-08-03: the old "Reports access without Inventory Reports View" state cannot exist under one permission; Chris Ward Q2=A + "they can exist and not do anything"; QA lead "ONE permission FOR NOW")</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
@@ -825,7 +826,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>SV-8642 (PV spec S2-R1; S3-R5 - 'Catalogue' RENAMED to the exact label 'Special Order' [Type filter; Type column; export] per Chris Ward msg 2026-07-29 [newest-wins] [cf video P31])</t>
+          <t>SV-8642 (PV spec v4 2026-07-29 S2-R1; S3-R5 — S2-R1 CLOSES the three Type options and the Both default; 'Catalogue'→'Special Order' per Chris Ward 2026-07-29 [newest-wins])</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
@@ -873,7 +874,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>SV-8642 (specs/parts-velocity.md S2-R2; §2 Out of Scope)</t>
+          <t>SV-8642 (PV spec v4 2026-07-29 S2-R2; §2 Out of Scope — S2-R2 CLOSES it in the spec's own words ("offering exactly these options") and rules out "All Time"; so the closed list IS the requirement)</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
@@ -1271,7 +1272,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>SV-8642 (specs/parts-velocity.md S2-R11; S2-N1; §7)</t>
+          <t>SV-8642 (PV spec v4 2026-07-29 S2-R11; S2-N1; §7 — §7 CLOSES the empty-state string verbatim ("Empty bays" ... "Get Going!") as the standard reports no-data label; so the exact string IS the requirement)</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
@@ -1725,7 +1726,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>SV-8643 (specs/parts-velocity.md S3-R6)</t>
+          <t>SV-8643 (PV spec v4 2026-07-29 S3-R6 — S3-R6 CLOSES the set (exactly three columns: Units Sold; Demand; Turns / Yr) and quotes each description verbatim; so the closed set and the exact strings ARE the requirement)</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
@@ -3156,7 +3157,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>SV-8646 (specs/parts-velocity.md S6-R1)</t>
+          <t>SV-8646 (PV spec v4 2026-07-29 S6-R1 — S6-R1 CLOSES it in the spec's own words ("an export menu with two items ... Download (PDF) and Download (CSV)"); so the closed list IS the requirement)</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr"/>
@@ -3204,7 +3205,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>SV-8646 (specs/parts-velocity.md S6-R2; §3 Key Decisions + Locations: line in every CSV/PDF export per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source; last-update-wins))</t>
+          <t>SV-8646 (PV spec v4 2026-07-29 S6-R2; S6-R11; §3 Key Decisions — both exports reflect the filters and search active at export time; S6-R11 = the "Locations:" line in both exports [Chris Ward 2026-07-29; newest-wins])</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr"/>
@@ -3546,7 +3547,7 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>SV-8646 (specs/parts-velocity.md S6-R9; S6-N1; §7 (casing note))</t>
+          <t>SV-8646 (PV spec v4 2026-07-29 S6-R9; S6-N1; §7 (casing note) — S6-R9/S6-N1 CLOSE the toast strings verbatim including the shipped UPPERCASE-success / lowercase-failure casing mix; so the exact strings ARE the requirement)</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr"/>
@@ -3728,18 +3729,19 @@
         <is>
           <t>1. Switch the application to dark mode.
 2. Look at the page background, toolbar, and cells.
-3. Check the grey ⓘ info icon against its cell background in dark mode, then again in light mode.</t>
+3. Look at the grey ⓘ info icon next to a column heading in dark mode, then switch back to light mode and look at it again.</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
           <t>1. The report supports dark mode: page background, toolbar, and cells use their dark-mode equivalents.
-2. The grey ⓘ info icon uses a token meeting at least a 3:1 contrast ratio against the cell background in BOTH light and dark mode.</t>
+2. In BOTH light mode and dark mode the grey ⓘ info icon is clearly visible against the cell behind it - you can see it at a glance without leaning in, and it does not disappear into the background.
+3. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether you can see the icon easily in both modes. Only report it if the icon is hard to see. (The design rule behind this is a minimum 3:1 contrast ratio, which the design and engineering team check with a contrast tool - not by hand.)</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>SV-8647 (specs/parts-velocity.md S7-R6)</t>
+          <t>SV-8647 (PV spec v4 2026-07-29 S7-R6 — dark-mode support + the grey info icon's colour token at ≥ 3:1 against the cell background in both modes; the ratio is a design-token property so the manual check is by-eye legibility)</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr"/>
@@ -3891,7 +3893,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>The backend denies report data AND export without Inventory Reports View</t>
+          <t>The back end serves report data and export on ordinary reports access</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -3911,7 +3913,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>1. You are signed in as a Reports-section user whose role lacks the Inventory Reports → View permission.
+          <t>1. You are signed in as a user whose role has the ordinary reports access turned on and no other reports-related permission turned on.
 2. Browser devtools (network tab) are open.</t>
         </is>
       </c>
@@ -3923,14 +3925,15 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>1. The backend REFUSES the report data request - the user is denied the data (the UI shows the standard access-denied state).
-2. The backend likewise refuses the export request - no file is produced.
-3. Both loading and exporting are gated by the same Inventory Reports → View permission.</t>
+          <t>1. The back end returns the report data - the request is not refused.
+2. The back end returns the export file - the request is not refused.
+3. Both requests succeed with only the ordinary reports access turned on - nothing else had to be enabled.
+4. Note for the tester: if the back end refuses either request for a user who has the ordinary reports access, mark this Failed and report it. If an extra Parts or Inventory reports permission exists in the system it must not change these results - for now it is hidden from the screen and enforces nothing. A per-report permission added on purpose in a later release is a planned change, not a bug, and this test will be updated first.</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>SV-8641 (specs/parts-velocity.md S1-R4; S1-N2)</t>
+          <t>SV-8641 (PV spec S1-R4; S1-N2 - RESCOPED 2026-08-03; same driver as C30327: Chris Ward Q2=A "single Reports permission" + "they can exist and not do anything"; QA lead "ONE permission FOR NOW")</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr"/>

--- a/testrail-import/Report-Suite_Parts-Velocity-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Parts-Velocity-Report_testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J72"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1682,7 +1682,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Info icons sit on Units Sold; Demand and Turns / Yr with descriptions</t>
+          <t>Info icons sit on Units Sold, Demand and Turns/Yr with descriptions</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1703,12 +1703,12 @@
       <c r="E26" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded.
-2. The Turns / Yr column has been enabled via the column picker (it is hidden by default).</t>
+2. The Turns/Yr column has been enabled via the column picker (it is hidden by default).</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1. Look immediately to the right of the Units Sold, Demand, and Turns / Yr header labels.
+          <t>1. Look immediately to the right of the Units Sold, Demand, and Turns/Yr header labels.
 2. Hover each grey info icon and read the description.
 3. Move focus to an icon with the keyboard (Tab) and check the same text is exposed.
 4. Click/activate an icon and watch whether the column sort changes.</t>
@@ -1716,10 +1716,10 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1. Each of the three headers carries a grey info icon, shown always (not hover-to-reveal) whenever its column is visible; the Turns / Yr icon appears only once that column is enabled.
+          <t>1. Each of the three headers carries a grey info icon, shown always (not hover-to-reveal) whenever its column is visible; the Turns/Yr icon appears only once that column is enabled.
 2. Units Sold shows exactly: "Units taken out of inventory stock on invoiced work orders in this date range. This is stock movement, so it can differ from the units billed behind Revenue and Sell Price."
 3. Demand shows exactly: "Number of separate transactions (work orders or parts sales) this part appeared on in the selected date range. Each transaction counts once, no matter how many units were sold on it."
-4. Turns / Yr shows exactly: "How many times you sell through this part in a year. Higher is better."
+4. Turns/Yr shows exactly: "How many times you sell through this part in a year. Higher is better."
 5. The icon is focusable and exposes the same text to assistive technology; activating it does NOT trigger a column sort.
 6. No other column header carries an info icon.</t>
         </is>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>1. The picker lists all 20 available columns, each with a toggle: Type, Part #, Description, Category, Vendor, Units Sold, Units Returned, Sold (WO), Sold (Parts Sale), Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand, Turns / Yr, Min, Max.
+          <t>1. The picker lists all 20 available columns, each with a toggle: Type, Part #, Description, Category, Vendor, Units Sold, Units Returned, Sold (WO), Sold (Parts Sale), Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand, Turns/Yr, Min, Max.
 2. No on-hand cost column is offered - the report computes one internally but it is never selectable and never displayed.</t>
         </is>
       </c>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1. In the column picker, enable Min, then Units Returned, then Turns / Yr - in that (non-canonical) order.
+          <t>1. In the column picker, enable Min, then Units Returned, then Turns/Yr - in that (non-canonical) order.
 2. Watch the table as each toggle is flipped.
 3. Read the resulting header order.</t>
         </is>
@@ -2058,8 +2058,8 @@
       <c r="G33" s="2" t="inlineStr">
         <is>
           <t>1. Each toggle takes effect immediately - the table re-renders without a page reload.
-2. Columns always render in the fixed canonical left-to-right order regardless of the order they were toggled on (with the automatic Location column, when shown, sitting leftmost before Type): Type, Part #, Description, Category, Vendor, Units Sold, Units Returned, Sold (WO), Sold (Parts Sale), Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand, Turns / Yr, Min, Max.
-3. So Units Returned slots in right after Units Sold, Turns / Yr after On Hand, and Min before Max - not appended at the end.</t>
+2. Columns always render in the fixed canonical left-to-right order regardless of the order they were toggled on (with the automatic Location column, when shown, sitting leftmost before Type): Type, Part #, Description, Category, Vendor, Units Sold, Units Returned, Sold (WO), Sold (Parts Sale), Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand, Turns/Yr, Min, Max.
+3. So Units Returned slots in right after Units Sold, Turns/Yr after On Hand, and Min before Max - not appended at the end.</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -3606,94 +3606,96 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>A large PDF download fails outright while the CSV of the same view works</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>PV — Exports</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in with ordinary reports access, on a desktop browser.
+2. Parts Velocity is open with a date range that returns a few hundred rows — narrow with the toolbar search until the list is roughly 300 to 500 rows.</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>1. Narrow the report with the toolbar search so it shows a few hundred rows.
+2. Open the three-dot menu and choose "Download (CSV)". Wait for the file.
+3. Open the three-dot menu again and choose "Download (PDF)". Wait up to a minute.
+4. Narrow the search further, to a couple of dozen rows, and choose "Download (PDF)" again.</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>1. The CSV downloads successfully at that size.
+2. The PDF also downloads successfully. If instead nothing downloads and a message appears saying something went wrong, that is a failure — record roughly how many rows were on screen.
+3. The small PDF downloads successfully, which shows the failure depends on size.
+4. Note for the tester: a very large view is refused politely with "This report is too large to export. Narrow the date range or filters, then try again." — that message is expected and is NOT this failure. This test is about a medium-sized view where the CSV works but the PDF errors.</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>SV-8646 (PV spec v4 2026-07-29 Story 6 exports — the spec is silent on a renderer size limit; tech-plan-2026-07-29 A3/FR-F4 covers only the ten-thousand-row export cap)</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
           <t>The report uses the standard two-tone layout</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>PV — Visual Conformance</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded, in light mode.</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>1. Look at the page background, the toolbar, and the table surfaces.
 2. Look at the card corners and the table's horizontal extent.</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>1. White card surfaces (toolbar + table cells) sit on the standard soft blue-grey page background (the application's two-tone report theme).
 2. There is NO card border-radius - the table runs edge to edge.
 3. The layout matches the application's other reports.</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>SV-8647 (specs/parts-velocity.md S7-R1; §2)</t>
-        </is>
-      </c>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>Toolbar and table detail styling matches the suite paddings and borders</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>PV — Visual Conformance</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>1. You are on the Parts Velocity report with data loaded (use browser devtools to measure paddings).</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>1. Inspect the toolbar's background and internal padding.
-2. Inspect the table header cells and the border between header and toolbar.
-3. Inspect the body cells and the first/last cell padding in a row.</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>1. The toolbar background is white (black in dark mode) with internal padding 32px top, 2rem right, 24px bottom, 2rem left.
-2. Header cells have a white background and a 1px top border separating them from the toolbar.
-3. Body cells have a white background.
-4. The leftmost cell in every row (header and body) has 2rem left padding; the rightmost cell has 2rem right padding.</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>SV-8647 (specs/parts-velocity.md S7-R2; S7-R3; S7-R4; S7-R5)</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr"/>
@@ -3702,228 +3704,279 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>Toolbar and table detail styling matches the suite paddings and borders</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>PV — Visual Conformance</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>1. You are on the Parts Velocity report with data loaded.</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>1. Look at the toolbar strip above the table and at the space between its controls and the edges of the strip.
+2. Look at the column-header band and at the line between it and the toolbar above it.
+3. Look at the data cells, and at the space between the first and last columns and the left and right edges of the table.
+4. Compare all of the above with another report in the suite (for example Inventory Value) opened side by side.</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>1. The toolbar strip is white (dark in dark mode), and its controls sit clear of the edges rather than pressed up against them.
+2. There is a thin dividing line between the toolbar and the column-header band, and the header band and the data cells are white.
+3. The first and last columns sit clear of the left and right edges of the table - the text is not touching the edge.
+4. It all looks the same as the other reports in the suite: put another report side by side and nothing should look out of place.
+5. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether the spacing and the dividing line look right and consistent with the other reports, and only report it if something looks obviously off. (The exact figures behind this - 32px/24px toolbar padding, a 1px header border, 2rem edge padding - are design-token values the design and engineering team check with their own tooling, not by hand.)</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>SV-8647 (specs/parts-velocity.md S7-R2; S7-R3; S7-R4; S7-R5)</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
           <t>Dark mode is supported and the grey info icon keeps 3:1 contrast in both</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>PV — Visual Conformance</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded and dark mode available in the application.</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>1. Switch the application to dark mode.
 2. Look at the page background, toolbar, and cells.
 3. Look at the grey ⓘ info icon next to a column heading in dark mode, then switch back to light mode and look at it again.</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>1. The report supports dark mode: page background, toolbar, and cells use their dark-mode equivalents.
 2. In BOTH light mode and dark mode the grey ⓘ info icon is clearly visible against the cell behind it - you can see it at a glance without leaning in, and it does not disappear into the background.
 3. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether you can see the icon easily in both modes. Only report it if the icon is hard to see. (The design rule behind this is a minimum 3:1 contrast ratio, which the design and engineering team check with a contrast tool - not by hand.)</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>SV-8647 (PV spec v4 2026-07-29 S7-R6 — dark-mode support + the grey info icon's colour token at ≥ 3:1 against the cell background in both modes; the ratio is a design-token property so the manual check is by-eye legibility)</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>The report is server-paginated - the backend returns one page of rows at a time</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>PV — API</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with more rows in the result set than one page holds.
 2. Browser devtools (network tab) are open to observe the backend requests.</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>1. Load the report and observe the backend data request and its response size.
 2. Move to the next page of rows and observe the traffic.</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>1. The backend returns ONE page of rows at a time - the full result set is not shipped to the browser.
 2. Paging is resolved on the server: moving to another page issues a fresh backend request for that page.
 3. This keeps the report responsive at scale (organizations can carry 50-60k parts, multiplied across locations).</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>SV-8642 (specs/parts-velocity.md §2 (server-paginated); S2-R10)</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>Each filter or search change re-queries the server and returns page one</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>PV — API</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded and the browser devtools network tab open.</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>1. Change each of these in turn and watch the network traffic: Type, date range, Bin, Location, Category, Vendor, and the toolbar search.
 2. After a filter change while on a later page, note which page of results is shown.</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>1. EACH change (Type, date range, Bin, Location, Category, Vendor, search) triggers a fresh server-side data load.
 2. There is no client-side-only narrowing - every filter or search change re-queries the server.
 3. Each change returns the FIRST page of the new result set.</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>SV-8642 (specs/parts-velocity.md S2-R10)</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>Header-click sorting re-queries the server; nulls first asc and last desc</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>PV — API</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded (including rows with null values in a sortable column) and the network tab open.</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>1. Click a column header and watch the network traffic and the returned order.
 2. Click it again (reverse direction) and observe.
 3. Note where the null rows land in the server-returned order for each direction.</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>1. Each header click re-fetches the data from the server, ordered by the chosen column and direction, returning the first page of the re-sorted result set.
 2. Null values are placed FIRST on ascending and LAST on descending - as a server sort semantic, so the same order appears on screen and in the exports.
 3. Ties keep a stable order (no explicit secondary key).</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>SV-8643 (specs/parts-velocity.md S3-R3)</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>The back end serves report data and export on ordinary reports access</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>PV — API</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in as a user whose role has the ordinary reports access turned on and no other reports-related permission turned on.
 2. Browser devtools (network tab) are open.</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>1. Open the Parts Velocity report and observe the backend data request's outcome.
 2. Attempt the export and observe the backend export request's outcome.</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>1. The back end returns the report data - the request is not refused.
 2. The back end returns the export file - the request is not refused.
@@ -3931,43 +3984,43 @@
 4. Note for the tester: if the back end refuses either request for a user who has the ordinary reports access, mark this Failed and report it. If an extra Parts or Inventory reports permission exists in the system it must not change these results - for now it is hidden from the screen and enforces nothing. A per-report permission added on purpose in a later release is a planned change, not a bug, and this test will be updated first.</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>SV-8641 (PV spec S1-R4; S1-N2 - RESCOPED 2026-08-03; same driver as C30327: Chris Ward Q2=A "single Reports permission" + "they can exist and not do anything"; QA lead "ONE permission FOR NOW")</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>QuickBooks amount for a part-of-a-unit sale is exact and never inflated</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>PV — API</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>1. The test company is connected to QuickBooks.
 2. The part-of-a-unit sale has been made and invoiced — a ZZAUTOTEST part sold in a quantity such as 2.5, at a known unit cost such as $10.00.
 3. You can sign in to that QuickBooks company and look at its journal entries.</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>1. Write down the quantity sold and the part's unit cost, and work out the correct amount by hand (2.5 x $10.00 = $25.00).
 2. Let the invoice go across to QuickBooks the normal way the shop does it.
@@ -3976,7 +4029,7 @@
 5. Go back to the Parts Velocity report and read the same part's Units Sold value.</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t>1. The QuickBooks amount is exactly the hand-worked figure to the cent — $25.00 for 2.5 at $10.00.
 2. It is NOT a whole-unit amount such as $20.00 or $30.00, and it is NOT a bigger, multiplied figure.
@@ -3984,13 +4037,13 @@
 4. No second or correcting journal entry is created to patch up a wrong amount.</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>SV-8589 (verbatim Tests: 'QB journal amount exact from fractional movement'; Goal: 'QB journal-entry sync multiplies these into dollar amounts'; tech-plan-2026-07-29 Phase 0 / PR-1 D2 - no report spec covers QuickBooks)</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr"/>
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/Report-Suite_Parts-Velocity-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Parts-Velocity-Report_testrail-import.xlsx
@@ -525,7 +525,9 @@
         <is>
           <t>1. A Parts section heading exists in the Reports navigation (this feature creates it - the application had no Parts reports before).
 2. Under Parts there is an entry labeled Parts Velocity; Inventory Value also lives under Parts. The order of the two inside the Parts section is not fixed — do not fail the test on which of them comes first.
-3. Clicking it opens the Parts Velocity report.</t>
+3. Clicking it opens the Parts Velocity report.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S1-R1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -573,12 +575,14 @@
         <is>
           <t>1. The date range selector shows This Year.
 2. Report data loads automatically - you do not have to press anything to fetch it.
-3. Rows appear ranked by Demand, highest first (the default order).</t>
+3. Rows appear ranked by Demand, highest first (the default order).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S1-R2, S4-R6).</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>SV-8641 (specs/parts-velocity.md S1-R2; S4-R6)</t>
+          <t>SV-8641 (PV spec v4 2026-07-29 S1-R2; S4-R6)</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -622,12 +626,14 @@
         <is>
           <t>1. During the initial load, the table shows a loading indicator.
 2. During a filter change, the loading indicator shows again.
-3. The rows already on screen are replaced only when the new data comes back - the table does not blank out and rebuild mid-request.</t>
+3. The rows already on screen are replaced only when the new data comes back - the table does not blank out and rebuild mid-request.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S1-R3).</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>SV-8641 (specs/parts-velocity.md S1-R3)</t>
+          <t>SV-8641 (PV spec v4 2026-07-29 S1-R3)</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
@@ -672,7 +678,9 @@
         <is>
           <t>1. The report data loads and rows are shown.
 2. The export downloads successfully — both opening the report and exporting it are allowed by the same ordinary reports access.
-3. Note for the tester: for now ONE ordinary reports access opens all six of these new reports; none of them has a permission of its own. If the build demands a separate report permission before this works, mark this Failed and report it — do not change the test.</t>
+3. Note for the tester: for now ONE ordinary reports access opens all six of these new reports; none of them has a permission of its own. If the build demands a separate report permission before this works, mark this Failed and report it — do not change the test.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S1-R4); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -718,12 +726,14 @@
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>1. The user cannot reach the Reports section.
-2. The Parts Velocity navigation entry is not shown (this is the Reports section's own access control, not a report-specific rule).</t>
+2. The Parts Velocity navigation entry is not shown (this is the Reports section's own access control, not a report-specific rule).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S1-N1).</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>SV-8641 (specs/parts-velocity.md S1-N1)</t>
+          <t>SV-8641 (PV spec v4 2026-07-29 S1-N1)</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
@@ -768,7 +778,9 @@
           <t>1. The Parts Velocity entry is visible in the Reports navigation under Parts.
 2. Opening it shows the report data - not an access-denied screen.
 3. The export downloads.
-4. Note for the tester: for now ONE ordinary reports access opens all six of these new reports, and no report has a permission of its own. If an extra Parts or Inventory reports permission does exist and switching it OFF blocks this report or its export, that is wrong - mark this Failed and report it. If a separate per-report permission is ever added on purpose in a later release, this test will be updated first, so treat that as a planned change and not as a bug.</t>
+4. Note for the tester: for now ONE ordinary reports access opens all six of these new reports, and no report has a permission of its own. If an extra Parts or Inventory reports permission does exist and switching it OFF blocks this report or its export, that is wrong - mark this Failed and report it. If a separate per-report permission is ever added on purpose in a later release, this test will be updated first, so treat that as a planned change and not as a bug.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S1-N2, S1-R4); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -821,7 +833,9 @@
 2. It is single-select and offers exactly three choices: Both, Inventory, and Special Order (special-order catalog parts that were never put into stock).
 3. On a first visit the default is Both.
 4. Both is an explicit selection returning inventory and Special Order rows together - a deliberate filter value, not the absence of a filter.
-5. Each selection immediately reloads the report limited to that type (no separate Apply step) - under Inventory every row's Type column reads Inventory; under Special Order every row's Type column reads Special Order; under Both, rows of both kinds appear.</t>
+5. Each selection immediately reloads the report limited to that type (no separate Apply step) - under Inventory every row's Type column reads Inventory; under Special Order every row's Type column reads Special Order; under Both, rows of both kinds appear.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R1, S3-R5); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -869,7 +883,9 @@
           <t>1. The options are exactly: Today, Yesterday, This Week, Last Week, This Month, Last Month, This Year, Last Year, This Quarter, Last Quarter, Custom.
 2. There is NO 'All Time' option - the report always operates over a bounded date window (deliberate, per the spec's Out of Scope).
 3. Selecting a non-custom option immediately reloads the report data.
-4. The named ranges use the application's standard shared calendar boundaries (the same boundaries every report's date picker uses).</t>
+4. The named ranges use the application's standard shared calendar boundaries (the same boundaries every report's date picker uses).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R2).</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -919,12 +935,14 @@
           <t>1. A date picker opens requiring both a start and an end date.
 2. The report does not reload until both dates are valid; a start after the end is not accepted.
 3. With both valid dates selected, the data reloads for that range.
-4. A span wider than 366 days (counting both the start and end dates) is rejected - the selection is not applied.</t>
+4. A span wider than 366 days (counting both the start and end dates) is rejected - the selection is not applied.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R3).</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>SV-8642 (specs/parts-velocity.md S2-R3)</t>
+          <t>SV-8642 (PV spec v4 2026-07-29 S2-R3)</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
@@ -969,12 +987,14 @@
           <t>1. Both filters allow selecting more than one value (multi-select).
 2. With categories selected, only parts in any of the selected categories are shown.
 3. With vendors selected, only parts supplied by any of the selected vendors are shown.
-4. Each change reloads the data from the server.</t>
+4. Each change reloads the data from the server.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R4, S2-R5, S2-R10).</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>SV-8642 (specs/parts-velocity.md S2-R4; S2-R5; S2-R10)</t>
+          <t>SV-8642 (PV spec v4 2026-07-29 S2-R4; S2-R5; S2-R10)</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
@@ -1020,12 +1040,14 @@
           <t>1. The search input is part of the report's toolbar (page-specific), separate from the global search bar.
 2. The part-number search matches despite the different letter case (case-insensitive 'contains' match).
 3. The description search returns rows whose description contains the word.
-4. Category and vendor names are NOT searched - use their dedicated filters instead (deliberate, to avoid false matches on common words).</t>
+4. Category and vendor names are NOT searched - use their dedicated filters instead (deliberate, to avoid false matches on common words).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R6).</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>SV-8642 (specs/parts-velocity.md S2-R6; §3 Key Decisions)</t>
+          <t>SV-8642 (PV spec v4 2026-07-29 S2-R6; §3 Key Decisions)</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
@@ -1070,12 +1092,14 @@
         <is>
           <t>1. After steps 1-2 the part is still listed (it satisfies both filters).
 2. After step 3 the part disappears - a part must satisfy EVERY active filter to appear (AND logic, not OR).
-3. After step 4 the part is listed again.</t>
+3. After step 4 the part is listed again.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R7).</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>SV-8642 (specs/parts-velocity.md S2-R7)</t>
+          <t>SV-8642 (PV spec v4 2026-07-29 S2-R7)</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
@@ -1118,12 +1142,14 @@
         <is>
           <t>1. Each selection reloads the data from the server.
 2. Only inventory parts stocked in ANY of the selected bins are shown.
-3. The filter allows more than one bin (multi-select).</t>
+3. The filter allows more than one bin (multi-select).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R8).</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>SV-8642 (specs/parts-velocity.md S2-R8)</t>
+          <t>SV-8642 (PV spec v4 2026-07-29 S2-R8)</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
@@ -1166,7 +1192,9 @@
       <c r="G15" s="2" t="inlineStr">
         <is>
           <t>1. With any Bin filter active, ALL Special Order rows are excluded (they have no bin location).
-2. Special Order combined with any Bin filter yields an empty result showing the empty state - this is by design, not a defect.</t>
+2. Special Order combined with any Bin filter yields an empty result showing the empty state - this is by design, not a defect.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R8); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1221,7 +1249,9 @@
 4. Each selection reloads the data scoped to the chosen set; 'All Locations' means all locations the user can ACCESS, never beyond - a location the user cannot access is never included.
 5. The location scope cascades through every metric like the other filters.
 6. With 'All Locations' active you can tell which location each row's data belongs to — a location label or marking is shown. (Exactly where and how it appears is confirmed in the build.)
-7. The page itself shows which location(s) the report is currently scoped to (the new on-screen scope indicator - exactly where and how it appears is confirmed in the build).</t>
+7. The page itself shows which location(s) the report is currently scoped to (the new on-screen scope indicator - exactly where and how it appears is confirmed in the build).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R9); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1267,7 +1297,9 @@
       <c r="G17" s="2" t="inlineStr">
         <is>
           <t>1. The server returns zero rows and the table shows the empty state.
-2. The empty-state label reads exactly: "Empty bays, endless possibilities. Get Going!" (the application's standard reports no-data label).</t>
+2. The empty-state label reads exactly: "Empty bays, endless possibilities. Get Going!" (the application's standard reports no-data label).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R11, S2-N1).</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1317,12 +1349,14 @@
         <is>
           <t>1. The part with no category does not appear when any Category filter is active.
 2. The part with no vendor does not appear when any Vendor filter is active.
-3. The inventory part with no bin location does not appear when any Bin filter is active.</t>
+3. The inventory part with no bin location does not appear when any Bin filter is active.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-E1, S2-E2, S2-E3).</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>SV-8642 (specs/parts-velocity.md S2-E1; S2-E2; S2-E3)</t>
+          <t>SV-8642 (PV spec v4 2026-07-29 S2-E1; S2-E2; S2-E3)</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
@@ -1364,7 +1398,9 @@
       <c r="G19" s="2" t="inlineStr">
         <is>
           <t>1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
-2. For the user with access to two or more locations the Location filter IS shown.</t>
+2. For the user with access to two or more locations the Location filter IS shown.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-E4); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1409,8 +1445,7 @@
 3. Read the Location cell on the merged Special Order row.
 4. Open the column picker and look for Location in the list.
 5. Narrow to a single location and read the headers again.
-6. Change the selection between one location, several, and "All Locations", watching the filter control's width.
-7. With more than one location still selected, download the CSV and the PDF and read their columns from the left.</t>
+6. With more than one location still selected, download the CSV and the PDF and read their columns from the left.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1420,8 +1455,9 @@
 3. The merged Special Order row shows "Multiple", because it is summed across the selected locations.
 4. Location is NOT one of the 20 columns in the picker — it is managed by the location scope, not by you.
 5. With a single location in scope the Location column is hidden.
-6. The Location filter control keeps the same width whichever label it shows — one location, several, or "All locations" — so the toolbar does not shift as you change the selection.
-7. Both downloads include the Location column in the same position it holds on screen (leftmost, before Type), with the same values — each inventory row's own location, and "Multiple" on the merged Special Order row.</t>
+6. Both downloads include the Location column in the same position it holds on screen (leftmost, before Type), with the same values — each inventory row's own location, and "Multiple" on the merged Special Order row.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R12, S3-R10, S7-R8, S6-R11).</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1469,12 +1505,14 @@
         <is>
           <t>1. The part appears as TWO inventory rows - one per selected location (an inventory part is a per-location stock record).
 2. Each row carries only that one location's On Hand, Min, and Max.
-3. On Hand / Min / Max are NEVER summed across locations.</t>
+3. On Hand / Min / Max are NEVER summed across locations.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S3-R1a).</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>SV-8643 (specs/parts-velocity.md S3-R1a; §3 Key Decisions)</t>
+          <t>SV-8643 (PV spec v4 2026-07-29 S3-R1a; §3 Key Decisions)</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
@@ -1518,12 +1556,14 @@
         <is>
           <t>1. The special-order part appears as a SINGLE row (one row per special-order part, merged across the selected locations).
 2. Its movement and profitability values are the SUM of the per-location values.
-3. Its inventory-only columns (On Hand, Turns / Yr, Min, Max) show — (em-dash), because special-order parts are not stocked.</t>
+3. Its inventory-only columns (On Hand, Turns / Yr, Min, Max) show — (em-dash), because special-order parts are not stocked.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S3-R1a).</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>SV-8643 (specs/parts-velocity.md S3-R1a; §3 Key Decisions)</t>
+          <t>SV-8643 (PV spec v4 2026-07-29 S3-R1a; §3 Key Decisions)</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
@@ -1569,12 +1609,14 @@
           <t>1. Rows are ranked by Demand, descending - the most-active parts first.
 2. Inventory and special-order rows are ranked together in one list.
 3. Rows with equal Demand keep inventory-before-special-order order.
-4. The Demand header shows the descending sort indicator - this initial order IS the active sort (it is what the remembered view saves until you click another header).</t>
+4. The Demand header shows the descending sort indicator - this initial order IS the active sort (it is what the remembered view saves until you click another header).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S3-R2).</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>SV-8643 (specs/parts-velocity.md S3-R2)</t>
+          <t>SV-8643 (PV spec v4 2026-07-29 S3-R2)</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
@@ -1620,12 +1662,14 @@
           <t>1. The first click sorts that column ASCENDING; the header shows a direction indicator (an arrow).
 2. Clicking the active sort column again reverses the direction; the arrow flips.
 3. Null / — values are placed FIRST on ascending and LAST on descending.
-4. Every column is sortable; each header click re-fetches the data (server-resolved) and shows the first page of the re-sorted result; ties keep a stable order.</t>
+4. Every column is sortable; each header click re-fetches the data (server-resolved) and shows the first page of the re-sorted result; ties keep a stable order.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S3-R3).</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>SV-8643 (specs/parts-velocity.md S3-R3)</t>
+          <t>SV-8643 (PV spec v4 2026-07-29 S3-R3)</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
@@ -1668,7 +1712,9 @@
         <is>
           <t>1. The header row is sticky - it stays visible while the body scrolls.
 2. The Type column shows each row's kind as plain text (no badge or chip styling): "Inventory" or "Special Order".
-3. ALL columns - header and cell data, including numbers and money - are left-aligned on screen. (The exports right-align numerics instead: a deliberate export-only difference.)</t>
+3. ALL columns - header and cell data, including numbers and money - are left-aligned on screen. (The exports right-align numerics instead: a deliberate export-only difference.)
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S3-R4, S3-R5, S3-R8); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1721,7 +1767,9 @@
 3. Demand shows exactly: "Number of separate transactions (work orders or parts sales) this part appeared on in the selected date range. Each transaction counts once, no matter how many units were sold on it."
 4. Turns/Yr shows exactly: "How many times you sell through this part in a year. Higher is better."
 5. The icon is focusable and exposes the same text to assistive technology; activating it does NOT trigger a column sort.
-6. No other column header carries an info icon.</t>
+6. No other column header carries an info icon.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S3-R6).</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1772,12 +1820,13 @@
           <t>1. Long Description, Category, and Vendor text is truncated with an ellipsis on screen.
 2. The full value shows on native hover (browser tooltip).
 3. Part # is NEVER truncated - on screen (and in the exports).
-4. The CSV export carries the full untruncated Description / Category / Vendor values.</t>
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S3-R7).</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>SV-8643 (specs/parts-velocity.md S3-R7)</t>
+          <t>SV-8643 (PV spec v4 2026-07-29 S3-R7)</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
@@ -1813,21 +1862,20 @@
       <c r="F28" s="2" t="inlineStr">
         <is>
           <t>1. On the special-order row, read On Hand, Turns / Yr, Min, and Max.
-2. On the no-activity inventory row, read Units Sold, Units Returned, Sold (WO), Sold (Parts Sale), Demand, Revenue, and Margin.
-3. On the same row, read Unit Cost, Sell Price, Margin %, and Last Sale (assuming no billed units, no revenue, and no recorded sale ever).</t>
+2. On the no-activity inventory row, read Units Sold, Units Returned, Sold (WO), Sold (Parts Sale), Demand, Revenue, and Margin.</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
           <t>1. On Hand, Turns / Yr, Min, and Max show — (em-dash) on special-order rows - always.
 2. The count metrics and money totals are NEVER null: Units Sold / Units Returned / Sold (WO) / Sold (Parts Sale) show 0.00, Demand shows 0, Revenue and Margin show $0.00.
-3. Unit Cost and Sell Price show — when billed units are zero or less; Margin % shows — when Revenue is zero or less; Last Sale shows — when the row has no recorded sale.
-4. Every null renders as the same — (em-dash) glyph, in the table and in all exports.</t>
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S3-R9, S5-R5).</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>SV-8643 (specs/parts-velocity.md S3-R9; S5-R5)</t>
+          <t>SV-8643 (PV spec v4 2026-07-29 S3-R9; S5-R5)</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
@@ -1870,12 +1918,14 @@
         <is>
           <t>1. Part A does NOT appear - it fails all three keep-criteria (no movement, under one on hand, no revenue) so it carries nothing to act on.
 2. Part B DOES appear - a part with billed Revenue &gt; 0 is always kept even with no stock movement and no on-hand stock.
-3. (Special Order parts have no such rule: a never-requested special-order part simply produces no row.)</t>
+3. (Special Order parts have no such rule: a never-requested special-order part simply produces no row.)
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S3-N1).</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>SV-8643 (specs/parts-velocity.md S3-N1)</t>
+          <t>SV-8643 (PV spec v4 2026-07-29 S3-N1)</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
@@ -1918,12 +1968,14 @@
         <is>
           <t>1. Part C shows Demand 1 (the reversal does not decrement the Demand count) with Units Sold 0.00 (the reversal nets the movement to zero).
 2. Part D shows a NEGATIVE Units Sold with a leading minus (e.g. -3.00) - negative movement is not floored to zero.
-3. A fully-reversed part with zero net movement, no on-hand stock, and no residual revenue would be excluded altogether (a Demand count alone does not keep a row).</t>
+3. A fully-reversed part with zero net movement, no on-hand stock, and no residual revenue would be excluded altogether (a Demand count alone does not keep a row).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S3-E1, S5-R5).</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>SV-8643 (specs/parts-velocity.md S3-E1; S5-R5)</t>
+          <t>SV-8643 (PV spec v4 2026-07-29 S3-E1; S5-R5)</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
@@ -1965,12 +2017,14 @@
       <c r="G31" s="2" t="inlineStr">
         <is>
           <t>1. The picker lists all 20 available columns, each with a toggle: Type, Part #, Description, Category, Vendor, Units Sold, Units Returned, Sold (WO), Sold (Parts Sale), Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand, Turns/Yr, Min, Max.
-2. No on-hand cost column is offered - the report computes one internally but it is never selectable and never displayed.</t>
+2. No on-hand cost column is offered - the report computes one internally but it is never selectable and never displayed.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S4-R1, S4-R4, S5-R6).</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>SV-8644 (specs/parts-velocity.md S4-R1; S4-R4; S5-R6)</t>
+          <t>SV-8644 (PV spec v4 2026-07-29 S4-R1; S4-R4; S5-R6)</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
@@ -2011,7 +2065,9 @@
         <is>
           <t>1. With a single location in scope exactly these 14 columns show, in this left-to-right order: Type, Part #, Description, Category, Vendor, Units Sold, Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand.
 2. The other 6 columns start hidden: Units Returned, Sold (WO), Sold (Parts Sale), Turns / Yr, Min, Max.
-3. When more than one location is in scope the automatic Location column shows as well, leftmost before Type — 15 columns. It is not part of the 14-column default set and is not in the column picker, so its presence is expected and is not a failure of this test.</t>
+3. When more than one location is in scope the automatic Location column shows as well, leftmost before Type — 15 columns. It is not part of the 14-column default set and is not in the column picker, so its presence is expected and is not a failure of this test.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S4-R2, S4-R3, S3-R10).</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2059,7 +2115,9 @@
         <is>
           <t>1. Each toggle takes effect immediately - the table re-renders without a page reload.
 2. Columns always render in the fixed canonical left-to-right order regardless of the order they were toggled on (with the automatic Location column, when shown, sitting leftmost before Type): Type, Part #, Description, Category, Vendor, Units Sold, Units Returned, Sold (WO), Sold (Parts Sale), Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand, Turns/Yr, Min, Max.
-3. So Units Returned slots in right after Units Sold, Turns/Yr after On Hand, and Min before Max - not appended at the end.</t>
+3. So Units Returned slots in right after Units Sold, Turns/Yr after On Hand, and Min before Max - not appended at the end.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S4-R4, S4-R5, S3-R10).</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2108,12 +2166,14 @@
           <t>1. On return, every saved setting is restored: Type = Inventory, Last Month, the chosen category, the column set including Turns / Yr, and the Revenue-descending sort.
 2. The saved values are applied BEFORE the first data fetch - the report does not flash the defaults and then re-query.
 3. The saved values take precedence over the first-visit defaults (This Year / Both / active location / 14 columns / Demand-descending).
-4. The same holds after a full page reload.</t>
+4. The same holds after a full page reload.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S4-R6, S1-R2).</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>SV-8644 (specs/parts-velocity.md S4-R6; S1-R2)</t>
+          <t>SV-8644 (PV spec v4 2026-07-29 S4-R6; S1-R2)</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
@@ -2155,12 +2215,14 @@
         <is>
           <t>1. The invalid saved value is NOT sent to the server.
 2. That one setting falls back to its default (e.g. the location falls back to the active location); the other saved settings still restore normally.
-3. The report loads without an error.</t>
+3. The report loads without an error.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S4-R6).</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>SV-8644 (specs/parts-velocity.md S4-R6)</t>
+          <t>SV-8644 (PV spec v4 2026-07-29 S4-R6)</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
@@ -2202,12 +2264,14 @@
       <c r="G36" s="2" t="inlineStr">
         <is>
           <t>1. User 2 sees user 1's saved view (Type = Special Order, Last Quarter, the saved columns and sort).
-2. This is by design: storage is per browser, not tied to the account - there is no per-account separation.</t>
+2. This is by design: storage is per browser, not tied to the account - there is no per-account separation.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S4-R6).</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>SV-8644 (specs/parts-velocity.md S4-R6)</t>
+          <t>SV-8644 (PV spec v4 2026-07-29 S4-R6)</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
@@ -2250,12 +2314,14 @@
         <is>
           <t>1. The picker enforces no minimum - all 20 columns can be switched off, leaving a grid with no data columns for the rest of the session.
 2. The export produces a file containing only the header/metadata rows and no data columns.
-3. On the next visit the all-hidden selection is NOT restored - the report falls back to the default 14-column set (the saved column selection returns to the last NON-EMPTY selection; all-hidden is the exception).</t>
+3. On the next visit the all-hidden selection is NOT restored - the report falls back to the default 14-column set (the saved column selection returns to the last NON-EMPTY selection; all-hidden is the exception).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S4-E1, S4-R6).</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>SV-8644 (specs/parts-velocity.md S4-E1; S4-R6)</t>
+          <t>SV-8644 (PV spec v4 2026-07-29 S4-E1; S4-R6)</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
@@ -2300,12 +2366,14 @@
           <t>1. After step 1, Units Sold increases by 5.00 (invoicing a work order adds the units sold - a stock-movement event).
 2. After step 2, Units Sold decreases by 2.00 (reversing/voiding an invoice adds stock back and is subtracted - Units Sold is net of invoice reversals).
 3. After step 3, Units Sold is UNCHANGED - part returns do not affect Units Sold (they feed Units Returned instead).
-4. Units Sold can be 0.00 or negative when reversals exceed sales.</t>
+4. Units Sold can be 0.00 or negative when reversals exceed sales.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R1, S5-R4).</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>SV-8645 (specs/parts-velocity.md S5-R1; S5-R4 (Units Sold; inventory); §4)</t>
+          <t>SV-8645 (PV spec v4 2026-07-29 S5-R1; S5-R4 (Units Sold; inventory); §4)</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
@@ -2348,12 +2416,14 @@
         <is>
           <t>1. Units Sold equals the total quantity across the part's in-window vendor requests (3 + 2 = 5.00 in the example), summed across the selected locations.
 2. The reversed/voided sale is EXCLUDED from the total (net of reversals).
-3. Only requests on work orders at status Invoiced or Paid count; the window is anchored to the work-order date.</t>
+3. Only requests on work orders at status Invoiced or Paid count; the window is anchored to the work-order date.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R2, S5-R4, S5-R4b).</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>SV-8645 (specs/parts-velocity.md S5-R2; S5-R4 (Units Sold; catalogue); S5-R4b)</t>
+          <t>SV-8645 (PV spec v4 2026-07-29 S5-R2; S5-R4 (Units Sold; catalogue); S5-R4b)</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
@@ -2399,12 +2469,14 @@
           <t>1. After step 1, Units Returned increases by 2.00 (the return record is counted when the return is initiated).
 2. After step 2, it increases by 1.00 more (a parts-sale credit also creates a part-return record).
 3. After step 3, it decreases by 2.00 - the column reflects the CURRENT state of return records (cancelled returns are excluded), not a snapshot.
-4. After step 4, Units Returned is UNCHANGED - invoice reversals are not returns (they affect Units Sold instead).</t>
+4. After step 4, Units Returned is UNCHANGED - invoice reversals are not returns (they affect Units Sold instead).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R3, S5-R4).</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>SV-8645 (specs/parts-velocity.md S5-R3; S5-R4 (Units Returned); §3 Key Decisions)</t>
+          <t>SV-8645 (PV spec v4 2026-07-29 S5-R3; S5-R4 (Units Returned); §3 Key Decisions)</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
@@ -2451,12 +2523,14 @@
 2. In the previous window the return does not count (only the sale's own metrics do).
 3. Core-charge returns are EXCLUDED from Units Returned.
 4. Units Returned is independent of the work order's current invoice status.
-5. A part whose ONLY in-window event is a return (no sale, no stock, no revenue) produces no row at all - accepted behavior, the row axis is sales/stock activity.</t>
+5. A part whose ONLY in-window event is a return (no sale, no stock, no revenue) produces no row at all - accepted behavior, the row axis is sales/stock activity.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R3).</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>SV-8645 (specs/parts-velocity.md S5-R3)</t>
+          <t>SV-8645 (PV spec v4 2026-07-29 S5-R3)</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
@@ -2501,12 +2575,14 @@
           <t>1. Sold (WO) shows the total part quantity on Service-type invoiced/paid work orders whose work-order date is in the window (4.00 in the example), net of reversed/voided sales.
 2. Sold (Parts Sale) shows the total on Parts-type invoiced/paid work orders (counter sales) in the window (3.00), net of reversed/voided sales.
 3. Both are windowed by the WORK-ORDER date (its end date) - with the range moved off those dates, both drop out.
-4. Both workflows feed the report - a parts sale is a separate workflow from a service work order but counts fully.</t>
+4. Both workflows feed the report - a parts sale is a separate workflow from a service work order but counts fully.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R4).</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>SV-8645 (specs/parts-velocity.md S5-R4 (Sold via WO / Sold via Parts Sale); §5 Assumptions)</t>
+          <t>SV-8645 (PV spec v4 2026-07-29 S5-R4 (Sold via WO / Sold via Parts Sale); §5 Assumptions)</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
@@ -2552,12 +2628,14 @@
           <t>1. The inventory part's Demand is 2 - each stock-decrementing invoicing event counts ONCE no matter how many units were on it (1 unit and 10 units each count as one).
 2. After the reversal, Demand is STILL 2 - a reversal event neither adds to nor subtracts from the count (while Units Sold nets down).
 3. The special-order part's Demand is 2 - the count of its in-window vendor part requests.
-4. Demand is the report's default ranking signal (a whole number, never null - 0 when none).</t>
+4. Demand is the report's default ranking signal (a whole number, never null - 0 when none).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R4).</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>SV-8645 (specs/parts-velocity.md S5-R4 (Demand); §4; §3 Key Decisions)</t>
+          <t>SV-8645 (PV spec v4 2026-07-29 S5-R4 (Demand); §4; §3 Key Decisions)</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
@@ -2605,12 +2683,14 @@
 2. It IS scoped to the selected location(s): with only location B selected, Last Sale reflects B's own most recent sale.
 3. Format is 'N days' (e.g. 42 days); a part with no recorded sale ever shows —.
 4. For a special-order part, the anchor is its most recent vendor-sourced invoiced/paid request.
-5. When the most recent sale is reversed, Last Sale re-anchors to the previous remaining sale (the day count grows accordingly); if no other sale remains it shows —.</t>
+5. When the most recent sale is reversed, Last Sale re-anchors to the previous remaining sale (the day count grows accordingly); if no other sale remains it shows —.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R4, S5-R5).</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>SV-8645 (specs/parts-velocity.md S5-R4 (Last Sale); §4; S5-R5; tech-plan-2026-07-29 B3.1 (last-sale re-anchor on reversal — spec-silent))</t>
+          <t>SV-8645 (PV spec v4 2026-07-29 S5-R4 (Last Sale); §4; S5-R5; tech-plan-2026-07-29 B3.1 (last-sale re-anchor on reversal — spec-silent))</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
@@ -2653,12 +2733,14 @@
         <is>
           <t>1. On Hand equals the part's CURRENT on-hand quantity at that row's location (never summed across locations).
 2. Min and Max show the stored minimum / maximum reorder thresholds for that location, as whole numbers (— when not set).
-3. Min and Max are READ-ONLY display columns - no edit control or slide-over opens; editing part attributes from this report is out of scope in this version.</t>
+3. Min and Max are READ-ONLY display columns - no edit control or slide-over opens; editing part attributes from this report is out of scope in this version.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R4, S5-R5).</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>SV-8645 (specs/parts-velocity.md S5-R4 (On Hand / Min / Max); §2 Out of Scope; S5-R5)</t>
+          <t>SV-8645 (PV spec v4 2026-07-29 S5-R4 (On Hand / Min / Max); §2 Out of Scope; S5-R5)</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
@@ -2705,12 +2787,15 @@
           <t>1. Part A's Turns / Yr matches the formula (two decimals, e.g. 24.33); the window is the whole-day span inclusive of both dates with a floor of 1 day.
 2. Part B shows 0.00 (renders 0.00 when On Hand is 0 - not an error, not —).
 3. Part C shows a NEGATIVE Turns / Yr with a leading minus (because Units Sold can be negative).
-4. Special Order rows always show — (not applicable).</t>
+4. Special Order rows always show — (not applicable).
+Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8819
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R4).</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>SV-8645 (specs/parts-velocity.md S5-R4 (Turns / Yr); S5 Definitions (Window))</t>
+          <t>SV-8645 (PV spec v4 2026-07-29 S5-R4 (Turns / Yr); S5 Definitions (Window))</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
@@ -2756,12 +2841,14 @@
 3. Unit Cost = COGS ÷ billed units; Sell Price = Revenue ÷ billed units.
 4. Margin % = (Revenue − COGS) ÷ Revenue × 100, shown to one decimal.
 5. All five are computed from the RAW (unrounded) Revenue / COGS / billed-units totals and rounded ONCE at the end - not built from already-rounded intermediates.
-6. The same formulas apply to inventory and special-order rows (for special-order, from the vendor part requests).</t>
+6. The same formulas apply to inventory and special-order rows (for special-order, from the vendor part requests).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R4a).</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>SV-8645 (specs/parts-velocity.md S5-R4a; §4)</t>
+          <t>SV-8645 (PV spec v4 2026-07-29 S5-R4a; §4)</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
@@ -2805,12 +2892,14 @@
         <is>
           <t>1. After the reversal, ALL the billed-line columns drop to reflect only the remaining sale - the reversed/voided sale is excluded from Revenue, Margin, Unit Cost, Sell Price, Margin %, Sold (WO), Sold (Parts Sale), and (for special-order) Units Sold.
 2. This netting is consistent with inventory Units Sold, which already nets reversals via the stock add-back.
-3. A voided sale therefore inflates NO column.</t>
+3. A voided sale therefore inflates NO column.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R4b, S5-R4a).</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>SV-8645 (specs/parts-velocity.md S5-R4b; S5-R4a; §3 Key Decisions)</t>
+          <t>SV-8645 (PV spec v4 2026-07-29 S5-R4b; S5-R4a; §3 Key Decisions)</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
@@ -2856,12 +2945,14 @@
           <t>1. Row 1: Unit Cost and Sell Price show — (billed units ≤ 0) while Revenue and Margin show dollar amounts AND Margin % is still computed from Revenue - a valid mixed row, not a defect.
 2. Row 2: Sell Price shows $0.00 (a number) while Margin % shows — (Revenue ≤ 0) - also valid.
 3. Row 3: Unit Cost, Sell Price, and Margin % all show — together - which happens ONLY when both billed units ≤ 0 AND Revenue ≤ 0.
-4. The three triggers are independent: Unit Cost/Sell Price null on billed units ≤ 0; Margin % null on Revenue ≤ 0.</t>
+4. The three triggers are independent: Unit Cost/Sell Price null on billed units ≤ 0; Margin % null on Revenue ≤ 0.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R4a, S3-R9).</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>SV-8645 (specs/parts-velocity.md S5-R4a (null rules + mixed-row paragraph); S3-R9)</t>
+          <t>SV-8645 (PV spec v4 2026-07-29 S5-R4a (null rules + mixed-row paragraph); S3-R9)</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
@@ -2905,12 +2996,14 @@
 2. Unit Cost, Sell Price, Revenue, Margin: currency with $, two decimals, thousands separators ($1,250.00); negatives with a leading minus and NO parentheses (-$45.00).
 3. Margin %: one decimal with a trailing % (33.8%); negatives with a leading minus, no + on positives (-8.4%).
 4. Demand: whole number. Min, Max: whole numbers (— when null). Last Sale: 'N days' (42 days), — when null.
-5. Rounding is half AWAY from zero: 8.45% displays 8.5% and -8.45% displays -8.5% (a tie rounds up in magnitude); this applies to all money and one-decimal values.</t>
+5. Rounding is half AWAY from zero: 8.45% displays 8.5% and -8.45% displays -8.5% (a tie rounds up in magnitude); this applies to all money and one-decimal values.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R5, S5-R7).</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>SV-8645 (specs/parts-velocity.md S5-R5; S5-R7 (rounding))</t>
+          <t>SV-8645 (PV spec v4 2026-07-29 S5-R5; S5-R7 (rounding))</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
@@ -2953,12 +3046,14 @@
         <is>
           <t>1. The inventory core part does NOT appear in the report despite its activity and stock.
 2. The special-order core part does NOT appear either.
-3. Parts flagged as a core are excluded from both result sets by design.</t>
+3. Parts flagged as a core are excluded from both result sets by design.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R1, S5-R2).</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>SV-8645 (specs/parts-velocity.md S5-R1; S5-R2; §3 Key Decisions)</t>
+          <t>SV-8645 (PV spec v4 2026-07-29 S5-R1; S5-R2; §3 Key Decisions)</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
@@ -3003,12 +3098,14 @@
         <is>
           <t>1. On the inventory row, Units Sold (stock movement) DIFFERS from the billed units behind Revenue/Sell Price - this is CORRECT behavior, not a defect (the Units Sold tooltip calls it out).
 2. Sold (WO) + Sold (Parts Sale) together DO equal the billed-units basis (work orders are only Service- or Parts-type) - but neither equals the movement-based Units Sold.
-3. On the special-order row, everything reconciles: Units Sold = Sold (WO) + Sold (Parts Sale) = billed units (they share the vendor-request quantity as one source).</t>
+3. On the special-order row, everything reconciles: Units Sold = Sold (WO) + Sold (Parts Sale) = billed units (they share the vendor-request quantity as one source).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R7).</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>SV-8645 (specs/parts-velocity.md S5-R7; §3 Key Decisions)</t>
+          <t>SV-8645 (PV spec v4 2026-07-29 S5-R7; §3 Key Decisions)</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
@@ -3053,12 +3150,15 @@
           <t>1. In W1 (work-order date in window): the billed columns (Revenue, Margin, Unit Cost, Sell Price, Margin %, Sold (WO), Sold (Parts Sale)) count the sale, while inventory Units Sold / Demand do NOT (their movement event is outside W1).
 2. In W2 (movement date in window): Units Sold / Demand count it, the billed columns do not - the two anchors CAN differ for an inventory part and that is intended.
 3. The window is the whole-day span inclusive of BOTH the start and end dates, with a floor of 1 day - a single-day range (Today) computes normally (Window = 1 for the Turns / Yr divisor).
-4. Last Sale is not windowed at all (all-time).</t>
+4. Last Sale is not windowed at all (all-time).
+Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8819
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R7).</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>SV-8645 (specs/parts-velocity.md S5 Definitions (Window / Work-order date); S5-R7)</t>
+          <t>SV-8645 (PV spec v4 2026-07-29 S5 Definitions (Window / Work-order date); S5-R7)</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
@@ -3106,7 +3206,9 @@
           <t>1. Units Sold reads exactly 2.50 — not 2.00, not 3.00, not blank and not a dash.
 2. It still reads exactly 2.50 after the sign-out and sign-back-in, which proves the part-of-a-unit quantity was really stored and not just shown once.
 3. On Hand has gone down by exactly 2.50 from what it was before the sale.
-4. No value anywhere on the row has been quietly rounded to a whole number.</t>
+4. No value anywhere on the row has been quietly rounded to a whole number.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R1, S5-R5).</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3152,7 +3254,9 @@
       <c r="G55" s="2" t="inlineStr">
         <is>
           <t>1. The ⋯ overflow button sits leftmost in the toolbar's action cluster.
-2. The menu holds exactly two items, in this order: Download (PDF), then Download (CSV).</t>
+2. The menu holds exactly two items, in this order: Download (PDF), then Download (CSV).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S6-R1).</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3200,7 +3304,9 @@
         <is>
           <t>1. Both files contain only the rows matching the date range, type, category, vendor, bin, location, and search active at export time - not a full unfiltered dump.
 2. The exported rows match what the on-screen grid was showing.
-3. Each file (PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to (exact position in the file is confirmed in the build).</t>
+3. Each file (PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to (exact position in the file is confirmed in the build).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S6-R2, S6-R11); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3248,12 +3354,14 @@
         <is>
           <t>1. Both exports contain ONLY the currently enabled columns - the hidden ones are absent.
 2. Columns appear in the CANONICAL order (the fixed on-screen order) - the re-enabled Units Returned sits right after Units Sold, NOT appended at the end.
-3. The export mirrors the visible grid.</t>
+3. The export mirrors the visible grid.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S6-R3, S4-R4).</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>SV-8646 (specs/parts-velocity.md S6-R3; S4-R4)</t>
+          <t>SV-8646 (PV spec v4 2026-07-29 S6-R3; S4-R4)</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr"/>
@@ -3297,12 +3405,14 @@
         <is>
           <t>1. The default Demand-descending order is exported when the user has not chosen another column.
 2. Every column's sort is honored in the export - including Min and Max.
-3. The export renders the EXACT server order, including null placement (nulls first on ascending, last on descending) - the export and the on-screen grid match; there is no on-screen-vs-export null-sorting difference.</t>
+3. The export renders the EXACT server order, including null placement (nulls first on ascending, last on descending) - the export and the on-screen grid match; there is no on-screen-vs-export null-sorting difference.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S6-R4, S3-R3).</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>SV-8646 (specs/parts-velocity.md S6-R4; S3-R3)</t>
+          <t>SV-8646 (PV spec v4 2026-07-29 S6-R4; S3-R3)</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
@@ -3347,12 +3457,14 @@
 2. The PDF is formatted for A3 landscape and titled Parts Velocity.
 3. Description, Category, and Vendor are truncated to 18 characters in the PDF.
 4. Part # is NOT truncated.
-5. The shop logo shows at the top of the PDF when one is set. With no uploaded logo the PDF shows the bundled ShopView default logo instead of a blank space, the same as the other reports in this suite. The CSV never includes a logo.</t>
+5. The shop logo shows at the top of the PDF when one is set. With no uploaded logo the PDF shows the bundled ShopView default logo instead of a blank space, the same as the other reports in this suite. The CSV never includes a logo.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S6-R5, S6-R6).</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>SV-8646 (specs/parts-velocity.md S6-R5; S6-R6 + same-logo-treatment for every report per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source; last-update-wins))</t>
+          <t>SV-8646 (PV spec v4 2026-07-29 S6-R5; S6-R6 + same-logo-treatment for every report per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source; last-update-wins))</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr"/>
@@ -3395,12 +3507,14 @@
         <is>
           <t>1. The file downloads as velocity-report.csv.
 2. The CSV carries the FULL, untruncated Description / Category / Vendor values (unlike the PDF's 18-character cut).
-3. Last Sale is a raw integer in the CSV (e.g. 42) - the 'N days' wording is PDF/on-screen only.</t>
+3. Last Sale is a raw integer in the CSV (e.g. 42) - the 'N days' wording is PDF/on-screen only.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S6-R5, S6-R6, S6-R8).</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>SV-8646 (specs/parts-velocity.md S6-R5; S6-R6; S6-R8)</t>
+          <t>SV-8646 (PV spec v4 2026-07-29 S6-R5; S6-R6; S6-R8)</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
@@ -3436,20 +3550,20 @@
       <c r="F61" s="2" t="inlineStr">
         <is>
           <t>1. Download the CSV and locate the null cells.
-2. Download the PDF and locate the same cells.
-3. In the PDF, read a non-null Last Sale value.</t>
+2. Download the PDF and locate the same cells.</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
           <t>1. A null value renders as — (em-dash) in BOTH the CSV and the PDF, in every nullable field: Unit Cost, Sell Price, Margin %, On Hand, Turns / Yr, Last Sale, Min, Max.
 2. Revenue, Margin, and the count metrics are never null in the exports either ($0.00 / 0.00 / 0).
-3. In the PDF, Last Sale renders as 'N days' (e.g. 42 days).</t>
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S6-R7, S6-R8, S3-R9).</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>SV-8646 (specs/parts-velocity.md S6-R7; S6-R8; S3-R9)</t>
+          <t>SV-8646 (PV spec v4 2026-07-29 S6-R7; S6-R8; S3-R9)</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr"/>
@@ -3493,12 +3607,14 @@
 2. In the PDF, the text columns (Part #, Description, Category, Vendor) are left-aligned.
 3. In the PDF, EVERY numeric and money column is right-aligned.
 4. This is a deliberate export-only treatment - the on-screen table is all-left-aligned; the difference is documented, not a defect.
-5. The CSV is plain data — the alignment assertions apply to the PDF only; how a spreadsheet displays the CSV is not part of this test.</t>
+5. The CSV is plain data — the alignment assertions apply to the PDF only; how a spreadsheet displays the CSV is not part of this test.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S6-R10, S3-R8).</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>SV-8646 (specs/parts-velocity.md S6-R10; S3-R8)</t>
+          <t>SV-8646 (PV spec v4 2026-07-29 S6-R10; S3-R8)</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr"/>
@@ -3542,7 +3658,9 @@
         <is>
           <t>1. On success the toasts read exactly "Velocity report exported (CSV)" / "Velocity report exported (PDF)" and auto-fade — UPPERCASE (CSV)/(PDF).
 2. An error toast is shown on failure; when the server provides a message, that server message is shown.
-3. Otherwise the failure toast reads exactly: "Failed to export velocity report (csv)" or "Failed to export velocity report (pdf)" — lowercase (csv)/(pdf); the success/failure casing mix is the shipped wording, documented as-is (not a bug).</t>
+3. Otherwise the failure toast reads exactly: "Failed to export velocity report (csv)" or "Failed to export velocity report (pdf)" — lowercase (csv)/(pdf); the success/failure casing mix is the shipped wording, documented as-is (not a bug).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S6-R9, S6-N1).</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3592,12 +3710,15 @@
         <is>
           <t>1. Neither the CSV nor the PDF is produced — no download starts.
 2. A clear too-large message appears telling the user to narrow the date range or filters, then try again — the standard wording is "This report is too large to export. Narrow the date range or filters, then try again."
-3. After narrowing below the cap, the downloads work again.</t>
+3. After narrowing below the cap, the downloads work again.
+Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (Story 6 exports).</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>SV-8646 (specs/parts-velocity.md Story 6 exports — spec silent on a cap; tech-plan-2026-07-29 A3/FR-F4: suite-wide 10; 000-row export cap; locked by Chris 2026-07-21)</t>
+          <t>SV-8646 (PV spec v4 2026-07-29 Story 6 exports — spec silent on a cap; tech-plan-2026-07-29 A3/FR-F4: suite-wide 10; 000-row export cap; locked by Chris 2026-07-21)</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr"/>
@@ -3643,7 +3764,10 @@
           <t>1. The CSV downloads successfully at that size.
 2. The PDF also downloads successfully. If instead nothing downloads and a message appears saying something went wrong, that is a failure — record roughly how many rows were on screen.
 3. The small PDF downloads successfully, which shows the failure depends on size.
-4. Note for the tester: a very large view is refused politely with "This report is too large to export. Narrow the date range or filters, then try again." — that message is expected and is NOT this failure. This test is about a medium-sized view where the CSV works but the PDF errors.</t>
+4. Note for the tester: a very large view is refused politely with "This report is too large to export. Narrow the date range or filters, then try again." — that message is expected and is NOT this failure. This test is about a medium-sized view where the CSV works but the PDF errors.
+Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (Story 6 exports).</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3690,12 +3814,14 @@
         <is>
           <t>1. White card surfaces (toolbar + table cells) sit on the standard soft blue-grey page background (the application's two-tone report theme).
 2. There is NO card border-radius - the table runs edge to edge.
-3. The layout matches the application's other reports.</t>
+3. The layout matches the application's other reports.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S7-R1).</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>SV-8647 (specs/parts-velocity.md S7-R1; §2)</t>
+          <t>SV-8647 (PV spec v4 2026-07-29 S7-R1; §2)</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr"/>
@@ -3741,12 +3867,14 @@
 2. There is a thin dividing line between the toolbar and the column-header band, and the header band and the data cells are white.
 3. The first and last columns sit clear of the left and right edges of the table - the text is not touching the edge.
 4. It all looks the same as the other reports in the suite: put another report side by side and nothing should look out of place.
-5. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether the spacing and the dividing line look right and consistent with the other reports, and only report it if something looks obviously off. (The exact figures behind this - 32px/24px toolbar padding, a 1px header border, 2rem edge padding - are design-token values the design and engineering team check with their own tooling, not by hand.)</t>
+5. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether the spacing and the dividing line look right and consistent with the other reports, and only report it if something looks obviously off. (The exact figures behind this - 32px/24px toolbar padding, a 1px header border, 2rem edge padding - are design-token values the design and engineering team check with their own tooling, not by hand.)
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S7-R2, S7-R3, S7-R4, S7-R5).</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>SV-8647 (specs/parts-velocity.md S7-R2; S7-R3; S7-R4; S7-R5)</t>
+          <t>SV-8647 (PV spec v4 2026-07-29 S7-R2; S7-R3; S7-R4; S7-R5)</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr"/>
@@ -3789,7 +3917,9 @@
         <is>
           <t>1. The report supports dark mode: page background, toolbar, and cells use their dark-mode equivalents.
 2. In BOTH light mode and dark mode the grey ⓘ info icon is clearly visible against the cell behind it - you can see it at a glance without leaning in, and it does not disappear into the background.
-3. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether you can see the icon easily in both modes. Only report it if the icon is hard to see. (The design rule behind this is a minimum 3:1 contrast ratio, which the design and engineering team check with a contrast tool - not by hand.)</t>
+3. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether you can see the icon easily in both modes. Only report it if the icon is hard to see. (The design rule behind this is a minimum 3:1 contrast ratio, which the design and engineering team check with a contrast tool - not by hand.)
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S7-R6).</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -3824,7 +3954,8 @@
       <c r="E69" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with more rows in the result set than one page holds.
-2. Browser devtools (network tab) are open to observe the backend requests.</t>
+2. Browser devtools (network tab) are open to observe the backend requests.
+3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -3837,12 +3968,14 @@
         <is>
           <t>1. The backend returns ONE page of rows at a time - the full result set is not shipped to the browser.
 2. Paging is resolved on the server: moving to another page issues a fresh backend request for that page.
-3. This keeps the report responsive at scale (organizations can carry 50-60k parts, multiplied across locations).</t>
+3. This keeps the report responsive at scale (organizations can carry 50-60k parts, multiplied across locations).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R10).</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>SV-8642 (specs/parts-velocity.md §2 (server-paginated); S2-R10)</t>
+          <t>SV-8642 (PV spec v4 2026-07-29 §2 (server-paginated); S2-R10)</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr"/>
@@ -3871,7 +4004,8 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>1. You are on the Parts Velocity report with data loaded and the browser devtools network tab open.</t>
+          <t>1. You are on the Parts Velocity report with data loaded and the browser devtools network tab open.
+2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -3884,12 +4018,14 @@
         <is>
           <t>1. EACH change (Type, date range, Bin, Location, Category, Vendor, search) triggers a fresh server-side data load.
 2. There is no client-side-only narrowing - every filter or search change re-queries the server.
-3. Each change returns the FIRST page of the new result set.</t>
+3. Each change returns the FIRST page of the new result set.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R10).</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>SV-8642 (specs/parts-velocity.md S2-R10)</t>
+          <t>SV-8642 (PV spec v4 2026-07-29 S2-R10)</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr"/>
@@ -3918,7 +4054,8 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>1. You are on the Parts Velocity report with data loaded (including rows with null values in a sortable column) and the network tab open.</t>
+          <t>1. You are on the Parts Velocity report with data loaded (including rows with null values in a sortable column) and the network tab open.
+2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -3932,12 +4069,14 @@
         <is>
           <t>1. Each header click re-fetches the data from the server, ordered by the chosen column and direction, returning the first page of the re-sorted result set.
 2. Null values are placed FIRST on ascending and LAST on descending - as a server sort semantic, so the same order appears on screen and in the exports.
-3. Ties keep a stable order (no explicit secondary key).</t>
+3. Ties keep a stable order (no explicit secondary key).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S3-R3).</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>SV-8643 (specs/parts-velocity.md S3-R3)</t>
+          <t>SV-8643 (PV spec v4 2026-07-29 S3-R3)</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr"/>
@@ -3967,7 +4106,8 @@
       <c r="E72" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in as a user whose role has the ordinary reports access turned on and no other reports-related permission turned on.
-2. Browser devtools (network tab) are open.</t>
+2. Browser devtools (network tab) are open.
+3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -3981,7 +4121,9 @@
           <t>1. The back end returns the report data - the request is not refused.
 2. The back end returns the export file - the request is not refused.
 3. Both requests succeed with only the ordinary reports access turned on - nothing else had to be enabled.
-4. Note for the tester: if the back end refuses either request for a user who has the ordinary reports access, mark this Failed and report it. If an extra Parts or Inventory reports permission exists in the system it must not change these results - for now it is hidden from the screen and enforces nothing. A per-report permission added on purpose in a later release is a planned change, not a bug, and this test will be updated first.</t>
+4. Note for the tester: if the back end refuses either request for a user who has the ordinary reports access, mark this Failed and report it. If an extra Parts or Inventory reports permission exists in the system it must not change these results - for now it is hidden from the screen and enforces nothing. A per-report permission added on purpose in a later release is a planned change, not a bug, and this test will be updated first.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S1-R4, S1-N2); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4017,7 +4159,8 @@
         <is>
           <t>1. The test company is connected to QuickBooks.
 2. The part-of-a-unit sale has been made and invoiced — a ZZAUTOTEST part sold in a quantity such as 2.5, at a known unit cost such as $10.00.
-3. You can sign in to that QuickBooks company and look at its journal entries.</t>
+3. You can sign in to that QuickBooks company and look at its journal entries.
+4. This test cannot be run without a company whose QuickBooks account is connected, because it checks what was sent to QuickBooks. If no QuickBooks-connected company is available, mark this test Blocked and say so — do not guess the result.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -4034,7 +4177,9 @@
           <t>1. The QuickBooks amount is exactly the hand-worked figure to the cent — $25.00 for 2.5 at $10.00.
 2. It is NOT a whole-unit amount such as $20.00 or $30.00, and it is NOT a bigger, multiplied figure.
 3. The quantity behind the QuickBooks amount matches the Units Sold value on the report (2.50) — the two systems agree.
-4. No second or correcting journal entry is created to patch up a wrong amount.</t>
+4. No second or correcting journal entry is created to patch up a wrong amount.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and this point is not covered by any of the six report specifications — it comes from the engineering technical plan.</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">

--- a/testrail-import/Report-Suite_Parts-Velocity-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Parts-Velocity-Report_testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J73"/>
+  <dimension ref="A1:J72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -885,6 +885,8 @@
 3. Selecting a non-custom option immediately reloads the report data.
 4. The named ranges use the application's standard shared calendar boundaries (the same boundaries every report's date picker uses).
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R2).</t>
         </is>
       </c>
@@ -1400,6 +1402,8 @@
           <t>1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
 2. For the user with access to two or more locations the Location filter IS shown.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-E4); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
@@ -1934,12 +1938,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>A sale invoiced then fully reversed shows Demand 1 with Units Sold 0.00</t>
+          <t>Column picker lists all 20 columns and never offers the internal cost</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>PV — Row Model</t>
+          <t>PV — Columns &amp; Remembered View</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1949,72 +1953,22 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1. Inventory part C: one sale invoiced AND fully reversed inside the window, and the part still has on-hand stock (so it stays in the result set).
-2. Inventory part D: reversals exceed sales in the window (net-negative movement), with on-hand stock or other billed revenue keeping it in the result set.</t>
+          <t>1. You are on the Parts Velocity report with data loaded.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>1. Find part C and read its Demand and Units Sold.
-2. Find part D and read its Units Sold.</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>1. Part C shows Demand 1 (the reversal does not decrement the Demand count) with Units Sold 0.00 (the reversal nets the movement to zero).
-2. Part D shows a NEGATIVE Units Sold with a leading minus (e.g. -3.00) - negative movement is not floored to zero.
-3. A fully-reversed part with zero net movement, no on-hand stock, and no residual revenue would be excluded altogether (a Demand count alone does not keep a row).
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S3-E1, S5-R5).</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>SV-8643 (PV spec v4 2026-07-29 S3-E1; S5-R5)</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>Column picker lists all 20 columns and never offers the internal cost</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>PV — Columns &amp; Remembered View</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>1. You are on the Parts Velocity report with data loaded.</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>1. Open the column picker from its toolbar button.
 2. Count the columns listed and check each has a toggle.
 3. Look for any on-hand cost / inventory-value entry.</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>1. The picker lists all 20 available columns, each with a toggle: Type, Part #, Description, Category, Vendor, Units Sold, Units Returned, Sold (WO), Sold (Parts Sale), Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand, Turns/Yr, Min, Max.
 2. No on-hand cost column is offered - the report computes one internally but it is never selectable and never displayed.
@@ -2022,46 +1976,46 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S4-R1, S4-R4, S5-R6).</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>SV-8644 (PV spec v4 2026-07-29 S4-R1; S4-R4; S5-R6)</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>First visit shows exactly the 14 default columns in the specified order</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>PV — Columns &amp; Remembered View</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report on a first visit (no saved column selection).</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>1. Read the visible column headers left to right without touching the picker.</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>1. With a single location in scope exactly these 14 columns show, in this left-to-right order: Type, Part #, Description, Category, Vendor, Units Sold, Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand.
 2. The other 6 columns start hidden: Units Returned, Sold (WO), Sold (Parts Sale), Turns / Yr, Min, Max.
@@ -2070,48 +2024,48 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S4-R2, S4-R3, S3-R10).</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>SV-8644; SV-8643 (PV spec v4 2026-07-29 S4-R2; S4-R3 + Story 3 S3-R10 — the 14 default-visible columns and the 6 hidden ones; plus the automatic Location column leftmost when more than one location is in scope)</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>A re-enabled column returns to its canonical slot, with no reload</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>PV — Columns &amp; Remembered View</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded.</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>1. In the column picker, enable Min, then Units Returned, then Turns/Yr - in that (non-canonical) order.
 2. Watch the table as each toggle is flipped.
 3. Read the resulting header order.</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>1. Each toggle takes effect immediately - the table re-renders without a page reload.
 2. Columns always render in the fixed canonical left-to-right order regardless of the order they were toggled on (with the automatic Location column, when shown, sitting leftmost before Type): Type, Part #, Description, Category, Vendor, Units Sold, Units Returned, Sold (WO), Sold (Parts Sale), Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand, Turns/Yr, Min, Max.
@@ -2120,48 +2074,48 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S4-R4, S4-R5, S3-R10).</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>SV-8644; SV-8643 (PV spec v4 2026-07-29 S4-R4; S4-R5 + Story 3 S3-R10 — canonical column order and immediate re-render; plus the automatic Location column leftmost when shown)</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>Filters; columns and sort are remembered per browser before the first fetch</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>PV — Columns &amp; Remembered View</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded.</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>1. Set a non-default view: Type = Inventory, date range = Last Month, pick a category, enable Turns / Yr, and sort by Revenue descending.
 2. Leave the report (navigate elsewhere), then return to it.
 3. Reload the page (browser refresh) and observe again.</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>1. On return, every saved setting is restored: Type = Inventory, Last Month, the chosen category, the column set including Turns / Yr, and the Revenue-descending sort.
 2. The saved values are applied BEFORE the first data fetch - the report does not flash the defaults and then re-query.
@@ -2171,47 +2125,47 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S4-R6, S1-R2).</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>SV-8644 (PV spec v4 2026-07-29 S4-R6; S1-R2)</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>A saved value that is no longer valid falls back to that setting's default</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>PV — Columns &amp; Remembered View</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>1. A saved view exists in this browser that includes a location the user can no longer access (e.g. access was removed after the view was saved), or a custom date range that is now malformed.</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>1. Return to the Parts Velocity report with that stale saved view in place.
 2. Observe which location / date range the report loads with.</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>1. The invalid saved value is NOT sent to the server.
 2. That one setting falls back to its default (e.g. the location falls back to the active location); the other saved settings still restore normally.
@@ -2220,6 +2174,55 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S4-R6).</t>
         </is>
       </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>SV-8644 (PV spec v4 2026-07-29 S4-R6)</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>A different user signing in on the same browser inherits the saved view</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>PV — Columns &amp; Remembered View</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>1. User 1 has saved a clearly non-default view on this browser (e.g. Type = Special Order, Last Quarter).
+2. User 2 can open the report.</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>1. Sign out user 1 and sign in user 2 on the SAME browser.
+2. Open the Parts Velocity report.</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>1. User 2 sees user 1's saved view (Type = Special Order, Last Quarter, the saved columns and sort).
+2. This is by design: storage is per browser, not tied to the account - there is no per-account separation.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S4-R6).</t>
+        </is>
+      </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
           <t>SV-8644 (PV spec v4 2026-07-29 S4-R6)</t>
@@ -2231,7 +2234,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>A different user signing in on the same browser inherits the saved view</t>
+          <t>All 20 columns can be hidden; the empty selection is never restored</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2251,66 +2254,17 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1. User 1 has saved a clearly non-default view on this browser (e.g. Type = Special Order, Last Quarter).
-2. User 2 can open the report.</t>
+          <t>1. You are on the Parts Velocity report with data loaded.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>1. Sign out user 1 and sign in user 2 on the SAME browser.
-2. Open the Parts Velocity report.</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>1. User 2 sees user 1's saved view (Type = Special Order, Last Quarter, the saved columns and sort).
-2. This is by design: storage is per browser, not tied to the account - there is no per-account separation.
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S4-R6).</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>SV-8644 (PV spec v4 2026-07-29 S4-R6)</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>All 20 columns can be hidden; the empty selection is never restored</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>PV — Columns &amp; Remembered View</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>1. You are on the Parts Velocity report with data loaded.</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>1. In the column picker, switch OFF all 20 columns.
 2. Trigger a CSV export while zero columns are enabled.
 3. Leave the report and return to it.</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>1. The picker enforces no minimum - all 20 columns can be switched off, leaving a grid with no data columns for the rest of the session.
 2. The export produces a file containing only the header/metadata rows and no data columns.
@@ -2319,49 +2273,49 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S4-E1, S4-R6).</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>SV-8644 (PV spec v4 2026-07-29 S4-E1; S4-R6)</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>Units Sold for an inventory part is net stock movement</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>PV — Columns &amp; Calculations</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>1. An inventory part with known starting stock.
 2. You can invoice work orders, reverse/void an invoice, and initiate a part return for that part inside the report window.</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>1. Invoice a work order selling 5 units of the part; reload the report and read Units Sold.
 2. Reverse/void an invoice that sold 2 units in the window; reload and read Units Sold.
 3. Initiate a part return for 1 unit of the part; reload and read Units Sold.</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>1. After step 1, Units Sold increases by 5.00 (invoicing a work order adds the units sold - a stock-movement event).
 2. After step 2, Units Sold decreases by 2.00 (reversing/voiding an invoice adds stock back and is subtracted - Units Sold is net of invoice reversals).
@@ -2371,48 +2325,48 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R1, S5-R4).</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>SV-8645 (PV spec v4 2026-07-29 S5-R1; S5-R4 (Units Sold; inventory); §4)</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>Special Order Units Sold = in-window request quantity, net of reversals</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>PV — Columns &amp; Calculations</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>1. A special-order (vendor-sourced) part is requested on invoiced or paid work orders in the window - e.g. 3 units on one work order and 2 on another.
 2. One further in-window sale of the same special-order part has been reversed/voided.</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>1. Find the special-order part's row and read Units Sold.
 2. Compare against the sum of the in-window vendor-request quantities, leaving out the reversed sale.</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>1. Units Sold equals the total quantity across the part's in-window vendor requests (3 + 2 = 5.00 in the example), summed across the selected locations.
 2. The reversed/voided sale is EXCLUDED from the total (net of reversals).
@@ -2421,42 +2375,42 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R2, S5-R4, S5-R4b).</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>SV-8645 (PV spec v4 2026-07-29 S5-R2; S5-R4 (Units Sold; catalogue); S5-R4b)</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>Units Returned counts initiated part returns and parts-sale credits</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>PV — Columns &amp; Calculations</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>1. A part with in-window sales (so its row exists) and the Units Returned column enabled via the column picker.
 2. You can initiate a work-order part return, a parts-sale credit, and cancel a return.</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>1. Initiate a work-order part return for 2 units of the part; reload and read Units Returned.
 2. Create a parts-sale credit returning 1 more unit; reload and read Units Returned.
@@ -2464,7 +2418,7 @@
 4. Reverse/void an unrelated invoice for the part; reload and read Units Returned.</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>1. After step 1, Units Returned increases by 2.00 (the return record is counted when the return is initiated).
 2. After step 2, it increases by 1.00 more (a parts-sale credit also creates a part-return record).
@@ -2474,50 +2428,50 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R3, S5-R4).</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>SV-8645 (PV spec v4 2026-07-29 S5-R3; S5-R4 (Units Returned); §3 Key Decisions)</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>Units Returned is windowed by initiation date, ignores invoice status</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>PV — Columns &amp; Calculations</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>1. A part sold in a PREVIOUS window whose return is initiated inside the CURRENT window (and the part has current-window activity or stock so its row exists).
 2. A core-charge return exists for a part in the window.
 3. The Units Returned column is enabled.</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>1. Select the current window and read the part's Units Returned.
 2. Select the previous window (when the sale happened) and read Units Returned again.
 3. Check the part with the core-charge return.</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>1. The return counts in the window of its INITIATION date - so it appears in the current window even though the sale was earlier (a return and its originating sale can fall in different report windows; each uses its own natural event date).
 2. In the previous window the return does not count (only the sale's own metrics do).
@@ -2528,49 +2482,49 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R3).</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>SV-8645 (PV spec v4 2026-07-29 S5-R3)</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>Sold (WO) counts Service work orders, Sold (Parts Sale) counts Parts</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>PV — Columns &amp; Calculations</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>1. A part sold in the window on an invoiced SERVICE work order (e.g. 4 units) and on an invoiced PARTS SALE / Parts-type work order created in Parts → Parts Sale (e.g. 3 units).
 2. The Sold (WO) and Sold (Parts Sale) columns are enabled.</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>1. Read the part's Sold (WO) value.
 2. Read the part's Sold (Parts Sale) value.
 3. Move the date range so the work orders' end dates fall outside the window and re-read both.</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>1. Sold (WO) shows the total part quantity on Service-type invoiced/paid work orders whose work-order date is in the window (4.00 in the example), net of reversed/voided sales.
 2. Sold (Parts Sale) shows the total on Parts-type invoiced/paid work orders (counter sales) in the window (3.00), net of reversed/voided sales.
@@ -2580,89 +2534,90 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R4).</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>SV-8645 (PV spec v4 2026-07-29 S5-R4 (Sold via WO / Sold via Parts Sale); §5 Assumptions)</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>Demand counts each transaction once; a reversal neither adds nor subtracts</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>PV — Columns &amp; Calculations</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>1. An inventory part sold in the window on two invoiced work orders - one for 1 unit, one for 10 units.
 2. A special-order part with two in-window vendor requests.
 3. One of the inventory part's in-window sales is then reversed/voided.</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>1. Read the inventory part's Demand before the reversal.
 2. Reverse/void one of its invoices and re-read Demand.
 3. Read the special-order part's Demand.</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>1. The inventory part's Demand is 2 - each stock-decrementing invoicing event counts ONCE no matter how many units were on it (1 unit and 10 units each count as one).
 2. After the reversal, Demand is STILL 2 - a reversal event neither adds to nor subtracts from the count (while Units Sold nets down).
 3. The special-order part's Demand is 2 - the count of its in-window vendor part requests.
 4. Demand is the report's default ranking signal (a whole number, never null - 0 when none).
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R4).</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>SV-8645 (PV spec v4 2026-07-29 S5-R4 (Demand); §4; §3 Key Decisions)</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+5. A part whose single in-window sale is invoiced and then fully reversed shows Demand 1 with Units Sold 0.00 — the Demand count is not decremented, while the movement nets to zero.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R4, S3-E1).</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>SV-8645 (PV spec v4 2026-07-29 S5-R4 (Demand); §4; §3 Key Decisions; S3-E1)</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>Last Sale is whole days since the most recent sale over all-time history</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>PV — Columns &amp; Calculations</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>1. A part whose most recent sale was N days ago, OUTSIDE the currently selected date range (e.g. range = This Month, last sale 42 days ago).
 2. The part still appears in the report (it has on-hand stock).
@@ -2670,14 +2625,14 @@
 4. For the reversal check: a ZZAUTOTEST part whose MOST RECENT sale can be reversed, and an older sale of the same part also exists.</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>1. Read the part's Last Sale value with the narrow date range selected.
 2. Switch the Location filter between location A and location B and re-read Last Sale.
 3. Reverse the part's most recent sale invoice and re-read Last Sale.</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>1. Last Sale shows the whole days between today and the part's most recent sale measured over ALL-TIME history - it IGNORES the selected date range (e.g. '42 days' even though the range is This Month).
 2. It IS scoped to the selected location(s): with only location B selected, Last Sale reflects B's own most recent sale.
@@ -2688,48 +2643,48 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R4, S5-R5).</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>SV-8645 (PV spec v4 2026-07-29 S5-R4 (Last Sale); §4; S5-R5; tech-plan-2026-07-29 B3.1 (last-sale re-anchor on reversal — spec-silent))</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>On Hand shows the row's own location stock</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>PV — Columns &amp; Calculations</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>1. An inventory part with a known on-hand quantity and stored Min / Max reorder thresholds at one location.
 2. The Min and Max columns are enabled via the column picker.</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>1. Read the part's On Hand, Min, and Max in the report and compare with the inventory record.
 2. Try clicking / double-clicking the Min and Max cells and look for any edit control or slide-over.</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>1. On Hand equals the part's CURRENT on-hand quantity at that row's location (never summed across locations).
 2. Min and Max show the stored minimum / maximum reorder thresholds for that location, as whole numbers (— when not set).
@@ -2738,36 +2693,36 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R4, S5-R5).</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>SV-8645 (PV spec v4 2026-07-29 S5-R4 (On Hand / Min / Max); §2 Out of Scope; S5-R5)</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>Turns / Yr annualizes the sales rate, is 0.00 at zero stock, can be negative</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>PV — Columns &amp; Calculations</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>1. The Turns / Yr column is enabled.
 2. Part A: known Units Sold over a known window with On Hand &gt; 0 (e.g. Units Sold 10.00 over a 30-day window with 5 on hand).
@@ -2775,14 +2730,14 @@
 4. Part C: negative Units Sold (reversals exceed sales) with stock on hand.</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>1. Compute the expected value for part A: (Units Sold ÷ Window days × 365) ÷ On Hand - e.g. (10 ÷ 30 × 365) ÷ 5 = 24.33.
 2. Compare against the displayed Turns / Yr for part A.
 3. Read Turns / Yr for parts B and C, and for any special-order row.</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>1. Part A's Turns / Yr matches the formula (two decimals, e.g. 24.33); the window is the whole-day span inclusive of both dates with a floor of 1 day.
 2. Part B shows 0.00 (renders 0.00 when On Hand is 0 - not an error, not —).
@@ -2793,48 +2748,48 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R4).</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>SV-8645 (PV spec v4 2026-07-29 S5-R4 (Turns / Yr); S5 Definitions (Window))</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>Revenue, Margin, Unit Cost, Sell Price and Margin % use the billed formulas</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>PV — Columns &amp; Calculations</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>1. A part with known billed lines in the window - e.g. two invoiced work-order part lines: 2 units at $50.00 sell / $30.00 cost, and 1 unit at $40.00 sell / $30.00 cost.
 2. All five profitability columns are visible.</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>1. Compute the expected values: Revenue = (2×50)+(1×40) = $140.00; COGS = (2×30)+(1×30) = $90.00; billed units = 3; Margin = 140−90 = $50.00; Unit Cost = 90÷3 = $30.00; Sell Price = 140÷3 = $46.67; Margin % = 50÷140×100 = 35.7%.
 2. Compare each against the part's displayed row.</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>1. Revenue = the summed billed sell amount (each line's stored sell price × quantity) in the window.
 2. Margin = Revenue − COGS (the summed billed cost captured at billing time).
@@ -2846,49 +2801,49 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R4a).</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>SV-8645 (PV spec v4 2026-07-29 S5-R4a; §4)</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>A reversed or voided sale is excluded from every billed-line column</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>PV — Columns &amp; Calculations</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>1. A part with two in-window billed sales of known amounts, one of which you then reverse/void.
 2. All movement and profitability columns are visible.</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>1. Record the part's Revenue, Margin, Unit Cost, Sell Price, Margin %, Sold (WO) / Sold (Parts Sale) (and Units Sold for a special-order part).
 2. Reverse/void one of the two sales.
 3. Reload the report and re-read every column.</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>1. After the reversal, ALL the billed-line columns drop to reflect only the remaining sale - the reversed/voided sale is excluded from Revenue, Margin, Unit Cost, Sell Price, Margin %, Sold (WO), Sold (Parts Sale), and (for special-order) Units Sold.
 2. This netting is consistent with inventory Units Sold, which already nets reversals via the stock add-back.
@@ -2897,50 +2852,50 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R4b, S5-R4a).</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>SV-8645 (PV spec v4 2026-07-29 S5-R4b; S5-R4a; §3 Key Decisions)</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Unit Cost / Sell Price and Margin % use independent null triggers</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>PV — Columns &amp; Calculations</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>1. Row 1: a part with booked revenue but ZERO billed units in the window (e.g. a credit/adjustment line carrying revenue with no billed quantity).
 2. Row 2: a part with billed units &gt; 0 but Revenue $0.00 (e.g. billed at a $0 sell price).
 3. Row 3: a part with both billed units ≤ 0 and Revenue ≤ 0.</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>1. Read Unit Cost, Sell Price, Margin %, Revenue, and Margin on row 1.
 2. Read the same columns on row 2.
 3. Read the same columns on row 3.</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>1. Row 1: Unit Cost and Sell Price show — (billed units ≤ 0) while Revenue and Margin show dollar amounts AND Margin % is still computed from Revenue - a valid mixed row, not a defect.
 2. Row 2: Sell Price shows $0.00 (a number) while Margin % shows — (Revenue ≤ 0) - also valid.
@@ -2950,47 +2905,47 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R4a, S3-R9).</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>SV-8645 (PV spec v4 2026-07-29 S5-R4a (null rules + mixed-row paragraph); S3-R9)</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>Number formats match the spec per column; rounding is half away from zero</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>PV — Columns &amp; Calculations</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>1. All 20 columns are enabled and rows exist with large (1,000+), negative, and null values across the column types.</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>1. Read a large count value (Units Sold etc.), a negative count, a large money value, a negative money value, a Margin % value, a Demand value, Min/Max values, and a Last Sale value.
 2. Seed a Margin % that lands exactly on a rounding tie (e.g. computes to 8.45% / -8.45%) and read the display.</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>1. Units Sold, Units Returned, Sold (WO), Sold (Parts Sale), On Hand, Turns / Yr: two decimals with thousands separators (1,250.00); negatives with a leading minus (-3.00).
 2. Unit Cost, Sell Price, Revenue, Margin: currency with $, two decimals, thousands separators ($1,250.00); negatives with a leading minus and NO parentheses (-$45.00).
@@ -3001,48 +2956,48 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R5, S5-R7).</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>SV-8645 (PV spec v4 2026-07-29 S5-R5; S5-R7 (rounding))</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>Core parts are excluded from both the inventory and special-order result sets</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>PV — Columns &amp; Calculations</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>1. An inventory part flagged as a core has in-window sales activity and on-hand stock.
 2. A vendor-sourced core part was requested on an invoiced/paid work order in the window.</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>1. Search the report for the inventory core part (Type = Both).
 2. Search for the special-order core part.</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>1. The inventory core part does NOT appear in the report despite its activity and stock.
 2. The special-order core part does NOT appear either.
@@ -3051,50 +3006,50 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R1, S5-R2).</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>SV-8645 (PV spec v4 2026-07-29 S5-R1; S5-R2; §3 Key Decisions)</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>Movement and billed bases may differ; Sold (WO) + Sold (Parts Sale) = billed</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>PV — Columns &amp; Calculations</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>1. An inventory part with a billed sale that produced NO matching stock decrement (e.g. a drop-ship or negative-stock sale) plus normal stocked sales in the window.
 2. A special-order part with in-window vendor requests.
 3. Units Sold, Sold (WO), Sold (Parts Sale), and the profitability columns are visible.</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>1. On the inventory row, compare Units Sold against Revenue ÷ Sell Price (the billed units).
 2. On the same row, add Sold (WO) + Sold (Parts Sale) and compare against the billed units.
 3. On the special-order row, compare Units Sold, Sold (WO) + Sold (Parts Sale), and the billed units.</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>1. On the inventory row, Units Sold (stock movement) DIFFERS from the billed units behind Revenue/Sell Price - this is CORRECT behavior, not a defect (the Units Sold tooltip calls it out).
 2. Sold (WO) + Sold (Parts Sale) together DO equal the billed-units basis (work orders are only Service- or Parts-type) - but neither equals the movement-based Units Sold.
@@ -3103,49 +3058,49 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R7).</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>SV-8645 (PV spec v4 2026-07-29 S5-R7; §3 Key Decisions)</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>Window anchors: movement uses the event date, billed uses the WO date</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>PV — Columns &amp; Calculations</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>1. A work order whose END date falls in window W1 but whose invoicing (stock-movement event) happened in window W2 for an inventory part.
 2. Both W1 and W2 are selectable ranges.</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>1. Select window W1 and read the part's Units Sold / Demand vs its Revenue / Sold (WO).
 2. Select window W2 and read the same columns.
 3. Select a single-day range (Today) and check the report still computes (window floor).</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>1. In W1 (work-order date in window): the billed columns (Revenue, Margin, Unit Cost, Sell Price, Margin %, Sold (WO), Sold (Parts Sale)) count the sale, while inventory Units Sold / Demand do NOT (their movement event is outside W1).
 2. In W2 (movement date in window): Units Sold / Demand count it, the billed columns do not - the two anchors CAN differ for an inventory part and that is intended.
@@ -3156,43 +3111,43 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R7).</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>SV-8645 (PV spec v4 2026-07-29 S5 Definitions (Window / Work-order date); S5-R7)</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>Units Sold keeps an exact part-of-a-unit quantity and is never rounded off</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>PV — Columns &amp; Calculations</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>1. You can sign in with a role that opens the Parts Velocity report.
 2. A ZZAUTOTEST inventory part is in stock with a known unit cost, and there is enough on the shelf to sell a part-of-a-unit quantity such as 2.5.
 3. Today's date falls inside the date range you will use on the report.</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>1. Open a ZZAUTOTEST work order and add that part to it with the quantity 2.5.
 2. Approve the part line, then invoice the work order.
@@ -3201,7 +3156,7 @@
 5. Read the Units Sold value, then switch the On Hand column on and read that too.</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>1. Units Sold reads exactly 2.50 — not 2.00, not 3.00, not blank and not a dash.
 2. It still reads exactly 2.50 after the sign-out and sign-back-in, which proves the part-of-a-unit quantity was really stored and not just shown once.
@@ -3211,9 +3166,57 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R1, S5-R5).</t>
         </is>
       </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>SV-8589 (PV spec S5-R1 Units Sold net stock movement + S5-R5 two-decimal movement format; tech-plan-2026-07-29 Phase 0 / PR-1 D2; SV-8589 verbatim Tests: 'fractional-quantity round-trip regression')</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>The overflow button opens Download (PDF) then Download (CSV) in that order</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>PV — Exports</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>1. You are on the Parts Velocity report with data loaded.</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>1. Find the ⋯ overflow button - the leftmost control in the toolbar's action cluster.
+2. Click it and read the menu items top to bottom.</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>1. The ⋯ overflow button sits leftmost in the toolbar's action cluster.
+2. The menu holds exactly two items, in this order: Download (PDF), then Download (CSV).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S6-R1).</t>
+        </is>
+      </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>SV-8589 (PV spec S5-R1 Units Sold net stock movement + S5-R5 two-decimal movement format; tech-plan-2026-07-29 Phase 0 / PR-1 D2; SV-8589 verbatim Tests: 'fractional-quantity round-trip regression')</t>
+          <t>SV-8646 (PV spec v4 2026-07-29 S6-R1 — S6-R1 CLOSES it in the spec's own words ("an export menu with two items ... Download (PDF) and Download (CSV)"); so the closed list IS the requirement)</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr"/>
@@ -3222,7 +3225,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>The overflow button opens Download (PDF) then Download (CSV) in that order</t>
+          <t>Both exports reflect the filters and search active at the time of export</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -3242,65 +3245,17 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>1. You are on the Parts Velocity report with data loaded.</t>
+          <t>1. You are on the Parts Velocity report with data loaded across types, categories, and locations.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>1. Find the ⋯ overflow button - the leftmost control in the toolbar's action cluster.
-2. Click it and read the menu items top to bottom.</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>1. The ⋯ overflow button sits leftmost in the toolbar's action cluster.
-2. The menu holds exactly two items, in this order: Download (PDF), then Download (CSV).
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S6-R1).</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>SV-8646 (PV spec v4 2026-07-29 S6-R1 — S6-R1 CLOSES it in the spec's own words ("an export menu with two items ... Download (PDF) and Download (CSV)"); so the closed list IS the requirement)</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>Both exports reflect the filters and search active at the time of export</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>PV — Exports</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>1. You are on the Parts Velocity report with data loaded across types, categories, and locations.</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>1. Set a distinctive filter mix: Type = Inventory, a single category, a short date range, and a search string.
 2. Download the CSV and open it.
 3. Download the PDF and open it.</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>1. Both files contain only the rows matching the date range, type, category, vendor, bin, location, and search active at export time - not a full unfiltered dump.
 2. The exported rows match what the on-screen grid was showing.
@@ -3309,48 +3264,48 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S6-R2, S6-R11); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>SV-8646 (PV spec v4 2026-07-29 S6-R2; S6-R11; §3 Key Decisions — both exports reflect the filters and search active at export time; S6-R11 = the "Locations:" line in both exports [Chris Ward 2026-07-29; newest-wins])</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>Exports include only the enabled columns, in the canonical on-screen order</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>PV — Exports</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded.</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>1. Hide two default columns (e.g. Category, Margin %) and enable a hidden one (e.g. Units Returned).
 2. Download the CSV and read its column headers in order.
 3. Download the PDF and read its columns in order.</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>1. Both exports contain ONLY the currently enabled columns - the hidden ones are absent.
 2. Columns appear in the CANONICAL order (the fixed on-screen order) - the re-enabled Units Returned sits right after Units Sold, NOT appended at the end.
@@ -3359,49 +3314,49 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S6-R3, S4-R4).</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>SV-8646 (PV spec v4 2026-07-29 S6-R3; S4-R4)</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>Exports reflect the active sort, including Min/Max and null placement</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>PV — Exports</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded, including rows with — values in a sortable column (e.g. On Hand on special-order rows).
 2. Min and Max are enabled.</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>1. Without clicking any header (default Demand descending), download the CSV and check the row order.
 2. Sort by Min ascending, export, and check the order including where the — rows land.
 3. Sort by On Hand descending, export, and check the null placement.</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>1. The default Demand-descending order is exported when the user has not chosen another column.
 2. Every column's sort is honored in the export - including Min and Max.
@@ -3410,48 +3365,48 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S6-R4, S3-R3).</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>SV-8646 (PV spec v4 2026-07-29 S6-R4; S3-R3)</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>PDF: filename, A3 landscape, title, text truncation, and the shop logo</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>PV — Exports</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded, including a part with a Description, Category, and Vendor each longer than 18 characters and a long Part #.</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>1. Download the PDF and check the saved filename.
 2. Open it and check the page format and title.
 3. Find the long-text part's row and read Description, Category, Vendor, and Part #.</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>1. The file downloads as velocity-report.pdf.
 2. The PDF is formatted for A3 landscape and titled Parts Velocity.
@@ -3459,62 +3414,115 @@
 4. Part # is NOT truncated.
 5. The shop logo shows at the top of the PDF when one is set. With no uploaded logo the PDF shows the bundled ShopView default logo instead of a blank space, the same as the other reports in this suite. The CSV never includes a logo.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S6-R5, S6-R6).</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>SV-8646 (PV spec v4 2026-07-29 S6-R5; S6-R6 + same-logo-treatment for every report per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source; last-update-wins))</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>CSV is named velocity-report.csv and holds full untruncated text values</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>PV — Exports</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded, including a part with a Description longer than 18 characters and a part with a Last Sale value.</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>1. Download the CSV and check the saved filename.
 2. Open it and read the long part's Description, Category, and Vendor.
 3. Read the Last Sale column value.</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>1. The file downloads as velocity-report.csv.
 2. The CSV carries the FULL, untruncated Description / Category / Vendor values (unlike the PDF's 18-character cut).
 3. Last Sale is a raw integer in the CSV (e.g. 42) - the 'N days' wording is PDF/on-screen only.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S6-R5, S6-R6, S6-R8).</t>
         </is>
       </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>SV-8646 (PV spec v4 2026-07-29 S6-R5; S6-R6; S6-R8)</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Em-dash in both exports; Last Sale reads "N days" in the PDF</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>PV — Exports</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>1. Rows with null values exist (a special-order row for On Hand / Turns / Yr / Min / Max; a row with billed units 0 for Unit Cost / Sell Price; a never-sold row for Last Sale).
+2. All nullable columns are enabled.</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>1. Download the CSV and locate the null cells.
+2. Download the PDF and locate the same cells.</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>1. A null value renders as — (em-dash) in BOTH the CSV and the PDF, in every nullable field: Unit Cost, Sell Price, Margin %, On Hand, Turns / Yr, Last Sale, Min, Max.
+2. Revenue, Margin, and the count metrics are never null in the exports either ($0.00 / 0.00 / 0).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S6-R7, S6-R8, S3-R9).</t>
+        </is>
+      </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>SV-8646 (PV spec v4 2026-07-29 S6-R5; S6-R6; S6-R8)</t>
+          <t>SV-8646 (PV spec v4 2026-07-29 S6-R7; S6-R8; S3-R9)</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
@@ -3523,7 +3531,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Em-dash in both exports; Last Sale reads "N days" in the PDF</t>
+          <t>PDF export alignment: Type centered, text left, numeric and money right</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3538,70 +3546,21 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>1. Rows with null values exist (a special-order row for On Hand / Turns / Yr / Min / Max; a row with billed units 0 for Unit Cost / Sell Price; a never-sold row for Last Sale).
-2. All nullable columns are enabled.</t>
+          <t>1. You are on the Parts Velocity report with data loaded and several columns of each kind visible.</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>1. Download the CSV and locate the null cells.
-2. Download the PDF and locate the same cells.</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>1. A null value renders as — (em-dash) in BOTH the CSV and the PDF, in every nullable field: Unit Cost, Sell Price, Margin %, On Hand, Turns / Yr, Last Sale, Min, Max.
-2. Revenue, Margin, and the count metrics are never null in the exports either ($0.00 / 0.00 / 0).
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S6-R7, S6-R8, S3-R9).</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>SV-8646 (PV spec v4 2026-07-29 S6-R7; S6-R8; S3-R9)</t>
-        </is>
-      </c>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>PDF export alignment: Type centered, text left, numeric and money right</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>PV — Exports</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>1. You are on the Parts Velocity report with data loaded and several columns of each kind visible.</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>1. Download the PDF and look at the alignment of each column.
 2. Download the CSV and open it in a plain text editor to confirm it is plain comma-separated values (a CSV file carries no alignment of its own).</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>1. In the PDF, the Type column is CENTERED.
 2. In the PDF, the text columns (Part #, Description, Category, Vendor) are left-aligned.
@@ -3612,49 +3571,49 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S6-R10, S3-R8).</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>SV-8646 (PV spec v4 2026-07-29 S6-R10; S3-R8)</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>Export toasts: exact success texts; server or fallback error text on failure</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>PV — Exports</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded.
 2. You can force an export failure (e.g. drop the network connection just before triggering the download, or induce a server error).</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>1. Download the CSV and the PDF normally and read each toast.
 2. Trigger a CSV export under the failure condition and read the toast.
 3. Trigger a PDF export under the failure condition and read the toast.</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>1. On success the toasts read exactly "Velocity report exported (CSV)" / "Velocity report exported (PDF)" and auto-fade — UPPERCASE (CSV)/(PDF).
 2. An error toast is shown on failure; when the server provides a message, that server message is shown.
@@ -3663,42 +3622,42 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S6-R9, S6-N1).</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>SV-8646 (PV spec v4 2026-07-29 S6-R9; S6-N1; §7 (casing note) — S6-R9/S6-N1 CLOSE the toast strings verbatim including the shipped UPPERCASE-success / lowercase-failure casing mix; so the exact strings ARE the requirement)</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>An over-cap Parts Velocity export is refused with the too-large message</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>PV — Exports</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. A filter/location combination exists whose filtered set EXCEEDS the export row cap (widest date range + all locations; seed ZZAUTOTEST parts in bulk if needed, or use the largest available data set).</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>1. Set the filters so the filtered set exceeds the export row cap.
 2. Request the CSV download and read what happens.
@@ -3706,7 +3665,7 @@
 4. Narrow the date range or filters below the cap and request a download again.</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>1. Neither the CSV nor the PDF is produced — no download starts.
 2. A clear too-large message appears telling the user to narrow the date range or filters, then try again — the standard wording is "This report is too large to export. Narrow the date range or filters, then try again."
@@ -3716,42 +3675,42 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (Story 6 exports).</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>SV-8646 (PV spec v4 2026-07-29 Story 6 exports — spec silent on a cap; tech-plan-2026-07-29 A3/FR-F4: suite-wide 10; 000-row export cap; locked by Chris 2026-07-21)</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>A large PDF download fails outright while the CSV of the same view works</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>PV — Exports</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with ordinary reports access, on a desktop browser.
 2. Parts Velocity is open with a date range that returns a few hundred rows — narrow with the toolbar search until the list is roughly 300 to 500 rows.</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>1. Narrow the report with the toolbar search so it shows a few hundred rows.
 2. Open the three-dot menu and choose "Download (CSV)". Wait for the file.
@@ -3759,7 +3718,7 @@
 4. Narrow the search further, to a couple of dozen rows, and choose "Download (PDF)" again.</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>1. The CSV downloads successfully at that size.
 2. The PDF also downloads successfully. If instead nothing downloads and a message appears saying something went wrong, that is a failure — record roughly how many rows were on screen.
@@ -3770,47 +3729,47 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (Story 6 exports).</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>SV-8646 (PV spec v4 2026-07-29 Story 6 exports — the spec is silent on a renderer size limit; tech-plan-2026-07-29 A3/FR-F4 covers only the ten-thousand-row export cap)</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>The report uses the standard two-tone layout</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>PV — Visual Conformance</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded, in light mode.</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>1. Look at the page background, the toolbar, and the table surfaces.
 2. Look at the card corners and the table's horizontal extent.</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>1. White card surfaces (toolbar + table cells) sit on the standard soft blue-grey page background (the application's two-tone report theme).
 2. There is NO card border-radius - the table runs edge to edge.
@@ -3819,41 +3778,41 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S7-R1).</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>SV-8647 (PV spec v4 2026-07-29 S7-R1; §2)</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>Toolbar and table detail styling matches the suite paddings and borders</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>PV — Visual Conformance</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded.</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>1. Look at the toolbar strip above the table and at the space between its controls and the edges of the strip.
 2. Look at the column-header band and at the line between it and the toolbar above it.
@@ -3861,7 +3820,7 @@
 4. Compare all of the above with another report in the suite (for example Inventory Value) opened side by side.</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>1. The toolbar strip is white (dark in dark mode), and its controls sit clear of the edges rather than pressed up against them.
 2. There is a thin dividing line between the toolbar and the column-header band, and the header band and the data cells are white.
@@ -3872,48 +3831,48 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S7-R2, S7-R3, S7-R4, S7-R5).</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>SV-8647 (PV spec v4 2026-07-29 S7-R2; S7-R3; S7-R4; S7-R5)</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>Dark mode is supported and the grey info icon keeps 3:1 contrast in both</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>PV — Visual Conformance</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded and dark mode available in the application.</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>1. Switch the application to dark mode.
 2. Look at the page background, toolbar, and cells.
 3. Look at the grey ⓘ info icon next to a column heading in dark mode, then switch back to light mode and look at it again.</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>1. The report supports dark mode: page background, toolbar, and cells use their dark-mode equivalents.
 2. In BOTH light mode and dark mode the grey ⓘ info icon is clearly visible against the cell behind it - you can see it at a glance without leaning in, and it does not disappear into the background.
@@ -3922,49 +3881,49 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S7-R6).</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>SV-8647 (PV spec v4 2026-07-29 S7-R6 — dark-mode support + the grey info icon's colour token at ≥ 3:1 against the cell background in both modes; the ratio is a design-token property so the manual check is by-eye legibility)</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>The report is server-paginated - the backend returns one page of rows at a time</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>PV — API</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with more rows in the result set than one page holds.
 2. Browser devtools (network tab) are open to observe the backend requests.
 3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>1. Load the report and observe the backend data request and its response size.
 2. Move to the next page of rows and observe the traffic.</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>1. The backend returns ONE page of rows at a time - the full result set is not shipped to the browser.
 2. Paging is resolved on the server: moving to another page issues a fresh backend request for that page.
@@ -3973,48 +3932,48 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R10).</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>SV-8642 (PV spec v4 2026-07-29 §2 (server-paginated); S2-R10)</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>Each filter or search change re-queries the server and returns page one</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>PV — API</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded and the browser devtools network tab open.
 2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>1. Change each of these in turn and watch the network traffic: Type, date range, Bin, Location, Category, Vendor, and the toolbar search.
 2. After a filter change while on a later page, note which page of results is shown.</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>1. EACH change (Type, date range, Bin, Location, Category, Vendor, search) triggers a fresh server-side data load.
 2. There is no client-side-only narrowing - every filter or search change re-queries the server.
@@ -4023,49 +3982,49 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R10).</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>SV-8642 (PV spec v4 2026-07-29 S2-R10)</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>Header-click sorting re-queries the server; nulls first asc and last desc</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>PV — API</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded (including rows with null values in a sortable column) and the network tab open.
 2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>1. Click a column header and watch the network traffic and the returned order.
 2. Click it again (reverse direction) and observe.
 3. Note where the null rows land in the server-returned order for each direction.</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>1. Each header click re-fetches the data from the server, ordered by the chosen column and direction, returning the first page of the re-sorted result set.
 2. Null values are placed FIRST on ascending and LAST on descending - as a server sort semantic, so the same order appears on screen and in the exports.
@@ -4074,49 +4033,49 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S3-R3).</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>SV-8643 (PV spec v4 2026-07-29 S3-R3)</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>The back end serves report data and export on ordinary reports access</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>PV — API</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in as a user whose role has the ordinary reports access turned on and no other reports-related permission turned on.
 2. Browser devtools (network tab) are open.
 3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>1. Open the Parts Velocity report and observe the backend data request's outcome.
 2. Attempt the export and observe the backend export request's outcome.</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>1. The back end returns the report data - the request is not refused.
 2. The back end returns the export file - the request is not refused.
@@ -4126,36 +4085,36 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S1-R4, S1-N2); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>SV-8641 (PV spec S1-R4; S1-N2 - RESCOPED 2026-08-03; same driver as C30327: Chris Ward Q2=A "single Reports permission" + "they can exist and not do anything"; QA lead "ONE permission FOR NOW")</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>QuickBooks amount for a part-of-a-unit sale is exact and never inflated</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>PV — API</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>1. The test company is connected to QuickBooks.
 2. The part-of-a-unit sale has been made and invoiced — a ZZAUTOTEST part sold in a quantity such as 2.5, at a known unit cost such as $10.00.
@@ -4163,7 +4122,7 @@
 4. This test cannot be run without a company whose QuickBooks account is connected, because it checks what was sent to QuickBooks. If no QuickBooks-connected company is available, mark this test Blocked and say so — do not guess the result.</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>1. Write down the quantity sold and the part's unit cost, and work out the correct amount by hand (2.5 x $10.00 = $25.00).
 2. Let the invoice go across to QuickBooks the normal way the shop does it.
@@ -4172,7 +4131,7 @@
 5. Go back to the Parts Velocity report and read the same part's Units Sold value.</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>1. The QuickBooks amount is exactly the hand-worked figure to the cent — $25.00 for 2.5 at $10.00.
 2. It is NOT a whole-unit amount such as $20.00 or $30.00, and it is NOT a bigger, multiplied figure.
@@ -4182,13 +4141,13 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and this point is not covered by any of the six report specifications — it comes from the engineering technical plan.</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>SV-8589 (verbatim Tests: 'QB journal amount exact from fractional movement'; Goal: 'QB journal-entry sync multiplies these into dollar amounts'; tech-plan-2026-07-29 Phase 0 / PR-1 D2 - no report spec covers QuickBooks)</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr"/>
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/Report-Suite_Parts-Velocity-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Parts-Velocity-Report_testrail-import.xlsx
@@ -885,8 +885,6 @@
 3. Selecting a non-custom option immediately reloads the report data.
 4. The named ranges use the application's standard shared calendar boundaries (the same boundaries every report's date picker uses).
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R2).</t>
         </is>
       </c>
@@ -1402,8 +1400,6 @@
           <t>1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
 2. For the user with access to two or more locations the Location filter IS shown.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-E4); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
@@ -2583,14 +2579,13 @@
 2. After the reversal, Demand is STILL 2 - a reversal event neither adds to nor subtracts from the count (while Units Sold nets down).
 3. The special-order part's Demand is 2 - the count of its in-window vendor part requests.
 4. Demand is the report's default ranking signal (a whole number, never null - 0 when none).
-5. A part whose single in-window sale is invoiced and then fully reversed shows Demand 1 with Units Sold 0.00 — the Demand count is not decremented, while the movement nets to zero.
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R4, S3-E1).</t>
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R4).</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>SV-8645 (PV spec v4 2026-07-29 S5-R4 (Demand); §4; §3 Key Decisions; S3-E1)</t>
+          <t>SV-8645 (PV spec v4 2026-07-29 S5-R4 (Demand); §4; §3 Key Decisions)</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
@@ -3414,8 +3409,6 @@
 4. Part # is NOT truncated.
 5. The shop logo shows at the top of the PDF when one is set. With no uploaded logo the PDF shows the bundled ShopView default logo instead of a blank space, the same as the other reports in this suite. The CSV never includes a logo.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S6-R5, S6-R6).</t>
         </is>
       </c>
@@ -3466,8 +3459,6 @@
 2. The CSV carries the FULL, untruncated Description / Category / Vendor values (unlike the PDF's 18-character cut).
 3. Last Sale is a raw integer in the CSV (e.g. 42) - the 'N days' wording is PDF/on-screen only.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S6-R5, S6-R6, S6-R8).</t>
         </is>
       </c>

--- a/testrail-import/Report-Suite_Parts-Velocity-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Parts-Velocity-Report_testrail-import.xlsx
@@ -885,6 +885,8 @@
 3. Selecting a non-custom option immediately reloads the report data.
 4. The named ranges use the application's standard shared calendar boundaries (the same boundaries every report's date picker uses).
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R2).</t>
         </is>
       </c>
@@ -1400,6 +1402,8 @@
           <t>1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
 2. For the user with access to two or more locations the Location filter IS shown.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-E4); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
@@ -2579,13 +2583,14 @@
 2. After the reversal, Demand is STILL 2 - a reversal event neither adds to nor subtracts from the count (while Units Sold nets down).
 3. The special-order part's Demand is 2 - the count of its in-window vendor part requests.
 4. Demand is the report's default ranking signal (a whole number, never null - 0 when none).
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R4).</t>
+5. A part whose single in-window sale is invoiced and then fully reversed shows Demand 1 with Units Sold 0.00 — the Demand count is not decremented, while the movement nets to zero.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R4, S3-E1).</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>SV-8645 (PV spec v4 2026-07-29 S5-R4 (Demand); §4; §3 Key Decisions)</t>
+          <t>SV-8645 (PV spec v4 2026-07-29 S5-R4 (Demand); §4; §3 Key Decisions; S3-E1)</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
@@ -3409,6 +3414,8 @@
 4. Part # is NOT truncated.
 5. The shop logo shows at the top of the PDF when one is set. With no uploaded logo the PDF shows the bundled ShopView default logo instead of a blank space, the same as the other reports in this suite. The CSV never includes a logo.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S6-R5, S6-R6).</t>
         </is>
       </c>
@@ -3459,6 +3466,8 @@
 2. The CSV carries the FULL, untruncated Description / Category / Vendor values (unlike the PDF's 18-character cut).
 3. Last Sale is a raw integer in the CSV (e.g. 42) - the 'N days' wording is PDF/on-screen only.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S6-R5, S6-R6, S6-R8).</t>
         </is>
       </c>

--- a/testrail-import/Report-Suite_Parts-Velocity-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Parts-Velocity-Report_testrail-import.xlsx
@@ -2743,7 +2743,6 @@
 2. Part B shows 0.00 (renders 0.00 when On Hand is 0 - not an error, not —).
 3. Part C shows a NEGATIVE Turns / Yr with a leading minus (because Units Sold can be negative).
 4. Special Order rows always show — (not applicable).
-Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8819
 ---
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R4).</t>
         </is>
@@ -3106,7 +3105,6 @@
 2. In W2 (movement date in window): Units Sold / Demand count it, the billed columns do not - the two anchors CAN differ for an inventory part and that is intended.
 3. The window is the whole-day span inclusive of BOTH the start and end dates, with a floor of 1 day - a single-day range (Today) computes normally (Window = 1 for the Turns / Yr divisor).
 4. Last Sale is not windowed at all (all-time).
-Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8819
 ---
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R7).</t>
         </is>

--- a/testrail-import/Report-Suite_Parts-Velocity-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Parts-Velocity-Report_testrail-import.xlsx
@@ -527,7 +527,7 @@
 2. Under Parts there is an entry labeled Parts Velocity; Inventory Value also lives under Parts. The order of the two inside the Parts section is not fixed — do not fail the test on which of them comes first.
 3. Clicking it opens the Parts Velocity report.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S1-R1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S1-R1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -577,7 +577,7 @@
 2. Report data loads automatically - you do not have to press anything to fetch it.
 3. Rows appear ranked by Demand, highest first (the default order).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S1-R2, S4-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S1-R2, S4-R6).</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -628,7 +628,7 @@
 2. During a filter change, the loading indicator shows again.
 3. The rows already on screen are replaced only when the new data comes back - the table does not blank out and rebuild mid-request.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S1-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S1-R3).</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -680,7 +680,7 @@
 2. The export downloads successfully — both opening the report and exporting it are allowed by the same ordinary reports access.
 3. Note for the tester: for now ONE ordinary reports access opens all six of these new reports; none of them has a permission of its own. If the build demands a separate report permission before this works, mark this Failed and report it — do not change the test.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S1-R4); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S1-R4); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -728,7 +728,7 @@
           <t>1. The user cannot reach the Reports section.
 2. The Parts Velocity navigation entry is not shown (this is the Reports section's own access control, not a report-specific rule).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S1-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S1-N1).</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
 3. The export downloads.
 4. Note for the tester: for now ONE ordinary reports access opens all six of these new reports, and no report has a permission of its own. If an extra Parts or Inventory reports permission does exist and switching it OFF blocks this report or its export, that is wrong - mark this Failed and report it. If a separate per-report permission is ever added on purpose in a later release, this test will be updated first, so treat that as a planned change and not as a bug.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S1-N2, S1-R4); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S1-N2, S1-R4); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -835,7 +835,7 @@
 4. Both is an explicit selection returning inventory and Special Order rows together - a deliberate filter value, not the absence of a filter.
 5. Each selection immediately reloads the report limited to that type (no separate Apply step) - under Inventory every row's Type column reads Inventory; under Special Order every row's Type column reads Special Order; under Both, rows of both kinds appear.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R1, S3-R5); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-R1, S3-R5); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -887,7 +887,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-R2).</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -939,7 +939,7 @@
 3. With both valid dates selected, the data reloads for that range.
 4. A span wider than 366 days (counting both the start and end dates) is rejected - the selection is not applied.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-R3).</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -991,7 +991,7 @@
 3. With vendors selected, only parts supplied by any of the selected vendors are shown.
 4. Each change reloads the data from the server.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R4, S2-R5, S2-R10).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-R4, S2-R5, S2-R10).</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
 3. The description search returns rows whose description contains the word.
 4. Category and vendor names are NOT searched - use their dedicated filters instead (deliberate, to avoid false matches on common words).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-R6).</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
 2. After step 3 the part disappears - a part must satisfy EVERY active filter to appear (AND logic, not OR).
 3. After step 4 the part is listed again.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-R7).</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
 2. Only inventory parts stocked in ANY of the selected bins are shown.
 3. The filter allows more than one bin (multi-select).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-R8).</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1196,7 +1196,7 @@
           <t>1. With any Bin filter active, ALL Special Order rows are excluded (they have no bin location).
 2. Special Order combined with any Bin filter yields an empty result showing the empty state - this is by design, not a defect.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R8); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-R8); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1253,7 +1253,7 @@
 6. With 'All Locations' active you can tell which location each row's data belongs to — a location label or marking is shown. (Exactly where and how it appears is confirmed in the build.)
 7. The page itself shows which location(s) the report is currently scoped to (the new on-screen scope indicator - exactly where and how it appears is confirmed in the build).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R9); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-R9); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1301,7 +1301,7 @@
           <t>1. The server returns zero rows and the table shows the empty state.
 2. The empty-state label reads exactly: "Empty bays, endless possibilities. Get Going!" (the application's standard reports no-data label).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R11, S2-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-R11, S2-N1).</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1353,7 +1353,7 @@
 2. The part with no vendor does not appear when any Vendor filter is active.
 3. The inventory part with no bin location does not appear when any Bin filter is active.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-E1, S2-E2, S2-E3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-E1, S2-E2, S2-E3).</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-E4); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-E4); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1461,7 +1461,7 @@
 5. With a single location in scope the Location column is hidden.
 6. Both downloads include the Location column in the same position it holds on screen (leftmost, before Type), with the same values — each inventory row's own location, and "Multiple" on the merged Special Order row.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R12, S3-R10, S7-R8, S6-R11).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-R12, S3-R10, S7-R8, S6-R11).</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1511,7 +1511,7 @@
 2. Each row carries only that one location's On Hand, Min, and Max.
 3. On Hand / Min / Max are NEVER summed across locations.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S3-R1a).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S3-R1a).</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1562,7 +1562,7 @@
 2. Its movement and profitability values are the SUM of the per-location values.
 3. Its inventory-only columns (On Hand, Turns / Yr, Min, Max) show — (em-dash), because special-order parts are not stocked.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S3-R1a).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S3-R1a).</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
 3. Rows with equal Demand keep inventory-before-special-order order.
 4. The Demand header shows the descending sort indicator - this initial order IS the active sort (it is what the remembered view saves until you click another header).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S3-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S3-R2).</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1668,7 +1668,7 @@
 3. Null / — values are placed FIRST on ascending and LAST on descending.
 4. Every column is sortable; each header click re-fetches the data (server-resolved) and shows the first page of the re-sorted result; ties keep a stable order.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S3-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S3-R3).</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1718,7 +1718,7 @@
 2. The Type column shows each row's kind as plain text (no badge or chip styling): "Inventory" or "Special Order".
 3. ALL columns - header and cell data, including numbers and money - are left-aligned on screen. (The exports right-align numerics instead: a deliberate export-only difference.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S3-R4, S3-R5, S3-R8); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S3-R4, S3-R5, S3-R8); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
 5. The icon is focusable and exposes the same text to assistive technology; activating it does NOT trigger a column sort.
 6. No other column header carries an info icon.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S3-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S3-R6).</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1825,7 +1825,7 @@
 2. The full value shows on native hover (browser tooltip).
 3. Part # is NEVER truncated - on screen (and in the exports).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S3-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S3-R7).</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1874,7 +1874,7 @@
           <t>1. On Hand, Turns / Yr, Min, and Max show — (em-dash) on special-order rows - always.
 2. The count metrics and money totals are NEVER null: Units Sold / Units Returned / Sold (WO) / Sold (Parts Sale) show 0.00, Demand shows 0, Revenue and Margin show $0.00.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S3-R9, S5-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S3-R9, S5-R5).</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
 2. Part B DOES appear - a part with billed Revenue &gt; 0 is always kept even with no stock movement and no on-hand stock.
 3. (Special Order parts have no such rule: a never-requested special-order part simply produces no row.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S3-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S3-N1).</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1973,7 +1973,7 @@
           <t>1. The picker lists all 20 available columns, each with a toggle: Type, Part #, Description, Category, Vendor, Units Sold, Units Returned, Sold (WO), Sold (Parts Sale), Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand, Turns/Yr, Min, Max.
 2. No on-hand cost column is offered - the report computes one internally but it is never selectable and never displayed.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S4-R1, S4-R4, S5-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S4-R1, S4-R4, S5-R6).</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2021,7 +2021,7 @@
 2. The other 6 columns start hidden: Units Returned, Sold (WO), Sold (Parts Sale), Turns / Yr, Min, Max.
 3. When more than one location is in scope the automatic Location column shows as well, leftmost before Type — 15 columns. It is not part of the 14-column default set and is not in the column picker, so its presence is expected and is not a failure of this test.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S4-R2, S4-R3, S3-R10).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S4-R2, S4-R3, S3-R10).</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2071,7 +2071,7 @@
 2. Columns always render in the fixed canonical left-to-right order regardless of the order they were toggled on (with the automatic Location column, when shown, sitting leftmost before Type): Type, Part #, Description, Category, Vendor, Units Sold, Units Returned, Sold (WO), Sold (Parts Sale), Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand, Turns/Yr, Min, Max.
 3. So Units Returned slots in right after Units Sold, Turns/Yr after On Hand, and Min before Max - not appended at the end.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S4-R4, S4-R5, S3-R10).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S4-R4, S4-R5, S3-R10).</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
 3. The saved values take precedence over the first-visit defaults (This Year / Both / active location / 14 columns / Demand-descending).
 4. The same holds after a full page reload.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S4-R6, S1-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S4-R6, S1-R2).</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2171,7 +2171,7 @@
 2. That one setting falls back to its default (e.g. the location falls back to the active location); the other saved settings still restore normally.
 3. The report loads without an error.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S4-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S4-R6).</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2220,7 +2220,7 @@
           <t>1. User 2 sees user 1's saved view (Type = Special Order, Last Quarter, the saved columns and sort).
 2. This is by design: storage is per browser, not tied to the account - there is no per-account separation.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S4-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S4-R6).</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
 2. The export produces a file containing only the header/metadata rows and no data columns.
 3. On the next visit the all-hidden selection is NOT restored - the report falls back to the default 14-column set (the saved column selection returns to the last NON-EMPTY selection; all-hidden is the exception).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S4-E1, S4-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S4-E1, S4-R6).</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2322,7 +2322,7 @@
 3. After step 3, Units Sold is UNCHANGED - part returns do not affect Units Sold (they feed Units Returned instead).
 4. Units Sold can be 0.00 or negative when reversals exceed sales.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R1, S5-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R1, S5-R4).</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2372,7 +2372,7 @@
 2. The reversed/voided sale is EXCLUDED from the total (net of reversals).
 3. Only requests on work orders at status Invoiced or Paid count; the window is anchored to the work-order date.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R2, S5-R4, S5-R4b).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R2, S5-R4, S5-R4b).</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
 3. After step 3, it decreases by 2.00 - the column reflects the CURRENT state of return records (cancelled returns are excluded), not a snapshot.
 4. After step 4, Units Returned is UNCHANGED - invoice reversals are not returns (they affect Units Sold instead).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R3, S5-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R3, S5-R4).</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2479,7 +2479,7 @@
 4. Units Returned is independent of the work order's current invoice status.
 5. A part whose ONLY in-window event is a return (no sale, no stock, no revenue) produces no row at all - accepted behavior, the row axis is sales/stock activity.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R3).</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2531,7 +2531,7 @@
 3. Both are windowed by the WORK-ORDER date (its end date) - with the range moved off those dates, both drop out.
 4. Both workflows feed the report - a parts sale is a separate workflow from a service work order but counts fully.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R4).</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2585,7 +2585,7 @@
 4. Demand is the report's default ranking signal (a whole number, never null - 0 when none).
 5. A part whose single in-window sale is invoiced and then fully reversed shows Demand 1 with Units Sold 0.00 — the Demand count is not decremented, while the movement nets to zero.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R4, S3-E1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R4, S3-E1).</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2640,7 +2640,7 @@
 4. For a special-order part, the anchor is its most recent vendor-sourced invoiced/paid request.
 5. When the most recent sale is reversed, Last Sale re-anchors to the previous remaining sale (the day count grows accordingly); if no other sale remains it shows —.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R4, S5-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R4, S5-R5).</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2690,7 +2690,7 @@
 2. Min and Max show the stored minimum / maximum reorder thresholds for that location, as whole numbers (— when not set).
 3. Min and Max are READ-ONLY display columns - no edit control or slide-over opens; editing part attributes from this report is out of scope in this version.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R4, S5-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R4, S5-R5).</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2744,7 +2744,7 @@
 3. Part C shows a NEGATIVE Turns / Yr with a leading minus (because Units Sold can be negative).
 4. Special Order rows always show — (not applicable).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R4).</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2797,7 +2797,7 @@
 5. All five are computed from the RAW (unrounded) Revenue / COGS / billed-units totals and rounded ONCE at the end - not built from already-rounded intermediates.
 6. The same formulas apply to inventory and special-order rows (for special-order, from the vendor part requests).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R4a).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R4a).</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2848,7 +2848,7 @@
 2. This netting is consistent with inventory Units Sold, which already nets reversals via the stock add-back.
 3. A voided sale therefore inflates NO column.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R4b, S5-R4a).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R4b, S5-R4a).</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2901,7 +2901,7 @@
 3. Row 3: Unit Cost, Sell Price, and Margin % all show — together - which happens ONLY when both billed units ≤ 0 AND Revenue ≤ 0.
 4. The three triggers are independent: Unit Cost/Sell Price null on billed units ≤ 0; Margin % null on Revenue ≤ 0.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R4a, S3-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R4a, S3-R9).</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2952,7 +2952,7 @@
 4. Demand: whole number. Min, Max: whole numbers (— when null). Last Sale: 'N days' (42 days), — when null.
 5. Rounding is half AWAY from zero: 8.45% displays 8.5% and -8.45% displays -8.5% (a tie rounds up in magnitude); this applies to all money and one-decimal values.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R5, S5-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R5, S5-R7).</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3002,7 +3002,7 @@
 2. The special-order core part does NOT appear either.
 3. Parts flagged as a core are excluded from both result sets by design.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R1, S5-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R1, S5-R2).</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3054,7 +3054,7 @@
 2. Sold (WO) + Sold (Parts Sale) together DO equal the billed-units basis (work orders are only Service- or Parts-type) - but neither equals the movement-based Units Sold.
 3. On the special-order row, everything reconciles: Units Sold = Sold (WO) + Sold (Parts Sale) = billed units (they share the vendor-request quantity as one source).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R7).</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -3106,7 +3106,7 @@
 3. The window is the whole-day span inclusive of BOTH the start and end dates, with a floor of 1 day - a single-day range (Today) computes normally (Window = 1 for the Turns / Yr divisor).
 4. Last Sale is not windowed at all (all-time).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R7).</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3161,7 +3161,7 @@
 3. On Hand has gone down by exactly 2.50 from what it was before the sale.
 4. No value anywhere on the row has been quietly rounded to a whole number.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R1, S5-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R1, S5-R5).</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -3209,7 +3209,7 @@
           <t>1. The ⋯ overflow button sits leftmost in the toolbar's action cluster.
 2. The menu holds exactly two items, in this order: Download (PDF), then Download (CSV).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S6-R1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S6-R1).</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3259,7 +3259,7 @@
 2. The exported rows match what the on-screen grid was showing.
 3. Each file (PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to (exact position in the file is confirmed in the build).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S6-R2, S6-R11); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S6-R2, S6-R11); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3309,7 +3309,7 @@
 2. Columns appear in the CANONICAL order (the fixed on-screen order) - the re-enabled Units Returned sits right after Units Sold, NOT appended at the end.
 3. The export mirrors the visible grid.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S6-R3, S4-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S6-R3, S4-R4).</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3360,7 +3360,7 @@
 2. Every column's sort is honored in the export - including Min and Max.
 3. The export renders the EXACT server order, including null placement (nulls first on ascending, last on descending) - the export and the on-screen grid match; there is no on-screen-vs-export null-sorting difference.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S6-R4, S3-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S6-R4, S3-R3).</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3414,7 +3414,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S6-R5, S6-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S6-R5, S6-R6).</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3466,7 +3466,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S6-R5, S6-R6, S6-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S6-R5, S6-R6, S6-R8).</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3515,7 +3515,7 @@
           <t>1. A null value renders as — (em-dash) in BOTH the CSV and the PDF, in every nullable field: Unit Cost, Sell Price, Margin %, On Hand, Turns / Yr, Last Sale, Min, Max.
 2. Revenue, Margin, and the count metrics are never null in the exports either ($0.00 / 0.00 / 0).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S6-R7, S6-R8, S3-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S6-R7, S6-R8, S3-R9).</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
 4. This is a deliberate export-only treatment - the on-screen table is all-left-aligned; the difference is documented, not a defect.
 5. The CSV is plain data — the alignment assertions apply to the PDF only; how a spreadsheet displays the CSV is not part of this test.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S6-R10, S3-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S6-R10, S3-R8).</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3617,7 +3617,7 @@
 2. An error toast is shown on failure; when the server provides a message, that server message is shown.
 3. Otherwise the failure toast reads exactly: "Failed to export velocity report (csv)" or "Failed to export velocity report (pdf)" — lowercase (csv)/(pdf); the success/failure casing mix is the shipped wording, documented as-is (not a bug).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S6-R9, S6-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S6-R9, S6-N1).</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3670,7 +3670,7 @@
 3. After narrowing below the cap, the downloads work again.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (Story 6 exports).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (Story 6 exports).</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3724,7 +3724,7 @@
 4. Note for the tester: a very large view is refused politely with "This report is too large to export. Narrow the date range or filters, then try again." — that message is expected and is NOT this failure. This test is about a medium-sized view where the CSV works but the PDF errors.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (Story 6 exports).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (Story 6 exports).</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3773,7 +3773,7 @@
 2. There is NO card border-radius - the table runs edge to edge.
 3. The layout matches the application's other reports.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S7-R1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S7-R1).</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3826,7 +3826,7 @@
 4. It all looks the same as the other reports in the suite: put another report side by side and nothing should look out of place.
 5. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether the spacing and the dividing line look right and consistent with the other reports, and only report it if something looks obviously off. (The exact figures behind this - 32px/24px toolbar padding, a 1px header border, 2rem edge padding - are design-token values the design and engineering team check with their own tooling, not by hand.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S7-R2, S7-R3, S7-R4, S7-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S7-R2, S7-R3, S7-R4, S7-R5).</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -3876,7 +3876,7 @@
 2. In BOTH light mode and dark mode the grey ⓘ info icon is clearly visible against the cell behind it - you can see it at a glance without leaning in, and it does not disappear into the background.
 3. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether you can see the icon easily in both modes. Only report it if the icon is hard to see. (The design rule behind this is a minimum 3:1 contrast ratio, which the design and engineering team check with a contrast tool - not by hand.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S7-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S7-R6).</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -3927,7 +3927,7 @@
 2. Paging is resolved on the server: moving to another page issues a fresh backend request for that page.
 3. This keeps the report responsive at scale (organizations can carry 50-60k parts, multiplied across locations).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R10).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-R10).</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -3977,7 +3977,7 @@
 2. There is no client-side-only narrowing - every filter or search change re-queries the server.
 3. Each change returns the FIRST page of the new result set.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R10).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-R10).</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4028,7 +4028,7 @@
 2. Null values are placed FIRST on ascending and LAST on descending - as a server sort semantic, so the same order appears on screen and in the exports.
 3. Ties keep a stable order (no explicit secondary key).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S3-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S3-R3).</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4080,7 +4080,7 @@
 3. Both requests succeed with only the ordinary reports access turned on - nothing else had to be enabled.
 4. Note for the tester: if the back end refuses either request for a user who has the ordinary reports access, mark this Failed and report it. If an extra Parts or Inventory reports permission exists in the system it must not change these results - for now it is hidden from the screen and enforces nothing. A per-report permission added on purpose in a later release is a planned change, not a bug, and this test will be updated first.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S1-R4, S1-N2); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S1-R4, S1-N2); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4136,7 +4136,7 @@
 3. The quantity behind the QuickBooks amount matches the Units Sold value on the report (2.50) — the two systems agree.
 4. No second or correcting journal entry is created to patch up a wrong amount.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and this point is not covered by any of the six report specifications — it comes from the engineering technical plan.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and this point is not covered by any of the six report specifications — it comes from the engineering technical plan.</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">

--- a/testrail-import/Report-Suite_Parts-Velocity-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Parts-Velocity-Report_testrail-import.xlsx
@@ -880,14 +880,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1. The options are exactly: Today, Yesterday, This Week, Last Week, This Month, Last Month, This Year, Last Year, This Quarter, Last Quarter, Custom.
-2. There is NO 'All Time' option - the report always operates over a bounded date window (deliberate, per the spec's Out of Scope).
+          <t>1. The chooser offers nine ready-made periods, in this order: Last 12 Months, This Year, Last Year, This Quarter, Last Quarter, This Month, Last Month, This Week, Last Week. Beside them it shows a month calendar you click dates on to build your own range, a live readout of how many days the range covers, and an Apply button. There is no "Today", no "Yesterday" and no item called "Custom" - you build your own range on the calendar instead. There is no "All Time" option.
+2. The report always operates over a bounded date window, which is why no All-Time period is offered.
 3. Selecting a non-custom option immediately reloads the report data.
 4. The named ranges use the application's standard shared calendar boundaries (the same boundaries every report's date picker uses).
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023). Where the Parts Velocity report specification version 4 (S2-R2) says something different, the behaviour above follows Chris Ward's decision of 8/5/2026 instead, which is the authority - that decision is recorded in his answers, in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1402,9 +1400,7 @@
           <t>1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
 2. For the user with access to two or more locations the Location filter IS shown.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-E4); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-E4). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1457,11 +1453,14 @@
           <t>1. With more than one location in scope a Location column is shown as the LEFTMOST column, before Type.
 2. Each inventory row shows its own location's name (an inventory row is one part at one location).
 3. The merged Special Order row shows "Multiple", because it is summed across the selected locations.
-4. Location is NOT one of the 20 columns in the picker — it is managed by the location scope, not by you.
+4. Location is one of the columns in the column-selection control, and with more than one location SELECTED it is already switched on for you - you do not have to turn it on. You can still switch it off. If the signed-in person only has access to ONE location, Location is not offered in the column-selection list at all.
 5. With a single location in scope the Location column is hidden.
 6. Both downloads include the Location column in the same position it holds on screen (leftmost, before Type), with the same values — each inventory row's own location, and "Multiple" on the merged Special Order row.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-R12, S3-R10, S7-R8, S6-R11).</t>
+Note for the tester: on this build the column does not yet behave this way - record what you see and carry on. The change is with the developers.
+DO NOT AUTOMATE YET: part of this behaviour is still waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
+This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Parts Velocity report specification version 4 (S2-R12, S3-R10, S7-R8, S6-R11) differs, his decision is the authority.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2019,9 +2018,11 @@
         <is>
           <t>1. With a single location in scope exactly these 14 columns show, in this left-to-right order: Type, Part #, Description, Category, Vendor, Units Sold, Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand.
 2. The other 6 columns start hidden: Units Returned, Sold (WO), Sold (Parts Sale), Turns / Yr, Min, Max.
-3. When more than one location is in scope the automatic Location column shows as well, leftmost before Type — 15 columns. It is not part of the 14-column default set and is not in the column picker, so its presence is expected and is not a failure of this test.
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S4-R2, S4-R3, S3-R10).</t>
+3. When more than one location is selected the Location column shows as well, leftmost before Type — 15 columns. It is already switched on for you; you do not have to turn it on, and you can switch it off again. It is not part of the 14-column default set, so its presence is expected and is not a failure of this test.
+---
+DO NOT AUTOMATE YET: part of this behaviour is still waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
+This is the expected behaviour as per the Parts Velocity report specification version 4 (S4-R2, S4-R3, S3-R10) for the 14 default columns and the 6 hidden ones. The part about the Location column follows Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true; his decision differs from what this case said before, which stated the Location column is not in the column picker, and we have taken his later decision as the one that prevails.</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -3410,11 +3411,10 @@
 2. The PDF is formatted for A3 landscape and titled Parts Velocity.
 3. Description, Category, and Vendor are truncated to 18 characters in the PDF.
 4. Part # is NOT truncated.
-5. The shop logo shows at the top of the PDF when one is set. With no uploaded logo the PDF shows the bundled ShopView default logo instead of a blank space, the same as the other reports in this suite. The CSV never includes a logo.
----
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S6-R5, S6-R6).</t>
+5. With a logo uploaded, that logo appears. If a logo is set but fails to load, the built-in ShopView logo is used instead. If no logo is uploaded at all, NO logo is printed and the text fills the space. The CSV never includes a logo.
+Note for the tester: on this build a report with no uploaded logo still prints the built-in ShopView logo. The product owner has decided it should print no logo at all, so record what you see; the change is with the developers.
+---
+This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Parts Velocity report specification version 4 (S6-R5, S6-R6) differs, his decision is the authority.</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3464,8 +3464,6 @@
 2. The CSV carries the FULL, untruncated Description / Category / Vendor values (unlike the PDF's 18-character cut).
 3. Last Sale is a raw integer in the CSV (e.g. 42) - the 'N days' wording is PDF/on-screen only.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S6-R5, S6-R6, S6-R8).</t>
         </is>
       </c>

--- a/testrail-import/Report-Suite_Parts-Velocity-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Parts-Velocity-Report_testrail-import.xlsx
@@ -523,11 +523,13 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>1. A Parts section heading exists in the Reports navigation (this feature creates it - the application had no Parts reports before).
+          <t xml:space="preserve">1. A Parts section heading exists in the Reports navigation (this feature creates it - the application had no Parts reports before).
 2. Under Parts there is an entry labeled Parts Velocity; Inventory Value also lives under Parts. The order of the two inside the Parts section is not fixed — do not fail the test on which of them comes first.
 3. Clicking it opens the Parts Velocity report.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S1-R1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S1-R1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -573,11 +575,13 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>1. The date range selector shows This Year.
+          <t xml:space="preserve">1. The date range selector shows This Year.
 2. Report data loads automatically - you do not have to press anything to fetch it.
 3. Rows appear ranked by Demand, highest first (the default order).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S1-R2, S4-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S1-R2, S4-R6).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -624,11 +628,13 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1. During the initial load, the table shows a loading indicator.
+          <t xml:space="preserve">1. During the initial load, the table shows a loading indicator.
 2. During a filter change, the loading indicator shows again.
 3. The rows already on screen are replaced only when the new data comes back - the table does not blank out and rebuild mid-request.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S1-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S1-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -676,11 +682,13 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1. The report data loads and rows are shown.
+          <t xml:space="preserve">1. The report data loads and rows are shown.
 2. The export downloads successfully — both opening the report and exporting it are allowed by the same ordinary reports access.
-3. Note for the tester: for now ONE ordinary reports access opens all six of these new reports; none of them has a permission of its own. If the build demands a separate report permission before this works, mark this Failed and report it — do not change the test.
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S1-R4); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+3. Note for the tester: the specification allows ONE ordinary reports access for all six of these new reports and no per-report permission. If the build demands a separate report permission before this works, mark this Failed and report it — do not change the test.
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S1-R4); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -725,10 +733,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1. The user cannot reach the Reports section.
+          <t xml:space="preserve">1. The user cannot reach the Reports section.
 2. The Parts Velocity navigation entry is not shown (this is the Reports section's own access control, not a report-specific rule).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S1-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S1-N1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -775,12 +785,14 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1. The Parts Velocity entry is visible in the Reports navigation under Parts.
+          <t xml:space="preserve">1. The Parts Velocity entry is visible in the Reports navigation under Parts.
 2. Opening it shows the report data - not an access-denied screen.
 3. The export downloads.
-4. Note for the tester: for now ONE ordinary reports access opens all six of these new reports, and no report has a permission of its own. If an extra Parts or Inventory reports permission does exist and switching it OFF blocks this report or its export, that is wrong - mark this Failed and report it. If a separate per-report permission is ever added on purpose in a later release, this test will be updated first, so treat that as a planned change and not as a bug.
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S1-N2, S1-R4); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+4. Note for the tester: the specification allows ONE ordinary reports access for all six of these new reports and no per-report permission. If an extra Parts or Inventory reports permission does exist and switching it OFF blocks this report or its export, that is wrong - mark this Failed and report it. If a separate per-report permission is ever added on purpose in a later release, this test will be updated first, so treat that as a planned change and not as a bug.
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S1-N2, S1-R4); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -829,13 +841,15 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1. The Type filter is the first control in the filter row.
+          <t xml:space="preserve">1. The Type filter is the first control in the filter row.
 2. It is single-select and offers exactly three choices: Both, Inventory, and Special Order (special-order catalog parts that were never put into stock).
 3. On a first visit the default is Both.
 4. Both is an explicit selection returning inventory and Special Order rows together - a deliberate filter value, not the absence of a filter.
 5. Each selection immediately reloads the report limited to that type (no separate Apply step) - under Inventory every row's Type column reads Inventory; under Special Order every row's Type column reads Special Order; under Both, rows of both kinds appear.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-R1, S3-R5); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S2-R1, S3-R5); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -880,12 +894,14 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1. The chooser offers nine ready-made periods, in this order: Last 12 Months, This Year, Last Year, This Quarter, Last Quarter, This Month, Last Month, This Week, Last Week. Beside them it shows a month calendar you click dates on to build your own range, a live readout of how many days the range covers, and an Apply button. There is no "Today", no "Yesterday" and no item called "Custom" - you build your own range on the calendar instead. There is no "All Time" option.
+          <t xml:space="preserve">1. The chooser offers nine ready-made periods, in this order: Last 12 Months, This Year, Last Year, This Quarter, Last Quarter, This Month, Last Month, This Week, Last Week. Beside them it shows a month calendar you click dates on to build your own range, a live readout of how many days the range covers, and an Apply button. There is no "Today", no "Yesterday" and no item called "Custom" - you build your own range on the calendar instead. There is no "All Time" option.
 2. The report always operates over a bounded date window, which is why no All-Time period is offered.
 3. Selecting a non-custom option immediately reloads the report data.
 4. The named ranges use the application's standard shared calendar boundaries (the same boundaries every report's date picker uses).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023). Where the Parts Velocity report specification version 4 (S2-R2) says something different, the behaviour above follows Chris Ward's decision of 8/5/2026 instead, which is the authority - that decision is recorded in his answers, in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023). Where the Parts Velocity report specification version 5 (S2-R2) says something different, the behaviour above follows Chris Ward's decision of 8/5/2026 instead, which is the authority - that decision is recorded in his answers, in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -932,12 +948,14 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1. A date picker opens requiring both a start and an end date.
+          <t xml:space="preserve">1. A date picker opens requiring both a start and an end date.
 2. The report does not reload until both dates are valid; a start after the end is not accepted.
 3. With both valid dates selected, the data reloads for that range.
 4. A span wider than 366 days (counting both the start and end dates) is rejected - the selection is not applied.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S2-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -984,12 +1002,14 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1. Both filters allow selecting more than one value (multi-select).
+          <t xml:space="preserve">1. Both filters allow selecting more than one value (multi-select).
 2. With categories selected, only parts in any of the selected categories are shown.
 3. With vendors selected, only parts supplied by any of the selected vendors are shown.
 4. Each change reloads the data from the server.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-R4, S2-R5, S2-R10).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S2-R4, S2-R5, S2-R10).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1037,12 +1057,14 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1. The search input is part of the report's toolbar (page-specific), separate from the global search bar.
+          <t xml:space="preserve">1. The search input is part of the report's toolbar (page-specific), separate from the global search bar.
 2. The part-number search matches despite the different letter case (case-insensitive 'contains' match).
 3. The description search returns rows whose description contains the word.
 4. Category and vendor names are NOT searched - use their dedicated filters instead (deliberate, to avoid false matches on common words).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S2-R6).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1090,11 +1112,13 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1. After steps 1-2 the part is still listed (it satisfies both filters).
+          <t xml:space="preserve">1. After steps 1-2 the part is still listed (it satisfies both filters).
 2. After step 3 the part disappears - a part must satisfy EVERY active filter to appear (AND logic, not OR).
 3. After step 4 the part is listed again.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S2-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1140,11 +1164,13 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1. Each selection reloads the data from the server.
+          <t xml:space="preserve">1. Each selection reloads the data from the server.
 2. Only inventory parts stocked in ANY of the selected bins are shown.
 3. The filter allows more than one bin (multi-select).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S2-R8).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1191,10 +1217,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1. With any Bin filter active, ALL Special Order rows are excluded (they have no bin location).
+          <t xml:space="preserve">1. With any Bin filter active, ALL Special Order rows are excluded (they have no bin location).
 2. Special Order combined with any Bin filter yields an empty result showing the empty state - this is by design, not a defect.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-R8); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S2-R8); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1243,15 +1271,16 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1. The Location filter is the rightmost control in the filter row and is multi-select.
+          <t xml:space="preserve">1. The Location filter is the rightmost control in the filter row and is multi-select.
 2. On a first visit it defaults to the user's currently active location (the one in the global location switcher).
 3. The list holds the locations the signed-in user has access to, plus an 'All Locations' option.
 4. Each selection reloads the data scoped to the chosen set; 'All Locations' means all locations the user can ACCESS, never beyond - a location the user cannot access is never included.
 5. The location scope cascades through every metric like the other filters.
-6. With 'All Locations' active you can tell which location each row's data belongs to — a location label or marking is shown. (Exactly where and how it appears is confirmed in the build.)
-7. The page itself shows which location(s) the report is currently scoped to (the new on-screen scope indicator - exactly where and how it appears is confirmed in the build).
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-R9); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+6. With 'All Locations' active you can tell which location each row's data belongs to — a location label or marking is shown.
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S2-R9); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1296,10 +1325,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1. The server returns zero rows and the table shows the empty state.
+          <t xml:space="preserve">1. The server returns zero rows and the table shows the empty state.
 2. The empty-state label reads exactly: "Empty bays, endless possibilities. Get Going!" (the application's standard reports no-data label).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-R11, S2-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S2-R11, S2-N1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1347,11 +1378,13 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1. The part with no category does not appear when any Category filter is active.
+          <t xml:space="preserve">1. The part with no category does not appear when any Category filter is active.
 2. The part with no vendor does not appear when any Vendor filter is active.
 3. The inventory part with no bin location does not appear when any Bin filter is active.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-E1, S2-E2, S2-E3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S2-E1, S2-E2, S2-E3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1397,10 +1430,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
+          <t xml:space="preserve">1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
 2. For the user with access to two or more locations the Location filter IS shown.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-E4). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S2-E4). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1450,17 +1485,20 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1. With more than one location in scope a Location column is shown as the LEFTMOST column, before Type.
+          <t xml:space="preserve">1. With more than one location in scope a Location column is shown as the LEFTMOST column, before Type.
 2. Each inventory row shows its own location's name (an inventory row is one part at one location).
 3. The merged Special Order row shows "Multiple", because it is summed across the selected locations.
-4. Location is one of the columns in the column-selection control, and with more than one location SELECTED it is already switched on for you - you do not have to turn it on. You can still switch it off. If the signed-in person only has access to ONE location, Location is not offered in the column-selection list at all.
-5. With a single location in scope the Location column is hidden.
-6. Both downloads include the Location column in the same position it holds on screen (leftmost, before Type), with the same values — each inventory row's own location, and "Multiple" on the merged Special Order row.
+4. With a single location in scope the Location column is hidden.
+5. Both downloads include the Location column in the same position it holds on screen (leftmost, before Type), with the same values — each inventory row's own location, and "Multiple" on the merged Special Order row.
 ---
 Note for the tester: on this build the column does not yet behave this way - record what you see and carry on. The change is with the developers.
-DO NOT AUTOMATE YET: part of this behaviour is still waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Parts Velocity report specification version 4 (S2-R12, S3-R10, S7-R8, S6-R11) differs, his decision is the authority.</t>
+The Location column is not one of the columns in the column-selection control and you cannot switch it on or off: it appears by itself whenever more than one location is in scope, and is hidden whenever a single location is in scope.
+Note for the tester: the product owner has been asked to confirm this one point and has not answered yet, so do not raise a bug either way — record what you see. The question is in Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
+---
+---
+This is the expected behaviour as per the Parts Velocity report specification version 5 (S2-R12, S3-R10, S7-R8, S6-R11), and as per the build tested on 8/4/2026 (build v3.4.1-3d03023). The product owner's answer of 8/5/2026 in this file reads both ways on the one point about the Location column, so it has NOT been treated as overriding the specification and he has been asked again: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: HOLD - waiting on one answer from the product owner about the Location column
+</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1506,11 +1544,13 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1. The part appears as TWO inventory rows - one per selected location (an inventory part is a per-location stock record).
+          <t xml:space="preserve">1. The part appears as TWO inventory rows - one per selected location (an inventory part is a per-location stock record).
 2. Each row carries only that one location's On Hand, Min, and Max.
 3. On Hand / Min / Max are NEVER summed across locations.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S3-R1a).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S3-R1a).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1557,11 +1597,13 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1. The special-order part appears as a SINGLE row (one row per special-order part, merged across the selected locations).
+          <t xml:space="preserve">1. The special-order part appears as a SINGLE row (one row per special-order part, merged across the selected locations).
 2. Its movement and profitability values are the SUM of the per-location values.
 3. Its inventory-only columns (On Hand, Turns / Yr, Min, Max) show — (em-dash), because special-order parts are not stocked.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S3-R1a).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S3-R1a).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1609,12 +1651,14 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1. Rows are ranked by Demand, descending - the most-active parts first.
+          <t xml:space="preserve">1. Rows are ranked by Demand, descending - the most-active parts first.
 2. Inventory and special-order rows are ranked together in one list.
 3. Rows with equal Demand keep inventory-before-special-order order.
 4. The Demand header shows the descending sort indicator - this initial order IS the active sort (it is what the remembered view saves until you click another header).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S3-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S3-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1662,12 +1706,14 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1. The first click sorts that column ASCENDING; the header shows a direction indicator (an arrow).
+          <t xml:space="preserve">1. The first click sorts that column ASCENDING; the header shows a direction indicator (an arrow).
 2. Clicking the active sort column again reverses the direction; the arrow flips.
 3. Null / — values are placed FIRST on ascending and LAST on descending.
 4. Every column is sortable; each header click re-fetches the data (server-resolved) and shows the first page of the re-sorted result; ties keep a stable order.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S3-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S3-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1713,11 +1759,13 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1. The header row is sticky - it stays visible while the body scrolls.
+          <t xml:space="preserve">1. The header row is sticky - it stays visible while the body scrolls.
 2. The Type column shows each row's kind as plain text (no badge or chip styling): "Inventory" or "Special Order".
 3. ALL columns - header and cell data, including numbers and money - are left-aligned on screen. (The exports right-align numerics instead: a deliberate export-only difference.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S3-R4, S3-R5, S3-R8); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S3-R4, S3-R5, S3-R8); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1765,14 +1813,16 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1. Each of the three headers carries a grey info icon, shown always (not hover-to-reveal) whenever its column is visible; the Turns/Yr icon appears only once that column is enabled.
+          <t xml:space="preserve">1. Each of the three headers carries a grey info icon, shown always (not hover-to-reveal) whenever its column is visible; the Turns/Yr icon appears only once that column is enabled.
 2. Units Sold shows exactly: "Units taken out of inventory stock on invoiced work orders in this date range. This is stock movement, so it can differ from the units billed behind Revenue and Sell Price."
 3. Demand shows exactly: "Number of separate transactions (work orders or parts sales) this part appeared on in the selected date range. Each transaction counts once, no matter how many units were sold on it."
 4. Turns/Yr shows exactly: "How many times you sell through this part in a year. Higher is better."
 5. The icon is focusable and exposes the same text to assistive technology; activating it does NOT trigger a column sort.
 6. No other column header carries an info icon.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S3-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S3-R6).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1820,11 +1870,13 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1. Long Description, Category, and Vendor text is truncated with an ellipsis on screen.
+          <t xml:space="preserve">1. Long Description, Category, and Vendor text is truncated with an ellipsis on screen.
 2. The full value shows on native hover (browser tooltip).
 3. Part # is NEVER truncated - on screen (and in the exports).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S3-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S3-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1870,10 +1922,12 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>1. On Hand, Turns / Yr, Min, and Max show — (em-dash) on special-order rows - always.
+          <t xml:space="preserve">1. On Hand, Turns / Yr, Min, and Max show — (em-dash) on special-order rows - always.
 2. The count metrics and money totals are NEVER null: Units Sold / Units Returned / Sold (WO) / Sold (Parts Sale) show 0.00, Demand shows 0, Revenue and Margin show $0.00.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S3-R9, S5-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S3-R9, S5-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1919,11 +1973,13 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1. Part A does NOT appear - it fails all three keep-criteria (no movement, under one on hand, no revenue) so it carries nothing to act on.
+          <t xml:space="preserve">1. Part A does NOT appear - it fails all three keep-criteria (no movement, under one on hand, no revenue) so it carries nothing to act on.
 2. Part B DOES appear - a part with billed Revenue &gt; 0 is always kept even with no stock movement and no on-hand stock.
 3. (Special Order parts have no such rule: a never-requested special-order part simply produces no row.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S3-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S3-N1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1969,10 +2025,12 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1. The picker lists all 20 available columns, each with a toggle: Type, Part #, Description, Category, Vendor, Units Sold, Units Returned, Sold (WO), Sold (Parts Sale), Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand, Turns/Yr, Min, Max.
+          <t xml:space="preserve">1. The picker lists all 20 available columns, each with a toggle: Type, Part #, Description, Category, Vendor, Units Sold, Units Returned, Sold (WO), Sold (Parts Sale), Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand, Turns/Yr, Min, Max.
 2. No on-hand cost column is offered - the report computes one internally but it is never selectable and never displayed.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S4-R1, S4-R4, S5-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S4-R1, S4-R4, S5-R6).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2016,13 +2074,15 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>1. With a single location in scope exactly these 14 columns show, in this left-to-right order: Type, Part #, Description, Category, Vendor, Units Sold, Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand.
+          <t xml:space="preserve">1. With a single location in scope exactly these 14 columns show, in this left-to-right order: Type, Part #, Description, Category, Vendor, Units Sold, Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand.
 2. The other 6 columns start hidden: Units Returned, Sold (WO), Sold (Parts Sale), Turns / Yr, Min, Max.
-3. When more than one location is selected the Location column shows as well, leftmost before Type — 15 columns. It is already switched on for you; you do not have to turn it on, and you can switch it off again. It is not part of the 14-column default set, so its presence is expected and is not a failure of this test.
----
-DO NOT AUTOMATE YET: part of this behaviour is still waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
-This is the expected behaviour as per the Parts Velocity report specification version 4 (S4-R2, S4-R3, S3-R10) for the 14 default columns and the 6 hidden ones. The part about the Location column follows Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true; his decision differs from what this case said before, which stated the Location column is not in the column picker, and we have taken his later decision as the one that prevails.</t>
+3. When more than one location is in scope the Location column shows as well, leftmost before Type — 15 columns. It is not one of the columns in the column-selection control and you cannot switch it on or off: it appears by itself whenever more than one location is in scope, and is hidden whenever a single location is in scope. It is not part of the 14-column default set, so its presence is expected and is not a failure of this test.
+Note for the tester: the product owner has been asked to confirm this one point and has not answered yet, so do not raise a bug either way — record what you see. The question is in Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
+---
+---
+This is the expected behaviour as per the Parts Velocity report specification version 5 (S3-R10), and as per the build tested on 8/4/2026 (build v3.4.1-3d03023). The product owner's answer of 8/5/2026 in this file reads both ways on the one point about the Location column, so it has NOT been treated as overriding the specification and he has been asked again: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: HOLD - waiting on one answer from the product owner about the Location column
+</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2068,11 +2128,13 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1. Each toggle takes effect immediately - the table re-renders without a page reload.
+          <t xml:space="preserve">1. Each toggle takes effect immediately - the table re-renders without a page reload.
 2. Columns always render in the fixed canonical left-to-right order regardless of the order they were toggled on (with the automatic Location column, when shown, sitting leftmost before Type): Type, Part #, Description, Category, Vendor, Units Sold, Units Returned, Sold (WO), Sold (Parts Sale), Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand, Turns/Yr, Min, Max.
 3. So Units Returned slots in right after Units Sold, Turns/Yr after On Hand, and Min before Max - not appended at the end.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S4-R4, S4-R5, S3-R10).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S4-R4, S4-R5, S3-R10).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2118,12 +2180,14 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1. On return, every saved setting is restored: Type = Inventory, Last Month, the chosen category, the column set including Turns / Yr, and the Revenue-descending sort.
+          <t xml:space="preserve">1. On return, every saved setting is restored: Type = Inventory, Last Month, the chosen category, the column set including Turns / Yr, and the Revenue-descending sort.
 2. The saved values are applied BEFORE the first data fetch - the report does not flash the defaults and then re-query.
 3. The saved values take precedence over the first-visit defaults (This Year / Both / active location / 14 columns / Demand-descending).
 4. The same holds after a full page reload.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S4-R6, S1-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S4-R6, S1-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2168,11 +2232,13 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>1. The invalid saved value is NOT sent to the server.
+          <t xml:space="preserve">1. The invalid saved value is NOT sent to the server.
 2. That one setting falls back to its default (e.g. the location falls back to the active location); the other saved settings still restore normally.
 3. The report loads without an error.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S4-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S4-R6).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2218,10 +2284,12 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>1. User 2 sees user 1's saved view (Type = Special Order, Last Quarter, the saved columns and sort).
+          <t xml:space="preserve">1. User 2 sees user 1's saved view (Type = Special Order, Last Quarter, the saved columns and sort).
 2. This is by design: storage is per browser, not tied to the account - there is no per-account separation.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S4-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S4-R6).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2267,11 +2335,13 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>1. The picker enforces no minimum - all 20 columns can be switched off, leaving a grid with no data columns for the rest of the session.
+          <t xml:space="preserve">1. The picker enforces no minimum - all 20 columns can be switched off, leaving a grid with no data columns for the rest of the session.
 2. The export produces a file containing only the header/metadata rows and no data columns.
 3. On the next visit the all-hidden selection is NOT restored - the report falls back to the default 14-column set (the saved column selection returns to the last NON-EMPTY selection; all-hidden is the exception).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S4-E1, S4-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S4-E1, S4-R6).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2318,12 +2388,14 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1. After step 1, Units Sold increases by 5.00 (invoicing a work order adds the units sold - a stock-movement event).
+          <t xml:space="preserve">1. After step 1, Units Sold increases by 5.00 (invoicing a work order adds the units sold - a stock-movement event).
 2. After step 2, Units Sold decreases by 2.00 (reversing/voiding an invoice adds stock back and is subtracted - Units Sold is net of invoice reversals).
 3. After step 3, Units Sold is UNCHANGED - part returns do not affect Units Sold (they feed Units Returned instead).
 4. Units Sold can be 0.00 or negative when reversals exceed sales.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R1, S5-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R1, S5-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2369,11 +2441,13 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>1. Units Sold equals the total quantity across the part's in-window vendor requests (3 + 2 = 5.00 in the example), summed across the selected locations.
+          <t xml:space="preserve">1. Units Sold equals the total quantity across the part's in-window vendor requests (3 + 2 = 5.00 in the example), summed across the selected locations.
 2. The reversed/voided sale is EXCLUDED from the total (net of reversals).
 3. Only requests on work orders at status Invoiced or Paid count; the window is anchored to the work-order date.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R2, S5-R4, S5-R4b).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R2, S5-R4, S5-R4b).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2421,12 +2495,14 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>1. After step 1, Units Returned increases by 2.00 (the return record is counted when the return is initiated).
+          <t xml:space="preserve">1. After step 1, Units Returned increases by 2.00 (the return record is counted when the return is initiated).
 2. After step 2, it increases by 1.00 more (a parts-sale credit also creates a part-return record).
 3. After step 3, it decreases by 2.00 - the column reflects the CURRENT state of return records (cancelled returns are excluded), not a snapshot.
 4. After step 4, Units Returned is UNCHANGED - invoice reversals are not returns (they affect Units Sold instead).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R3, S5-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R3, S5-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2474,13 +2550,15 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>1. The return counts in the window of its INITIATION date - so it appears in the current window even though the sale was earlier (a return and its originating sale can fall in different report windows; each uses its own natural event date).
+          <t xml:space="preserve">1. The return counts in the window of its INITIATION date - so it appears in the current window even though the sale was earlier (a return and its originating sale can fall in different report windows; each uses its own natural event date).
 2. In the previous window the return does not count (only the sale's own metrics do).
 3. Core-charge returns are EXCLUDED from Units Returned.
 4. Units Returned is independent of the work order's current invoice status.
-5. A part whose ONLY in-window event is a return (no sale, no stock, no revenue) produces no row at all - accepted behavior, the row axis is sales/stock activity.
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R3).</t>
+5. A part whose ONLY in-window event is a return (no sale, no stock, no revenue) produces no row at all - the rows of this report are built from sales and stock activity, so a return on its own does not create one.
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2527,12 +2605,14 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>1. Sold (WO) shows the total part quantity on Service-type invoiced/paid work orders whose work-order date is in the window (4.00 in the example), net of reversed/voided sales.
+          <t xml:space="preserve">1. Sold (WO) shows the total part quantity on Service-type invoiced/paid work orders whose work-order date is in the window (4.00 in the example), net of reversed/voided sales.
 2. Sold (Parts Sale) shows the total on Parts-type invoiced/paid work orders (counter sales) in the window (3.00), net of reversed/voided sales.
 3. Both are windowed by the WORK-ORDER date (its end date) - with the range moved off those dates, both drop out.
 4. Both workflows feed the report - a parts sale is a separate workflow from a service work order but counts fully.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2580,13 +2660,15 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>1. The inventory part's Demand is 2 - each stock-decrementing invoicing event counts ONCE no matter how many units were on it (1 unit and 10 units each count as one).
+          <t xml:space="preserve">1. The inventory part's Demand is 2 - each stock-decrementing invoicing event counts ONCE no matter how many units were on it (1 unit and 10 units each count as one).
 2. After the reversal, Demand is STILL 2 - a reversal event neither adds to nor subtracts from the count (while Units Sold nets down).
 3. The special-order part's Demand is 2 - the count of its in-window vendor part requests.
 4. Demand is the report's default ranking signal (a whole number, never null - 0 when none).
 5. A part whose single in-window sale is invoiced and then fully reversed shows Demand 1 with Units Sold 0.00 — the Demand count is not decremented, while the movement nets to zero.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R4, S3-E1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R4, S3-E1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2635,13 +2717,15 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>1. Last Sale shows the whole days between today and the part's most recent sale measured over ALL-TIME history - it IGNORES the selected date range (e.g. '42 days' even though the range is This Month).
+          <t xml:space="preserve">1. Last Sale shows the whole days between today and the part's most recent sale measured over ALL-TIME history - it IGNORES the selected date range (e.g. '42 days' even though the range is This Month).
 2. It IS scoped to the selected location(s): with only location B selected, Last Sale reflects B's own most recent sale.
 3. Format is 'N days' (e.g. 42 days); a part with no recorded sale ever shows —.
 4. For a special-order part, the anchor is its most recent vendor-sourced invoiced/paid request.
 5. When the most recent sale is reversed, Last Sale re-anchors to the previous remaining sale (the day count grows accordingly); if no other sale remains it shows —.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R4, S5-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R4, S5-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2687,11 +2771,13 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>1. On Hand equals the part's CURRENT on-hand quantity at that row's location (never summed across locations).
+          <t xml:space="preserve">1. On Hand equals the part's CURRENT on-hand quantity at that row's location (never summed across locations).
 2. Min and Max show the stored minimum / maximum reorder thresholds for that location, as whole numbers (— when not set).
 3. Min and Max are READ-ONLY display columns - no edit control or slide-over opens; editing part attributes from this report is out of scope in this version.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R4, S5-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R4, S5-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2740,12 +2826,14 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>1. Part A's Turns / Yr matches the formula (two decimals, e.g. 24.33); the window is the whole-day span inclusive of both dates with a floor of 1 day.
+          <t xml:space="preserve">1. Part A's Turns / Yr matches the formula (two decimals, e.g. 24.33); the window is the whole-day span inclusive of both dates with a floor of 1 day.
 2. Part B shows 0.00 (renders 0.00 when On Hand is 0 - not an error, not —).
 3. Part C shows a NEGATIVE Turns / Yr with a leading minus (because Units Sold can be negative).
 4. Special Order rows always show — (not applicable).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2791,14 +2879,16 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>1. Revenue = the summed billed sell amount (each line's stored sell price × quantity) in the window.
+          <t xml:space="preserve">1. Revenue = the summed billed sell amount (each line's stored sell price × quantity) in the window.
 2. Margin = Revenue − COGS (the summed billed cost captured at billing time).
 3. Unit Cost = COGS ÷ billed units; Sell Price = Revenue ÷ billed units.
 4. Margin % = (Revenue − COGS) ÷ Revenue × 100, shown to one decimal.
 5. All five are computed from the RAW (unrounded) Revenue / COGS / billed-units totals and rounded ONCE at the end - not built from already-rounded intermediates.
 6. The same formulas apply to inventory and special-order rows (for special-order, from the vendor part requests).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R4a).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R4a).
+AUTOMATION: HOLD - this part of the report is not built yet
+</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2845,11 +2935,13 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>1. After the reversal, ALL the billed-line columns drop to reflect only the remaining sale - the reversed/voided sale is excluded from Revenue, Margin, Unit Cost, Sell Price, Margin %, Sold (WO), Sold (Parts Sale), and (for special-order) Units Sold.
+          <t xml:space="preserve">1. After the reversal, ALL the billed-line columns drop to reflect only the remaining sale - the reversed/voided sale is excluded from Revenue, Margin, Unit Cost, Sell Price, Margin %, Sold (WO), Sold (Parts Sale), and (for special-order) Units Sold.
 2. This netting is consistent with inventory Units Sold, which already nets reversals via the stock add-back.
 3. A voided sale therefore inflates NO column.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R4b, S5-R4a).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R4b, S5-R4a).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2897,12 +2989,14 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>1. Row 1: Unit Cost and Sell Price show — (billed units ≤ 0) while Revenue and Margin show dollar amounts AND Margin % is still computed from Revenue - a valid mixed row, not a defect.
+          <t xml:space="preserve">1. Row 1: Unit Cost and Sell Price show — (billed units ≤ 0) while Revenue and Margin show dollar amounts AND Margin % is still computed from Revenue - a valid mixed row, not a defect.
 2. Row 2: Sell Price shows $0.00 (a number) while Margin % shows — (Revenue ≤ 0) - also valid.
 3. Row 3: Unit Cost, Sell Price, and Margin % all show — together - which happens ONLY when both billed units ≤ 0 AND Revenue ≤ 0.
 4. The three triggers are independent: Unit Cost/Sell Price null on billed units ≤ 0; Margin % null on Revenue ≤ 0.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R4a, S3-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R4a, S3-R9).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2947,13 +3041,15 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>1. Units Sold, Units Returned, Sold (WO), Sold (Parts Sale), On Hand, Turns / Yr: two decimals with thousands separators (1,250.00); negatives with a leading minus (-3.00).
+          <t xml:space="preserve">1. Units Sold, Units Returned, Sold (WO), Sold (Parts Sale), On Hand, Turns / Yr: two decimals with thousands separators (1,250.00); negatives with a leading minus (-3.00).
 2. Unit Cost, Sell Price, Revenue, Margin: currency with $, two decimals, thousands separators ($1,250.00); negatives with a leading minus and NO parentheses (-$45.00).
 3. Margin %: one decimal with a trailing % (33.8%); negatives with a leading minus, no + on positives (-8.4%).
 4. Demand: whole number. Min, Max: whole numbers (— when null). Last Sale: 'N days' (42 days), — when null.
 5. Rounding is half AWAY from zero: 8.45% displays 8.5% and -8.45% displays -8.5% (a tie rounds up in magnitude); this applies to all money and one-decimal values.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R5, S5-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R5, S5-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -2999,11 +3095,13 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>1. The inventory core part does NOT appear in the report despite its activity and stock.
+          <t xml:space="preserve">1. The inventory core part does NOT appear in the report despite its activity and stock.
 2. The special-order core part does NOT appear either.
 3. Parts flagged as a core are excluded from both result sets by design.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R1, S5-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R1, S5-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3051,11 +3149,13 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>1. On the inventory row, Units Sold (stock movement) DIFFERS from the billed units behind Revenue/Sell Price - this is CORRECT behavior, not a defect (the Units Sold tooltip calls it out).
+          <t xml:space="preserve">1. On the inventory row, Units Sold (stock movement) DIFFERS from the billed units behind Revenue/Sell Price - this is CORRECT behavior, not a defect (the Units Sold tooltip calls it out).
 2. Sold (WO) + Sold (Parts Sale) together DO equal the billed-units basis (work orders are only Service- or Parts-type) - but neither equals the movement-based Units Sold.
 3. On the special-order row, everything reconciles: Units Sold = Sold (WO) + Sold (Parts Sale) = billed units (they share the vendor-request quantity as one source).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -3102,12 +3202,14 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>1. In W1 (work-order date in window): the billed columns (Revenue, Margin, Unit Cost, Sell Price, Margin %, Sold (WO), Sold (Parts Sale)) count the sale, while inventory Units Sold / Demand do NOT (their movement event is outside W1).
+          <t xml:space="preserve">1. In W1 (work-order date in window): the billed columns (Revenue, Margin, Unit Cost, Sell Price, Margin %, Sold (WO), Sold (Parts Sale)) count the sale, while inventory Units Sold / Demand do NOT (their movement event is outside W1).
 2. In W2 (movement date in window): Units Sold / Demand count it, the billed columns do not - the two anchors CAN differ for an inventory part and that is intended.
 3. The window is the whole-day span inclusive of BOTH the start and end dates, with a floor of 1 day - a single-day range (Today) computes normally (Window = 1 for the Turns / Yr divisor).
 4. Last Sale is not windowed at all (all-time).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3157,12 +3259,14 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>1. Units Sold reads exactly 2.50 — not 2.00, not 3.00, not blank and not a dash.
+          <t xml:space="preserve">1. Units Sold reads exactly 2.50 — not 2.00, not 3.00, not blank and not a dash.
 2. It still reads exactly 2.50 after the sign-out and sign-back-in, which proves the part-of-a-unit quantity was really stored and not just shown once.
 3. On Hand has gone down by exactly 2.50 from what it was before the sale.
 4. No value anywhere on the row has been quietly rounded to a whole number.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R1, S5-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R1, S5-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -3207,10 +3311,12 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>1. The ⋯ overflow button sits leftmost in the toolbar's action cluster.
+          <t xml:space="preserve">1. The ⋯ overflow button sits leftmost in the toolbar's action cluster.
 2. The menu holds exactly two items, in this order: Download (PDF), then Download (CSV).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S6-R1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S6-R1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3256,11 +3362,13 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>1. Both files contain only the rows matching the date range, type, category, vendor, bin, location, and search active at export time - not a full unfiltered dump.
+          <t xml:space="preserve">1. Both files contain only the rows matching the date range, type, category, vendor, bin, location, and search active at export time - not a full unfiltered dump.
 2. The exported rows match what the on-screen grid was showing.
-3. Each file (PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to (exact position in the file is confirmed in the build).
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S6-R2, S6-R11); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+3. Each file (PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to.
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S6-R2, S6-R11); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3306,11 +3414,13 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>1. Both exports contain ONLY the currently enabled columns - the hidden ones are absent.
+          <t xml:space="preserve">1. Both exports contain ONLY the currently enabled columns - the hidden ones are absent.
 2. Columns appear in the CANONICAL order (the fixed on-screen order) - the re-enabled Units Returned sits right after Units Sold, NOT appended at the end.
 3. The export mirrors the visible grid.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S6-R3, S4-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S6-R3, S4-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3357,11 +3467,13 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>1. The default Demand-descending order is exported when the user has not chosen another column.
+          <t xml:space="preserve">1. The default Demand-descending order is exported when the user has not chosen another column.
 2. Every column's sort is honored in the export - including Min and Max.
 3. The export renders the EXACT server order, including null placement (nulls first on ascending, last on descending) - the export and the on-screen grid match; there is no on-screen-vs-export null-sorting difference.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S6-R4, S3-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S6-R4, S3-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3407,14 +3519,16 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>1. The file downloads as velocity-report.pdf.
+          <t xml:space="preserve">1. The file downloads as velocity-report.pdf.
 2. The PDF is formatted for A3 landscape and titled Parts Velocity.
 3. Description, Category, and Vendor are truncated to 18 characters in the PDF.
 4. Part # is NOT truncated.
 5. With a logo uploaded, that logo appears. If a logo is set but fails to load, the built-in ShopView logo is used instead. If no logo is uploaded at all, NO logo is printed and the text fills the space. The CSV never includes a logo.
 Note for the tester: on this build a report with no uploaded logo still prints the built-in ShopView logo. The product owner has decided it should print no logo at all, so record what you see; the change is with the developers.
 ---
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Parts Velocity report specification version 4 (S6-R5, S6-R6) differs, his decision is the authority.</t>
+This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Parts Velocity report specification version 5 (S6-R5, S6-R6) differs, his decision is the authority.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3460,11 +3574,13 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>1. The file downloads as velocity-report.csv.
+          <t xml:space="preserve">1. The file downloads as velocity-report.csv.
 2. The CSV carries the FULL, untruncated Description / Category / Vendor values (unlike the PDF's 18-character cut).
 3. Last Sale is a raw integer in the CSV (e.g. 42) - the 'N days' wording is PDF/on-screen only.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S6-R5, S6-R6, S6-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S6-R5, S6-R6, S6-R8).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3510,10 +3626,12 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>1. A null value renders as — (em-dash) in BOTH the CSV and the PDF, in every nullable field: Unit Cost, Sell Price, Margin %, On Hand, Turns / Yr, Last Sale, Min, Max.
+          <t xml:space="preserve">1. A null value renders as — (em-dash) in BOTH the CSV and the PDF, in every nullable field: Unit Cost, Sell Price, Margin %, On Hand, Turns / Yr, Last Sale, Min, Max.
 2. Revenue, Margin, and the count metrics are never null in the exports either ($0.00 / 0.00 / 0).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S6-R7, S6-R8, S3-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S6-R7, S6-R8, S3-R9).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3558,13 +3676,15 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>1. In the PDF, the Type column is CENTERED.
+          <t xml:space="preserve">1. In the PDF, the Type column is CENTERED.
 2. In the PDF, the text columns (Part #, Description, Category, Vendor) are left-aligned.
 3. In the PDF, EVERY numeric and money column is right-aligned.
 4. This is a deliberate export-only treatment - the on-screen table is all-left-aligned; the difference is documented, not a defect.
 5. The CSV is plain data — the alignment assertions apply to the PDF only; how a spreadsheet displays the CSV is not part of this test.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S6-R10, S3-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S6-R10, S3-R8).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3611,11 +3731,13 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>1. On success the toasts read exactly "Velocity report exported (CSV)" / "Velocity report exported (PDF)" and auto-fade — UPPERCASE (CSV)/(PDF).
+          <t xml:space="preserve">1. On success the toasts read exactly "Velocity report exported (CSV)" / "Velocity report exported (PDF)" and auto-fade — UPPERCASE (CSV)/(PDF).
 2. An error toast is shown on failure; when the server provides a message, that server message is shown.
-3. Otherwise the failure toast reads exactly: "Failed to export velocity report (csv)" or "Failed to export velocity report (pdf)" — lowercase (csv)/(pdf); the success/failure casing mix is the shipped wording, documented as-is (not a bug).
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S6-R9, S6-N1).</t>
+3. Otherwise the failure toast reads exactly: "Failed to export velocity report (csv)" or "Failed to export velocity report (pdf)" — lowercase (csv)/(pdf); the success/failure casing mix is the specified wording (not a bug).
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S6-R9, S6-N1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3663,12 +3785,14 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>1. Neither the CSV nor the PDF is produced — no download starts.
+          <t xml:space="preserve">1. Neither the CSV nor the PDF is produced — no download starts.
 2. A clear too-large message appears telling the user to narrow the date range or filters, then try again — the standard wording is "This report is too large to export. Narrow the date range or filters, then try again."
 3. After narrowing below the cap, the downloads work again.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (Story 6 exports).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (Story 6 exports).
+AUTOMATION: READY - EXPECT FAIL (SV-8818)
+</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3716,13 +3840,15 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>1. The CSV downloads successfully at that size.
+          <t xml:space="preserve">1. The CSV downloads successfully at that size.
 2. The PDF also downloads successfully. If instead nothing downloads and a message appears saying something went wrong, that is a failure — record roughly how many rows were on screen.
 3. The small PDF downloads successfully, which shows the failure depends on size.
 4. Note for the tester: a very large view is refused politely with "This report is too large to export. Narrow the date range or filters, then try again." — that message is expected and is NOT this failure. This test is about a medium-sized view where the CSV works but the PDF errors.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (Story 6 exports).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (Story 6 exports).
+AUTOMATION: READY - EXPECT FAIL (SV-8818)
+</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3767,11 +3893,13 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>1. White card surfaces (toolbar + table cells) sit on the standard soft blue-grey page background (the application's two-tone report theme).
+          <t xml:space="preserve">1. White card surfaces (toolbar + table cells) sit on the standard soft blue-grey page background (the application's two-tone report theme).
 2. There is NO card border-radius - the table runs edge to edge.
 3. The layout matches the application's other reports.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S7-R1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S7-R1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3818,13 +3946,15 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>1. The toolbar strip is white (dark in dark mode), and its controls sit clear of the edges rather than pressed up against them.
+          <t xml:space="preserve">1. The toolbar strip is white (dark in dark mode), and its controls sit clear of the edges rather than pressed up against them.
 2. There is a thin dividing line between the toolbar and the column-header band, and the header band and the data cells are white.
 3. The first and last columns sit clear of the left and right edges of the table - the text is not touching the edge.
 4. It all looks the same as the other reports in the suite: put another report side by side and nothing should look out of place.
 5. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether the spacing and the dividing line look right and consistent with the other reports, and only report it if something looks obviously off. (The exact figures behind this - 32px/24px toolbar padding, a 1px header border, 2rem edge padding - are design-token values the design and engineering team check with their own tooling, not by hand.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S7-R2, S7-R3, S7-R4, S7-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S7-R2, S7-R3, S7-R4, S7-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -3870,11 +4000,13 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>1. The report supports dark mode: page background, toolbar, and cells use their dark-mode equivalents.
+          <t xml:space="preserve">1. The report supports dark mode: page background, toolbar, and cells use their dark-mode equivalents.
 2. In BOTH light mode and dark mode the grey ⓘ info icon is clearly visible against the cell behind it - you can see it at a glance without leaning in, and it does not disappear into the background.
 3. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether you can see the icon easily in both modes. Only report it if the icon is hard to see. (The design rule behind this is a minimum 3:1 contrast ratio, which the design and engineering team check with a contrast tool - not by hand.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S7-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S7-R6).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -3921,11 +4053,13 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>1. The backend returns ONE page of rows at a time - the full result set is not shipped to the browser.
+          <t xml:space="preserve">1. The backend returns ONE page of rows at a time - the full result set is not shipped to the browser.
 2. Paging is resolved on the server: moving to another page issues a fresh backend request for that page.
 3. This keeps the report responsive at scale (organizations can carry 50-60k parts, multiplied across locations).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-R10).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S2-R10).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -3971,11 +4105,13 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>1. EACH change (Type, date range, Bin, Location, Category, Vendor, search) triggers a fresh server-side data load.
+          <t xml:space="preserve">1. EACH change (Type, date range, Bin, Location, Category, Vendor, search) triggers a fresh server-side data load.
 2. There is no client-side-only narrowing - every filter or search change re-queries the server.
 3. Each change returns the FIRST page of the new result set.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-R10).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S2-R10).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4022,11 +4158,13 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>1. Each header click re-fetches the data from the server, ordered by the chosen column and direction, returning the first page of the re-sorted result set.
+          <t xml:space="preserve">1. Each header click re-fetches the data from the server, ordered by the chosen column and direction, returning the first page of the re-sorted result set.
 2. Null values are placed FIRST on ascending and LAST on descending - as a server sort semantic, so the same order appears on screen and in the exports.
 3. Ties keep a stable order (no explicit secondary key).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S3-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S3-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4073,12 +4211,14 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>1. The back end returns the report data - the request is not refused.
+          <t xml:space="preserve">1. The back end returns the report data - the request is not refused.
 2. The back end returns the export file - the request is not refused.
 3. Both requests succeed with only the ordinary reports access turned on - nothing else had to be enabled.
-4. Note for the tester: if the back end refuses either request for a user who has the ordinary reports access, mark this Failed and report it. If an extra Parts or Inventory reports permission exists in the system it must not change these results - for now it is hidden from the screen and enforces nothing. A per-report permission added on purpose in a later release is a planned change, not a bug, and this test will be updated first.
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S1-R4, S1-N2); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+4. Note for the tester: if the back end refuses either request for a user who has the ordinary reports access, mark this Failed and report it. If an extra Parts or Inventory reports permission exists in the system it must not change these results - the specification allows no per-report permission at all. A per-report permission added on purpose in a later release is a planned change, not a bug, and this test will be updated first.
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S1-R4, S1-N2); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4129,12 +4269,14 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>1. The QuickBooks amount is exactly the hand-worked figure to the cent — $25.00 for 2.5 at $10.00.
+          <t xml:space="preserve">1. The QuickBooks amount is exactly the hand-worked figure to the cent — $25.00 for 2.5 at $10.00.
 2. It is NOT a whole-unit amount such as $20.00 or $30.00, and it is NOT a bigger, multiplied figure.
 3. The quantity behind the QuickBooks amount matches the Units Sold value on the report (2.50) — the two systems agree.
 4. No second or correcting journal entry is created to patch up a wrong amount.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and this point is not covered by any of the six report specifications — it comes from the engineering technical plan.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and this point is not covered by any of the six report specifications — it comes from the engineering technical plan.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">

--- a/testrail-import/Report-Suite_Parts-Velocity-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Parts-Velocity-Report_testrail-import.xlsx
@@ -527,7 +527,8 @@
 2. Under Parts there is an entry labeled Parts Velocity; Inventory Value also lives under Parts. The order of the two inside the Parts section is not fixed — do not fail the test on which of them comes first.
 3. Clicking it opens the Parts Velocity report.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S1-R1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S1-R1); where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, which is the authority.
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -579,7 +580,8 @@
 2. Report data loads automatically - you do not have to press anything to fetch it.
 3. Rows appear ranked by Demand, highest first (the default order).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S1-R2, S4-R6).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S1-R2, S4-R6).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -632,7 +634,8 @@
 2. During a filter change, the loading indicator shows again.
 3. The rows already on screen are replaced only when the new data comes back - the table does not blank out and rebuild mid-request.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S1-R3).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S1-R3).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -686,7 +689,8 @@
 2. The export downloads successfully — both opening the report and exporting it are allowed by the same ordinary reports access.
 3. Note for the tester: the specification allows ONE ordinary reports access for all six of these new reports and no per-report permission. If the build demands a separate report permission before this works, mark this Failed and report it — do not change the test.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S1-R4); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S1-R4).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -736,7 +740,8 @@
           <t xml:space="preserve">1. The user cannot reach the Reports section.
 2. The Parts Velocity navigation entry is not shown (this is the Reports section's own access control, not a report-specific rule).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S1-N1).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S1-N1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -790,7 +795,8 @@
 3. The export downloads.
 4. Note for the tester: the specification allows ONE ordinary reports access for all six of these new reports and no per-report permission. If an extra Parts or Inventory reports permission does exist and switching it OFF blocks this report or its export, that is wrong - mark this Failed and report it. If a separate per-report permission is ever added on purpose in a later release, this test will be updated first, so treat that as a planned change and not as a bug.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S1-N2, S1-R4); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S1-N2, S1-R4).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -847,7 +853,8 @@
 4. Both is an explicit selection returning inventory and Special Order rows together - a deliberate filter value, not the absence of a filter.
 5. Each selection immediately reloads the report limited to that type (no separate Apply step) - under Inventory every row's Type column reads Inventory; under Special Order every row's Type column reads Special Order; under Both, rows of both kinds appear.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S2-R1, S3-R5); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S2-R1, S3-R5).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -899,7 +906,8 @@
 3. Selecting a non-custom option immediately reloads the report data.
 4. The named ranges use the application's standard shared calendar boundaries (the same boundaries every report's date picker uses).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023). Where the Parts Velocity report specification version 5 (S2-R2) says something different, the behaviour above follows Chris Ward's decision of 8/5/2026 instead, which is the authority - that decision is recorded in his answers, in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. Where the Parts Velocity report specification version 5 (S2-R2) says something different, his decision is the later word and is the authority.
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -953,7 +961,8 @@
 3. With both valid dates selected, the data reloads for that range.
 4. A span wider than 366 days (counting both the start and end dates) is rejected - the selection is not applied.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S2-R3).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S2-R3).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1007,7 +1016,8 @@
 3. With vendors selected, only parts supplied by any of the selected vendors are shown.
 4. Each change reloads the data from the server.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S2-R4, S2-R5, S2-R10).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S2-R4, S2-R5, S2-R10).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1062,7 +1072,8 @@
 3. The description search returns rows whose description contains the word.
 4. Category and vendor names are NOT searched - use their dedicated filters instead (deliberate, to avoid false matches on common words).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S2-R6).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S2-R6).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1116,7 +1127,8 @@
 2. After step 3 the part disappears - a part must satisfy EVERY active filter to appear (AND logic, not OR).
 3. After step 4 the part is listed again.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S2-R7).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S2-R7).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1168,7 +1180,8 @@
 2. Only inventory parts stocked in ANY of the selected bins are shown.
 3. The filter allows more than one bin (multi-select).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S2-R8).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S2-R8).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1220,7 +1233,8 @@
           <t xml:space="preserve">1. With any Bin filter active, ALL Special Order rows are excluded (they have no bin location).
 2. Special Order combined with any Bin filter yields an empty result showing the empty state - this is by design, not a defect.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S2-R8); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S2-R8); where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, which is the authority.
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1278,7 +1292,8 @@
 5. The location scope cascades through every metric like the other filters.
 6. With 'All Locations' active you can tell which location each row's data belongs to — a location label or marking is shown.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S2-R9); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S2-R9); where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, which is the authority.
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1328,7 +1343,8 @@
           <t xml:space="preserve">1. The server returns zero rows and the table shows the empty state.
 2. The empty-state label reads exactly: "Empty bays, endless possibilities. Get Going!" (the application's standard reports no-data label).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S2-R11, S2-N1).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S2-R11, S2-N1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1382,7 +1398,8 @@
 2. The part with no vendor does not appear when any Vendor filter is active.
 3. The inventory part with no bin location does not appear when any Bin filter is active.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S2-E1, S2-E2, S2-E3).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S2-E1, S2-E2, S2-E3).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1433,7 +1450,8 @@
           <t xml:space="preserve">1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
 2. For the user with access to two or more locations the Location filter IS shown.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S2-E4). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S2-E4). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1488,16 +1506,14 @@
           <t xml:space="preserve">1. With more than one location in scope a Location column is shown as the LEFTMOST column, before Type.
 2. Each inventory row shows its own location's name (an inventory row is one part at one location).
 3. The merged Special Order row shows "Multiple", because it is summed across the selected locations.
-4. With a single location in scope the Location column is hidden.
+4. With only one location involved the Location column is not shown.
 5. Both downloads include the Location column in the same position it holds on screen (leftmost, before Type), with the same values — each inventory row's own location, and "Multiple" on the merged Special Order row.
 ---
-Note for the tester: on this build the column does not yet behave this way - record what you see and carry on. The change is with the developers.
-The Location column is not one of the columns in the column-selection control and you cannot switch it on or off: it appears by itself whenever more than one location is in scope, and is hidden whenever a single location is in scope.
-Note for the tester: the product owner has been asked to confirm this one point and has not answered yet, so do not raise a bug either way — record what you see. The question is in Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
----
----
-This is the expected behaviour as per the Parts Velocity report specification version 5 (S2-R12, S3-R10, S7-R8, S6-R11), and as per the build tested on 8/4/2026 (build v3.4.1-3d03023). The product owner's answer of 8/5/2026 in this file reads both ways on the one point about the Location column, so it has NOT been treated as overriding the specification and he has been asked again: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
-AUTOMATION: HOLD - waiting on one answer from the product owner about the Location column
+Note for the tester: the written description is inconsistent about one point here. One part of it says the Location column is offered in the column-selection control and can be switched on and off; another part says it is never in that list and simply appears by itself whenever more than one location is involved. Parts Velocity is one of the reports where this has not been settled. The product owner has been asked which is right and has not answered yet, so do not raise a bug either way - record what you see and carry on. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
+---
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S2-R12, S3-R10, S7-R8, S6-R11). That specification is inconsistent about the one point of whether the Location column is offered in the column-selection control: version 5 added a summary and a change note saying it can be toggled there, while the requirement that governs the column still says it is not user-toggleable. Chris Ward has been asked which is right and has not answered, so neither reading is asserted here. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
+AUTOMATION: HOLD - the written description says two different things about the Location column and the product owner has been asked
 </t>
         </is>
       </c>
@@ -1548,7 +1564,8 @@
 2. Each row carries only that one location's On Hand, Min, and Max.
 3. On Hand / Min / Max are NEVER summed across locations.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S3-R1a).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S3-R1a).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1601,7 +1618,8 @@
 2. Its movement and profitability values are the SUM of the per-location values.
 3. Its inventory-only columns (On Hand, Turns / Yr, Min, Max) show — (em-dash), because special-order parts are not stocked.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S3-R1a).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S3-R1a).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1656,7 +1674,8 @@
 3. Rows with equal Demand keep inventory-before-special-order order.
 4. The Demand header shows the descending sort indicator - this initial order IS the active sort (it is what the remembered view saves until you click another header).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S3-R2).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S3-R2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1711,7 +1730,8 @@
 3. Null / — values are placed FIRST on ascending and LAST on descending.
 4. Every column is sortable; each header click re-fetches the data (server-resolved) and shows the first page of the re-sorted result; ties keep a stable order.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S3-R3).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S3-R3).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1763,7 +1783,8 @@
 2. The Type column shows each row's kind as plain text (no badge or chip styling): "Inventory" or "Special Order".
 3. ALL columns - header and cell data, including numbers and money - are left-aligned on screen. (The exports right-align numerics instead: a deliberate export-only difference.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S3-R4, S3-R5, S3-R8); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S3-R4, S3-R5, S3-R8); where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, which is the authority.
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1820,7 +1841,8 @@
 5. The icon is focusable and exposes the same text to assistive technology; activating it does NOT trigger a column sort.
 6. No other column header carries an info icon.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S3-R6).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S3-R6).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1874,7 +1896,8 @@
 2. The full value shows on native hover (browser tooltip).
 3. Part # is NEVER truncated - on screen (and in the exports).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S3-R7).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S3-R7).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1925,7 +1948,8 @@
           <t xml:space="preserve">1. On Hand, Turns / Yr, Min, and Max show — (em-dash) on special-order rows - always.
 2. The count metrics and money totals are NEVER null: Units Sold / Units Returned / Sold (WO) / Sold (Parts Sale) show 0.00, Demand shows 0, Revenue and Margin show $0.00.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S3-R9, S5-R5).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S3-R9, S5-R5).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1977,7 +2001,8 @@
 2. Part B DOES appear - a part with billed Revenue &gt; 0 is always kept even with no stock movement and no on-hand stock.
 3. (Special Order parts have no such rule: a never-requested special-order part simply produces no row.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S3-N1).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S3-N1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2028,7 +2053,8 @@
           <t xml:space="preserve">1. The picker lists all 20 available columns, each with a toggle: Type, Part #, Description, Category, Vendor, Units Sold, Units Returned, Sold (WO), Sold (Parts Sale), Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand, Turns/Yr, Min, Max.
 2. No on-hand cost column is offered - the report computes one internally but it is never selectable and never displayed.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S4-R1, S4-R4, S5-R6).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S4-R1, S4-R4, S5-R6).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2076,12 +2102,11 @@
         <is>
           <t xml:space="preserve">1. With a single location in scope exactly these 14 columns show, in this left-to-right order: Type, Part #, Description, Category, Vendor, Units Sold, Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand.
 2. The other 6 columns start hidden: Units Returned, Sold (WO), Sold (Parts Sale), Turns / Yr, Min, Max.
-3. When more than one location is in scope the Location column shows as well, leftmost before Type — 15 columns. It is not one of the columns in the column-selection control and you cannot switch it on or off: it appears by itself whenever more than one location is in scope, and is hidden whenever a single location is in scope. It is not part of the 14-column default set, so its presence is expected and is not a failure of this test.
-Note for the tester: the product owner has been asked to confirm this one point and has not answered yet, so do not raise a bug either way — record what you see. The question is in Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
----
----
-This is the expected behaviour as per the Parts Velocity report specification version 5 (S3-R10), and as per the build tested on 8/4/2026 (build v3.4.1-3d03023). The product owner's answer of 8/5/2026 in this file reads both ways on the one point about the Location column, so it has NOT been treated as overriding the specification and he has been asked again: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
-AUTOMATION: HOLD - waiting on one answer from the product owner about the Location column
+3. When more than one location is in scope the Location column shows as well, leftmost before Type — 15 columns. Note for the tester: the written description is inconsistent about one point here. One part of it says the Location column is offered in the column-selection control and can be switched on and off; another part says it is never in that list and simply appears by itself whenever more than one location is involved. Parts Velocity is one of the reports where this has not been settled. The product owner has been asked which is right and has not answered yet, so do not raise a bug either way - record what you see and carry on. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx It is not part of the 14-column default set, so its presence is expected and is not a failure of this test.
+---
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S3-R10). That specification is inconsistent about the one point of whether the Location column is offered in the column-selection control: version 5 added a summary and a change note saying it can be toggled there, while the requirement that governs the column still says it is not user-toggleable. Chris Ward has been asked which is right and has not answered, so neither reading is asserted here. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
+AUTOMATION: HOLD - the written description says two different things about the Location column and the product owner has been asked
 </t>
         </is>
       </c>
@@ -2132,7 +2157,8 @@
 2. Columns always render in the fixed canonical left-to-right order regardless of the order they were toggled on (with the automatic Location column, when shown, sitting leftmost before Type): Type, Part #, Description, Category, Vendor, Units Sold, Units Returned, Sold (WO), Sold (Parts Sale), Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand, Turns/Yr, Min, Max.
 3. So Units Returned slots in right after Units Sold, Turns/Yr after On Hand, and Min before Max - not appended at the end.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S4-R4, S4-R5, S3-R10).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S4-R4, S4-R5, S3-R10).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2185,7 +2211,8 @@
 3. The saved values take precedence over the first-visit defaults (This Year / Both / active location / 14 columns / Demand-descending).
 4. The same holds after a full page reload.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S4-R6, S1-R2).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S4-R6, S1-R2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2236,7 +2263,8 @@
 2. That one setting falls back to its default (e.g. the location falls back to the active location); the other saved settings still restore normally.
 3. The report loads without an error.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S4-R6).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S4-R6).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2287,7 +2315,8 @@
           <t xml:space="preserve">1. User 2 sees user 1's saved view (Type = Special Order, Last Quarter, the saved columns and sort).
 2. This is by design: storage is per browser, not tied to the account - there is no per-account separation.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S4-R6).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S4-R6).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2339,7 +2368,8 @@
 2. The export produces a file containing only the header/metadata rows and no data columns.
 3. On the next visit the all-hidden selection is NOT restored - the report falls back to the default 14-column set (the saved column selection returns to the last NON-EMPTY selection; all-hidden is the exception).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S4-E1, S4-R6).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S4-E1, S4-R6).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2393,7 +2423,8 @@
 3. After step 3, Units Sold is UNCHANGED - part returns do not affect Units Sold (they feed Units Returned instead).
 4. Units Sold can be 0.00 or negative when reversals exceed sales.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R1, S5-R4).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S5-R1, S5-R4).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2445,7 +2476,8 @@
 2. The reversed/voided sale is EXCLUDED from the total (net of reversals).
 3. Only requests on work orders at status Invoiced or Paid count; the window is anchored to the work-order date.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R2, S5-R4, S5-R4b).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S5-R2, S5-R4, S5-R4b).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2500,7 +2532,8 @@
 3. After step 3, it decreases by 2.00 - the column reflects the CURRENT state of return records (cancelled returns are excluded), not a snapshot.
 4. After step 4, Units Returned is UNCHANGED - invoice reversals are not returns (they affect Units Sold instead).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R3, S5-R4).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S5-R3, S5-R4).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2556,7 +2589,8 @@
 4. Units Returned is independent of the work order's current invoice status.
 5. A part whose ONLY in-window event is a return (no sale, no stock, no revenue) produces no row at all - the rows of this report are built from sales and stock activity, so a return on its own does not create one.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R3).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S5-R3).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2610,7 +2644,8 @@
 3. Both are windowed by the WORK-ORDER date (its end date) - with the range moved off those dates, both drop out.
 4. Both workflows feed the report - a parts sale is a separate workflow from a service work order but counts fully.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R4).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S5-R4).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2666,7 +2701,8 @@
 4. Demand is the report's default ranking signal (a whole number, never null - 0 when none).
 5. A part whose single in-window sale is invoiced and then fully reversed shows Demand 1 with Units Sold 0.00 — the Demand count is not decremented, while the movement nets to zero.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R4, S3-E1).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S5-R4, S3-E1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2723,7 +2759,8 @@
 4. For a special-order part, the anchor is its most recent vendor-sourced invoiced/paid request.
 5. When the most recent sale is reversed, Last Sale re-anchors to the previous remaining sale (the day count grows accordingly); if no other sale remains it shows —.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R4, S5-R5).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S5-R4, S5-R5).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2775,7 +2812,8 @@
 2. Min and Max show the stored minimum / maximum reorder thresholds for that location, as whole numbers (— when not set).
 3. Min and Max are READ-ONLY display columns - no edit control or slide-over opens; editing part attributes from this report is out of scope in this version.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R4, S5-R5).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S5-R4, S5-R5).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2831,7 +2869,8 @@
 3. Part C shows a NEGATIVE Turns / Yr with a leading minus (because Units Sold can be negative).
 4. Special Order rows always show — (not applicable).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R4).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S5-R4).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2886,7 +2925,8 @@
 5. All five are computed from the RAW (unrounded) Revenue / COGS / billed-units totals and rounded ONCE at the end - not built from already-rounded intermediates.
 6. The same formulas apply to inventory and special-order rows (for special-order, from the vendor part requests).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R4a).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S5-R4a).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: HOLD - this part of the report is not built yet
 </t>
         </is>
@@ -2939,7 +2979,8 @@
 2. This netting is consistent with inventory Units Sold, which already nets reversals via the stock add-back.
 3. A voided sale therefore inflates NO column.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R4b, S5-R4a).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S5-R4b, S5-R4a).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2994,7 +3035,8 @@
 3. Row 3: Unit Cost, Sell Price, and Margin % all show — together - which happens ONLY when both billed units ≤ 0 AND Revenue ≤ 0.
 4. The three triggers are independent: Unit Cost/Sell Price null on billed units ≤ 0; Margin % null on Revenue ≤ 0.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R4a, S3-R9).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S5-R4a, S3-R9).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3047,7 +3089,8 @@
 4. Demand: whole number. Min, Max: whole numbers (— when null). Last Sale: 'N days' (42 days), — when null.
 5. Rounding is half AWAY from zero: 8.45% displays 8.5% and -8.45% displays -8.5% (a tie rounds up in magnitude); this applies to all money and one-decimal values.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R5, S5-R7).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S5-R5, S5-R7).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3099,7 +3142,8 @@
 2. The special-order core part does NOT appear either.
 3. Parts flagged as a core are excluded from both result sets by design.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R1, S5-R2).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S5-R1, S5-R2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3153,7 +3197,8 @@
 2. Sold (WO) + Sold (Parts Sale) together DO equal the billed-units basis (work orders are only Service- or Parts-type) - but neither equals the movement-based Units Sold.
 3. On the special-order row, everything reconciles: Units Sold = Sold (WO) + Sold (Parts Sale) = billed units (they share the vendor-request quantity as one source).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R7).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S5-R7).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3207,7 +3252,8 @@
 3. The window is the whole-day span inclusive of BOTH the start and end dates, with a floor of 1 day - a single-day range (Today) computes normally (Window = 1 for the Turns / Yr divisor).
 4. Last Sale is not windowed at all (all-time).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R7).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S5-R7).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3264,7 +3310,8 @@
 3. On Hand has gone down by exactly 2.50 from what it was before the sale.
 4. No value anywhere on the row has been quietly rounded to a whole number.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R1, S5-R5).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S5-R1, S5-R5).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3314,7 +3361,8 @@
           <t xml:space="preserve">1. The ⋯ overflow button sits leftmost in the toolbar's action cluster.
 2. The menu holds exactly two items, in this order: Download (PDF), then Download (CSV).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S6-R1).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S6-R1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3366,7 +3414,8 @@
 2. The exported rows match what the on-screen grid was showing.
 3. Each file (PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S6-R2, S6-R11); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S6-R2, S6-R11); where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, which is the authority.
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3418,7 +3467,8 @@
 2. Columns appear in the CANONICAL order (the fixed on-screen order) - the re-enabled Units Returned sits right after Units Sold, NOT appended at the end.
 3. The export mirrors the visible grid.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S6-R3, S4-R4).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S6-R3, S4-R4).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3471,7 +3521,8 @@
 2. Every column's sort is honored in the export - including Min and Max.
 3. The export renders the EXACT server order, including null placement (nulls first on ascending, last on descending) - the export and the on-screen grid match; there is no on-screen-vs-export null-sorting difference.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S6-R4, S3-R3).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S6-R4, S3-R3).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3526,7 +3577,8 @@
 5. With a logo uploaded, that logo appears. If a logo is set but fails to load, the built-in ShopView logo is used instead. If no logo is uploaded at all, NO logo is printed and the text fills the space. The CSV never includes a logo.
 Note for the tester: on this build a report with no uploaded logo still prints the built-in ShopView logo. The product owner has decided it should print no logo at all, so record what you see; the change is with the developers.
 ---
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Parts Velocity report specification version 5 (S6-R5, S6-R6) differs, his decision is the authority.
+This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true; where the Parts Velocity report specification version 5 (S6-R5, S6-R6) differs, his decision is the authority.
+Last checked against build v3.4.1-3d03023 on 8/4/2026, which does not yet match it - that change is with the developers.
 AUTOMATION: READY
 </t>
         </is>
@@ -3578,7 +3630,8 @@
 2. The CSV carries the FULL, untruncated Description / Category / Vendor values (unlike the PDF's 18-character cut).
 3. Last Sale is a raw integer in the CSV (e.g. 42) - the 'N days' wording is PDF/on-screen only.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S6-R5, S6-R6, S6-R8).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S6-R5, S6-R6, S6-R8).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3629,7 +3682,8 @@
           <t xml:space="preserve">1. A null value renders as — (em-dash) in BOTH the CSV and the PDF, in every nullable field: Unit Cost, Sell Price, Margin %, On Hand, Turns / Yr, Last Sale, Min, Max.
 2. Revenue, Margin, and the count metrics are never null in the exports either ($0.00 / 0.00 / 0).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S6-R7, S6-R8, S3-R9).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S6-R7, S6-R8, S3-R9).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3682,7 +3736,8 @@
 4. This is a deliberate export-only treatment - the on-screen table is all-left-aligned; the difference is documented, not a defect.
 5. The CSV is plain data — the alignment assertions apply to the PDF only; how a spreadsheet displays the CSV is not part of this test.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S6-R10, S3-R8).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S6-R10, S3-R8).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3735,7 +3790,8 @@
 2. An error toast is shown on failure; when the server provides a message, that server message is shown.
 3. Otherwise the failure toast reads exactly: "Failed to export velocity report (csv)" or "Failed to export velocity report (pdf)" — lowercase (csv)/(pdf); the success/failure casing mix is the specified wording (not a bug).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S6-R9, S6-N1).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S6-R9, S6-N1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3790,7 +3846,8 @@
 3. After narrowing below the cap, the downloads work again.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (Story 6 exports).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (Story 6 exports).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8818)
 </t>
         </is>
@@ -3846,7 +3903,8 @@
 4. Note for the tester: a very large view is refused politely with "This report is too large to export. Narrow the date range or filters, then try again." — that message is expected and is NOT this failure. This test is about a medium-sized view where the CSV works but the PDF errors.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (Story 6 exports).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (Story 6 exports).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8818)
 </t>
         </is>
@@ -3897,7 +3955,8 @@
 2. There is NO card border-radius - the table runs edge to edge.
 3. The layout matches the application's other reports.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S7-R1).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S7-R1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3952,7 +4011,8 @@
 4. It all looks the same as the other reports in the suite: put another report side by side and nothing should look out of place.
 5. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether the spacing and the dividing line look right and consistent with the other reports, and only report it if something looks obviously off. (The exact figures behind this - 32px/24px toolbar padding, a 1px header border, 2rem edge padding - are design-token values the design and engineering team check with their own tooling, not by hand.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S7-R2, S7-R3, S7-R4, S7-R5).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S7-R2, S7-R3, S7-R4, S7-R5).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4004,7 +4064,8 @@
 2. In BOTH light mode and dark mode the grey ⓘ info icon is clearly visible against the cell behind it - you can see it at a glance without leaning in, and it does not disappear into the background.
 3. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether you can see the icon easily in both modes. Only report it if the icon is hard to see. (The design rule behind this is a minimum 3:1 contrast ratio, which the design and engineering team check with a contrast tool - not by hand.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S7-R6).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S7-R6).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4057,7 +4118,8 @@
 2. Paging is resolved on the server: moving to another page issues a fresh backend request for that page.
 3. This keeps the report responsive at scale (organizations can carry 50-60k parts, multiplied across locations).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S2-R10).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S2-R10).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4109,7 +4171,8 @@
 2. There is no client-side-only narrowing - every filter or search change re-queries the server.
 3. Each change returns the FIRST page of the new result set.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S2-R10).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S2-R10).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4162,7 +4225,8 @@
 2. Null values are placed FIRST on ascending and LAST on descending - as a server sort semantic, so the same order appears on screen and in the exports.
 3. Ties keep a stable order (no explicit secondary key).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S3-R3).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S3-R3).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4216,7 +4280,8 @@
 3. Both requests succeed with only the ordinary reports access turned on - nothing else had to be enabled.
 4. Note for the tester: if the back end refuses either request for a user who has the ordinary reports access, mark this Failed and report it. If an extra Parts or Inventory reports permission exists in the system it must not change these results - the specification allows no per-report permission at all. A per-report permission added on purpose in a later release is a planned change, not a bug, and this test will be updated first.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S1-R4, S1-N2); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S1-R4, S1-N2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4274,7 +4339,8 @@
 3. The quantity behind the QuickBooks amount matches the Units Sold value on the report (2.50) — the two systems agree.
 4. No second or correcting journal entry is created to patch up a wrong amount.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and this point is not covered by any of the six report specifications — it comes from the engineering technical plan.
+This is the expected behaviour as per epic SV-8582 and the engineering technical plan; this point is not covered by any of the six report specifications.
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>

--- a/testrail-import/Report-Suite_Parts-Velocity-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Parts-Velocity-Report_testrail-import.xlsx
@@ -523,178 +523,175 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. A Parts section heading exists in the Reports navigation (this feature creates it - the application had no Parts reports before).
+          <t>1. A Parts section heading exists in the Reports navigation (this feature creates it - the application had no Parts reports before).
 2. Under Parts there is an entry labeled Parts Velocity; Inventory Value also lives under Parts. The order of the two inside the Parts section is not fixed — do not fail the test on which of them comes first.
 3. Clicking it opens the Parts Velocity report.
 ---
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S1-R1); where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, which is the authority.
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S1-R1), read on 11 August 2026; where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026, which is the authority.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>SV-8641 (PV spec S1-R1 — the "only report" sentence is superseded: Parts Velocity and Inventory Value BOTH live under Parts per the PRD video 2026-07-30; access = the one ordinary reports permission per QA lead 2026-08-03)</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>First visit: date range defaults to This Year and data is fetched automatically</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>PV — Access &amp; Defaults</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in as a user allowed to open the report.
+2. You are using a browser with NO saved view for this report (e.g. a fresh browser profile or after clearing the site's browser storage), so first-visit defaults apply.</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>1. Open Reports → Parts → Parts Velocity.
+2. Look at the date range selector and the table without touching anything.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>1. The date range selector shows This Year.
+2. Report data loads automatically - you do not have to press anything to fetch it.
+3. Rows appear ranked by Demand, highest first (the default order).
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S1-R2, S4-R6), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>SV-8641 (PV spec v4 2026-07-29 S1-R2; S4-R6)</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>A loading indicator shows and old rows are replaced only when data returns</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>PV — Access &amp; Defaults</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in as a user allowed to open the report.
+2. Enough parts data exists that the report visibly takes a moment to load.</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Parts Velocity report and watch the table area during the initial load.
+2. After it loads, change any filter that reloads the data from the server (for example the Type filter).
+3. Watch the table while the new data is being fetched.</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1. During the initial load, the table shows a loading indicator.
+2. During a filter change, the loading indicator shows again.
+3. The rows already on screen are replaced only when the new data comes back - the table does not blank out and rebuild mid-request.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S1-R3), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>SV-8641 (PV spec v4 2026-07-29 S1-R3)</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>A user with ordinary reports access can load the report and export it</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>PV — Permissions</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in as a user with the Manager or Office User role.
+2. That user's role has the ordinary reports access (the standard "can this person see reports" setting).
+3. Some parts have sales activity in the selected date range.</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1. Open Reports → Parts → Parts Velocity.
+2. Wait for the data to load.
+3. Open the export menu and download the CSV.</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The report data loads and rows are shown.
+2. The export downloads successfully — both opening the report and exporting it are allowed by the same ordinary reports access.
+3. Note for the tester: the specification allows ONE ordinary reports access for all six of these new reports and no per-report permission. If the build demands a separate report permission before this works, mark this Failed and report it — do not change the test.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S1-R4), read on 11 August 2026.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>SV-8641 (PV spec S1-R1 — the "only report" sentence is superseded: Parts Velocity and Inventory Value BOTH live under Parts per the PRD video 2026-07-30; access = the one ordinary reports permission per QA lead 2026-08-03)</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>First visit: date range defaults to This Year and data is fetched automatically</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>PV — Access &amp; Defaults</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in as a user allowed to open the report.
-2. You are using a browser with NO saved view for this report (e.g. a fresh browser profile or after clearing the site's browser storage), so first-visit defaults apply.</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>1. Open Reports → Parts → Parts Velocity.
-2. Look at the date range selector and the table without touching anything.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The date range selector shows This Year.
-2. Report data loads automatically - you do not have to press anything to fetch it.
-3. Rows appear ranked by Demand, highest first (the default order).
----
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S1-R2, S4-R6).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>SV-8641 (PV spec v4 2026-07-29 S1-R2; S4-R6)</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>A loading indicator shows and old rows are replaced only when data returns</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>PV — Access &amp; Defaults</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in as a user allowed to open the report.
-2. Enough parts data exists that the report visibly takes a moment to load.</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the Parts Velocity report and watch the table area during the initial load.
-2. After it loads, change any filter that reloads the data from the server (for example the Type filter).
-3. Watch the table while the new data is being fetched.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. During the initial load, the table shows a loading indicator.
-2. During a filter change, the loading indicator shows again.
-3. The rows already on screen are replaced only when the new data comes back - the table does not blank out and rebuild mid-request.
----
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S1-R3).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>SV-8641 (PV spec v4 2026-07-29 S1-R3)</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>A user with ordinary reports access can load the report and export it</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>PV — Permissions</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in as a user with the Manager or Office User role.
-2. That user's role has the ordinary reports access (the standard "can this person see reports" setting).
-3. Some parts have sales activity in the selected date range.</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1. Open Reports → Parts → Parts Velocity.
-2. Wait for the data to load.
-3. Open the export menu and download the CSV.</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The report data loads and rows are shown.
-2. The export downloads successfully — both opening the report and exporting it are allowed by the same ordinary reports access.
-3. Note for the tester: the specification allows ONE ordinary reports access for all six of these new reports and no per-report permission. If the build demands a separate report permission before this works, mark this Failed and report it — do not change the test.
----
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S1-R4).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
           <t>SV-8641 (PV spec S1-R4 — one reports permission for all six ruled by Chris Ward Q2=A + QA lead 2026-08-03 "ONE permission FOR NOW"; PV S1-R4 still names Inventory Reports &gt; View — his spec edit owed)</t>
@@ -740,7 +737,7 @@
           <t xml:space="preserve">1. The user cannot reach the Reports section.
 2. The Parts Velocity navigation entry is not shown (this is the Reports section's own access control, not a report-specific rule).
 ---
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S1-N1).
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S1-N1), read on 11 August 2026.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -795,7 +792,7 @@
 3. The export downloads.
 4. Note for the tester: the specification allows ONE ordinary reports access for all six of these new reports and no per-report permission. If an extra Parts or Inventory reports permission does exist and switching it OFF blocks this report or its export, that is wrong - mark this Failed and report it. If a separate per-report permission is ever added on purpose in a later release, this test will be updated first, so treat that as a planned change and not as a bug.
 ---
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S1-N2, S1-R4).
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S1-N2, S1-R4), read on 11 August 2026.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -847,16 +844,15 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The Type filter is the first control in the filter row.
+          <t>1. The Type filter is the first control in the filter row.
 2. It is single-select and offers exactly three choices: Both, Inventory, and Special Order (special-order catalog parts that were never put into stock).
 3. On a first visit the default is Both.
 4. Both is an explicit selection returning inventory and Special Order rows together - a deliberate filter value, not the absence of a filter.
 5. Each selection immediately reloads the report limited to that type (no separate Apply step) - under Inventory every row's Type column reads Inventory; under Special Order every row's Type column reads Special Order; under Both, rows of both kinds appear.
 ---
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S2-R1, S3-R5).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S2-R1, S3-R5), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -901,15 +897,14 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The chooser offers nine ready-made periods, in this order: Last 12 Months, This Year, Last Year, This Quarter, Last Quarter, This Month, Last Month, This Week, Last Week. Beside them it shows a month calendar you click dates on to build your own range, a live readout of how many days the range covers, and an Apply button. There is no "Today", no "Yesterday" and no item called "Custom" - you build your own range on the calendar instead. There is no "All Time" option.
+          <t>1. The chooser offers nine ready-made periods, in this order: Last 12 Months, This Year, Last Year, This Quarter, Last Quarter, This Month, Last Month, This Week, Last Week. Beside them it shows a month calendar you click dates on to build your own range, a live readout of how many days the range covers, and an Apply button. There is no "Today", no "Yesterday" and no item called "Custom" - you build your own range on the calendar instead. There is no "All Time" option.
 2. The report always operates over a bounded date window, which is why no All-Time period is offered.
 3. Selecting a non-custom option immediately reloads the report data.
 4. The named ranges use the application's standard shared calendar boundaries (the same boundaries every report's date picker uses).
 ---
-This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. Where the Parts Velocity report specification version 5 (S2-R2) says something different, his decision is the later word and is the authority.
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026. Where the Parts Velocity report specification version 6 (S2-R2), read on 11 August 2026, says something different, his decision is the later word and is the authority.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -961,7 +956,7 @@
 3. With both valid dates selected, the data reloads for that range.
 4. A span wider than 366 days (counting both the start and end dates) is rejected - the selection is not applied.
 ---
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S2-R3).
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S2-R3), read on 11 August 2026.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1016,7 +1011,7 @@
 3. With vendors selected, only parts supplied by any of the selected vendors are shown.
 4. Each change reloads the data from the server.
 ---
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S2-R4, S2-R5, S2-R10).
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S2-R4, S2-R5, S2-R10), read on 11 August 2026.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1067,15 +1062,14 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The search input is part of the report's toolbar (page-specific), separate from the global search bar.
+          <t>1. The search input is part of the report's toolbar (page-specific), separate from the global search bar.
 2. The part-number search matches despite the different letter case (case-insensitive 'contains' match).
 3. The description search returns rows whose description contains the word.
 4. Category and vendor names are NOT searched - use their dedicated filters instead (deliberate, to avoid false matches on common words).
 ---
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S2-R6).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S2-R6), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1127,7 +1121,7 @@
 2. After step 3 the part disappears - a part must satisfy EVERY active filter to appear (AND logic, not OR).
 3. After step 4 the part is listed again.
 ---
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S2-R7).
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S2-R7), read on 11 August 2026.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1176,14 +1170,13 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Each selection reloads the data from the server.
+          <t>1. Each selection reloads the data from the server.
 2. Only inventory parts stocked in ANY of the selected bins are shown.
 3. The filter allows more than one bin (multi-select).
 ---
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S2-R8).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S2-R8), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1230,13 +1223,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. With any Bin filter active, ALL Special Order rows are excluded (they have no bin location).
+          <t>1. With any Bin filter active, ALL Special Order rows are excluded (they have no bin location).
 2. Special Order combined with any Bin filter yields an empty result showing the empty state - this is by design, not a defect.
 ---
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S2-R8); where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, which is the authority.
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S2-R8), read on 11 August 2026; where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026, which is the authority.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1285,17 +1277,20 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The Location filter is the rightmost control in the filter row and is multi-select.
+          <t>1. The Location filter is the rightmost control in the filter row and is multi-select.
 2. On a first visit it defaults to the user's currently active location (the one in the global location switcher).
 3. The list holds the locations the signed-in user has access to, plus an 'All Locations' option.
 4. Each selection reloads the data scoped to the chosen set; 'All Locations' means all locations the user can ACCESS, never beyond - a location the user cannot access is never included.
 5. The location scope cascades through every metric like the other filters.
 6. With 'All Locations' active you can tell which location each row's data belongs to — a location label or marking is shown.
----
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S2-R9); where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, which is the authority.
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+What you should see today: On a brand-new browser the Location filter opens showing "All locations" instead of the one location you are working in, and the table returns rows from both locations at once. Everything else about the filter is right: it is the rightmost control, it lists only the locations you can reach, and choosing one location does narrow the report. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8939
+- If you see exactly that, mark this test FAILED and do not raise anything new.
+- If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+- If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S2-R9), read on 11 August 2026; where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026, which is the authority.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8939)</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1340,13 +1335,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The server returns zero rows and the table shows the empty state.
+          <t>1. The server returns zero rows and the table shows the empty state.
 2. The empty-state label reads exactly: "Empty bays, endless possibilities. Get Going!" (the application's standard reports no-data label).
 ---
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S2-R11, S2-N1).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S2-R11, S2-N1), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1398,7 +1392,7 @@
 2. The part with no vendor does not appear when any Vendor filter is active.
 3. The inventory part with no bin location does not appear when any Bin filter is active.
 ---
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S2-E1, S2-E2, S2-E3).
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S2-E1, S2-E2, S2-E3), read on 11 August 2026.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1450,7 +1444,7 @@
           <t xml:space="preserve">1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
 2. For the user with access to two or more locations the Location filter IS shown.
 ---
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S2-E4). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S2-E4), read on 11 August 2026. Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -1503,18 +1497,21 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. With more than one location in scope a Location column is shown as the LEFTMOST column, before Type.
+          <t>1. With more than one location in scope a Location column is shown as the LEFTMOST column, before Type.
 2. Each inventory row shows its own location's name (an inventory row is one part at one location).
 3. The merged Special Order row shows "Multiple", because it is summed across the selected locations.
 4. With only one location involved the Location column is not shown.
 5. Both downloads include the Location column in the same position it holds on screen (leftmost, before Type), with the same values — each inventory row's own location, and "Multiple" on the merged Special Order row.
+What you should see today: The Location column is shown, and its values are right - each stocked row shows its own location's name and a special-order row that covers several locations reads "Multiple" - but the column sits sixth, straight after Vendor, instead of first before Type. Both downloads put it in that same sixth place. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8938
+- If you see exactly that, mark this test FAILED and do not raise anything new.
+- If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+- If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
 Note for the tester: the written description is inconsistent about one point here. One part of it says the Location column is offered in the column-selection control and can be switched on and off; another part says it is never in that list and simply appears by itself whenever more than one location is involved. Parts Velocity is one of the reports where this has not been settled. The product owner has been asked which is right and has not answered yet, so do not raise a bug either way - record what you see and carry on. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
 ---
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S2-R12, S3-R10, S7-R8, S6-R11). That specification is inconsistent about the one point of whether the Location column is offered in the column-selection control: version 5 added a summary and a change note saying it can be toggled there, while the requirement that governs the column still says it is not user-toggleable. Chris Ward has been asked which is right and has not answered, so neither reading is asserted here. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: HOLD - the written description says two different things about the Location column and the product owner has been asked
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S2-R12, S3-R10, S7-R8, S6-R11), read on 11 August 2026. That specification is inconsistent about the one point of whether the Location column is offered in the column-selection control: version 5 added a summary and a change note saying it can be toggled there, while the requirement that governs the column still says it is not user-toggleable. Chris Ward has been asked which is right and has not answered, so neither reading is asserted here. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8938)</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1560,14 +1557,13 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The part appears as TWO inventory rows - one per selected location (an inventory part is a per-location stock record).
+          <t>1. The part appears as TWO inventory rows - one per selected location (an inventory part is a per-location stock record).
 2. Each row carries only that one location's On Hand, Min, and Max.
 3. On Hand / Min / Max are NEVER summed across locations.
 ---
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S3-R1a).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S3-R1a), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1614,14 +1610,13 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The special-order part appears as a SINGLE row (one row per special-order part, merged across the selected locations).
+          <t>1. The special-order part appears as a SINGLE row (one row per special-order part, merged across the selected locations).
 2. Its movement and profitability values are the SUM of the per-location values.
 3. Its inventory-only columns (On Hand, Turns / Yr, Min, Max) show — (em-dash), because special-order parts are not stocked.
 ---
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S3-R1a).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S3-R1a), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1669,15 +1664,14 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Rows are ranked by Demand, descending - the most-active parts first.
+          <t>1. Rows are ranked by Demand, descending - the most-active parts first.
 2. Inventory and special-order rows are ranked together in one list.
 3. Rows with equal Demand keep inventory-before-special-order order.
 4. The Demand header shows the descending sort indicator - this initial order IS the active sort (it is what the remembered view saves until you click another header).
 ---
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S3-R2).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S3-R2), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1725,15 +1719,14 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The first click sorts that column ASCENDING; the header shows a direction indicator (an arrow).
+          <t>1. The first click sorts that column ASCENDING; the header shows a direction indicator (an arrow).
 2. Clicking the active sort column again reverses the direction; the arrow flips.
 3. Null / — values are placed FIRST on ascending and LAST on descending.
 4. Every column is sortable; each header click re-fetches the data (server-resolved) and shows the first page of the re-sorted result; ties keep a stable order.
 ---
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S3-R3).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S3-R3), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1779,14 +1772,13 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The header row is sticky - it stays visible while the body scrolls.
+          <t>1. The header row is sticky - it stays visible while the body scrolls.
 2. The Type column shows each row's kind as plain text (no badge or chip styling): "Inventory" or "Special Order".
 3. ALL columns - header and cell data, including numbers and money - are left-aligned on screen. (The exports right-align numerics instead: a deliberate export-only difference.)
 ---
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S3-R4, S3-R5, S3-R8); where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, which is the authority.
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S3-R4, S3-R5, S3-R8), read on 11 August 2026; where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026, which is the authority.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1834,493 +1826,494 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Each of the three headers carries a grey info icon, shown always (not hover-to-reveal) whenever its column is visible; the Turns/Yr icon appears only once that column is enabled.
+          <t>1. Each of the three headers carries a grey info icon, shown always (not hover-to-reveal) whenever its column is visible; the Turns/Yr icon appears only once that column is enabled.
 2. Units Sold shows exactly: "Units taken out of inventory stock on invoiced work orders in this date range. This is stock movement, so it can differ from the units billed behind Revenue and Sell Price."
 3. Demand shows exactly: "Number of separate transactions (work orders or parts sales) this part appeared on in the selected date range. Each transaction counts once, no matter how many units were sold on it."
 4. Turns/Yr shows exactly: "How many times you sell through this part in a year. Higher is better."
 5. The icon is focusable and exposes the same text to assistive technology; activating it does NOT trigger a column sort.
 6. No other column header carries an info icon.
 ---
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S3-R6).
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S3-R6), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>SV-8643 (PV spec v4 2026-07-29 S3-R6 — S3-R6 CLOSES the set (exactly three columns: Units Sold; Demand; Turns / Yr) and quotes each description verbatim; so the closed set and the exact strings ARE the requirement)</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Description; Category and Vendor truncate on hover; Part # never does</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>PV — Row Model</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>1. A part with a very long description (and a long category and vendor name) has in-window activity.
+2. A part with a long part number exists.
+3. You are on the Parts Velocity report with those parts visible.</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>1. Look at the long Description, Category, and Vendor cells.
+2. Hover each truncated cell.
+3. Look at the long Part # cell.</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>1. Long Description, Category, and Vendor text is truncated with an ellipsis on screen.
+2. The full value shows on native hover (browser tooltip).
+3. Part # is NEVER truncated - on screen (and in the exports).
+What you should see today: Part # is correctly never shortened, but Description, Category and Vendor are not shortened either - a 117-character description is shown complete, there is no ellipsis and resting the pointer on it shows no tooltip. The table grows to about 2,400 pixels wide inside a 1,370-pixel space, so you have to scroll sideways to reach the numbers. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8940
+- If you see exactly that, mark this test FAILED and do not raise anything new.
+- If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+- If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S3-R7), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8940)</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>SV-8643 (PV spec v4 2026-07-29 S3-R7)</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Em-dash only in nullable fields; counts and Revenue/Margin are never null</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>PV — Row Model</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>1. You are on the Parts Velocity report with all 20 columns enabled.
+2. A special-order row is visible, plus an inventory row with no in-window activity that stays in the report via on-hand stock.</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>1. On the special-order row, read On Hand, Turns / Yr, Min, and Max.
+2. On the no-activity inventory row, read Units Sold, Units Returned, Sold (WO), Sold (Parts Sale), Demand, Revenue, and Margin.</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>1. On Hand, Turns / Yr, Min, and Max show — (em-dash) on special-order rows - always.
+2. The count metrics and money totals are NEVER null: Units Sold / Units Returned / Sold (WO) / Sold (Parts Sale) show 0.00, Demand shows 0, Revenue and Margin show $0.00.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S3-R9, S5-R5), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>SV-8643 (PV spec v4 2026-07-29 S3-R9; S5-R5)</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>An inventory part drops out only with no movement, no stock and no revenue</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>PV — Row Model</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>1. Inventory part A: zero stock movement in the window, less than one unit on hand, zero billed revenue in the window.
+2. Inventory part B: zero stock movement and zero on hand, but billed revenue in the window (e.g. a drop-ship sale billed without a stock decrement).</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>1. Search for part A in the report.
+2. Search for part B in the report.</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Part A does NOT appear - it fails all three keep-criteria (no movement, under one on hand, no revenue) so it carries nothing to act on.
+2. Part B DOES appear - a part with billed Revenue &gt; 0 is always kept even with no stock movement and no on-hand stock.
+3. (Special Order parts have no such rule: a never-requested special-order part simply produces no row.)
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S3-N1), read on 11 August 2026.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>SV-8643 (PV spec v4 2026-07-29 S3-R6 — S3-R6 CLOSES the set (exactly three columns: Units Sold; Demand; Turns / Yr) and quotes each description verbatim; so the closed set and the exact strings ARE the requirement)</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Description; Category and Vendor truncate on hover; Part # never does</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>PV — Row Model</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>SV-8643 (PV spec v4 2026-07-29 S3-N1)</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Column picker lists all 20 columns and never offers the internal cost</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>PV — Columns &amp; Remembered View</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>1. You are on the Parts Velocity report with data loaded.</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the column picker from its toolbar button.
+2. Count the columns listed and check each has a toggle.
+3. Look for any on-hand cost / inventory-value entry.</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>1. The picker lists all 20 available columns, each with a toggle: Type, Part #, Description, Category, Vendor, Units Sold, Units Returned, Sold (WO), Sold (Parts Sale), Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand, Turns/Yr, Min, Max.
+2. No on-hand cost column is offered - the report computes one internally but it is never selectable and never displayed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S4-R1, S4-R4, S5-R6), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>SV-8644 (PV spec v4 2026-07-29 S4-R1; S4-R4; S5-R6)</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>First visit shows exactly the 14 default columns in the specified order</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>PV — Columns &amp; Remembered View</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>1. You are on the Parts Velocity report on a first visit (no saved column selection).</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>1. Read the visible column headers left to right without touching the picker.</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>1. With a single location in scope exactly these 14 columns show, in this left-to-right order: Type, Part #, Description, Category, Vendor, Units Sold, Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand.
+2. The other 6 columns start hidden: Units Returned, Sold (WO), Sold (Parts Sale), Turns / Yr, Min, Max.
+3. When more than one location is in scope the Location column shows as well, leftmost before Type — 15 columns. Note for the tester: the written description is inconsistent about one point here. One part of it says the Location column is offered in the column-selection control and can be switched on and off; another part says it is never in that list and simply appears by itself whenever more than one location is involved. Parts Velocity is one of the reports where this has not been settled. The product owner has been asked which is right and has not answered yet, so do not raise a bug either way - record what you see and carry on. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx It is not part of the 14-column default set, so its presence is expected and is not a failure of this test.
+What you should see today: The fourteen default columns and their order are correct, but the Location column is NOT first. It sits sixth, straight after Vendor, so the headings read Type, Part #, Description, Category, Vendor, Location, Units Sold and so on. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8938
+- If you see exactly that, mark this test FAILED and do not raise anything new.
+- If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+- If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S3-R10), read on 11 August 2026. That specification is inconsistent about the one point of whether the Location column is offered in the column-selection control: version 5 added a summary and a change note saying it can be toggled there, while the requirement that governs the column still says it is not user-toggleable. Chris Ward has been asked which is right and has not answered, so neither reading is asserted here. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8938)</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>SV-8644; SV-8643 (PV spec v4 2026-07-29 S4-R2; S4-R3 + Story 3 S3-R10 — the 14 default-visible columns and the 6 hidden ones; plus the automatic Location column leftmost when more than one location is in scope)</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>A re-enabled column returns to its canonical slot, with no reload</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>PV — Columns &amp; Remembered View</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>1. A part with a very long description (and a long category and vendor name) has in-window activity.
-2. A part with a long part number exists.
-3. You are on the Parts Velocity report with those parts visible.</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>1. Look at the long Description, Category, and Vendor cells.
-2. Hover each truncated cell.
-3. Look at the long Part # cell.</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Long Description, Category, and Vendor text is truncated with an ellipsis on screen.
-2. The full value shows on native hover (browser tooltip).
-3. Part # is NEVER truncated - on screen (and in the exports).
----
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S3-R7).
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>1. You are on the Parts Velocity report with data loaded.</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>1. In the column picker, enable Min, then Units Returned, then Turns/Yr - in that (non-canonical) order.
+2. Watch the table as each toggle is flipped.
+3. Read the resulting header order.</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>1. Each toggle takes effect immediately - the table re-renders without a page reload.
+2. Columns always render in the fixed canonical left-to-right order regardless of the order they were toggled on (with the automatic Location column, when shown, sitting leftmost before Type): Type, Part #, Description, Category, Vendor, Units Sold, Units Returned, Sold (WO), Sold (Parts Sale), Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand, Turns/Yr, Min, Max.
+3. So Units Returned slots in right after Units Sold, Turns/Yr after On Hand, and Min before Max - not appended at the end.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S4-R4, S4-R5, S3-R10), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>SV-8644; SV-8643 (PV spec v4 2026-07-29 S4-R4; S4-R5 + Story 3 S3-R10 — canonical column order and immediate re-render; plus the automatic Location column leftmost when shown)</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Filters; columns and sort are remembered per browser before the first fetch</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>PV — Columns &amp; Remembered View</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>1. You are on the Parts Velocity report with data loaded.</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>1. Set a non-default view: Type = Inventory, date range = Last Month, pick a category, enable Turns / Yr, and sort by Revenue descending.
+2. Leave the report (navigate elsewhere), then return to it.
+3. Reload the page (browser refresh) and observe again.</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>1. On return, every saved setting is restored: Type = Inventory, Last Month, the chosen category, the column set including Turns / Yr, and the Revenue-descending sort.
+2. The saved values are applied BEFORE the first data fetch - the report does not flash the defaults and then re-query.
+3. The saved values take precedence over the first-visit defaults (This Year / Both / active location / 14 columns / Demand-descending).
+4. The same holds after a full page reload.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S4-R6, S1-R2), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>SV-8644 (PV spec v4 2026-07-29 S4-R6; S1-R2)</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>A saved value that is no longer valid falls back to that setting's default</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>PV — Columns &amp; Remembered View</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>1. A saved view exists in this browser that includes a location the user can no longer access (e.g. access was removed after the view was saved), or a custom date range that is now malformed.</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>1. Return to the Parts Velocity report with that stale saved view in place.
+2. Observe which location / date range the report loads with.</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. The invalid saved value is NOT sent to the server.
+2. That one setting falls back to its default (e.g. the location falls back to the active location); the other saved settings still restore normally.
+3. The report loads without an error.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S4-R6), read on 11 August 2026.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>SV-8643 (PV spec v4 2026-07-29 S3-R7)</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>Em-dash only in nullable fields; counts and Revenue/Margin are never null</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>PV — Row Model</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>1. You are on the Parts Velocity report with all 20 columns enabled.
-2. A special-order row is visible, plus an inventory row with no in-window activity that stays in the report via on-hand stock.</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>1. On the special-order row, read On Hand, Turns / Yr, Min, and Max.
-2. On the no-activity inventory row, read Units Sold, Units Returned, Sold (WO), Sold (Parts Sale), Demand, Revenue, and Margin.</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. On Hand, Turns / Yr, Min, and Max show — (em-dash) on special-order rows - always.
-2. The count metrics and money totals are NEVER null: Units Sold / Units Returned / Sold (WO) / Sold (Parts Sale) show 0.00, Demand shows 0, Revenue and Margin show $0.00.
----
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S3-R9, S5-R5).
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>SV-8644 (PV spec v4 2026-07-29 S4-R6)</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>A different user signing in on the same browser inherits the saved view</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>PV — Columns &amp; Remembered View</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>1. User 1 has saved a clearly non-default view on this browser (e.g. Type = Special Order, Last Quarter).
+2. User 2 can open the report.</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>1. Sign out user 1 and sign in user 2 on the SAME browser.
+2. Open the Parts Velocity report.</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. User 2 sees user 1's saved view (Type = Special Order, Last Quarter, the saved columns and sort).
+2. This is by design: storage is per browser, not tied to the account - there is no per-account separation.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S4-R6), read on 11 August 2026.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>SV-8643 (PV spec v4 2026-07-29 S3-R9; S5-R5)</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>An inventory part drops out only with no movement, no stock and no revenue</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>PV — Row Model</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>1. Inventory part A: zero stock movement in the window, less than one unit on hand, zero billed revenue in the window.
-2. Inventory part B: zero stock movement and zero on hand, but billed revenue in the window (e.g. a drop-ship sale billed without a stock decrement).</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>1. Search for part A in the report.
-2. Search for part B in the report.</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Part A does NOT appear - it fails all three keep-criteria (no movement, under one on hand, no revenue) so it carries nothing to act on.
-2. Part B DOES appear - a part with billed Revenue &gt; 0 is always kept even with no stock movement and no on-hand stock.
-3. (Special Order parts have no such rule: a never-requested special-order part simply produces no row.)
----
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S3-N1).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>SV-8643 (PV spec v4 2026-07-29 S3-N1)</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>Column picker lists all 20 columns and never offers the internal cost</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>PV — Columns &amp; Remembered View</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>1. You are on the Parts Velocity report with data loaded.</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the column picker from its toolbar button.
-2. Count the columns listed and check each has a toggle.
-3. Look for any on-hand cost / inventory-value entry.</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The picker lists all 20 available columns, each with a toggle: Type, Part #, Description, Category, Vendor, Units Sold, Units Returned, Sold (WO), Sold (Parts Sale), Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand, Turns/Yr, Min, Max.
-2. No on-hand cost column is offered - the report computes one internally but it is never selectable and never displayed.
----
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S4-R1, S4-R4, S5-R6).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>SV-8644 (PV spec v4 2026-07-29 S4-R1; S4-R4; S5-R6)</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>First visit shows exactly the 14 default columns in the specified order</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>PV — Columns &amp; Remembered View</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>1. You are on the Parts Velocity report on a first visit (no saved column selection).</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>1. Read the visible column headers left to right without touching the picker.</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. With a single location in scope exactly these 14 columns show, in this left-to-right order: Type, Part #, Description, Category, Vendor, Units Sold, Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand.
-2. The other 6 columns start hidden: Units Returned, Sold (WO), Sold (Parts Sale), Turns / Yr, Min, Max.
-3. When more than one location is in scope the Location column shows as well, leftmost before Type — 15 columns. Note for the tester: the written description is inconsistent about one point here. One part of it says the Location column is offered in the column-selection control and can be switched on and off; another part says it is never in that list and simply appears by itself whenever more than one location is involved. Parts Velocity is one of the reports where this has not been settled. The product owner has been asked which is right and has not answered yet, so do not raise a bug either way - record what you see and carry on. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx It is not part of the 14-column default set, so its presence is expected and is not a failure of this test.
----
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S3-R10). That specification is inconsistent about the one point of whether the Location column is offered in the column-selection control: version 5 added a summary and a change note saying it can be toggled there, while the requirement that governs the column still says it is not user-toggleable. Chris Ward has been asked which is right and has not answered, so neither reading is asserted here. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: HOLD - the written description says two different things about the Location column and the product owner has been asked
-</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>SV-8644; SV-8643 (PV spec v4 2026-07-29 S4-R2; S4-R3 + Story 3 S3-R10 — the 14 default-visible columns and the 6 hidden ones; plus the automatic Location column leftmost when more than one location is in scope)</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>A re-enabled column returns to its canonical slot, with no reload</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>PV — Columns &amp; Remembered View</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>1. You are on the Parts Velocity report with data loaded.</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>1. In the column picker, enable Min, then Units Returned, then Turns/Yr - in that (non-canonical) order.
-2. Watch the table as each toggle is flipped.
-3. Read the resulting header order.</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Each toggle takes effect immediately - the table re-renders without a page reload.
-2. Columns always render in the fixed canonical left-to-right order regardless of the order they were toggled on (with the automatic Location column, when shown, sitting leftmost before Type): Type, Part #, Description, Category, Vendor, Units Sold, Units Returned, Sold (WO), Sold (Parts Sale), Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand, Turns/Yr, Min, Max.
-3. So Units Returned slots in right after Units Sold, Turns/Yr after On Hand, and Min before Max - not appended at the end.
----
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S4-R4, S4-R5, S3-R10).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>SV-8644; SV-8643 (PV spec v4 2026-07-29 S4-R4; S4-R5 + Story 3 S3-R10 — canonical column order and immediate re-render; plus the automatic Location column leftmost when shown)</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>Filters; columns and sort are remembered per browser before the first fetch</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>PV — Columns &amp; Remembered View</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>1. You are on the Parts Velocity report with data loaded.</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>1. Set a non-default view: Type = Inventory, date range = Last Month, pick a category, enable Turns / Yr, and sort by Revenue descending.
-2. Leave the report (navigate elsewhere), then return to it.
-3. Reload the page (browser refresh) and observe again.</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. On return, every saved setting is restored: Type = Inventory, Last Month, the chosen category, the column set including Turns / Yr, and the Revenue-descending sort.
-2. The saved values are applied BEFORE the first data fetch - the report does not flash the defaults and then re-query.
-3. The saved values take precedence over the first-visit defaults (This Year / Both / active location / 14 columns / Demand-descending).
-4. The same holds after a full page reload.
----
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S4-R6, S1-R2).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>SV-8644 (PV spec v4 2026-07-29 S4-R6; S1-R2)</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>A saved value that is no longer valid falls back to that setting's default</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>PV — Columns &amp; Remembered View</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>1. A saved view exists in this browser that includes a location the user can no longer access (e.g. access was removed after the view was saved), or a custom date range that is now malformed.</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>1. Return to the Parts Velocity report with that stale saved view in place.
-2. Observe which location / date range the report loads with.</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The invalid saved value is NOT sent to the server.
-2. That one setting falls back to its default (e.g. the location falls back to the active location); the other saved settings still restore normally.
-3. The report loads without an error.
----
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S4-R6).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>SV-8644 (PV spec v4 2026-07-29 S4-R6)</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>A different user signing in on the same browser inherits the saved view</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>PV — Columns &amp; Remembered View</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>1. User 1 has saved a clearly non-default view on this browser (e.g. Type = Special Order, Last Quarter).
-2. User 2 can open the report.</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>1. Sign out user 1 and sign in user 2 on the SAME browser.
-2. Open the Parts Velocity report.</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. User 2 sees user 1's saved view (Type = Special Order, Last Quarter, the saved columns and sort).
-2. This is by design: storage is per browser, not tied to the account - there is no per-account separation.
----
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S4-R6).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
-        </is>
-      </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
           <t>SV-8644 (PV spec v4 2026-07-29 S4-R6)</t>
@@ -2364,14 +2357,13 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The picker enforces no minimum - all 20 columns can be switched off, leaving a grid with no data columns for the rest of the session.
+          <t>1. The picker enforces no minimum - all 20 columns can be switched off, leaving a grid with no data columns for the rest of the session.
 2. The export produces a file containing only the header/metadata rows and no data columns.
 3. On the next visit the all-hidden selection is NOT restored - the report falls back to the default 14-column set (the saved column selection returns to the last NON-EMPTY selection; all-hidden is the exception).
 ---
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S4-E1, S4-R6).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S4-E1, S4-R6), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2418,15 +2410,14 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. After step 1, Units Sold increases by 5.00 (invoicing a work order adds the units sold - a stock-movement event).
+          <t>1. After step 1, Units Sold increases by 5.00 (invoicing a work order adds the units sold - a stock-movement event).
 2. After step 2, Units Sold decreases by 2.00 (reversing/voiding an invoice adds stock back and is subtracted - Units Sold is net of invoice reversals).
 3. After step 3, Units Sold is UNCHANGED - part returns do not affect Units Sold (they feed Units Returned instead).
 4. Units Sold can be 0.00 or negative when reversals exceed sales.
 ---
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S5-R1, S5-R4).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S5-R1, S5-R4), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2472,14 +2463,13 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Units Sold equals the total quantity across the part's in-window vendor requests (3 + 2 = 5.00 in the example), summed across the selected locations.
+          <t>1. Units Sold equals the total quantity across the part's in-window vendor requests (3 + 2 = 5.00 in the example), summed across the selected locations.
 2. The reversed/voided sale is EXCLUDED from the total (net of reversals).
 3. Only requests on work orders at status Invoiced or Paid count; the window is anchored to the work-order date.
 ---
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S5-R2, S5-R4, S5-R4b).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S5-R2, S5-R4, S5-R4b), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2527,15 +2517,14 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. After step 1, Units Returned increases by 2.00 (the return record is counted when the return is initiated).
+          <t>1. After step 1, Units Returned increases by 2.00 (the return record is counted when the return is initiated).
 2. After step 2, it increases by 1.00 more (a parts-sale credit also creates a part-return record).
 3. After step 3, it decreases by 2.00 - the column reflects the CURRENT state of return records (cancelled returns are excluded), not a snapshot.
 4. After step 4, Units Returned is UNCHANGED - invoice reversals are not returns (they affect Units Sold instead).
 ---
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S5-R3, S5-R4).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S5-R3, S5-R4), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2583,16 +2572,15 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The return counts in the window of its INITIATION date - so it appears in the current window even though the sale was earlier (a return and its originating sale can fall in different report windows; each uses its own natural event date).
+          <t>1. The return counts in the window of its INITIATION date - so it appears in the current window even though the sale was earlier (a return and its originating sale can fall in different report windows; each uses its own natural event date).
 2. In the previous window the return does not count (only the sale's own metrics do).
 3. Core-charge returns are EXCLUDED from Units Returned.
 4. Units Returned is independent of the work order's current invoice status.
 5. A part whose ONLY in-window event is a return (no sale, no stock, no revenue) produces no row at all - the rows of this report are built from sales and stock activity, so a return on its own does not create one.
 ---
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S5-R3).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S5-R3), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2639,15 +2627,14 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Sold (WO) shows the total part quantity on Service-type invoiced/paid work orders whose work-order date is in the window (4.00 in the example), net of reversed/voided sales.
+          <t>1. Sold (WO) shows the total part quantity on Service-type invoiced/paid work orders whose work-order date is in the window (4.00 in the example), net of reversed/voided sales.
 2. Sold (Parts Sale) shows the total on Parts-type invoiced/paid work orders (counter sales) in the window (3.00), net of reversed/voided sales.
 3. Both are windowed by the WORK-ORDER date (its end date) - with the range moved off those dates, both drop out.
 4. Both workflows feed the report - a parts sale is a separate workflow from a service work order but counts fully.
 ---
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S5-R4).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S5-R4), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2695,16 +2682,15 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The inventory part's Demand is 2 - each stock-decrementing invoicing event counts ONCE no matter how many units were on it (1 unit and 10 units each count as one).
+          <t>1. The inventory part's Demand is 2 - each stock-decrementing invoicing event counts ONCE no matter how many units were on it (1 unit and 10 units each count as one).
 2. After the reversal, Demand is STILL 2 - a reversal event neither adds to nor subtracts from the count (while Units Sold nets down).
 3. The special-order part's Demand is 2 - the count of its in-window vendor part requests.
 4. Demand is the report's default ranking signal (a whole number, never null - 0 when none).
 5. A part whose single in-window sale is invoiced and then fully reversed shows Demand 1 with Units Sold 0.00 — the Demand count is not decremented, while the movement nets to zero.
 ---
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S5-R4, S3-E1).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S5-R4, S3-E1), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2753,16 +2739,15 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Last Sale shows the whole days between today and the part's most recent sale measured over ALL-TIME history - it IGNORES the selected date range (e.g. '42 days' even though the range is This Month).
+          <t>1. Last Sale shows the whole days between today and the part's most recent sale measured over ALL-TIME history - it IGNORES the selected date range (e.g. '42 days' even though the range is This Month).
 2. It IS scoped to the selected location(s): with only location B selected, Last Sale reflects B's own most recent sale.
 3. Format is 'N days' (e.g. 42 days); a part with no recorded sale ever shows —.
 4. For a special-order part, the anchor is its most recent vendor-sourced invoiced/paid request.
 5. When the most recent sale is reversed, Last Sale re-anchors to the previous remaining sale (the day count grows accordingly); if no other sale remains it shows —.
 ---
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S5-R4, S5-R5).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S5-R4, S5-R5), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2808,14 +2793,13 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. On Hand equals the part's CURRENT on-hand quantity at that row's location (never summed across locations).
+          <t>1. On Hand equals the part's CURRENT on-hand quantity at that row's location (never summed across locations).
 2. Min and Max show the stored minimum / maximum reorder thresholds for that location, as whole numbers (— when not set).
 3. Min and Max are READ-ONLY display columns - no edit control or slide-over opens; editing part attributes from this report is out of scope in this version.
 ---
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S5-R4, S5-R5).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S5-R4, S5-R5), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2864,15 +2848,14 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Part A's Turns / Yr matches the formula (two decimals, e.g. 24.33); the window is the whole-day span inclusive of both dates with a floor of 1 day.
+          <t>1. Part A's Turns / Yr matches the formula (two decimals, e.g. 24.33); the window is the whole-day span inclusive of both dates with a floor of 1 day.
 2. Part B shows 0.00 (renders 0.00 when On Hand is 0 - not an error, not —).
 3. Part C shows a NEGATIVE Turns / Yr with a leading minus (because Units Sold can be negative).
 4. Special Order rows always show — (not applicable).
 ---
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S5-R4).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S5-R4), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2918,17 +2901,16 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Revenue = the summed billed sell amount (each line's stored sell price × quantity) in the window.
+          <t>1. Revenue = the summed billed sell amount (each line's stored sell price × quantity) in the window.
 2. Margin = Revenue − COGS (the summed billed cost captured at billing time).
 3. Unit Cost = COGS ÷ billed units; Sell Price = Revenue ÷ billed units.
 4. Margin % = (Revenue − COGS) ÷ Revenue × 100, shown to one decimal.
 5. All five are computed from the RAW (unrounded) Revenue / COGS / billed-units totals and rounded ONCE at the end - not built from already-rounded intermediates.
 6. The same formulas apply to inventory and special-order rows (for special-order, from the vendor part requests).
 ---
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S5-R4a).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: HOLD - this part of the report is not built yet
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S5-R4a), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2975,14 +2957,13 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. After the reversal, ALL the billed-line columns drop to reflect only the remaining sale - the reversed/voided sale is excluded from Revenue, Margin, Unit Cost, Sell Price, Margin %, Sold (WO), Sold (Parts Sale), and (for special-order) Units Sold.
+          <t>1. After the reversal, ALL the billed-line columns drop to reflect only the remaining sale - the reversed/voided sale is excluded from Revenue, Margin, Unit Cost, Sell Price, Margin %, Sold (WO), Sold (Parts Sale), and (for special-order) Units Sold.
 2. This netting is consistent with inventory Units Sold, which already nets reversals via the stock add-back.
 3. A voided sale therefore inflates NO column.
 ---
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S5-R4b, S5-R4a).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S5-R4b, S5-R4a), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3030,15 +3011,14 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Row 1: Unit Cost and Sell Price show — (billed units ≤ 0) while Revenue and Margin show dollar amounts AND Margin % is still computed from Revenue - a valid mixed row, not a defect.
+          <t>1. Row 1: Unit Cost and Sell Price show — (billed units ≤ 0) while Revenue and Margin show dollar amounts AND Margin % is still computed from Revenue - a valid mixed row, not a defect.
 2. Row 2: Sell Price shows $0.00 (a number) while Margin % shows — (Revenue ≤ 0) - also valid.
 3. Row 3: Unit Cost, Sell Price, and Margin % all show — together - which happens ONLY when both billed units ≤ 0 AND Revenue ≤ 0.
 4. The three triggers are independent: Unit Cost/Sell Price null on billed units ≤ 0; Margin % null on Revenue ≤ 0.
 ---
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S5-R4a, S3-R9).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S5-R4a, S3-R9), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3083,16 +3063,15 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Units Sold, Units Returned, Sold (WO), Sold (Parts Sale), On Hand, Turns / Yr: two decimals with thousands separators (1,250.00); negatives with a leading minus (-3.00).
+          <t>1. Units Sold, Units Returned, Sold (WO), Sold (Parts Sale), On Hand, Turns / Yr: two decimals with thousands separators (1,250.00); negatives with a leading minus (-3.00).
 2. Unit Cost, Sell Price, Revenue, Margin: currency with $, two decimals, thousands separators ($1,250.00); negatives with a leading minus and NO parentheses (-$45.00).
 3. Margin %: one decimal with a trailing % (33.8%); negatives with a leading minus, no + on positives (-8.4%).
 4. Demand: whole number. Min, Max: whole numbers (— when null). Last Sale: 'N days' (42 days), — when null.
 5. Rounding is half AWAY from zero: 8.45% displays 8.5% and -8.45% displays -8.5% (a tie rounds up in magnitude); this applies to all money and one-decimal values.
 ---
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S5-R5, S5-R7).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S5-R5, S5-R7), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3138,14 +3117,13 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The inventory core part does NOT appear in the report despite its activity and stock.
+          <t>1. The inventory core part does NOT appear in the report despite its activity and stock.
 2. The special-order core part does NOT appear either.
 3. Parts flagged as a core are excluded from both result sets by design.
 ---
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S5-R1, S5-R2).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S5-R1, S5-R2), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: HOLD - no part in this organisation carries the core flag, so core exclusion cannot be exercised</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3193,14 +3171,13 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. On the inventory row, Units Sold (stock movement) DIFFERS from the billed units behind Revenue/Sell Price - this is CORRECT behavior, not a defect (the Units Sold tooltip calls it out).
+          <t>1. On the inventory row, Units Sold (stock movement) DIFFERS from the billed units behind Revenue/Sell Price - this is CORRECT behavior, not a defect (the Units Sold tooltip calls it out).
 2. Sold (WO) + Sold (Parts Sale) together DO equal the billed-units basis (work orders are only Service- or Parts-type) - but neither equals the movement-based Units Sold.
 3. On the special-order row, everything reconciles: Units Sold = Sold (WO) + Sold (Parts Sale) = billed units (they share the vendor-request quantity as one source).
 ---
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S5-R7).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S5-R7), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -3247,15 +3224,14 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. In W1 (work-order date in window): the billed columns (Revenue, Margin, Unit Cost, Sell Price, Margin %, Sold (WO), Sold (Parts Sale)) count the sale, while inventory Units Sold / Demand do NOT (their movement event is outside W1).
+          <t>1. In W1 (work-order date in window): the billed columns (Revenue, Margin, Unit Cost, Sell Price, Margin %, Sold (WO), Sold (Parts Sale)) count the sale, while inventory Units Sold / Demand do NOT (their movement event is outside W1).
 2. In W2 (movement date in window): Units Sold / Demand count it, the billed columns do not - the two anchors CAN differ for an inventory part and that is intended.
 3. The window is the whole-day span inclusive of BOTH the start and end dates, with a floor of 1 day - a single-day range (Today) computes normally (Window = 1 for the Turns / Yr divisor).
 4. Last Sale is not windowed at all (all-time).
 ---
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S5-R7).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S5-R7), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3305,15 +3281,14 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Units Sold reads exactly 2.50 — not 2.00, not 3.00, not blank and not a dash.
+          <t>1. Units Sold reads exactly 2.50 — not 2.00, not 3.00, not blank and not a dash.
 2. It still reads exactly 2.50 after the sign-out and sign-back-in, which proves the part-of-a-unit quantity was really stored and not just shown once.
 3. On Hand has gone down by exactly 2.50 from what it was before the sale.
 4. No value anywhere on the row has been quietly rounded to a whole number.
 ---
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S5-R1, S5-R5).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S5-R1, S5-R5), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -3358,13 +3333,12 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The ⋯ overflow button sits leftmost in the toolbar's action cluster.
+          <t>1. The ⋯ overflow button sits leftmost in the toolbar's action cluster.
 2. The menu holds exactly two items, in this order: Download (PDF), then Download (CSV).
 ---
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S6-R1).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S6-R1), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3410,14 +3384,13 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Both files contain only the rows matching the date range, type, category, vendor, bin, location, and search active at export time - not a full unfiltered dump.
+          <t>1. Both files contain only the rows matching the date range, type, category, vendor, bin, location, and search active at export time - not a full unfiltered dump.
 2. The exported rows match what the on-screen grid was showing.
 3. Each file (PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to.
 ---
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S6-R2, S6-R11); where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, which is the authority.
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S6-R2, S6-R11), read on 11 August 2026; where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026, which is the authority.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3463,14 +3436,13 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Both exports contain ONLY the currently enabled columns - the hidden ones are absent.
+          <t>1. Both exports contain ONLY the currently enabled columns - the hidden ones are absent.
 2. Columns appear in the CANONICAL order (the fixed on-screen order) - the re-enabled Units Returned sits right after Units Sold, NOT appended at the end.
 3. The export mirrors the visible grid.
 ---
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S6-R3, S4-R4).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S6-R3, S4-R4), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3517,14 +3489,13 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The default Demand-descending order is exported when the user has not chosen another column.
+          <t>1. The default Demand-descending order is exported when the user has not chosen another column.
 2. Every column's sort is honored in the export - including Min and Max.
 3. The export renders the EXACT server order, including null placement (nulls first on ascending, last on descending) - the export and the on-screen grid match; there is no on-screen-vs-export null-sorting difference.
 ---
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S6-R4, S3-R3).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S6-R4, S3-R3), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3570,17 +3541,20 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The file downloads as velocity-report.pdf.
+          <t>1. The file downloads as velocity-report.pdf.
 2. The PDF is formatted for A3 landscape and titled Parts Velocity.
 3. Description, Category, and Vendor are truncated to 18 characters in the PDF.
 4. Part # is NOT truncated.
 5. With a logo uploaded, that logo appears. If a logo is set but fails to load, the built-in ShopView logo is used instead. If no logo is uploaded at all, NO logo is printed and the text fills the space. The CSV never includes a logo.
 Note for the tester: on this build a report with no uploaded logo still prints the built-in ShopView logo. The product owner has decided it should print no logo at all, so record what you see; the change is with the developers.
----
-This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true; where the Parts Velocity report specification version 5 (S6-R5, S6-R6) differs, his decision is the authority.
-Last checked against build v3.4.1-3d03023 on 8/4/2026, which does not yet match it - that change is with the developers.
-AUTOMATION: READY
-</t>
+What you should see today: The file, the A3 landscape page, the title and the logo are all correct, but nothing is shortened: Description, Category and Vendor are printed in full and wrap onto several lines. A 117-character description prints complete. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8934
+- If you see exactly that, mark this test FAILED and do not raise anything new.
+- If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+- If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026; where the Parts Velocity report specification version 6 (S6-R5, S6-R6), read on 11 August 2026, differs, his decision is the authority.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8934)</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3626,14 +3600,17 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The file downloads as velocity-report.csv.
+          <t>1. The file downloads as velocity-report.csv.
 2. The CSV carries the FULL, untruncated Description / Category / Vendor values (unlike the PDF's 18-character cut).
 3. Last Sale is a raw integer in the CSV (e.g. 42) - the 'N days' wording is PDF/on-screen only.
----
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S6-R5, S6-R6, S6-R8).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+What you should see today: The file is correctly named velocity-report.csv and the long text is correctly carried in full, but the Last Sale column reads the words "54 days" instead of the plain number 54. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8935
+- If you see exactly that, mark this test FAILED and do not raise anything new.
+- If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+- If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S6-R5, S6-R6, S6-R8), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8935)</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3679,13 +3656,12 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. A null value renders as — (em-dash) in BOTH the CSV and the PDF, in every nullable field: Unit Cost, Sell Price, Margin %, On Hand, Turns / Yr, Last Sale, Min, Max.
+          <t>1. A null value renders as — (em-dash) in BOTH the CSV and the PDF, in every nullable field: Unit Cost, Sell Price, Margin %, On Hand, Turns / Yr, Last Sale, Min, Max.
 2. Revenue, Margin, and the count metrics are never null in the exports either ($0.00 / 0.00 / 0).
 ---
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S6-R7, S6-R8, S3-R9).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S6-R7, S6-R8, S3-R9), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3736,7 +3712,7 @@
 4. This is a deliberate export-only treatment - the on-screen table is all-left-aligned; the difference is documented, not a defect.
 5. The CSV is plain data — the alignment assertions apply to the PDF only; how a spreadsheet displays the CSV is not part of this test.
 ---
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S6-R10, S3-R8).
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S6-R10, S3-R8), read on 11 August 2026.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -3786,14 +3762,17 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. On success the toasts read exactly "Velocity report exported (CSV)" / "Velocity report exported (PDF)" and auto-fade — UPPERCASE (CSV)/(PDF).
+          <t>1. On success the toasts read exactly "Velocity report exported (CSV)" / "Velocity report exported (PDF)" and auto-fade — UPPERCASE (CSV)/(PDF).
 2. An error toast is shown on failure; when the server provides a message, that server message is shown.
 3. Otherwise the failure toast reads exactly: "Failed to export velocity report (csv)" or "Failed to export velocity report (pdf)" — lowercase (csv)/(pdf); the success/failure casing mix is the specified wording (not a bug).
----
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S6-R9, S6-N1).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+What you should see today: The failure message is right - when a download is refused the server's own words are shown - but the success message is a general one reading "Success / Data exported successfully." for both file types, instead of "Velocity report exported (CSV)" or "Velocity report exported (PDF)". This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8936
+- If you see exactly that, mark this test FAILED and do not raise anything new.
+- If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+- If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S6-R9, S6-N1), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8936)</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3841,15 +3820,17 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Neither the CSV nor the PDF is produced — no download starts.
+          <t>1. Neither the CSV nor the PDF is produced — no download starts.
 2. A clear too-large message appears telling the user to narrow the date range or filters, then try again — the standard wording is "This report is too large to export. Narrow the date range or filters, then try again."
 3. After narrowing below the cap, the downloads work again.
-Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
----
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (Story 6 exports).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8818)
-</t>
+What you should see today: the spreadsheet download works and produces a file, but the PDF download of the same view fails with a server error and no file arrives. It depends on how much is in the view, not on which report - filtered down to one or two rows the PDF downloads normally, and on a full unfiltered view of several thousand rows it fails every time. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8818
+- If you see exactly that, mark this test FAILED and do not raise anything new.
+- If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+- If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (Story 6 exports), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8818)</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3897,16 +3878,18 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The CSV downloads successfully at that size.
+          <t>1. The CSV downloads successfully at that size.
 2. The PDF also downloads successfully. If instead nothing downloads and a message appears saying something went wrong, that is a failure — record roughly how many rows were on screen.
 3. The small PDF downloads successfully, which shows the failure depends on size.
 4. Note for the tester: a very large view is refused politely with "This report is too large to export. Narrow the date range or filters, then try again." — that message is expected and is NOT this failure. This test is about a medium-sized view where the CSV works but the PDF errors.
-Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
----
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (Story 6 exports).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8818)
-</t>
+What you should see today: the spreadsheet download works and produces a file, but the PDF download of the same view fails with a server error and no file arrives. It depends on how much is in the view, not on which report - filtered down to one or two rows the PDF downloads normally, and on a full unfiltered view of several thousand rows it fails every time. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8818
+- If you see exactly that, mark this test FAILED and do not raise anything new.
+- If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+- If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (Story 6 exports), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8818)</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3955,7 +3938,7 @@
 2. There is NO card border-radius - the table runs edge to edge.
 3. The layout matches the application's other reports.
 ---
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S7-R1).
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S7-R1), read on 11 August 2026.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -4011,7 +3994,7 @@
 4. It all looks the same as the other reports in the suite: put another report side by side and nothing should look out of place.
 5. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether the spacing and the dividing line look right and consistent with the other reports, and only report it if something looks obviously off. (The exact figures behind this - 32px/24px toolbar padding, a 1px header border, 2rem edge padding - are design-token values the design and engineering team check with their own tooling, not by hand.)
 ---
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S7-R2, S7-R3, S7-R4, S7-R5).
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S7-R2, S7-R3, S7-R4, S7-R5), read on 11 August 2026.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -4064,7 +4047,7 @@
 2. In BOTH light mode and dark mode the grey ⓘ info icon is clearly visible against the cell behind it - you can see it at a glance without leaning in, and it does not disappear into the background.
 3. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether you can see the icon easily in both modes. Only report it if the icon is hard to see. (The design rule behind this is a minimum 3:1 contrast ratio, which the design and engineering team check with a contrast tool - not by hand.)
 ---
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S7-R6).
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S7-R6), read on 11 August 2026.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -4114,14 +4097,13 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The backend returns ONE page of rows at a time - the full result set is not shipped to the browser.
+          <t>1. The backend returns ONE page of rows at a time - the full result set is not shipped to the browser.
 2. Paging is resolved on the server: moving to another page issues a fresh backend request for that page.
 3. This keeps the report responsive at scale (organizations can carry 50-60k parts, multiplied across locations).
 ---
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S2-R10).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S2-R10), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -4167,14 +4149,13 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. EACH change (Type, date range, Bin, Location, Category, Vendor, search) triggers a fresh server-side data load.
+          <t>1. EACH change (Type, date range, Bin, Location, Category, Vendor, search) triggers a fresh server-side data load.
 2. There is no client-side-only narrowing - every filter or search change re-queries the server.
 3. Each change returns the FIRST page of the new result set.
 ---
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S2-R10).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S2-R10), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4221,14 +4202,13 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Each header click re-fetches the data from the server, ordered by the chosen column and direction, returning the first page of the re-sorted result set.
+          <t>1. Each header click re-fetches the data from the server, ordered by the chosen column and direction, returning the first page of the re-sorted result set.
 2. Null values are placed FIRST on ascending and LAST on descending - as a server sort semantic, so the same order appears on screen and in the exports.
 3. Ties keep a stable order (no explicit secondary key).
 ---
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S3-R3).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S3-R3), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4280,7 +4260,7 @@
 3. Both requests succeed with only the ordinary reports access turned on - nothing else had to be enabled.
 4. Note for the tester: if the back end refuses either request for a user who has the ordinary reports access, mark this Failed and report it. If an extra Parts or Inventory reports permission exists in the system it must not change these results - the specification allows no per-report permission at all. A per-report permission added on purpose in a later release is a planned change, not a bug, and this test will be updated first.
 ---
-This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S1-R4, S1-N2).
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S1-R4, S1-N2), read on 11 August 2026.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
@@ -4339,7 +4319,7 @@
 3. The quantity behind the QuickBooks amount matches the Units Sold value on the report (2.50) — the two systems agree.
 4. No second or correcting journal entry is created to patch up a wrong amount.
 ---
-This is the expected behaviour as per epic SV-8582 and the engineering technical plan; this point is not covered by any of the six report specifications.
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the engineering technical plan, read on 11 August 2026; this point is not covered by any of the six report specifications.
 Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>

--- a/testrail-import/Report-Suite_Parts-Velocity-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Parts-Velocity-Report_testrail-import.xlsx
@@ -1461,7 +1461,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>The Location column shows only with more than one location, leftmost before Type</t>
+          <t>Location column: leftmost before Type; own location per row; Multiple on merged</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1497,19 +1497,14 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1. With more than one location in scope a Location column is shown as the LEFTMOST column, before Type.
+          <t>1. Because you have access to more than one location, a Location column is shown as the LEFTMOST column, before Type.
 2. Each inventory row shows its own location's name (an inventory row is one part at one location).
 3. The merged Special Order row shows "Multiple", because it is summed across the selected locations.
-4. With only one location involved the Location column is not shown.
-5. Both downloads include the Location column in the same position it holds on screen (leftmost, before Type), with the same values — each inventory row's own location, and "Multiple" on the merged Special Order row.
-What you should see today: The Location column is shown, and its values are right - each stocked row shows its own location's name and a special-order row that covers several locations reads "Multiple" - but the column sits sixth, straight after Vendor, instead of first before Type. Both downloads put it in that same sixth place. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8938
-- If you see exactly that, mark this test FAILED and do not raise anything new.
-- If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
-- If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
----
-Note for the tester: the written description is inconsistent about one point here. One part of it says the Location column is offered in the column-selection control and can be switched on and off; another part says it is never in that list and simply appears by itself whenever more than one location is involved. Parts Velocity is one of the reports where this has not been settled. The product owner has been asked which is right and has not answered yet, so do not raise a bug either way - record what you see and carry on. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
----
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S2-R12, S3-R10, S7-R8, S6-R11), read on 11 August 2026. That specification is inconsistent about the one point of whether the Location column is offered in the column-selection control: version 5 added a summary and a change note saying it can be toggled there, while the requirement that governs the column still says it is not user-toggleable. Chris Ward has been asked which is right and has not answered, so neither reading is asserted here. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
+4. A user who can reach only one location never sees the column at all.
+5. Whenever the column is shown on screen, both downloads include it in the same position (leftmost, before Type), with the same values — each inventory row's own location, and "Multiple" on the merged Special Order row.
+Note for the tester: two points about this column are still unsettled for Parts Velocity, and the product owner has been asked. One is whether narrowing the location selection hides it; the other is whether it can be switched off in the column picker and whether it counts toward the fourteen default columns. Whatever you see on those two points, do not raise a bug and do not fail the test for them — record what you see and carry on. The question is here: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/questions-2026-08-06/Questions-for-Chris-Ward_Report-Suite_2026-08-11.xlsx
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S2-R12, S3-R10, S7-R8, S6-R11), read on 11 August 2026. That specification still says two different things about this column: S3-R10 was rewritten in version 6 to make it access-gated and toggleable in the column picker, while S2-R12 still ties it to the current location scope and S4-R2/S4-R3 list twenty picker columns that do not include it. Chris Ward has been asked which is right, so neither reading is asserted here.
 Last checked against build v3.5-16cf83f on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8938)</t>
         </is>
@@ -2094,13 +2089,14 @@
         <is>
           <t>1. With a single location in scope exactly these 14 columns show, in this left-to-right order: Type, Part #, Description, Category, Vendor, Units Sold, Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand.
 2. The other 6 columns start hidden: Units Returned, Sold (WO), Sold (Parts Sale), Turns / Yr, Min, Max.
-3. When more than one location is in scope the Location column shows as well, leftmost before Type — 15 columns. Note for the tester: the written description is inconsistent about one point here. One part of it says the Location column is offered in the column-selection control and can be switched on and off; another part says it is never in that list and simply appears by itself whenever more than one location is involved. Parts Velocity is one of the reports where this has not been settled. The product owner has been asked which is right and has not answered yet, so do not raise a bug either way - record what you see and carry on. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx It is not part of the 14-column default set, so its presence is expected and is not a failure of this test.
+3. If your login can reach more than one location the Location column shows as well, leftmost before Type — 15 columns. It is not part of the 14-column default set, so its presence is expected and is not a failure of this test.
+Note for the tester: two points about this column are still unsettled for Parts Velocity, and the product owner has been asked. One is whether narrowing the location selection hides it; the other is whether it can be switched off in the column picker and whether it counts toward the fourteen default columns. Whatever you see on those two points, do not raise a bug and do not fail the test for them — record what you see and carry on. The question is here: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/questions-2026-08-06/Questions-for-Chris-Ward_Report-Suite_2026-08-11.xlsx
 What you should see today: The fourteen default columns and their order are correct, but the Location column is NOT first. It sits sixth, straight after Vendor, so the headings read Type, Part #, Description, Category, Vendor, Location, Units Sold and so on. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8938
 - If you see exactly that, mark this test FAILED and do not raise anything new.
 - If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 - If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S3-R10), read on 11 August 2026. That specification is inconsistent about the one point of whether the Location column is offered in the column-selection control: version 5 added a summary and a change note saying it can be toggled there, while the requirement that governs the column still says it is not user-toggleable. Chris Ward has been asked which is right and has not answered, so neither reading is asserted here. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S4-R1, S4-R2, S4-R3), read on 11 August 2026. That specification still says two different things about the Location column: S3-R10 was rewritten in version 6 to say it is shown by default and toggleable in the picker, while S4-R2 and S4-R3 enumerate twenty picker columns that do not include it. Chris Ward has been asked which is right, so neither reading is asserted here.
 Last checked against build v3.5-16cf83f on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8938)</t>
         </is>
@@ -3828,7 +3824,7 @@
 - If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 - If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (Story 6 exports), read on 11 August 2026.
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S6-R12), read on 11 August 2026, which added this row limit and its exact message on 2026-08-07.
 Last checked against build v3.5-16cf83f on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8818)</t>
         </is>

--- a/testrail-import/Report-Suite_Parts-Velocity-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Parts-Velocity-Report_testrail-import.xlsx
@@ -1503,6 +1503,10 @@
 4. A user who can reach only one location never sees the column at all.
 5. Whenever the column is shown on screen, both downloads include it in the same position (leftmost, before Type), with the same values — each inventory row's own location, and "Multiple" on the merged Special Order row.
 Note for the tester: two points about this column are still unsettled for Parts Velocity, and the product owner has been asked. One is whether narrowing the location selection hides it; the other is whether it can be switched off in the column picker and whether it counts toward the fourteen default columns. Whatever you see on those two points, do not raise a bug and do not fail the test for them — record what you see and carry on. The question is here: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/questions-2026-08-06/Questions-for-Chris-Ward_Report-Suite_2026-08-11.xlsx
+What you should see today: the Location column is not the leftmost column. It sits sixth, after Vendor, in all three places - on screen and in both downloads. The values themselves are right, including "Multiple" on the merged Special Order row. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8938
+- If you see exactly that, mark this test FAILED and do not raise anything new.
+- If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+- If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
 This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S2-R12, S3-R10, S7-R8, S6-R11), read on 11 August 2026. That specification still says two different things about this column: S3-R10 was rewritten in version 6 to make it access-gated and toggleable in the column picker, while S2-R12 still ties it to the current location scope and S4-R2/S4-R3 list twenty picker columns that do not include it. Chris Ward has been asked which is right, so neither reading is asserted here.
 Last checked against build v3.5-16cf83f on 8/6/2026.

--- a/testrail-import/Report-Suite_Parts-Velocity-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Parts-Velocity-Report_testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J72"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -3903,36 +3903,89 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>CSV export repeats the PDF header's date range and Locations filter lines</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>PV — Exports</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. The Parts Velocity report is open with at least one filter narrowed (for example a chosen date/scope and one or more locations) so the PDF header would show more than one filter line.</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>1. Download the report as a PDF and read the filter-summary lines in its header area.
+2. Download the report as a CSV and open it in a plain text editor or spreadsheet.
+3. Compare the leading rows of the CSV (above the column-header row) with the PDF header lines.</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>1. The CSV carries the same filter-summary lines as the PDF header - the date range and the "Locations:" line, plus any report-specific filter lines the PDF header names - each as a leading metadata row above the column-header row.
+2. The lines appear verbatim (the same wording) and in the same order as in the PDF header.
+3. A CSV saved or forwarded later is never ambiguous about which filters produced it: every filter the PDF header names is present in the CSV.
+4. Note for the tester: this is the suite-wide rule that the CSV must name the same filters as the PDF. If your report shows no narrowed filters, widen or narrow one so at least one filter line appears, then compare again.
+---
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 10 (S6-R11a), both read on 17 August 2026. S6-R11a is the suite-wide rule (added 2026-08-12, SV-9283) that the CSV carries every filter-summary line the PDF header names.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>SV-8646 (PV spec v10 2026-08-17 S6-R11a; suite-wide CSV filter-summary rule SV-9283)</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
           <t>The report uses the standard two-tone layout</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>PV — Visual Conformance</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded, in light mode.</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>1. Look at the page background, the toolbar, and the table surfaces.
 2. Look at the card corners and the table's horizontal extent.</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. White card surfaces (toolbar + table cells) sit on the standard soft blue-grey page background (the application's two-tone report theme).
 2. There is NO card border-radius - the table runs edge to edge.
@@ -3944,41 +3997,41 @@
 </t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>SV-8647 (PV spec v4 2026-07-29 S7-R1; §2)</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>Toolbar and table detail styling matches the suite paddings and borders</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>PV — Visual Conformance</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded.</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>1. Look at the toolbar strip above the table and at the space between its controls and the edges of the strip.
 2. Look at the column-header band and at the line between it and the toolbar above it.
@@ -3986,7 +4039,7 @@
 4. Compare all of the above with another report in the suite (for example Inventory Value) opened side by side.</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The toolbar strip is white (dark in dark mode), and its controls sit clear of the edges rather than pressed up against them.
 2. There is a thin dividing line between the toolbar and the column-header band, and the header band and the data cells are white.
@@ -4000,48 +4053,48 @@
 </t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>SV-8647 (PV spec v4 2026-07-29 S7-R2; S7-R3; S7-R4; S7-R5)</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>Dark mode is supported and the grey info icon keeps 3:1 contrast in both</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>PV — Visual Conformance</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded and dark mode available in the application.</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>1. Switch the application to dark mode.
 2. Look at the page background, toolbar, and cells.
 3. Look at the grey ⓘ info icon next to a column heading in dark mode, then switch back to light mode and look at it again.</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The report supports dark mode: page background, toolbar, and cells use their dark-mode equivalents.
 2. In BOTH light mode and dark mode the grey ⓘ info icon is clearly visible against the cell behind it - you can see it at a glance without leaning in, and it does not disappear into the background.
@@ -4053,49 +4106,49 @@
 </t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>SV-8647 (PV spec v4 2026-07-29 S7-R6 — dark-mode support + the grey info icon's colour token at ≥ 3:1 against the cell background in both modes; the ratio is a design-token property so the manual check is by-eye legibility)</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>The report is server-paginated - the backend returns one page of rows at a time</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>PV — API</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with more rows in the result set than one page holds.
 2. Browser devtools (network tab) are open to observe the backend requests.
 3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>1. Load the report and observe the backend data request and its response size.
 2. Move to the next page of rows and observe the traffic.</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>1. The backend returns ONE page of rows at a time - the full result set is not shipped to the browser.
 2. Paging is resolved on the server: moving to another page issues a fresh backend request for that page.
@@ -4106,48 +4159,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>SV-8642 (PV spec v4 2026-07-29 §2 (server-paginated); S2-R10)</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>Each filter or search change re-queries the server and returns page one</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>PV — API</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded and the browser devtools network tab open.
 2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>1. Change each of these in turn and watch the network traffic: Type, date range, Bin, Location, Category, Vendor, and the toolbar search.
 2. After a filter change while on a later page, note which page of results is shown.</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>1. EACH change (Type, date range, Bin, Location, Category, Vendor, search) triggers a fresh server-side data load.
 2. There is no client-side-only narrowing - every filter or search change re-queries the server.
@@ -4158,49 +4211,49 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>SV-8642 (PV spec v4 2026-07-29 S2-R10)</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>Header-click sorting re-queries the server; nulls first asc and last desc</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>PV — API</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with data loaded (including rows with null values in a sortable column) and the network tab open.
 2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>1. Click a column header and watch the network traffic and the returned order.
 2. Click it again (reverse direction) and observe.
 3. Note where the null rows land in the server-returned order for each direction.</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>1. Each header click re-fetches the data from the server, ordered by the chosen column and direction, returning the first page of the re-sorted result set.
 2. Null values are placed FIRST on ascending and LAST on descending - as a server sort semantic, so the same order appears on screen and in the exports.
@@ -4211,49 +4264,49 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>SV-8643 (PV spec v4 2026-07-29 S3-R3)</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>The back end serves report data and export on ordinary reports access</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>PV — API</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in as a user whose role has the ordinary reports access turned on and no other reports-related permission turned on.
 2. Browser devtools (network tab) are open.
 3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>1. Open the Parts Velocity report and observe the backend data request's outcome.
 2. Attempt the export and observe the backend export request's outcome.</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The back end returns the report data - the request is not refused.
 2. The back end returns the export file - the request is not refused.
@@ -4266,36 +4319,36 @@
 </t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>SV-8641 (PV spec S1-R4; S1-N2 - RESCOPED 2026-08-03; same driver as C30327: Chris Ward Q2=A "single Reports permission" + "they can exist and not do anything"; QA lead "ONE permission FOR NOW")</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>QuickBooks amount for a part-of-a-unit sale is exact and never inflated</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>PV — API</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>1. The test company is connected to QuickBooks.
 2. The part-of-a-unit sale has been made and invoiced — a ZZAUTOTEST part sold in a quantity such as 2.5, at a known unit cost such as $10.00.
@@ -4303,7 +4356,7 @@
 4. This test cannot be run without a company whose QuickBooks account is connected, because it checks what was sent to QuickBooks. If no QuickBooks-connected company is available, mark this test Blocked and say so — do not guess the result.</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>1. Write down the quantity sold and the part's unit cost, and work out the correct amount by hand (2.5 x $10.00 = $25.00).
 2. Let the invoice go across to QuickBooks the normal way the shop does it.
@@ -4312,7 +4365,7 @@
 5. Go back to the Parts Velocity report and read the same part's Units Sold value.</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The QuickBooks amount is exactly the hand-worked figure to the cent — $25.00 for 2.5 at $10.00.
 2. It is NOT a whole-unit amount such as $20.00 or $30.00, and it is NOT a bigger, multiplied figure.
@@ -4325,13 +4378,13 @@
 </t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>SV-8589 (verbatim Tests: 'QB journal amount exact from fractional movement'; Goal: 'QB journal-entry sync multiplies these into dollar amounts'; tech-plan-2026-07-29 Phase 0 / PR-1 D2 - no report spec covers QuickBooks)</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr"/>
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/Report-Suite_Parts-Velocity-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Parts-Velocity-Report_testrail-import.xlsx
@@ -527,14 +527,13 @@
 2. Under Parts there is an entry labeled Parts Velocity; Inventory Value also lives under Parts. The order of the two inside the Parts section is not fixed — do not fail the test on which of them comes first.
 3. Clicking it opens the Parts Velocity report.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S1-R1), read on 11 August 2026; where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026, which is the authority.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S1-R1), read on 17 August 2026; where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 17 August 2026, which is the authority.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>SV-8641 (PV spec S1-R1 — the "only report" sentence is superseded: Parts Velocity and Inventory Value BOTH live under Parts per the PRD video 2026-07-30; access = the one ordinary reports permission per QA lead 2026-08-03)</t>
+          <t>SV-8641 (PV spec v10 2026-08-17 S1-R1 — the "only report" sentence is superseded: Parts Velocity and Inventory Value BOTH live under Parts per the PRD video 2026-07-30; access = the one ordinary reports permission per QA lead 2026-08-03)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -579,14 +578,13 @@
 2. Report data loads automatically - you do not have to press anything to fetch it.
 3. Rows appear ranked by Demand, highest first (the default order).
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S1-R2, S4-R6), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S1-R2, S4-R6), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>SV-8641 (PV spec v4 2026-07-29 S1-R2; S4-R6)</t>
+          <t>SV-8641 (PV spec v10 2026-08-17 S1-R2; S4-R6)</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -632,14 +630,13 @@
 2. During a filter change, the loading indicator shows again.
 3. The rows already on screen are replaced only when the new data comes back - the table does not blank out and rebuild mid-request.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S1-R3), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S1-R3), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>SV-8641 (PV spec v4 2026-07-29 S1-R3)</t>
+          <t>SV-8641 (PV spec v10 2026-08-17 S1-R3)</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
@@ -682,19 +679,17 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The report data loads and rows are shown.
+          <t>1. The report data loads and rows are shown.
 2. The export downloads successfully — both opening the report and exporting it are allowed by the same ordinary reports access.
 3. Note for the tester: the specification allows ONE ordinary reports access for all six of these new reports and no per-report permission. If the build demands a separate report permission before this works, mark this Failed and report it — do not change the test.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S1-R4), read on 11 August 2026.
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S1-R4), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>SV-8641 (PV spec S1-R4 — one reports permission for all six ruled by Chris Ward Q2=A + QA lead 2026-08-03 "ONE permission FOR NOW"; PV S1-R4 still names Inventory Reports &gt; View — his spec edit owed)</t>
+          <t>SV-8641 (PV spec v10 2026-08-17 S1-R4 — one reports permission for all six ruled by Chris Ward Q2=A + QA lead 2026-08-03 "ONE permission FOR NOW"; PV S1-R4 still names Inventory Reports &gt; View — his spec edit owed)</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
@@ -734,18 +729,16 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The user cannot reach the Reports section.
+          <t>1. The user cannot reach the Reports section.
 2. The Parts Velocity navigation entry is not shown (this is the Reports section's own access control, not a report-specific rule).
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S1-N1), read on 11 August 2026.
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S1-N1), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>SV-8641 (PV spec v4 2026-07-29 S1-N1)</t>
+          <t>SV-8641 (PV spec v10 2026-08-17 S1-N1)</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
@@ -787,20 +780,18 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The Parts Velocity entry is visible in the Reports navigation under Parts.
+          <t>1. The Parts Velocity entry is visible in the Reports navigation under Parts.
 2. Opening it shows the report data - not an access-denied screen.
 3. The export downloads.
 4. Note for the tester: the specification allows ONE ordinary reports access for all six of these new reports and no per-report permission. If an extra Parts or Inventory reports permission does exist and switching it OFF blocks this report or its export, that is wrong - mark this Failed and report it. If a separate per-report permission is ever added on purpose in a later release, this test will be updated first, so treat that as a planned change and not as a bug.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S1-N2, S1-R4), read on 11 August 2026.
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S1-N2, S1-R4), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>SV-8641 (PV spec S1-N2; S1-R4 - RESCOPED 2026-08-03: the old "Reports access without Inventory Reports View" state cannot exist under one permission; Chris Ward Q2=A + "they can exist and not do anything"; QA lead "ONE permission FOR NOW")</t>
+          <t>SV-8641 (PV spec v10 2026-08-17 S1-N2; S1-R4 - RESCOPED 2026-08-03: "Reports access without Inventory Reports View" state cannot exist under one permission; Chris Ward Q2=A + "they can exist and not do anything"; QA lead "ONE permission FOR NOW")</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
@@ -850,14 +841,13 @@
 4. Both is an explicit selection returning inventory and Special Order rows together - a deliberate filter value, not the absence of a filter.
 5. Each selection immediately reloads the report limited to that type (no separate Apply step) - under Inventory every row's Type column reads Inventory; under Special Order every row's Type column reads Special Order; under Both, rows of both kinds appear.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S2-R1, S3-R5), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S2-R1, S3-R5), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>SV-8642 (PV spec v4 2026-07-29 S2-R1; S3-R5 — S2-R1 CLOSES the three Type options and the Both default; 'Catalogue'→'Special Order' per Chris Ward 2026-07-29 [newest-wins])</t>
+          <t>SV-8642 (PV spec v10 2026-08-17 S2-R1; S3-R5 — S2-R1 CLOSES the three Type options and the Both default; 'Catalogue'→'Special Order' per Chris Ward 2026-07-29 [newest-wins])</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
@@ -902,14 +892,13 @@
 3. Selecting a non-custom option immediately reloads the report data.
 4. The named ranges use the application's standard shared calendar boundaries (the same boundaries every report's date picker uses).
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026. Where the Parts Velocity report specification version 6 (S2-R2), read on 11 August 2026, says something different, his decision is the later word and is the authority.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 17 August 2026. Where the Parts Velocity report specification version 10 (S2-R2), read on 17 August 2026, says something different, his decision is the later word and is the authority.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>SV-8642 (PV spec v4 2026-07-29 S2-R2; §2 Out of Scope — S2-R2 CLOSES it in the spec's own words ("offering exactly these options") and rules out "All Time"; so the closed list IS the requirement)</t>
+          <t>SV-8642 (PV spec v10 2026-08-17 S2-R2; §2 Out of Scope — S2-R2 CLOSES it in the spec's own words ("offering exactly these options") and rules out "All Time"; so the closed list IS the requirement)</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
@@ -951,20 +940,18 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. A date picker opens requiring both a start and an end date.
+          <t>1. A date picker opens requiring both a start and an end date.
 2. The report does not reload until both dates are valid; a start after the end is not accepted.
 3. With both valid dates selected, the data reloads for that range.
 4. A span wider than 366 days (counting both the start and end dates) is rejected - the selection is not applied.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S2-R3), read on 11 August 2026.
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S2-R3), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>SV-8642 (PV spec v4 2026-07-29 S2-R3)</t>
+          <t>SV-8642 (PV spec v10 2026-08-17 S2-R3)</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
@@ -1006,20 +993,18 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Both filters allow selecting more than one value (multi-select).
+          <t>1. Both filters allow selecting more than one value (multi-select).
 2. With categories selected, only parts in any of the selected categories are shown.
 3. With vendors selected, only parts supplied by any of the selected vendors are shown.
 4. Each change reloads the data from the server.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S2-R4, S2-R5, S2-R10), read on 11 August 2026.
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S2-R4, S2-R5, S2-R10), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>SV-8642 (PV spec v4 2026-07-29 S2-R4; S2-R5; S2-R10)</t>
+          <t>SV-8642 (PV spec v10 2026-08-17 S2-R4; S2-R5; S2-R10)</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
@@ -1067,14 +1052,13 @@
 3. The description search returns rows whose description contains the word.
 4. Category and vendor names are NOT searched - use their dedicated filters instead (deliberate, to avoid false matches on common words).
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S2-R6), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S2-R6), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>SV-8642 (PV spec v4 2026-07-29 S2-R6; §3 Key Decisions)</t>
+          <t>SV-8642 (PV spec v10 2026-08-17 S2-R6; §3 Key Decisions)</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
@@ -1117,19 +1101,17 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. After steps 1-2 the part is still listed (it satisfies both filters).
+          <t>1. After steps 1-2 the part is still listed (it satisfies both filters).
 2. After step 3 the part disappears - a part must satisfy EVERY active filter to appear (AND logic, not OR).
 3. After step 4 the part is listed again.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S2-R7), read on 11 August 2026.
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S2-R7), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>SV-8642 (PV spec v4 2026-07-29 S2-R7)</t>
+          <t>SV-8642 (PV spec v10 2026-08-17 S2-R7)</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
@@ -1174,14 +1156,13 @@
 2. Only inventory parts stocked in ANY of the selected bins are shown.
 3. The filter allows more than one bin (multi-select).
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S2-R8), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S2-R8), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>SV-8642 (PV spec v4 2026-07-29 S2-R8)</t>
+          <t>SV-8642 (PV spec v10 2026-08-17 S2-R8)</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
@@ -1226,14 +1207,13 @@
           <t>1. With any Bin filter active, ALL Special Order rows are excluded (they have no bin location).
 2. Special Order combined with any Bin filter yields an empty result showing the empty state - this is by design, not a defect.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S2-R8), read on 11 August 2026; where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026, which is the authority.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S2-R8), read on 17 August 2026; where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 17 August 2026, which is the authority.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>SV-8642 (PV spec S2-R8 - 'Catalogue' RENAMED to the exact label 'Special Order' per Chris Ward msg 2026-07-29 [newest-wins] [cf video P31])</t>
+          <t>SV-8642 (PV spec v10 2026-08-17 S2-R8 - 'Catalogue' RENAMED to the exact label 'Special Order' per Chris Ward msg 2026-07-29 [newest-wins] [cf video P31])</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
@@ -1288,14 +1268,14 @@
 - If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 - If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S2-R9), read on 11 August 2026; where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026, which is the authority.
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S2-R9), read on 17 August 2026; where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 17 August 2026, which is the authority.
 Last checked against build v3.5-16cf83f on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8939)</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>SV-8642 (PV spec S2-R9 — per-row location identifier in All-Locations view ADDED per kickoff video P10; [ruling 2026-07-28 video-overrides-spec]) + on-screen location-scope indicator per Chris Ward msg 2026-07-29 [newest-wins]</t>
+          <t>SV-8642 (PV spec v10 2026-08-17 S2-R9 — per-row location identifier in All-Locations view ADDED per kickoff video P10; [ruling 2026-07-28 video-overrides-spec]) + on-screen location-scope indicator per Chris Ward msg 2026-07-29 [newest-wins]</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
@@ -1338,14 +1318,13 @@
           <t>1. The server returns zero rows and the table shows the empty state.
 2. The empty-state label reads exactly: "Empty bays, endless possibilities. Get Going!" (the application's standard reports no-data label).
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S2-R11, S2-N1), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S2-R11, S2-N1), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>SV-8642 (PV spec v4 2026-07-29 S2-R11; S2-N1; §7 — §7 CLOSES the empty-state string verbatim ("Empty bays" ... "Get Going!") as the standard reports no-data label; so the exact string IS the requirement)</t>
+          <t>SV-8642 (PV spec v10 2026-08-17 S2-R11; S2-N1; §7 — §7 CLOSES the empty-state string verbatim ("Empty bays" ... "Get Going!") as the standard reports no-data label; so the exact string IS the requirement)</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
@@ -1388,19 +1367,17 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The part with no category does not appear when any Category filter is active.
+          <t>1. The part with no category does not appear when any Category filter is active.
 2. The part with no vendor does not appear when any Vendor filter is active.
 3. The inventory part with no bin location does not appear when any Bin filter is active.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S2-E1, S2-E2, S2-E3), read on 11 August 2026.
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S2-E1, S2-E2, S2-E3), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>SV-8642 (PV spec v4 2026-07-29 S2-E1; S2-E2; S2-E3)</t>
+          <t>SV-8642 (PV spec v10 2026-08-17 S2-E1; S2-E2; S2-E3)</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
@@ -1441,18 +1418,16 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
+          <t>1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
 2. For the user with access to two or more locations the Location filter IS shown.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S2-E4), read on 11 August 2026. Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S2-E4), read on 17 August 2026. Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 17 August 2026
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>SV-8642 (PV spec S2-E4 — RULED HIDDEN by Chris Ward answer 2026-07-31 Q1=A "classic spec drift"; the S2-E4 "still sees the filter" note is stale; spec edit pending)</t>
+          <t>SV-8642 (PV spec v10 2026-08-17 S2-E4 — RULED HIDDEN by Chris Ward answer 2026-07-31 Q1=A "classic spec drift"; the S2-E4 "still sees the filter" note is stale; spec edit pending)</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
@@ -1508,14 +1483,14 @@
 - If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 - If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S2-R12, S3-R10, S7-R8, S6-R11), read on 11 August 2026. That specification still says two different things about this column: S3-R10 was rewritten in version 6 to make it access-gated and toggleable in the column picker, while S2-R12 still ties it to the current location scope and S4-R2/S4-R3 list twenty picker columns that do not include it. Chris Ward has been asked which is right, so neither reading is asserted here.
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S2-R12, S3-R10, S7-R8, S6-R11), read on 17 August 2026. That specification still says two different things about this column: S3-R10 was rewritten in version 6 to make it access-gated and toggleable in the column picker, while S2-R12 still ties it to the current location scope and S4-R2/S4-R3 list twenty picker columns that do not include it. Chris Ward has been asked which is right, so neither reading is asserted here.
 Last checked against build v3.5-16cf83f on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8938)</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>SV-8642; SV-8646 (PV spec v4 2026-07-29 S2-R12; S3-R10; S7-R8; S6-R11 — per-row Location column; leftmost before Type; "Multiple" on the merged special-order row; not in the picker; S6-R11 = the same column in both exports)</t>
+          <t>SV-8642; SV-8646 (PV spec v10 2026-08-17 S2-R12; S3-R10; S7-R8; S6-R11 — v6 rewrote S3-R10 to access-gated and picker-toggleable but left S2-R12 scope-driven and Location out of S4-R2/S4-R3; contested points not asserted)</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
@@ -1560,14 +1535,13 @@
 2. Each row carries only that one location's On Hand, Min, and Max.
 3. On Hand / Min / Max are NEVER summed across locations.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S3-R1a), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S3-R1a), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>SV-8643 (PV spec v4 2026-07-29 S3-R1a; §3 Key Decisions)</t>
+          <t>SV-8643 (PV spec v10 2026-08-17 S3-R1a; §3 Key Decisions)</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
@@ -1613,14 +1587,13 @@
 2. Its movement and profitability values are the SUM of the per-location values.
 3. Its inventory-only columns (On Hand, Turns / Yr, Min, Max) show — (em-dash), because special-order parts are not stocked.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S3-R1a), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S3-R1a), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>SV-8643 (PV spec v4 2026-07-29 S3-R1a; §3 Key Decisions)</t>
+          <t>SV-8643 (PV spec v10 2026-08-17 S3-R1a; §3 Key Decisions)</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
@@ -1668,14 +1641,13 @@
 3. Rows with equal Demand keep inventory-before-special-order order.
 4. The Demand header shows the descending sort indicator - this initial order IS the active sort (it is what the remembered view saves until you click another header).
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S3-R2), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S3-R2), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>SV-8643 (PV spec v4 2026-07-29 S3-R2)</t>
+          <t>SV-8643 (PV spec v10 2026-08-17 S3-R2)</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
@@ -1723,14 +1695,13 @@
 3. Null / — values are placed FIRST on ascending and LAST on descending.
 4. Every column is sortable; each header click re-fetches the data (server-resolved) and shows the first page of the re-sorted result; ties keep a stable order.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S3-R3), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S3-R3), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>SV-8643 (PV spec v4 2026-07-29 S3-R3)</t>
+          <t>SV-8643 (PV spec v10 2026-08-17 S3-R3)</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
@@ -1775,14 +1746,13 @@
 2. The Type column shows each row's kind as plain text (no badge or chip styling): "Inventory" or "Special Order".
 3. ALL columns - header and cell data, including numbers and money - are left-aligned on screen. (The exports right-align numerics instead: a deliberate export-only difference.)
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S3-R4, S3-R5, S3-R8), read on 11 August 2026; where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026, which is the authority.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S3-R4, S3-R5, S3-R8), read on 17 August 2026; where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 17 August 2026, which is the authority.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>SV-8643 (PV spec S3-R4; S3-R5; S3-R8 - Type value 'Catalogue' RENAMED to the exact label 'Special Order' per Chris Ward msg 2026-07-29 [newest-wins] [cf video P31])</t>
+          <t>SV-8643 (PV spec v10 2026-08-17 S3-R4; S3-R5; S3-R8 - Type value 'Catalogue' RENAMED to the exact label 'Special Order' per Chris Ward msg 2026-07-29 [newest-wins] [cf video P31])</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
@@ -1826,20 +1796,19 @@
       <c r="G26" s="2" t="inlineStr">
         <is>
           <t>1. Each of the three headers carries a grey info icon, shown always (not hover-to-reveal) whenever its column is visible; the Turns/Yr icon appears only once that column is enabled.
-2. Units Sold shows exactly: "Units taken out of inventory stock on invoiced work orders in this date range. This is stock movement, so it can differ from the units billed behind Revenue and Sell Price."
+2. Units Sold shows exactly: "Units taken out of inventory stock on invoiced work orders in this date range. This is stock movement, so it can differ from the units billed behind Revenue and Avg Sell."
 3. Demand shows exactly: "Number of separate transactions (work orders or parts sales) this part appeared on in the selected date range. Each transaction counts once, no matter how many units were sold on it."
 4. Turns/Yr shows exactly: "How many times you sell through this part in a year. Higher is better."
 5. The icon is focusable and exposes the same text to assistive technology; activating it does NOT trigger a column sort.
 6. No other column header carries an info icon.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S3-R6), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S3-R6), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>SV-8643 (PV spec v4 2026-07-29 S3-R6 — S3-R6 CLOSES the set (exactly three columns: Units Sold; Demand; Turns / Yr) and quotes each description verbatim; so the closed set and the exact strings ARE the requirement)</t>
+          <t>SV-8643 (PV spec v10 2026-08-17 S3-R6 — S3-R6 CLOSES the set (exactly three columns: Units Sold; Demand; Turns / Yr) and quotes each description verbatim; so the closed set and the exact strings ARE the requirement)</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
@@ -1890,14 +1859,14 @@
 - If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 - If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S3-R7), read on 11 August 2026.
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S3-R7), read on 17 August 2026.
 Last checked against build v3.5-16cf83f on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8940)</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>SV-8643 (PV spec v4 2026-07-29 S3-R7)</t>
+          <t>SV-8643 (PV spec v10 2026-08-17 S3-R7)</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
@@ -1941,14 +1910,13 @@
           <t>1. On Hand, Turns / Yr, Min, and Max show — (em-dash) on special-order rows - always.
 2. The count metrics and money totals are NEVER null: Units Sold / Units Returned / Sold (WO) / Sold (Parts Sale) show 0.00, Demand shows 0, Revenue and Margin show $0.00.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S3-R9, S5-R5), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S3-R9, S5-R5), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>SV-8643 (PV spec v4 2026-07-29 S3-R9; S5-R5)</t>
+          <t>SV-8643 (PV spec v10 2026-08-17 S3-R9; S5-R5)</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
@@ -1989,19 +1957,17 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Part A does NOT appear - it fails all three keep-criteria (no movement, under one on hand, no revenue) so it carries nothing to act on.
+          <t>1. Part A does NOT appear - it fails all three keep-criteria (no movement, under one on hand, no revenue) so it carries nothing to act on.
 2. Part B DOES appear - a part with billed Revenue &gt; 0 is always kept even with no stock movement and no on-hand stock.
 3. (Special Order parts have no such rule: a never-requested special-order part simply produces no row.)
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S3-N1), read on 11 August 2026.
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S3-N1), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>SV-8643 (PV spec v4 2026-07-29 S3-N1)</t>
+          <t>SV-8643 (PV spec v10 2026-08-17 S3-N1)</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
@@ -2042,17 +2008,16 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1. The picker lists all 20 available columns, each with a toggle: Type, Part #, Description, Category, Vendor, Units Sold, Units Returned, Sold (WO), Sold (Parts Sale), Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand, Turns/Yr, Min, Max.
+          <t>1. The picker lists all 20 available columns, each with a toggle: Type, Part #, Description, Category, Vendor, Units Sold, Units Returned, Sold (WO), Sold (Parts Sale), Avg Cost, Avg Sell, Revenue, Margin, Margin %, Demand, Last Sale, On Hand, Turns/Yr, Min, Max.
 2. No on-hand cost column is offered - the report computes one internally but it is never selectable and never displayed.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S4-R1, S4-R4, S5-R6), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S4-R1, S4-R4, S5-R6), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>SV-8644 (PV spec v4 2026-07-29 S4-R1; S4-R4; S5-R6)</t>
+          <t>SV-8644 (PV spec v10 2026-08-17 S4-R1; S4-R4; S5-R6)</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
@@ -2091,7 +2056,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>1. With a single location in scope exactly these 14 columns show, in this left-to-right order: Type, Part #, Description, Category, Vendor, Units Sold, Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand.
+          <t>1. With a single location in scope exactly these 14 columns show, in this left-to-right order: Type, Part #, Description, Category, Vendor, Units Sold, Avg Cost, Avg Sell, Revenue, Margin, Margin %, Demand, Last Sale, On Hand.
 2. The other 6 columns start hidden: Units Returned, Sold (WO), Sold (Parts Sale), Turns / Yr, Min, Max.
 3. If your login can reach more than one location the Location column shows as well, leftmost before Type — 15 columns. It is not part of the 14-column default set, so its presence is expected and is not a failure of this test.
 Note for the tester: two points about this column are still unsettled for Parts Velocity, and the product owner has been asked. One is whether narrowing the location selection hides it; the other is whether it can be switched off in the column picker and whether it counts toward the fourteen default columns. Whatever you see on those two points, do not raise a bug and do not fail the test for them — record what you see and carry on. The question is here: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/questions-2026-08-06/Questions-for-Chris-Ward_Report-Suite_2026-08-11.xlsx
@@ -2100,14 +2065,13 @@
 - If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 - If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S4-R1, S4-R2, S4-R3), read on 11 August 2026. That specification still says two different things about the Location column: S3-R10 was rewritten in version 6 to say it is shown by default and toggleable in the picker, while S4-R2 and S4-R3 enumerate twenty picker columns that do not include it. Chris Ward has been asked which is right, so neither reading is asserted here.
-Last checked against build v3.5-16cf83f on 8/6/2026.
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S4-R1, S4-R2, S4-R3), read on 17 August 2026. That specification still says two different things about the Location column: S3-R10 was rewritten in version 6 to say it is shown by default and toggleable in the picker, while S4-R2 and S4-R3 enumerate twenty picker columns that do not include it. Chris Ward has been asked which is right, so neither reading is asserted here.
 AUTOMATION: READY - EXPECT FAIL (SV-8938)</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>SV-8644; SV-8643 (PV spec v4 2026-07-29 S4-R2; S4-R3 + Story 3 S3-R10 — the 14 default-visible columns and the 6 hidden ones; plus the automatic Location column leftmost when more than one location is in scope)</t>
+          <t>SV-8644; SV-8646 (PV spec v10 2026-08-17 Story 4 S4-R1; S4-R2; S4-R3 + S3-R10 — the fourteen first-visit default columns and the six hidden ones; S3-R10 says Location is shown by default which S4-R2 does not list; contested and not asserted)</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
@@ -2149,17 +2113,16 @@
       <c r="G32" s="2" t="inlineStr">
         <is>
           <t>1. Each toggle takes effect immediately - the table re-renders without a page reload.
-2. Columns always render in the fixed canonical left-to-right order regardless of the order they were toggled on (with the automatic Location column, when shown, sitting leftmost before Type): Type, Part #, Description, Category, Vendor, Units Sold, Units Returned, Sold (WO), Sold (Parts Sale), Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand, Turns/Yr, Min, Max.
+2. Columns always render in the fixed canonical left-to-right order regardless of the order they were toggled on (with the automatic Location column, when shown, sitting leftmost before Type): Type, Part #, Description, Category, Vendor, Units Sold, Units Returned, Sold (WO), Sold (Parts Sale), Avg Cost, Avg Sell, Revenue, Margin, Margin %, Demand, Last Sale, On Hand, Turns/Yr, Min, Max.
 3. So Units Returned slots in right after Units Sold, Turns/Yr after On Hand, and Min before Max - not appended at the end.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S4-R4, S4-R5, S3-R10), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S4-R4, S4-R5, S3-R10), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>SV-8644; SV-8643 (PV spec v4 2026-07-29 S4-R4; S4-R5 + Story 3 S3-R10 — canonical column order and immediate re-render; plus the automatic Location column leftmost when shown)</t>
+          <t>SV-8644; SV-8643 (PV spec v10 2026-08-17 S4-R4; S4-R5 + Story 3 S3-R10 — canonical column order and immediate re-render; plus the automatic Location column leftmost when shown)</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
@@ -2205,14 +2168,13 @@
 3. The saved values take precedence over the first-visit defaults (This Year / Both / active location / 14 columns / Demand-descending).
 4. The same holds after a full page reload.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S4-R6, S1-R2), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S4-R6, S1-R2), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>SV-8644 (PV spec v4 2026-07-29 S4-R6; S1-R2)</t>
+          <t>SV-8644 (PV spec v10 2026-08-17 S4-R6; S1-R2)</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
@@ -2252,19 +2214,17 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The invalid saved value is NOT sent to the server.
+          <t>1. The invalid saved value is NOT sent to the server.
 2. That one setting falls back to its default (e.g. the location falls back to the active location); the other saved settings still restore normally.
 3. The report loads without an error.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S4-R6), read on 11 August 2026.
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S4-R6), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>SV-8644 (PV spec v4 2026-07-29 S4-R6)</t>
+          <t>SV-8644 (PV spec v10 2026-08-17 S4-R6)</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
@@ -2305,18 +2265,16 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. User 2 sees user 1's saved view (Type = Special Order, Last Quarter, the saved columns and sort).
+          <t>1. User 2 sees user 1's saved view (Type = Special Order, Last Quarter, the saved columns and sort).
 2. This is by design: storage is per browser, not tied to the account - there is no per-account separation.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S4-R6), read on 11 August 2026.
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S4-R6), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>SV-8644 (PV spec v4 2026-07-29 S4-R6)</t>
+          <t>SV-8644 (PV spec v10 2026-08-17 S4-R6)</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
@@ -2361,14 +2319,13 @@
 2. The export produces a file containing only the header/metadata rows and no data columns.
 3. On the next visit the all-hidden selection is NOT restored - the report falls back to the default 14-column set (the saved column selection returns to the last NON-EMPTY selection; all-hidden is the exception).
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S4-E1, S4-R6), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S4-E1, S4-R6), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>SV-8644 (PV spec v4 2026-07-29 S4-E1; S4-R6)</t>
+          <t>SV-8644 (PV spec v10 2026-08-17 S4-E1; S4-R6)</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
@@ -2415,14 +2372,13 @@
 3. After step 3, Units Sold is UNCHANGED - part returns do not affect Units Sold (they feed Units Returned instead).
 4. Units Sold can be 0.00 or negative when reversals exceed sales.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S5-R1, S5-R4), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S5-R1, S5-R4), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>SV-8645 (PV spec v4 2026-07-29 S5-R1; S5-R4 (Units Sold; inventory); §4)</t>
+          <t>SV-8645 (PV spec v10 2026-08-17 S5-R1; S5-R4 (Units Sold; inventory); §4)</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
@@ -2467,14 +2423,13 @@
 2. The reversed/voided sale is EXCLUDED from the total (net of reversals).
 3. Only requests on work orders at status Invoiced or Paid count; the window is anchored to the work-order date.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S5-R2, S5-R4, S5-R4b), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S5-R2, S5-R4, S5-R4b), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>SV-8645 (PV spec v4 2026-07-29 S5-R2; S5-R4 (Units Sold; catalogue); S5-R4b)</t>
+          <t>SV-8645 (PV spec v10 2026-08-17 S5-R2; S5-R4 (Units Sold; catalogue); S5-R4b)</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
@@ -2522,14 +2477,13 @@
 3. After step 3, it decreases by 2.00 - the column reflects the CURRENT state of return records (cancelled returns are excluded), not a snapshot.
 4. After step 4, Units Returned is UNCHANGED - invoice reversals are not returns (they affect Units Sold instead).
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S5-R3, S5-R4), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S5-R3, S5-R4), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>SV-8645 (PV spec v4 2026-07-29 S5-R3; S5-R4 (Units Returned); §3 Key Decisions)</t>
+          <t>SV-8645 (PV spec v10 2026-08-17 S5-R3; S5-R4 (Units Returned); §3 Key Decisions)</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
@@ -2578,14 +2532,13 @@
 4. Units Returned is independent of the work order's current invoice status.
 5. A part whose ONLY in-window event is a return (no sale, no stock, no revenue) produces no row at all - the rows of this report are built from sales and stock activity, so a return on its own does not create one.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S5-R3), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S5-R3), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>SV-8645 (PV spec v4 2026-07-29 S5-R3)</t>
+          <t>SV-8645 (PV spec v10 2026-08-17 S5-R3)</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
@@ -2632,14 +2585,13 @@
 3. Both are windowed by the WORK-ORDER date (its end date) - with the range moved off those dates, both drop out.
 4. Both workflows feed the report - a parts sale is a separate workflow from a service work order but counts fully.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S5-R4), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S5-R4), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>SV-8645 (PV spec v4 2026-07-29 S5-R4 (Sold via WO / Sold via Parts Sale); §5 Assumptions)</t>
+          <t>SV-8645 (PV spec v10 2026-08-17 S5-R4 (Sold via WO / Sold via Parts Sale); §5 Assumptions)</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
@@ -2688,14 +2640,13 @@
 4. Demand is the report's default ranking signal (a whole number, never null - 0 when none).
 5. A part whose single in-window sale is invoiced and then fully reversed shows Demand 1 with Units Sold 0.00 — the Demand count is not decremented, while the movement nets to zero.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S5-R4, S3-E1), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S5-R4, S3-E1), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>SV-8645 (PV spec v4 2026-07-29 S5-R4 (Demand); §4; §3 Key Decisions; S3-E1)</t>
+          <t>SV-8645 (PV spec v10 2026-08-17 S5-R4 (Demand); §4; §3 Key Decisions; S3-E1)</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
@@ -2745,14 +2696,13 @@
 4. For a special-order part, the anchor is its most recent vendor-sourced invoiced/paid request.
 5. When the most recent sale is reversed, Last Sale re-anchors to the previous remaining sale (the day count grows accordingly); if no other sale remains it shows —.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S5-R4, S5-R5), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S5-R4, S5-R5), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>SV-8645 (PV spec v4 2026-07-29 S5-R4 (Last Sale); §4; S5-R5; tech-plan-2026-07-29 B3.1 (last-sale re-anchor on reversal — spec-silent))</t>
+          <t>SV-8645 (PV spec v10 2026-08-17 S5-R4 (Last Sale); §4; S5-R5; tech-plan-2026-07-29 B3.1 (last-sale re-anchor on reversal — spec-silent))</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
@@ -2797,14 +2747,13 @@
 2. Min and Max show the stored minimum / maximum reorder thresholds for that location, as whole numbers (— when not set).
 3. Min and Max are READ-ONLY display columns - no edit control or slide-over opens; editing part attributes from this report is out of scope in this version.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S5-R4, S5-R5), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S5-R4, S5-R5), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>SV-8645 (PV spec v4 2026-07-29 S5-R4 (On Hand / Min / Max); §2 Out of Scope; S5-R5)</t>
+          <t>SV-8645 (PV spec v10 2026-08-17 S5-R4 (On Hand / Min / Max); §2 Out of Scope; S5-R5)</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
@@ -2853,14 +2802,13 @@
 3. Part C shows a NEGATIVE Turns / Yr with a leading minus (because Units Sold can be negative).
 4. Special Order rows always show — (not applicable).
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S5-R4), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S5-R4), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>SV-8645 (PV spec v4 2026-07-29 S5-R4 (Turns / Yr); S5 Definitions (Window))</t>
+          <t>SV-8645 (PV spec v10 2026-08-17 S5-R4 (Turns / Yr); S5 Definitions (Window))</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
@@ -2869,7 +2817,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Revenue, Margin, Unit Cost, Sell Price and Margin % use the billed formulas</t>
+          <t>Revenue, Margin, Avg Cost, Avg Sell and Margin % use the billed formulas</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2895,7 +2843,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>1. Compute the expected values: Revenue = (2×50)+(1×40) = $140.00; COGS = (2×30)+(1×30) = $90.00; billed units = 3; Margin = 140−90 = $50.00; Unit Cost = 90÷3 = $30.00; Sell Price = 140÷3 = $46.67; Margin % = 50÷140×100 = 35.7%.
+          <t>1. Compute the expected values: Revenue = (2×50)+(1×40) = $140.00; COGS = (2×30)+(1×30) = $90.00; billed units = 3; Margin = 140−90 = $50.00; Avg Cost = 90÷3 = $30.00; Avg Sell = 140÷3 = $46.67; Margin % = 50÷140×100 = 35.7%.
 2. Compare each against the part's displayed row.</t>
         </is>
       </c>
@@ -2903,19 +2851,18 @@
         <is>
           <t>1. Revenue = the summed billed sell amount (each line's stored sell price × quantity) in the window.
 2. Margin = Revenue − COGS (the summed billed cost captured at billing time).
-3. Unit Cost = COGS ÷ billed units; Sell Price = Revenue ÷ billed units.
+3. Avg Cost = COGS ÷ billed units; Avg Sell = Revenue ÷ billed units.
 4. Margin % = (Revenue − COGS) ÷ Revenue × 100, shown to one decimal.
 5. All five are computed from the RAW (unrounded) Revenue / COGS / billed-units totals and rounded ONCE at the end - not built from already-rounded intermediates.
 6. The same formulas apply to inventory and special-order rows (for special-order, from the vendor part requests).
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S5-R4a), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S5-R4a), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>SV-8645 (PV spec v4 2026-07-29 S5-R4a; §4)</t>
+          <t>SV-8645 (PV spec v10 2026-08-17 S5-R4a; §4)</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
@@ -2950,25 +2897,24 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>1. Record the part's Revenue, Margin, Unit Cost, Sell Price, Margin %, Sold (WO) / Sold (Parts Sale) (and Units Sold for a special-order part).
+          <t>1. Record the part's Revenue, Margin, Avg Cost, Avg Sell, Margin %, Sold (WO) / Sold (Parts Sale) (and Units Sold for a special-order part).
 2. Reverse/void one of the two sales.
 3. Reload the report and re-read every column.</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>1. After the reversal, ALL the billed-line columns drop to reflect only the remaining sale - the reversed/voided sale is excluded from Revenue, Margin, Unit Cost, Sell Price, Margin %, Sold (WO), Sold (Parts Sale), and (for special-order) Units Sold.
+          <t>1. After the reversal, ALL the billed-line columns drop to reflect only the remaining sale - the reversed/voided sale is excluded from Revenue, Margin, Avg Cost, Avg Sell, Margin %, Sold (WO), Sold (Parts Sale), and (for special-order) Units Sold.
 2. This netting is consistent with inventory Units Sold, which already nets reversals via the stock add-back.
 3. A voided sale therefore inflates NO column.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S5-R4b, S5-R4a), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S5-R4b, S5-R4a), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>SV-8645 (PV spec v4 2026-07-29 S5-R4b; S5-R4a; §3 Key Decisions)</t>
+          <t>SV-8645 (PV spec v10 2026-08-17 S5-R4b; S5-R4a; §3 Key Decisions)</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
@@ -2977,7 +2923,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Unit Cost / Sell Price and Margin % use independent null triggers</t>
+          <t>Avg Cost / Avg Sell and Margin % use independent null triggers</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -3004,26 +2950,25 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>1. Read Unit Cost, Sell Price, Margin %, Revenue, and Margin on row 1.
+          <t>1. Read Avg Cost, Avg Sell, Margin %, Revenue, and Margin on row 1.
 2. Read the same columns on row 2.
 3. Read the same columns on row 3.</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>1. Row 1: Unit Cost and Sell Price show — (billed units ≤ 0) while Revenue and Margin show dollar amounts AND Margin % is still computed from Revenue - a valid mixed row, not a defect.
-2. Row 2: Sell Price shows $0.00 (a number) while Margin % shows — (Revenue ≤ 0) - also valid.
-3. Row 3: Unit Cost, Sell Price, and Margin % all show — together - which happens ONLY when both billed units ≤ 0 AND Revenue ≤ 0.
-4. The three triggers are independent: Unit Cost/Sell Price null on billed units ≤ 0; Margin % null on Revenue ≤ 0.
----
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S5-R4a, S3-R9), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+          <t>1. Row 1: Avg Cost and Avg Sell show — (billed units ≤ 0) while Revenue and Margin show dollar amounts AND Margin % is still computed from Revenue - a valid mixed row, not a defect.
+2. Row 2: Avg Sell shows $0.00 (a number) while Margin % shows — (Revenue ≤ 0) - also valid.
+3. Row 3: Avg Cost, Avg Sell, and Margin % all show — together - which happens ONLY when both billed units ≤ 0 AND Revenue ≤ 0.
+4. The three triggers are independent: Avg Cost/Avg Sell null on billed units ≤ 0; Margin % null on Revenue ≤ 0.
+---
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S5-R4a, S3-R9), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>SV-8645 (PV spec v4 2026-07-29 S5-R4a (null rules + mixed-row paragraph); S3-R9)</t>
+          <t>SV-8645 (PV spec v10 2026-08-17 S5-R4a (null rules + mixed-row paragraph); S3-R9)</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
@@ -3064,19 +3009,18 @@
       <c r="G49" s="2" t="inlineStr">
         <is>
           <t>1. Units Sold, Units Returned, Sold (WO), Sold (Parts Sale), On Hand, Turns / Yr: two decimals with thousands separators (1,250.00); negatives with a leading minus (-3.00).
-2. Unit Cost, Sell Price, Revenue, Margin: currency with $, two decimals, thousands separators ($1,250.00); negatives with a leading minus and NO parentheses (-$45.00).
+2. Avg Cost, Avg Sell, Revenue, Margin: currency with $, two decimals, thousands separators ($1,250.00); negatives with a leading minus and NO parentheses (-$45.00).
 3. Margin %: one decimal with a trailing % (33.8%); negatives with a leading minus, no + on positives (-8.4%).
 4. Demand: whole number. Min, Max: whole numbers (— when null). Last Sale: 'N days' (42 days), — when null.
 5. Rounding is half AWAY from zero: 8.45% displays 8.5% and -8.45% displays -8.5% (a tie rounds up in magnitude); this applies to all money and one-decimal values.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S5-R5, S5-R7), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S5-R5, S5-R7), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>SV-8645 (PV spec v4 2026-07-29 S5-R5; S5-R7 (rounding))</t>
+          <t>SV-8645 (PV spec v10 2026-08-17 S5-R5; S5-R7 (rounding))</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
@@ -3121,14 +3065,14 @@
 2. The special-order core part does NOT appear either.
 3. Parts flagged as a core are excluded from both result sets by design.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S5-R1, S5-R2), read on 11 August 2026.
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S5-R1, S5-R2), read on 17 August 2026.
 Last checked against build v3.5-16cf83f on 8/6/2026.
 AUTOMATION: HOLD - no part in this organisation carries the core flag, so core exclusion cannot be exercised</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>SV-8645 (PV spec v4 2026-07-29 S5-R1; S5-R2; §3 Key Decisions)</t>
+          <t>SV-8645 (PV spec v10 2026-08-17 S5-R1; S5-R2; §3 Key Decisions)</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
@@ -3164,25 +3108,24 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>1. On the inventory row, compare Units Sold against Revenue ÷ Sell Price (the billed units).
+          <t>1. On the inventory row, compare Units Sold against Revenue ÷ Avg Sell (the billed units).
 2. On the same row, add Sold (WO) + Sold (Parts Sale) and compare against the billed units.
 3. On the special-order row, compare Units Sold, Sold (WO) + Sold (Parts Sale), and the billed units.</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>1. On the inventory row, Units Sold (stock movement) DIFFERS from the billed units behind Revenue/Sell Price - this is CORRECT behavior, not a defect (the Units Sold tooltip calls it out).
+          <t>1. On the inventory row, Units Sold (stock movement) DIFFERS from the billed units behind Revenue/Avg Sell - this is CORRECT behavior, not a defect (the Units Sold tooltip calls it out).
 2. Sold (WO) + Sold (Parts Sale) together DO equal the billed-units basis (work orders are only Service- or Parts-type) - but neither equals the movement-based Units Sold.
 3. On the special-order row, everything reconciles: Units Sold = Sold (WO) + Sold (Parts Sale) = billed units (they share the vendor-request quantity as one source).
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S5-R7), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S5-R7), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>SV-8645 (PV spec v4 2026-07-29 S5-R7; §3 Key Decisions)</t>
+          <t>SV-8645 (PV spec v10 2026-08-17 S5-R7; §3 Key Decisions)</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
@@ -3224,19 +3167,18 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>1. In W1 (work-order date in window): the billed columns (Revenue, Margin, Unit Cost, Sell Price, Margin %, Sold (WO), Sold (Parts Sale)) count the sale, while inventory Units Sold / Demand do NOT (their movement event is outside W1).
+          <t>1. In W1 (work-order date in window): the billed columns (Revenue, Margin, Avg Cost, Avg Sell, Margin %, Sold (WO), Sold (Parts Sale)) count the sale, while inventory Units Sold / Demand do NOT (their movement event is outside W1).
 2. In W2 (movement date in window): Units Sold / Demand count it, the billed columns do not - the two anchors CAN differ for an inventory part and that is intended.
 3. The window is the whole-day span inclusive of BOTH the start and end dates, with a floor of 1 day - a single-day range (Today) computes normally (Window = 1 for the Turns / Yr divisor).
 4. Last Sale is not windowed at all (all-time).
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S5-R7), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S5-R7), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>SV-8645 (PV spec v4 2026-07-29 S5 Definitions (Window / Work-order date); S5-R7)</t>
+          <t>SV-8645 (PV spec v10 2026-08-17 S5 Definitions (Window / Work-order date); S5-R7)</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
@@ -3286,14 +3228,13 @@
 3. On Hand has gone down by exactly 2.50 from what it was before the sale.
 4. No value anywhere on the row has been quietly rounded to a whole number.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S5-R1, S5-R5), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S5-R1, S5-R5), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>SV-8589 (PV spec S5-R1 Units Sold net stock movement + S5-R5 two-decimal movement format; tech-plan-2026-07-29 Phase 0 / PR-1 D2; SV-8589 verbatim Tests: 'fractional-quantity round-trip regression')</t>
+          <t>SV-8589 (PV spec v10 2026-08-17 S5-R1 Units Sold net stock movement + S5-R5 two-decimal movement format; tech-plan-2026-07-29 Phase 0 / PR-1 D2; SV-8589 verbatim Tests: 'fractional-quantity round-trip regression')</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
@@ -3336,14 +3277,13 @@
           <t>1. The ⋯ overflow button sits leftmost in the toolbar's action cluster.
 2. The menu holds exactly two items, in this order: Download (PDF), then Download (CSV).
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S6-R1), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S6-R1), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>SV-8646 (PV spec v4 2026-07-29 S6-R1 — S6-R1 CLOSES it in the spec's own words ("an export menu with two items ... Download (PDF) and Download (CSV)"); so the closed list IS the requirement)</t>
+          <t>SV-8646 (PV spec v10 2026-08-17 S6-R1 — S6-R1 CLOSES it in the spec's own words ("an export menu with two items ... Download (PDF) and Download (CSV)"); so the closed list IS the requirement)</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr"/>
@@ -3388,14 +3328,13 @@
 2. The exported rows match what the on-screen grid was showing.
 3. Each file (PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S6-R2, S6-R11), read on 11 August 2026; where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026, which is the authority.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S6-R2, S6-R11), read on 17 August 2026; where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 17 August 2026, which is the authority.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>SV-8646 (PV spec v4 2026-07-29 S6-R2; S6-R11; §3 Key Decisions — both exports reflect the filters and search active at export time; S6-R11 = the "Locations:" line in both exports [Chris Ward 2026-07-29; newest-wins])</t>
+          <t>SV-8646 (PV spec v10 2026-08-17 S6-R2; S6-R11; §3 Key Decisions — both exports reflect the filters and search active at export time; S6-R11 = the "Locations:" line in both exports [Chris Ward 2026-07-29; newest-wins])</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr"/>
@@ -3440,14 +3379,13 @@
 2. Columns appear in the CANONICAL order (the fixed on-screen order) - the re-enabled Units Returned sits right after Units Sold, NOT appended at the end.
 3. The export mirrors the visible grid.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S6-R3, S4-R4), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S6-R3, S4-R4), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>SV-8646 (PV spec v4 2026-07-29 S6-R3; S4-R4)</t>
+          <t>SV-8646 (PV spec v10 2026-08-17 S6-R3; S4-R4)</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr"/>
@@ -3493,14 +3431,13 @@
 2. Every column's sort is honored in the export - including Min and Max.
 3. The export renders the EXACT server order, including null placement (nulls first on ascending, last on descending) - the export and the on-screen grid match; there is no on-screen-vs-export null-sorting difference.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S6-R4, S3-R3), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S6-R4, S3-R3), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>SV-8646 (PV spec v4 2026-07-29 S6-R4; S3-R3)</t>
+          <t>SV-8646 (PV spec v10 2026-08-17 S6-R4; S3-R3)</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr"/>
@@ -3552,14 +3489,14 @@
 - If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 - If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026; where the Parts Velocity report specification version 6 (S6-R5, S6-R6), read on 11 August 2026, differs, his decision is the authority.
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 17 August 2026; where the Parts Velocity report specification version 10 (S6-R5, S6-R6), read on 17 August 2026, differs, his decision is the authority.
 Last checked against build v3.5-16cf83f on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8934)</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>SV-8646 (PV spec v4 2026-07-29 S6-R5; S6-R6 + same-logo-treatment for every report per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source; last-update-wins))</t>
+          <t>SV-8646 (PV spec v10 2026-08-17 S6-R5; S6-R6 + same-logo-treatment for every report per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source; last-update-wins))</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
@@ -3608,14 +3545,14 @@
 - If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 - If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S6-R5, S6-R6, S6-R8), read on 11 August 2026.
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S6-R5, S6-R6, S6-R8), read on 17 August 2026.
 Last checked against build v3.5-16cf83f on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8935)</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>SV-8646 (PV spec v4 2026-07-29 S6-R5; S6-R6; S6-R8)</t>
+          <t>SV-8646 (PV spec v10 2026-08-17 S6-R5; S6-R6; S6-R8)</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr"/>
@@ -3644,7 +3581,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>1. Rows with null values exist (a special-order row for On Hand / Turns / Yr / Min / Max; a row with billed units 0 for Unit Cost / Sell Price; a never-sold row for Last Sale).
+          <t>1. Rows with null values exist (a special-order row for On Hand / Turns / Yr / Min / Max; a row with billed units 0 for Avg Cost / Avg Sell; a never-sold row for Last Sale).
 2. All nullable columns are enabled.</t>
         </is>
       </c>
@@ -3656,17 +3593,17 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>1. A null value renders as — (em-dash) in BOTH the CSV and the PDF, in every nullable field: Unit Cost, Sell Price, Margin %, On Hand, Turns / Yr, Last Sale, Min, Max.
+          <t>1. A null value renders as — (em-dash) in the PDF, and as an empty cell in the CSV (no em-dash), in every nullable field: Avg Cost, Avg Sell, Margin %, On Hand, Turns / Yr, Last Sale, Min, Max. The CSV leaves the cell empty so a spreadsheet can still total the column.
 2. Revenue, Margin, and the count metrics are never null in the exports either ($0.00 / 0.00 / 0).
----
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S6-R7, S6-R8, S3-R9), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+Note for the tester: an earlier version of this report showed the em-dash for empty cells in the CSV as well. The current Parts Velocity report specification (version 10) changes the CSV to leave those cells empty; the PDF still shows the em-dash. Follow the current specification.
+---
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S6-R7, S6-R8, S3-R9), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>SV-8646 (PV spec v4 2026-07-29 S6-R7; S6-R8; S3-R9)</t>
+          <t>SV-8646 (PV spec v10 2026-08-17 S6-R7; S6-R8; S3-R9)</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
@@ -3706,21 +3643,19 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. In the PDF, the Type column is CENTERED.
+          <t>1. In the PDF, the Type column is CENTERED.
 2. In the PDF, the text columns (Part #, Description, Category, Vendor) are left-aligned.
 3. In the PDF, EVERY numeric and money column is right-aligned.
 4. This is a deliberate export-only treatment - the on-screen table is all-left-aligned; the difference is documented, not a defect.
 5. The CSV is plain data — the alignment assertions apply to the PDF only; how a spreadsheet displays the CSV is not part of this test.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S6-R10, S3-R8), read on 11 August 2026.
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S6-R10, S3-R8), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>SV-8646 (PV spec v4 2026-07-29 S6-R10; S3-R8)</t>
+          <t>SV-8646 (PV spec v10 2026-08-17 S6-R10; S3-R8)</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr"/>
@@ -3770,14 +3705,14 @@
 - If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 - If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S6-R9, S6-N1), read on 11 August 2026.
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S6-R9, S6-N1), read on 17 August 2026.
 Last checked against build v3.5-16cf83f on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8936)</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>SV-8646 (PV spec v4 2026-07-29 S6-R9; S6-N1; §7 (casing note) — S6-R9/S6-N1 CLOSE the toast strings verbatim including the shipped UPPERCASE-success / lowercase-failure casing mix; so the exact strings ARE the requirement)</t>
+          <t>SV-8646 (PV spec v10 2026-08-17 S6-R9; S6-N1; §7 (casing note) — S6-R9/S6-N1 CLOSE the toast strings verbatim including the shipped UPPERCASE-success / lowercase-failure casing mix; so the exact strings ARE the requirement)</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr"/>
@@ -3828,14 +3763,14 @@
 - If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 - If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S6-R12), read on 11 August 2026, which added this row limit and its exact message on 2026-08-07.
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S6-R12), read on 17 August 2026, which added this row limit and its exact message on 2026-08-07.
 Last checked against build v3.5-16cf83f on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8818)</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>SV-8646 (PV spec v4 2026-07-29 Story 6 exports — spec silent on a cap; tech-plan-2026-07-29 A3/FR-F4: suite-wide 10; 000-row export cap; locked by Chris 2026-07-21)</t>
+          <t>SV-8646 (PV spec v10 2026-08-17 S6-R12 — the 10;000-row export cap and its verbatim "too large to export" message are now IN the PV spec; previously spec-silent and sourced from tech-plan-2026-07-29 A3/FR-F4 locked by Chris 2026-07-21)</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr"/>
@@ -3887,14 +3822,14 @@
 - If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 - If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (Story 6 exports), read on 11 August 2026.
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (Story 6 exports), read on 17 August 2026.
 Last checked against build v3.5-16cf83f on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8818)</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>SV-8646 (PV spec v4 2026-07-29 Story 6 exports — the spec is silent on a renderer size limit; tech-plan-2026-07-29 A3/FR-F4 covers only the ten-thousand-row export cap)</t>
+          <t>SV-8646 (PV spec v10 2026-08-17 Story 6 exports — the spec is silent on a renderer size limit; tech-plan-2026-07-29 A3/FR-F4 covers only the ten-thousand-row export cap)</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr"/>
@@ -3987,19 +3922,17 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. White card surfaces (toolbar + table cells) sit on the standard soft blue-grey page background (the application's two-tone report theme).
+          <t>1. White card surfaces (toolbar + table cells) sit on the standard soft blue-grey page background (the application's two-tone report theme).
 2. There is NO card border-radius - the table runs edge to edge.
 3. The layout matches the application's other reports.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S7-R1), read on 11 August 2026.
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S7-R1), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>SV-8647 (PV spec v4 2026-07-29 S7-R1; §2)</t>
+          <t>SV-8647 (PV spec v10 2026-08-17 S7-R1; §2)</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr"/>
@@ -4041,21 +3974,19 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The toolbar strip is white (dark in dark mode), and its controls sit clear of the edges rather than pressed up against them.
+          <t>1. The toolbar strip is white (dark in dark mode), and its controls sit clear of the edges rather than pressed up against them.
 2. There is a thin dividing line between the toolbar and the column-header band, and the header band and the data cells are white.
 3. The first and last columns sit clear of the left and right edges of the table - the text is not touching the edge.
 4. It all looks the same as the other reports in the suite: put another report side by side and nothing should look out of place.
 5. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether the spacing and the dividing line look right and consistent with the other reports, and only report it if something looks obviously off. (The exact figures behind this - 32px/24px toolbar padding, a 1px header border, 2rem edge padding - are design-token values the design and engineering team check with their own tooling, not by hand.)
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S7-R2, S7-R3, S7-R4, S7-R5), read on 11 August 2026.
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S7-R2, S7-R3, S7-R4, S7-R5), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>SV-8647 (PV spec v4 2026-07-29 S7-R2; S7-R3; S7-R4; S7-R5)</t>
+          <t>SV-8647 (PV spec v10 2026-08-17 S7-R2; S7-R3; S7-R4; S7-R5)</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr"/>
@@ -4096,19 +4027,17 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The report supports dark mode: page background, toolbar, and cells use their dark-mode equivalents.
+          <t>1. The report supports dark mode: page background, toolbar, and cells use their dark-mode equivalents.
 2. In BOTH light mode and dark mode the grey ⓘ info icon is clearly visible against the cell behind it - you can see it at a glance without leaning in, and it does not disappear into the background.
 3. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether you can see the icon easily in both modes. Only report it if the icon is hard to see. (The design rule behind this is a minimum 3:1 contrast ratio, which the design and engineering team check with a contrast tool - not by hand.)
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S7-R6), read on 11 August 2026.
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S7-R6), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>SV-8647 (PV spec v4 2026-07-29 S7-R6 — dark-mode support + the grey info icon's colour token at ≥ 3:1 against the cell background in both modes; the ratio is a design-token property so the manual check is by-eye legibility)</t>
+          <t>SV-8647 (PV spec v10 2026-08-17 S7-R6 — dark-mode support + the grey info icon's colour token at ≥ 3:1 against the cell background in both modes; the ratio is a design-token property so the manual check is by-eye legibility)</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr"/>
@@ -4154,14 +4083,13 @@
 2. Paging is resolved on the server: moving to another page issues a fresh backend request for that page.
 3. This keeps the report responsive at scale (organizations can carry 50-60k parts, multiplied across locations).
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S2-R10), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S2-R10), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>SV-8642 (PV spec v4 2026-07-29 §2 (server-paginated); S2-R10)</t>
+          <t>SV-8642 (PV spec v10 2026-08-17 §2 (server-paginated); S2-R10)</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr"/>
@@ -4206,14 +4134,13 @@
 2. There is no client-side-only narrowing - every filter or search change re-queries the server.
 3. Each change returns the FIRST page of the new result set.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S2-R10), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S2-R10), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>SV-8642 (PV spec v4 2026-07-29 S2-R10)</t>
+          <t>SV-8642 (PV spec v10 2026-08-17 S2-R10)</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr"/>
@@ -4259,14 +4186,13 @@
 2. Null values are placed FIRST on ascending and LAST on descending - as a server sort semantic, so the same order appears on screen and in the exports.
 3. Ties keep a stable order (no explicit secondary key).
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S3-R3), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S3-R3), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>SV-8643 (PV spec v4 2026-07-29 S3-R3)</t>
+          <t>SV-8643 (PV spec v10 2026-08-17 S3-R3)</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr"/>
@@ -4308,20 +4234,18 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The back end returns the report data - the request is not refused.
+          <t>1. The back end returns the report data - the request is not refused.
 2. The back end returns the export file - the request is not refused.
 3. Both requests succeed with only the ordinary reports access turned on - nothing else had to be enabled.
 4. Note for the tester: if the back end refuses either request for a user who has the ordinary reports access, mark this Failed and report it. If an extra Parts or Inventory reports permission exists in the system it must not change these results - the specification allows no per-report permission at all. A per-report permission added on purpose in a later release is a planned change, not a bug, and this test will be updated first.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Parts Velocity report specification version 6 (S1-R4, S1-N2), read on 11 August 2026.
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S1-R4, S1-N2), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>SV-8641 (PV spec S1-R4; S1-N2 - RESCOPED 2026-08-03; same driver as C30327: Chris Ward Q2=A "single Reports permission" + "they can exist and not do anything"; QA lead "ONE permission FOR NOW")</t>
+          <t>SV-8641 (PV spec v10 2026-08-17 S1-R4; S1-N2 - RESCOPED 2026-08-03; same driver as C30327: Chris Ward Q2=A "single Reports permission" + "they can exist and not do anything"; QA lead "ONE permission FOR NOW")</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr"/>
@@ -4367,15 +4291,13 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The QuickBooks amount is exactly the hand-worked figure to the cent — $25.00 for 2.5 at $10.00.
+          <t>1. The QuickBooks amount is exactly the hand-worked figure to the cent — $25.00 for 2.5 at $10.00.
 2. It is NOT a whole-unit amount such as $20.00 or $30.00, and it is NOT a bigger, multiplied figure.
 3. The quantity behind the QuickBooks amount matches the Units Sold value on the report (2.50) — the two systems agree.
 4. No second or correcting journal entry is created to patch up a wrong amount.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the engineering technical plan, read on 11 August 2026; this point is not covered by any of the six report specifications.
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the engineering technical plan, read on 17 August 2026; this point is not covered by any of the six report specifications.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">

--- a/testrail-import/Report-Suite_Parts-Velocity-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Parts-Velocity-Report_testrail-import.xlsx
@@ -528,7 +528,7 @@
 3. Clicking it opens the Parts Velocity report.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S1-R1), read on 17 August 2026; where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 17 August 2026, which is the authority.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -579,7 +579,7 @@
 3. Rows appear ranked by Demand, highest first (the default order).
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S1-R2, S4-R6), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -631,7 +631,7 @@
 3. The rows already on screen are replaced only when the new data comes back - the table does not blank out and rebuild mid-request.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S1-R3), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
 3. Note for the tester: the specification allows ONE ordinary reports access for all six of these new reports and no per-report permission. If the build demands a separate report permission before this works, mark this Failed and report it — do not change the test.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S1-R4), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -733,7 +733,7 @@
 2. The Parts Velocity navigation entry is not shown (this is the Reports section's own access control, not a report-specific rule).
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S1-N1), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -786,7 +786,7 @@
 4. Note for the tester: the specification allows ONE ordinary reports access for all six of these new reports and no per-report permission. If an extra Parts or Inventory reports permission does exist and switching it OFF blocks this report or its export, that is wrong - mark this Failed and report it. If a separate per-report permission is ever added on purpose in a later release, this test will be updated first, so treat that as a planned change and not as a bug.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S1-N2, S1-R4), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
 5. Each selection immediately reloads the report limited to that type (no separate Apply step) - under Inventory every row's Type column reads Inventory; under Special Order every row's Type column reads Special Order; under Both, rows of both kinds appear.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S2-R1, S3-R5), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
 4. The named ranges use the application's standard shared calendar boundaries (the same boundaries every report's date picker uses).
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 17 August 2026. Where the Parts Velocity report specification version 10 (S2-R2), read on 17 August 2026, says something different, his decision is the later word and is the authority.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
 4. A span wider than 366 days (counting both the start and end dates) is rejected - the selection is not applied.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S2-R3), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -999,7 +999,7 @@
 4. Each change reloads the data from the server.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S2-R4, S2-R5, S2-R10), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1053,7 +1053,7 @@
 4. Category and vendor names are NOT searched - use their dedicated filters instead (deliberate, to avoid false matches on common words).
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S2-R6), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1106,7 +1106,7 @@
 3. After step 4 the part is listed again.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S2-R7), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1157,7 +1157,7 @@
 3. The filter allows more than one bin (multi-select).
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S2-R8), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1208,7 +1208,7 @@
 2. Special Order combined with any Bin filter yields an empty result showing the empty state - this is by design, not a defect.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S2-R8), read on 17 August 2026; where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 17 August 2026, which is the authority.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
 2. The empty-state label reads exactly: "Empty bays, endless possibilities. Get Going!" (the application's standard reports no-data label).
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S2-R11, S2-N1), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1372,7 +1372,7 @@
 3. The inventory part with no bin location does not appear when any Bin filter is active.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S2-E1, S2-E2, S2-E3), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
 2. For the user with access to two or more locations the Location filter IS shown.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S2-E4), read on 17 August 2026. Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 17 August 2026
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1536,7 +1536,7 @@
 3. On Hand / Min / Max are NEVER summed across locations.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S3-R1a), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1588,7 +1588,7 @@
 3. Its inventory-only columns (On Hand, Turns / Yr, Min, Max) show — (em-dash), because special-order parts are not stocked.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S3-R1a), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1642,7 +1642,7 @@
 4. The Demand header shows the descending sort indicator - this initial order IS the active sort (it is what the remembered view saves until you click another header).
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S3-R2), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1696,7 +1696,7 @@
 4. Every column is sortable; each header click re-fetches the data (server-resolved) and shows the first page of the re-sorted result; ties keep a stable order.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S3-R3), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1747,7 +1747,7 @@
 3. ALL columns - header and cell data, including numbers and money - are left-aligned on screen. (The exports right-align numerics instead: a deliberate export-only difference.)
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S3-R4, S3-R5, S3-R8), read on 17 August 2026; where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 17 August 2026, which is the authority.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1911,7 +1911,7 @@
 2. The count metrics and money totals are NEVER null: Units Sold / Units Returned / Sold (WO) / Sold (Parts Sale) show 0.00, Demand shows 0, Revenue and Margin show $0.00.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S3-R9, S5-R5), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
 3. (Special Order parts have no such rule: a never-requested special-order part simply produces no row.)
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S3-N1), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2169,7 +2169,7 @@
 4. The same holds after a full page reload.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S4-R6, S1-R2), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2219,7 +2219,7 @@
 3. The report loads without an error.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S4-R6), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
 2. This is by design: storage is per browser, not tied to the account - there is no per-account separation.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S4-R6), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2320,7 +2320,7 @@
 3. On the next visit the all-hidden selection is NOT restored - the report falls back to the default 14-column set (the saved column selection returns to the last NON-EMPTY selection; all-hidden is the exception).
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S4-E1, S4-R6), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2373,7 +2373,7 @@
 4. Units Sold can be 0.00 or negative when reversals exceed sales.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S5-R1, S5-R4), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2424,7 +2424,7 @@
 3. Only requests on work orders at status Invoiced or Paid count; the window is anchored to the work-order date.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S5-R2, S5-R4, S5-R4b), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2478,7 +2478,7 @@
 4. After step 4, Units Returned is UNCHANGED - invoice reversals are not returns (they affect Units Sold instead).
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S5-R3, S5-R4), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
 5. A part whose ONLY in-window event is a return (no sale, no stock, no revenue) produces no row at all - the rows of this report are built from sales and stock activity, so a return on its own does not create one.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S5-R3), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2586,7 +2586,7 @@
 4. Both workflows feed the report - a parts sale is a separate workflow from a service work order but counts fully.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S5-R4), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2641,7 +2641,7 @@
 5. A part whose single in-window sale is invoiced and then fully reversed shows Demand 1 with Units Sold 0.00 — the Demand count is not decremented, while the movement nets to zero.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S5-R4, S3-E1), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2697,7 +2697,7 @@
 5. When the most recent sale is reversed, Last Sale re-anchors to the previous remaining sale (the day count grows accordingly); if no other sale remains it shows —.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S5-R4, S5-R5), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2748,7 +2748,7 @@
 3. Min and Max are READ-ONLY display columns - no edit control or slide-over opens; editing part attributes from this report is out of scope in this version.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S5-R4, S5-R5), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2803,7 +2803,7 @@
 4. Special Order rows always show — (not applicable).
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S5-R4), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3229,7 +3229,7 @@
 4. No value anywhere on the row has been quietly rounded to a whole number.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S5-R1, S5-R5), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -3278,7 +3278,7 @@
 2. The menu holds exactly two items, in this order: Download (PDF), then Download (CSV).
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S6-R1), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
 3. Each file (PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S6-R2, S6-R11), read on 17 August 2026; where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 17 August 2026, which is the authority.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3380,7 +3380,7 @@
 3. The export mirrors the visible grid.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S6-R3, S4-R4), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3432,7 +3432,7 @@
 3. The export renders the EXACT server order, including null placement (nulls first on ascending, last on descending) - the export and the on-screen grid match; there is no on-screen-vs-export null-sorting difference.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S6-R4, S3-R3), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3650,7 +3650,7 @@
 5. The CSV is plain data — the alignment assertions apply to the PDF only; how a spreadsheet displays the CSV is not part of this test.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S6-R10, S3-R8), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3927,7 +3927,7 @@
 3. The layout matches the application's other reports.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S7-R1), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -3981,7 +3981,7 @@
 5. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether the spacing and the dividing line look right and consistent with the other reports, and only report it if something looks obviously off. (The exact figures behind this - 32px/24px toolbar padding, a 1px header border, 2rem edge padding - are design-token values the design and engineering team check with their own tooling, not by hand.)
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S7-R2, S7-R3, S7-R4, S7-R5), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -4032,7 +4032,7 @@
 3. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether you can see the icon easily in both modes. Only report it if the icon is hard to see. (The design rule behind this is a minimum 3:1 contrast ratio, which the design and engineering team check with a contrast tool - not by hand.)
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S7-R6), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -4084,7 +4084,7 @@
 3. This keeps the report responsive at scale (organizations can carry 50-60k parts, multiplied across locations).
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S2-R10), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4135,7 +4135,7 @@
 3. Each change returns the FIRST page of the new result set.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S2-R10), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4187,7 +4187,7 @@
 3. Ties keep a stable order (no explicit secondary key).
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S3-R3), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4240,7 +4240,7 @@
 4. Note for the tester: if the back end refuses either request for a user who has the ordinary reports access, mark this Failed and report it. If an extra Parts or Inventory reports permission exists in the system it must not change these results - the specification allows no per-report permission at all. A per-report permission added on purpose in a later release is a planned change, not a bug, and this test will be updated first.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Parts Velocity report specification version 10 (S1-R4, S1-N2), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4297,7 +4297,7 @@
 4. No second or correcting journal entry is created to patch up a wrong amount.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the engineering technical plan, read on 17 August 2026; this point is not covered by any of the six report specifications.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
